--- a/data/default/ManureMgmt.xlsx
+++ b/data/default/ManureMgmt.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1500" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1484" uniqueCount="162">
   <si>
     <t>value</t>
   </si>
@@ -497,6 +497,15 @@
   </si>
   <si>
     <t>assumed included in sows</t>
+  </si>
+  <si>
+    <t>share_feed_on_pasture</t>
+  </si>
+  <si>
+    <t>Share of feed (excl. grazing) fed to the animals while on pasture</t>
+  </si>
+  <si>
+    <t>N losses</t>
   </si>
 </sst>
 </file>
@@ -1031,7 +1040,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1056,6 +1065,7 @@
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1382,7 +1392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O309"/>
+  <dimension ref="A1:O311"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
@@ -1460,323 +1470,370 @@
       <c r="N2" s="3"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
+      <c r="A3" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F3" t="s">
+      <c r="E3" s="8"/>
+      <c r="F3" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="J3" t="s">
-        <v>20</v>
-      </c>
-      <c r="K3">
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+      <c r="K3" s="8">
         <v>25.3</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="N3" t="s">
+      <c r="M3" s="8"/>
+      <c r="N3" s="8" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="A4" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" s="8"/>
+      <c r="C4" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="8" t="s">
         <v>3</v>
       </c>
-      <c r="F4" t="s">
+      <c r="E4" s="8"/>
+      <c r="F4" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="J4" t="s">
-        <v>20</v>
-      </c>
-      <c r="K4">
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="8"/>
+      <c r="K4" s="8">
         <v>57.4</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="N4" t="s">
+      <c r="M4" s="8"/>
+      <c r="N4" s="8" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>1</v>
-      </c>
-      <c r="D5" t="s">
+      <c r="A5" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" s="8"/>
+      <c r="C5" s="8"/>
+      <c r="D5" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="F5" t="s">
+      <c r="E5" s="8"/>
+      <c r="F5" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="J5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K5">
+      <c r="G5" s="8"/>
+      <c r="H5" s="8"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="8"/>
+      <c r="K5" s="8">
         <v>52.7</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="N5" t="s">
+      <c r="M5" s="8"/>
+      <c r="N5" s="8" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" t="s">
+      <c r="A6" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" s="8"/>
+      <c r="C6" s="8"/>
+      <c r="D6" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="F6" t="s">
+      <c r="E6" s="8"/>
+      <c r="F6" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="J6" t="s">
-        <v>20</v>
-      </c>
-      <c r="K6">
+      <c r="G6" s="8"/>
+      <c r="H6" s="8"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="8"/>
+      <c r="K6" s="8">
         <v>35.700000000000003</v>
       </c>
-      <c r="L6" t="s">
+      <c r="L6" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="N6" t="s">
+      <c r="M6" s="8"/>
+      <c r="N6" s="8" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>1</v>
-      </c>
-      <c r="D7" t="s">
+      <c r="A7" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="8"/>
+      <c r="C7" s="8"/>
+      <c r="D7" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="F7" t="s">
+      <c r="E7" s="8"/>
+      <c r="F7" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="J7" t="s">
-        <v>20</v>
-      </c>
-      <c r="K7">
+      <c r="G7" s="8"/>
+      <c r="H7" s="8"/>
+      <c r="I7" s="8"/>
+      <c r="J7" s="8"/>
+      <c r="K7" s="8">
         <v>23.9</v>
       </c>
-      <c r="L7" t="s">
+      <c r="L7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M7" s="1" t="s">
+      <c r="M7" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="N7" t="s">
+      <c r="N7" s="8" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>1</v>
-      </c>
-      <c r="D8" t="s">
+      <c r="A8" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" s="8"/>
+      <c r="C8" s="8"/>
+      <c r="D8" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="F8" t="s">
+      <c r="E8" s="8"/>
+      <c r="F8" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="J8" t="s">
-        <v>20</v>
-      </c>
-      <c r="K8">
+      <c r="G8" s="8"/>
+      <c r="H8" s="8"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="8"/>
+      <c r="K8" s="8">
         <v>23.9</v>
       </c>
-      <c r="L8" t="s">
+      <c r="L8" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M8" s="1" t="s">
+      <c r="M8" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="N8" t="s">
+      <c r="N8" s="8" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>1</v>
-      </c>
-      <c r="D9" t="s">
+      <c r="A9" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" s="8"/>
+      <c r="C9" s="8"/>
+      <c r="D9" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="F9" t="s">
+      <c r="E9" s="8"/>
+      <c r="F9" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="J9" t="s">
-        <v>20</v>
-      </c>
-      <c r="K9">
+      <c r="G9" s="8"/>
+      <c r="H9" s="8"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="8"/>
+      <c r="K9" s="8">
         <v>23.9</v>
       </c>
-      <c r="L9" t="s">
+      <c r="L9" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M9" t="s">
+      <c r="M9" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="N9" t="s">
+      <c r="N9" s="8" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="24" t="s">
         <v>68</v>
       </c>
-      <c r="B10" s="5"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="5" t="s">
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K10" s="5">
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="24">
         <v>50</v>
       </c>
-      <c r="L10" s="5" t="s">
+      <c r="L10" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="M10" s="1"/>
-      <c r="N10" t="s">
+      <c r="M10" s="9"/>
+      <c r="N10" s="8" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5" t="s">
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24" t="s">
         <v>19</v>
       </c>
-      <c r="G11" s="5"/>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="K11" s="5">
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="24">
         <v>50</v>
       </c>
-      <c r="L11" s="5" t="s">
+      <c r="L11" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="M11" s="1"/>
-      <c r="N11" t="s">
+      <c r="M11" s="9"/>
+      <c r="N11" s="8" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="F12" t="s">
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="J12" t="s">
-        <v>20</v>
-      </c>
-      <c r="K12">
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8">
         <v>0</v>
       </c>
-      <c r="L12" t="s">
+      <c r="L12" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M12" s="1" t="s">
+      <c r="M12" s="9" t="s">
         <v>59</v>
       </c>
+      <c r="N12" s="8"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
+      <c r="A13" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="8" t="s">
         <v>58</v>
       </c>
-      <c r="F13" t="s">
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="J13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K13">
+      <c r="G13" s="8"/>
+      <c r="H13" s="8"/>
+      <c r="I13" s="8"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8">
         <v>0</v>
       </c>
-      <c r="L13" t="s">
+      <c r="L13" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M13" s="1" t="s">
+      <c r="M13" s="9" t="s">
         <v>59</v>
       </c>
+      <c r="N13" s="8"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
+      <c r="A14" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C14" t="s">
+      <c r="B14" s="8"/>
+      <c r="C14" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="F14" t="s">
+      <c r="D14" s="8"/>
+      <c r="E14" s="8"/>
+      <c r="F14" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="J14" t="s">
-        <v>20</v>
-      </c>
-      <c r="K14">
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="8"/>
+      <c r="K14" s="8">
         <v>0</v>
       </c>
-      <c r="L14" t="s">
+      <c r="L14" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="M14" s="1"/>
+      <c r="M14" s="9"/>
+      <c r="N14" s="8"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
+      <c r="A15" s="8" t="s">
         <v>63</v>
       </c>
-      <c r="C15" t="s">
+      <c r="B15" s="8"/>
+      <c r="C15" s="8" t="s">
         <v>64</v>
       </c>
-      <c r="F15" t="s">
+      <c r="D15" s="8"/>
+      <c r="E15" s="8"/>
+      <c r="F15" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="J15" t="s">
-        <v>20</v>
-      </c>
-      <c r="K15">
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8">
         <v>0</v>
       </c>
-      <c r="L15" t="s">
+      <c r="L15" s="8" t="s">
         <v>21</v>
       </c>
+      <c r="M15" s="8"/>
+      <c r="N15" s="8"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
@@ -1911,9 +1968,7 @@
       <c r="L21" t="s">
         <v>21</v>
       </c>
-      <c r="M21" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="M21" s="1"/>
       <c r="N21" t="s">
         <v>88</v>
       </c>
@@ -1941,9 +1996,7 @@
       <c r="L22" t="s">
         <v>21</v>
       </c>
-      <c r="M22" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="M22" s="1"/>
       <c r="N22" t="s">
         <v>88</v>
       </c>
@@ -2321,9 +2374,7 @@
       <c r="L37" t="s">
         <v>21</v>
       </c>
-      <c r="M37" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="M37" s="1"/>
       <c r="N37" t="s">
         <v>89</v>
       </c>
@@ -2347,9 +2398,7 @@
       <c r="L38" t="s">
         <v>21</v>
       </c>
-      <c r="M38" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="M38" s="1"/>
       <c r="N38" t="s">
         <v>89</v>
       </c>
@@ -2687,9 +2736,7 @@
       <c r="L53" t="s">
         <v>21</v>
       </c>
-      <c r="M53" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="M53" s="1"/>
       <c r="N53" t="s">
         <v>90</v>
       </c>
@@ -2713,9 +2760,7 @@
       <c r="L54" t="s">
         <v>21</v>
       </c>
-      <c r="M54" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="M54" s="1"/>
       <c r="N54" t="s">
         <v>90</v>
       </c>
@@ -2937,164 +2982,136 @@
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A65" s="2" t="s">
+      <c r="J65" t="s">
+        <v>159</v>
+      </c>
+      <c r="K65">
+        <v>0</v>
+      </c>
+      <c r="L65" t="s">
+        <v>21</v>
+      </c>
+      <c r="M65" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A67" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="B65" s="2"/>
-      <c r="C65" s="2"/>
-      <c r="D65" s="2"/>
-      <c r="E65" s="2"/>
-      <c r="F65" s="2"/>
-      <c r="G65" s="2"/>
-      <c r="H65" s="2"/>
-      <c r="I65" s="2"/>
-      <c r="J65" s="2"/>
-      <c r="K65" s="2"/>
-      <c r="L65" s="21" t="s">
+      <c r="B67" s="2"/>
+      <c r="C67" s="2"/>
+      <c r="D67" s="2"/>
+      <c r="E67" s="2"/>
+      <c r="F67" s="2"/>
+      <c r="G67" s="2"/>
+      <c r="H67" s="2"/>
+      <c r="I67" s="2"/>
+      <c r="J67" s="2"/>
+      <c r="K67" s="2"/>
+      <c r="L67" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="M65" s="2"/>
-      <c r="N65" s="2"/>
-    </row>
-    <row r="67" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J67" t="s">
-        <v>149</v>
-      </c>
-      <c r="K67">
-        <v>0</v>
-      </c>
-      <c r="M67" t="s">
-        <v>122</v>
-      </c>
+      <c r="M67" s="2"/>
+      <c r="N67" s="2"/>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>1</v>
-      </c>
-      <c r="C69" t="s">
-        <v>2</v>
-      </c>
-      <c r="D69" t="s">
-        <v>3</v>
-      </c>
-      <c r="I69" t="s">
-        <v>152</v>
-      </c>
       <c r="J69" t="s">
         <v>149</v>
       </c>
-      <c r="K69" s="19">
+      <c r="K69">
+        <v>0</v>
+      </c>
+      <c r="M69" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>1</v>
+      </c>
+      <c r="C71" t="s">
+        <v>2</v>
+      </c>
+      <c r="D71" t="s">
+        <v>3</v>
+      </c>
+      <c r="I71" t="s">
+        <v>152</v>
+      </c>
+      <c r="J71" t="s">
+        <v>149</v>
+      </c>
+      <c r="K71" s="19">
         <f>1.5*0.85</f>
         <v>1.2749999999999999</v>
       </c>
-      <c r="N69" t="s">
+      <c r="N71" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="70" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>1</v>
-      </c>
-      <c r="C70" t="s">
+    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>1</v>
+      </c>
+      <c r="C72" t="s">
         <v>9</v>
       </c>
-      <c r="D70" t="s">
+      <c r="D72" t="s">
         <v>3</v>
       </c>
-      <c r="I70" t="s">
+      <c r="I72" t="s">
         <v>152</v>
       </c>
-      <c r="J70" t="s">
+      <c r="J72" t="s">
         <v>149</v>
       </c>
-      <c r="K70" s="19">
+      <c r="K72" s="19">
         <f>5.5*0.85</f>
         <v>4.6749999999999998</v>
       </c>
-      <c r="N70" t="s">
+      <c r="N72" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="71" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A71" t="s">
-        <v>1</v>
-      </c>
-      <c r="D71" t="s">
+    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>1</v>
+      </c>
+      <c r="D73" t="s">
         <v>13</v>
       </c>
-      <c r="I71" t="s">
+      <c r="I73" t="s">
         <v>152</v>
       </c>
-      <c r="J71" t="s">
+      <c r="J73" t="s">
         <v>149</v>
       </c>
-      <c r="K71" s="19">
+      <c r="K73" s="19">
         <f>5*0.85</f>
         <v>4.25</v>
       </c>
-      <c r="N71" t="s">
+      <c r="N73" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="72" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>1</v>
-      </c>
-      <c r="D72" t="s">
+    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>1</v>
+      </c>
+      <c r="D74" t="s">
         <v>12</v>
       </c>
-      <c r="I72" t="s">
+      <c r="I74" t="s">
         <v>152</v>
       </c>
-      <c r="J72" t="s">
+      <c r="J74" t="s">
         <v>149</v>
       </c>
-      <c r="K72" s="19">
+      <c r="K74" s="19">
         <f>3.5*0.85</f>
         <v>2.9750000000000001</v>
       </c>
-      <c r="N72" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="73" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A73" t="s">
-        <v>1</v>
-      </c>
-      <c r="D73" t="s">
-        <v>15</v>
-      </c>
-      <c r="I73" t="s">
-        <v>152</v>
-      </c>
-      <c r="J73" t="s">
-        <v>149</v>
-      </c>
-      <c r="K73" s="19">
-        <f>K72</f>
-        <v>2.9750000000000001</v>
-      </c>
-      <c r="N73" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="74" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A74" t="s">
-        <v>1</v>
-      </c>
-      <c r="D74" t="s">
-        <v>16</v>
-      </c>
-      <c r="I74" t="s">
-        <v>152</v>
-      </c>
-      <c r="J74" t="s">
-        <v>149</v>
-      </c>
-      <c r="K74" s="19">
-        <f>K72</f>
-        <v>2.9750000000000001</v>
-      </c>
       <c r="N74" t="s">
         <v>157</v>
       </c>
@@ -3104,7 +3121,7 @@
         <v>1</v>
       </c>
       <c r="D75" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I75" t="s">
         <v>152</v>
@@ -3113,7 +3130,7 @@
         <v>149</v>
       </c>
       <c r="K75" s="19">
-        <f>K72</f>
+        <f>K74</f>
         <v>2.9750000000000001</v>
       </c>
       <c r="N75" t="s">
@@ -3121,11 +3138,32 @@
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K76" s="19"/>
+      <c r="A76" t="s">
+        <v>1</v>
+      </c>
+      <c r="D76" t="s">
+        <v>16</v>
+      </c>
+      <c r="I76" t="s">
+        <v>152</v>
+      </c>
+      <c r="J76" t="s">
+        <v>149</v>
+      </c>
+      <c r="K76" s="19">
+        <f>K74</f>
+        <v>2.9750000000000001</v>
+      </c>
+      <c r="N76" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>68</v>
+        <v>1</v>
+      </c>
+      <c r="D77" t="s">
+        <v>17</v>
       </c>
       <c r="I77" t="s">
         <v>152</v>
@@ -3134,87 +3172,70 @@
         <v>149</v>
       </c>
       <c r="K77" s="19">
+        <f>K74</f>
+        <v>2.9750000000000001</v>
+      </c>
+      <c r="N77" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K78" s="19"/>
+    </row>
+    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>68</v>
+      </c>
+      <c r="I79" t="s">
+        <v>152</v>
+      </c>
+      <c r="J79" t="s">
+        <v>149</v>
+      </c>
+      <c r="K79" s="19">
         <f>6*0.85</f>
         <v>5.0999999999999996</v>
       </c>
-      <c r="N77" t="s">
+      <c r="N79" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="78" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K78" s="19"/>
-    </row>
-    <row r="79" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A79" t="s">
+    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K80" s="19"/>
+    </row>
+    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
         <v>82</v>
       </c>
-      <c r="D79" t="s">
+      <c r="D81" t="s">
         <v>154</v>
       </c>
-      <c r="I79" t="s">
+      <c r="I81" t="s">
         <v>152</v>
       </c>
-      <c r="J79" t="s">
+      <c r="J81" t="s">
         <v>149</v>
       </c>
-      <c r="K79" s="19">
+      <c r="K81" s="19">
         <f>100/(365.25/2)*0.85</f>
         <v>0.4654346338124572</v>
       </c>
-      <c r="M79" t="s">
+      <c r="M81" t="s">
         <v>155</v>
-      </c>
-      <c r="N79" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="80" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K80" s="19"/>
-    </row>
-    <row r="81" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A81" t="s">
-        <v>43</v>
-      </c>
-      <c r="D81" t="s">
-        <v>50</v>
-      </c>
-      <c r="I81" t="s">
-        <v>152</v>
-      </c>
-      <c r="J81" t="s">
-        <v>149</v>
-      </c>
-      <c r="K81" s="19">
-        <f>1.5*0.85</f>
-        <v>1.2749999999999999</v>
       </c>
       <c r="N81" t="s">
         <v>157</v>
       </c>
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A82" t="s">
-        <v>43</v>
-      </c>
-      <c r="D82" t="s">
-        <v>51</v>
-      </c>
-      <c r="I82" t="s">
-        <v>152</v>
-      </c>
-      <c r="J82" t="s">
-        <v>149</v>
-      </c>
-      <c r="K82" s="22">
-        <v>0</v>
-      </c>
+      <c r="K82" s="19"/>
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>43</v>
       </c>
       <c r="D83" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="I83" t="s">
         <v>152</v>
@@ -3222,12 +3243,12 @@
       <c r="J83" t="s">
         <v>149</v>
       </c>
-      <c r="K83" s="23">
-        <f>K85</f>
-        <v>5.9500000000000004E-2</v>
-      </c>
-      <c r="M83" t="s">
-        <v>153</v>
+      <c r="K83" s="19">
+        <f>1.5*0.85</f>
+        <v>1.2749999999999999</v>
+      </c>
+      <c r="N83" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
@@ -3235,7 +3256,7 @@
         <v>43</v>
       </c>
       <c r="D84" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="I84" t="s">
         <v>152</v>
@@ -3243,14 +3264,8 @@
       <c r="J84" t="s">
         <v>149</v>
       </c>
-      <c r="K84" s="19">
+      <c r="K84" s="22">
         <v>0</v>
-      </c>
-      <c r="M84" t="s">
-        <v>158</v>
-      </c>
-      <c r="N84" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
@@ -3258,7 +3273,7 @@
         <v>43</v>
       </c>
       <c r="D85" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="I85" t="s">
         <v>152</v>
@@ -3266,12 +3281,12 @@
       <c r="J85" t="s">
         <v>149</v>
       </c>
-      <c r="K85" s="19">
-        <f>0.07*0.85</f>
+      <c r="K85" s="23">
+        <f>K87</f>
         <v>5.9500000000000004E-2</v>
       </c>
-      <c r="N85" t="s">
-        <v>157</v>
+      <c r="M85" t="s">
+        <v>153</v>
       </c>
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
@@ -3279,7 +3294,7 @@
         <v>43</v>
       </c>
       <c r="D86" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="I86" t="s">
         <v>152</v>
@@ -3287,22 +3302,54 @@
       <c r="J86" t="s">
         <v>149</v>
       </c>
-      <c r="K86" s="23">
-        <f>K85</f>
+      <c r="K86" s="19">
+        <v>0</v>
+      </c>
+      <c r="M86" t="s">
+        <v>158</v>
+      </c>
+      <c r="N86" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>43</v>
+      </c>
+      <c r="D87" t="s">
+        <v>44</v>
+      </c>
+      <c r="I87" t="s">
+        <v>152</v>
+      </c>
+      <c r="J87" t="s">
+        <v>149</v>
+      </c>
+      <c r="K87" s="19">
+        <f>0.07*0.85</f>
         <v>5.9500000000000004E-2</v>
       </c>
-    </row>
-    <row r="87" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K87" s="23"/>
+      <c r="N87" t="s">
+        <v>157</v>
+      </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>63</v>
-      </c>
-      <c r="C88" t="s">
-        <v>83</v>
-      </c>
-      <c r="K88" s="23"/>
+        <v>43</v>
+      </c>
+      <c r="D88" t="s">
+        <v>45</v>
+      </c>
+      <c r="I88" t="s">
+        <v>152</v>
+      </c>
+      <c r="J88" t="s">
+        <v>149</v>
+      </c>
+      <c r="K88" s="23">
+        <f>K87</f>
+        <v>5.9500000000000004E-2</v>
+      </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="K89" s="23"/>
@@ -3312,227 +3359,202 @@
         <v>63</v>
       </c>
       <c r="C90" t="s">
+        <v>83</v>
+      </c>
+      <c r="K90" s="23"/>
+    </row>
+    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K91" s="23"/>
+    </row>
+    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>63</v>
+      </c>
+      <c r="C92" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="91" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J91" s="1"/>
-      <c r="K91" s="1"/>
-      <c r="L91" s="1"/>
-      <c r="M91" s="1"/>
-    </row>
-    <row r="92" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A92" s="2" t="s">
+    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J93" s="1"/>
+      <c r="K93" s="1"/>
+      <c r="L93" s="1"/>
+      <c r="M93" s="1"/>
+    </row>
+    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A94" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="B92" s="3"/>
-      <c r="C92" s="3"/>
-      <c r="D92" s="3"/>
-      <c r="E92" s="3"/>
-      <c r="F92" s="3"/>
-      <c r="G92" s="3"/>
-      <c r="H92" s="3"/>
-      <c r="I92" s="3"/>
-      <c r="J92" s="3"/>
-      <c r="K92" s="3"/>
-      <c r="L92" s="3"/>
-      <c r="M92" s="3"/>
-      <c r="N92" s="3"/>
-    </row>
-    <row r="93" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A93" s="14" t="s">
+      <c r="B94" s="3"/>
+      <c r="C94" s="3"/>
+      <c r="D94" s="3"/>
+      <c r="E94" s="3"/>
+      <c r="F94" s="3"/>
+      <c r="G94" s="3"/>
+      <c r="H94" s="3"/>
+      <c r="I94" s="3"/>
+      <c r="J94" s="3"/>
+      <c r="K94" s="3"/>
+      <c r="L94" s="3"/>
+      <c r="M94" s="3"/>
+      <c r="N94" s="3"/>
+    </row>
+    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A95" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="B93" s="15"/>
-      <c r="C93" s="15"/>
-      <c r="D93" s="15"/>
-      <c r="E93" s="15"/>
-      <c r="F93" s="15"/>
-      <c r="G93" s="15"/>
-      <c r="H93" s="15"/>
-      <c r="I93" s="15"/>
-      <c r="J93" s="15"/>
-      <c r="K93" s="15"/>
-      <c r="L93" s="15"/>
-      <c r="M93" s="15"/>
-      <c r="N93" s="15"/>
-    </row>
-    <row r="94" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J94" s="5" t="s">
+      <c r="B95" s="15"/>
+      <c r="C95" s="15"/>
+      <c r="D95" s="15"/>
+      <c r="E95" s="15"/>
+      <c r="F95" s="15"/>
+      <c r="G95" s="15"/>
+      <c r="H95" s="15"/>
+      <c r="I95" s="15"/>
+      <c r="J95" s="15"/>
+      <c r="K95" s="15"/>
+      <c r="L95" s="15"/>
+      <c r="M95" s="15"/>
+      <c r="N95" s="15"/>
+    </row>
+    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J96" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="K94" s="5">
+      <c r="K96" s="5">
         <v>0.04</v>
       </c>
-      <c r="L94" s="5" t="s">
+      <c r="L96" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="M94" s="5" t="s">
+      <c r="M96" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="N94" s="5" t="s">
+      <c r="N96" s="5" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="95" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A95" s="5" t="s">
+    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A97" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="J95" s="5" t="s">
+      <c r="J97" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="K95" s="5">
+      <c r="K97" s="5">
         <v>0.02</v>
       </c>
-      <c r="L95" s="5" t="s">
+      <c r="L97" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="N95" s="5" t="s">
+      <c r="N97" s="5" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="96" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A96" s="5"/>
-      <c r="J96" s="5"/>
-      <c r="K96" s="5"/>
-      <c r="L96" s="5"/>
-      <c r="N96" s="5"/>
-    </row>
-    <row r="97" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A97" s="14" t="s">
+    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A98" s="5"/>
+      <c r="J98" s="5"/>
+      <c r="K98" s="5"/>
+      <c r="L98" s="5"/>
+      <c r="N98" s="5"/>
+    </row>
+    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A99" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="B97" s="15"/>
-      <c r="C97" s="15"/>
-      <c r="D97" s="15"/>
-      <c r="E97" s="15"/>
-      <c r="F97" s="16"/>
-      <c r="G97" s="15"/>
-      <c r="H97" s="15"/>
-      <c r="I97" s="15"/>
-      <c r="J97" s="15"/>
-      <c r="K97" s="15"/>
-      <c r="L97" s="15"/>
-      <c r="M97" s="15"/>
-      <c r="N97" s="15"/>
-    </row>
-    <row r="98" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J98" s="6" t="s">
+      <c r="B99" s="15"/>
+      <c r="C99" s="15"/>
+      <c r="D99" s="15"/>
+      <c r="E99" s="15"/>
+      <c r="F99" s="16"/>
+      <c r="G99" s="15"/>
+      <c r="H99" s="15"/>
+      <c r="I99" s="15"/>
+      <c r="J99" s="15"/>
+      <c r="K99" s="15"/>
+      <c r="L99" s="15"/>
+      <c r="M99" s="15"/>
+      <c r="N99" s="15"/>
+    </row>
+    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J100" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="K98" s="6">
+      <c r="K100" s="6">
         <v>0</v>
       </c>
-      <c r="L98" s="6" t="s">
+      <c r="L100" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="M98" s="6" t="s">
+      <c r="M100" s="6" t="s">
         <v>79</v>
-      </c>
-    </row>
-    <row r="99" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A99" t="s">
-        <v>1</v>
-      </c>
-      <c r="C99" t="s">
-        <v>2</v>
-      </c>
-      <c r="D99" t="s">
-        <v>3</v>
-      </c>
-      <c r="J99" t="s">
-        <v>77</v>
-      </c>
-      <c r="K99">
-        <v>0.24</v>
-      </c>
-      <c r="L99" t="s">
-        <v>78</v>
-      </c>
-      <c r="N99" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="100" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A100" t="s">
-        <v>1</v>
-      </c>
-      <c r="J100" t="s">
-        <v>77</v>
-      </c>
-      <c r="K100">
-        <v>0.18</v>
-      </c>
-      <c r="L100" t="s">
-        <v>78</v>
-      </c>
-      <c r="N100" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>82</v>
+        <v>1</v>
+      </c>
+      <c r="C101" t="s">
+        <v>2</v>
+      </c>
+      <c r="D101" t="s">
+        <v>3</v>
       </c>
       <c r="J101" t="s">
         <v>77</v>
       </c>
       <c r="K101">
-        <v>0.19</v>
+        <v>0.24</v>
       </c>
       <c r="L101" t="s">
         <v>78</v>
       </c>
       <c r="N101" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="J102" t="s">
         <v>77</v>
       </c>
       <c r="K102">
-        <v>0.3</v>
+        <v>0.18</v>
       </c>
       <c r="L102" t="s">
         <v>78</v>
       </c>
       <c r="N102" t="s">
-        <v>95</v>
+        <v>86</v>
       </c>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="J103" t="s">
         <v>77</v>
       </c>
       <c r="K103">
-        <v>0.45</v>
+        <v>0.19</v>
       </c>
       <c r="L103" t="s">
         <v>78</v>
       </c>
       <c r="N103" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>63</v>
-      </c>
-      <c r="C104" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="J104" t="s">
         <v>77</v>
       </c>
       <c r="K104">
-        <v>0.36</v>
+        <v>0.3</v>
       </c>
       <c r="L104" t="s">
         <v>78</v>
@@ -3543,67 +3565,70 @@
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>63</v>
-      </c>
-      <c r="C105" t="s">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="J105" t="s">
         <v>77</v>
       </c>
       <c r="K105">
-        <v>0.39</v>
+        <v>0.45</v>
       </c>
       <c r="L105" t="s">
         <v>78</v>
       </c>
       <c r="N105" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="106" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>63</v>
+      </c>
+      <c r="C106" t="s">
+        <v>64</v>
+      </c>
+      <c r="J106" t="s">
+        <v>77</v>
+      </c>
+      <c r="K106">
+        <v>0.36</v>
+      </c>
+      <c r="L106" t="s">
+        <v>78</v>
+      </c>
+      <c r="N106" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F107" s="5" t="s">
-        <v>19</v>
+      <c r="A107" t="s">
+        <v>63</v>
+      </c>
+      <c r="C107" t="s">
+        <v>83</v>
       </c>
       <c r="J107" t="s">
-        <v>84</v>
+        <v>77</v>
       </c>
       <c r="K107">
-        <v>1</v>
+        <v>0.39</v>
       </c>
       <c r="L107" t="s">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="N107" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="108" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F108" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="J108" t="s">
-        <v>84</v>
-      </c>
-      <c r="K108">
-        <v>3.5</v>
-      </c>
-      <c r="L108" t="s">
-        <v>85</v>
-      </c>
-      <c r="N108" t="s">
-        <v>86</v>
+        <v>95</v>
       </c>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F109" s="5" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="J109" t="s">
         <v>84</v>
       </c>
       <c r="K109">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L109" t="s">
         <v>85</v>
@@ -3614,13 +3639,13 @@
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F110" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J110" t="s">
         <v>84</v>
       </c>
       <c r="K110">
-        <v>17</v>
+        <v>3.5</v>
       </c>
       <c r="L110" t="s">
         <v>85</v>
@@ -3629,168 +3654,144 @@
         <v>86</v>
       </c>
     </row>
+    <row r="111" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F111" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J111" t="s">
+        <v>84</v>
+      </c>
+      <c r="K111">
+        <v>2</v>
+      </c>
+      <c r="L111" t="s">
+        <v>85</v>
+      </c>
+      <c r="N111" t="s">
+        <v>86</v>
+      </c>
+    </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F112" s="5" t="s">
+        <v>26</v>
+      </c>
       <c r="J112" t="s">
+        <v>84</v>
+      </c>
+      <c r="K112">
+        <v>17</v>
+      </c>
+      <c r="L112" t="s">
+        <v>85</v>
+      </c>
+      <c r="N112" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J114" t="s">
         <v>97</v>
       </c>
-      <c r="K112">
+      <c r="K114">
         <v>55</v>
-      </c>
-      <c r="L112" t="s">
-        <v>21</v>
-      </c>
-      <c r="M112" t="s">
-        <v>100</v>
-      </c>
-      <c r="N112" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="113" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F113" s="5"/>
-      <c r="J113" t="s">
-        <v>99</v>
-      </c>
-      <c r="K113">
-        <v>10</v>
-      </c>
-      <c r="L113" t="s">
-        <v>21</v>
-      </c>
-      <c r="M113" t="s">
-        <v>101</v>
-      </c>
-      <c r="N113" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="114" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F114" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J114" t="s">
-        <v>99</v>
-      </c>
-      <c r="K114">
-        <v>0</v>
       </c>
       <c r="L114" t="s">
         <v>21</v>
       </c>
+      <c r="M114" t="s">
+        <v>100</v>
+      </c>
+      <c r="N114" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="115" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F115" s="5"/>
+      <c r="J115" t="s">
+        <v>99</v>
+      </c>
+      <c r="K115">
+        <v>10</v>
+      </c>
+      <c r="L115" t="s">
+        <v>21</v>
+      </c>
+      <c r="M115" t="s">
+        <v>101</v>
+      </c>
+      <c r="N115" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="116" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A116" s="2" t="s">
+      <c r="F116" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J116" t="s">
+        <v>99</v>
+      </c>
+      <c r="K116">
+        <v>0</v>
+      </c>
+      <c r="L116" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="118" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A118" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B116" s="3"/>
-      <c r="C116" s="3"/>
-      <c r="D116" s="3"/>
-      <c r="E116" s="3"/>
-      <c r="F116" s="3"/>
-      <c r="G116" s="3"/>
-      <c r="H116" s="3"/>
-      <c r="I116" s="3"/>
-      <c r="J116" s="3"/>
-      <c r="K116" s="3"/>
-      <c r="L116" s="3"/>
-      <c r="M116" s="3"/>
-      <c r="N116" s="3"/>
-    </row>
-    <row r="117" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="14" t="s">
+      <c r="B118" s="3"/>
+      <c r="C118" s="3"/>
+      <c r="D118" s="3"/>
+      <c r="E118" s="3"/>
+      <c r="F118" s="3"/>
+      <c r="G118" s="3"/>
+      <c r="H118" s="3"/>
+      <c r="I118" s="3"/>
+      <c r="J118" s="3"/>
+      <c r="K118" s="3"/>
+      <c r="L118" s="3"/>
+      <c r="M118" s="3"/>
+      <c r="N118" s="3"/>
+    </row>
+    <row r="119" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="B117" s="15"/>
-      <c r="C117" s="15"/>
-      <c r="D117" s="15"/>
-      <c r="E117" s="15"/>
-      <c r="F117" s="15"/>
-      <c r="G117" s="15"/>
-      <c r="H117" s="15"/>
-      <c r="I117" s="15"/>
-      <c r="J117" s="15"/>
-      <c r="K117" s="15"/>
-      <c r="L117" s="15"/>
-      <c r="M117" s="15"/>
-      <c r="N117" s="15"/>
-    </row>
-    <row r="118" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="13"/>
-    </row>
-    <row r="119" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="13"/>
+      <c r="B119" s="15"/>
+      <c r="C119" s="15"/>
+      <c r="D119" s="15"/>
+      <c r="E119" s="15"/>
+      <c r="F119" s="15"/>
+      <c r="G119" s="15"/>
+      <c r="H119" s="15"/>
+      <c r="I119" s="15"/>
+      <c r="J119" s="15"/>
+      <c r="K119" s="15"/>
+      <c r="L119" s="15"/>
+      <c r="M119" s="15"/>
+      <c r="N119" s="15"/>
     </row>
     <row r="120" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="13"/>
     </row>
-    <row r="121" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A121" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B121" s="8"/>
-      <c r="C121" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="D121" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E121" s="8"/>
-      <c r="F121" s="8"/>
-      <c r="G121" s="8"/>
-      <c r="H121" s="8"/>
-      <c r="I121" s="8"/>
-      <c r="J121" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="K121" s="8">
-        <v>137</v>
-      </c>
-      <c r="L121" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M121" s="8"/>
-      <c r="N121" s="8" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="122" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A122" s="8" t="s">
-        <v>1</v>
-      </c>
-      <c r="B122" s="8"/>
-      <c r="C122" s="8" t="s">
-        <v>9</v>
-      </c>
-      <c r="D122" s="8" t="s">
-        <v>3</v>
-      </c>
-      <c r="E122" s="8"/>
-      <c r="F122" s="8"/>
-      <c r="G122" s="8"/>
-      <c r="H122" s="8"/>
-      <c r="I122" s="8"/>
-      <c r="J122" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="K122" s="8">
-        <v>63</v>
-      </c>
-      <c r="L122" s="8" t="s">
-        <v>8</v>
-      </c>
-      <c r="M122" s="8"/>
-      <c r="N122" s="8" t="s">
-        <v>11</v>
-      </c>
+    <row r="121" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="13"/>
+    </row>
+    <row r="122" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="13"/>
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A123" s="8" t="s">
         <v>1</v>
       </c>
       <c r="B123" s="8"/>
-      <c r="C123" s="8"/>
+      <c r="C123" s="8" t="s">
+        <v>2</v>
+      </c>
       <c r="D123" s="8" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E123" s="8"/>
       <c r="F123" s="8"/>
@@ -3801,14 +3802,14 @@
         <v>7</v>
       </c>
       <c r="K123" s="8">
-        <v>47</v>
+        <v>137</v>
       </c>
       <c r="L123" s="8" t="s">
         <v>8</v>
       </c>
       <c r="M123" s="8"/>
       <c r="N123" s="8" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.25">
@@ -3816,9 +3817,11 @@
         <v>1</v>
       </c>
       <c r="B124" s="8"/>
-      <c r="C124" s="8"/>
+      <c r="C124" s="8" t="s">
+        <v>9</v>
+      </c>
       <c r="D124" s="8" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E124" s="8"/>
       <c r="F124" s="8"/>
@@ -3829,7 +3832,7 @@
         <v>7</v>
       </c>
       <c r="K124" s="8">
-        <v>28</v>
+        <v>63</v>
       </c>
       <c r="L124" s="8" t="s">
         <v>8</v>
@@ -3846,7 +3849,7 @@
       <c r="B125" s="8"/>
       <c r="C125" s="8"/>
       <c r="D125" s="8" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E125" s="8"/>
       <c r="F125" s="8"/>
@@ -3874,7 +3877,7 @@
       <c r="B126" s="8"/>
       <c r="C126" s="8"/>
       <c r="D126" s="8" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E126" s="8"/>
       <c r="F126" s="8"/>
@@ -3885,7 +3888,7 @@
         <v>7</v>
       </c>
       <c r="K126" s="8">
-        <v>47</v>
+        <v>28</v>
       </c>
       <c r="L126" s="8" t="s">
         <v>8</v>
@@ -3902,7 +3905,7 @@
       <c r="B127" s="8"/>
       <c r="C127" s="8"/>
       <c r="D127" s="8" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E127" s="8"/>
       <c r="F127" s="8"/>
@@ -3918,21 +3921,19 @@
       <c r="L127" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="M127" s="8" t="s">
-        <v>18</v>
-      </c>
+      <c r="M127" s="8"/>
       <c r="N127" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A128" s="8" t="s">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="B128" s="8"/>
       <c r="C128" s="8"/>
       <c r="D128" s="8" t="s">
-        <v>50</v>
+        <v>16</v>
       </c>
       <c r="E128" s="8"/>
       <c r="F128" s="8"/>
@@ -3943,7 +3944,7 @@
         <v>7</v>
       </c>
       <c r="K128" s="8">
-        <v>22.5</v>
+        <v>47</v>
       </c>
       <c r="L128" s="8" t="s">
         <v>8</v>
@@ -3955,12 +3956,12 @@
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A129" s="8" t="s">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="B129" s="8"/>
       <c r="C129" s="8"/>
       <c r="D129" s="8" t="s">
-        <v>51</v>
+        <v>17</v>
       </c>
       <c r="E129" s="8"/>
       <c r="F129" s="8"/>
@@ -3971,12 +3972,14 @@
         <v>7</v>
       </c>
       <c r="K129" s="8">
-        <v>13</v>
+        <v>47</v>
       </c>
       <c r="L129" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="M129" s="8"/>
+      <c r="M129" s="8" t="s">
+        <v>18</v>
+      </c>
       <c r="N129" s="8" t="s">
         <v>11</v>
       </c>
@@ -3988,7 +3991,7 @@
       <c r="B130" s="8"/>
       <c r="C130" s="8"/>
       <c r="D130" s="8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E130" s="8"/>
       <c r="F130" s="8"/>
@@ -3999,14 +4002,12 @@
         <v>7</v>
       </c>
       <c r="K130" s="8">
-        <v>1.2</v>
+        <v>22.5</v>
       </c>
       <c r="L130" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="M130" s="9" t="s">
-        <v>56</v>
-      </c>
+      <c r="M130" s="8"/>
       <c r="N130" s="8" t="s">
         <v>11</v>
       </c>
@@ -4018,7 +4019,7 @@
       <c r="B131" s="8"/>
       <c r="C131" s="8"/>
       <c r="D131" s="8" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E131" s="8"/>
       <c r="F131" s="8"/>
@@ -4029,14 +4030,12 @@
         <v>7</v>
       </c>
       <c r="K131" s="8">
-        <v>9.5</v>
+        <v>13</v>
       </c>
       <c r="L131" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="M131" s="8" t="s">
-        <v>54</v>
-      </c>
+      <c r="M131" s="8"/>
       <c r="N131" s="8" t="s">
         <v>11</v>
       </c>
@@ -4048,7 +4047,7 @@
       <c r="B132" s="8"/>
       <c r="C132" s="8"/>
       <c r="D132" s="8" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E132" s="8"/>
       <c r="F132" s="8"/>
@@ -4059,13 +4058,13 @@
         <v>7</v>
       </c>
       <c r="K132" s="8">
-        <v>9.5</v>
+        <v>1.2</v>
       </c>
       <c r="L132" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="M132" s="8" t="s">
-        <v>55</v>
+      <c r="M132" s="9" t="s">
+        <v>56</v>
       </c>
       <c r="N132" s="8" t="s">
         <v>11</v>
@@ -4078,7 +4077,7 @@
       <c r="B133" s="8"/>
       <c r="C133" s="8"/>
       <c r="D133" s="8" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E133" s="8"/>
       <c r="F133" s="8"/>
@@ -4095,48 +4094,70 @@
         <v>8</v>
       </c>
       <c r="M133" s="8" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="N133" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A134" t="s">
-        <v>68</v>
-      </c>
-      <c r="J134" t="s">
+      <c r="A134" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B134" s="8"/>
+      <c r="C134" s="8"/>
+      <c r="D134" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="E134" s="8"/>
+      <c r="F134" s="8"/>
+      <c r="G134" s="8"/>
+      <c r="H134" s="8"/>
+      <c r="I134" s="8"/>
+      <c r="J134" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="K134">
-        <v>48</v>
-      </c>
-      <c r="L134" t="s">
+      <c r="K134" s="8">
+        <v>9.5</v>
+      </c>
+      <c r="L134" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="N134" t="s">
+      <c r="M134" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="N134" s="8" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="135" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A135" t="s">
-        <v>68</v>
-      </c>
-      <c r="J135" t="s">
-        <v>127</v>
-      </c>
-      <c r="K135" s="17">
-        <f>K134 * (6.4/2.29)/16</f>
-        <v>8.3842794759825345</v>
-      </c>
-      <c r="L135" t="s">
-        <v>130</v>
-      </c>
-      <c r="M135" t="s">
-        <v>132</v>
-      </c>
-      <c r="N135" t="s">
-        <v>136</v>
+      <c r="A135" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B135" s="8"/>
+      <c r="C135" s="8"/>
+      <c r="D135" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="E135" s="8"/>
+      <c r="F135" s="8"/>
+      <c r="G135" s="8"/>
+      <c r="H135" s="8"/>
+      <c r="I135" s="8"/>
+      <c r="J135" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="K135" s="8">
+        <v>9.5</v>
+      </c>
+      <c r="L135" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="M135" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="N135" s="8" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.25">
@@ -4144,64 +4165,58 @@
         <v>68</v>
       </c>
       <c r="J136" t="s">
-        <v>128</v>
-      </c>
-      <c r="K136" s="17">
-        <f>K134 * (15.9/(47/39))/16</f>
-        <v>39.58085106382979</v>
+        <v>7</v>
+      </c>
+      <c r="K136">
+        <v>48</v>
       </c>
       <c r="L136" t="s">
-        <v>131</v>
-      </c>
-      <c r="M136" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="N136" t="s">
-        <v>136</v>
+        <v>11</v>
       </c>
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>63</v>
-      </c>
-      <c r="C137" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="J137" t="s">
-        <v>7</v>
-      </c>
-      <c r="K137" s="19">
-        <v>0.6</v>
+        <v>127</v>
+      </c>
+      <c r="K137" s="17">
+        <f>K136 * (6.4/2.29)/16</f>
+        <v>8.3842794759825345</v>
       </c>
       <c r="L137" t="s">
-        <v>8</v>
+        <v>130</v>
+      </c>
+      <c r="M137" t="s">
+        <v>132</v>
       </c>
       <c r="N137" t="s">
-        <v>11</v>
+        <v>136</v>
       </c>
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>63</v>
-      </c>
-      <c r="C138" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="J138" t="s">
-        <v>127</v>
-      </c>
-      <c r="K138" s="19">
-        <f>K137 * (0.39/2.29)/0.75</f>
-        <v>0.13624454148471615</v>
+        <v>128</v>
+      </c>
+      <c r="K138" s="17">
+        <f>K136 * (15.9/(47/39))/16</f>
+        <v>39.58085106382979</v>
       </c>
       <c r="L138" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M138" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N138" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.25">
@@ -4212,20 +4227,16 @@
         <v>83</v>
       </c>
       <c r="J139" t="s">
-        <v>128</v>
+        <v>7</v>
       </c>
       <c r="K139" s="19">
-        <f>K137 * (0.33/(47/39))/0.75</f>
-        <v>0.21906382978723404</v>
+        <v>0.6</v>
       </c>
       <c r="L139" t="s">
-        <v>131</v>
-      </c>
-      <c r="M139" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="N139" t="s">
-        <v>135</v>
+        <v>11</v>
       </c>
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.25">
@@ -4233,22 +4244,23 @@
         <v>63</v>
       </c>
       <c r="C140" t="s">
-        <v>64</v>
-      </c>
-      <c r="D140" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="J140" t="s">
-        <v>7</v>
-      </c>
-      <c r="K140">
-        <v>0.28999999999999998</v>
+        <v>127</v>
+      </c>
+      <c r="K140" s="19">
+        <f>K139 * (0.39/2.29)/0.75</f>
+        <v>0.13624454148471615</v>
       </c>
       <c r="L140" t="s">
-        <v>8</v>
+        <v>130</v>
+      </c>
+      <c r="M140" t="s">
+        <v>132</v>
       </c>
       <c r="N140" t="s">
-        <v>11</v>
+        <v>135</v>
       </c>
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.25">
@@ -4256,26 +4268,23 @@
         <v>63</v>
       </c>
       <c r="C141" t="s">
-        <v>64</v>
-      </c>
-      <c r="D141" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="J141" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K141" s="19">
-        <f>K140 * (0.19/2.29)/0.53</f>
-        <v>4.5398368624866105E-2</v>
+        <f>K139 * (0.33/(47/39))/0.75</f>
+        <v>0.21906382978723404</v>
       </c>
       <c r="L141" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M141" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N141" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.25">
@@ -4289,20 +4298,16 @@
         <v>65</v>
       </c>
       <c r="J142" t="s">
-        <v>128</v>
-      </c>
-      <c r="K142" s="19">
-        <f>K140 * (0.26/(47/39))/0.53</f>
-        <v>0.11804897631473303</v>
+        <v>7</v>
+      </c>
+      <c r="K142">
+        <v>0.28999999999999998</v>
       </c>
       <c r="L142" t="s">
-        <v>131</v>
-      </c>
-      <c r="M142" t="s">
-        <v>133</v>
+        <v>8</v>
       </c>
       <c r="N142" t="s">
-        <v>129</v>
+        <v>11</v>
       </c>
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.25">
@@ -4312,20 +4317,24 @@
       <c r="C143" t="s">
         <v>64</v>
       </c>
+      <c r="D143" t="s">
+        <v>65</v>
+      </c>
       <c r="J143" t="s">
-        <v>7</v>
+        <v>127</v>
       </c>
       <c r="K143" s="19">
-        <v>0.6</v>
+        <f>K142 * (0.19/2.29)/0.53</f>
+        <v>4.5398368624866105E-2</v>
       </c>
       <c r="L143" t="s">
-        <v>8</v>
+        <v>130</v>
       </c>
       <c r="M143" t="s">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="N143" t="s">
-        <v>11</v>
+        <v>129</v>
       </c>
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.25">
@@ -4335,21 +4344,24 @@
       <c r="C144" t="s">
         <v>64</v>
       </c>
+      <c r="D144" t="s">
+        <v>65</v>
+      </c>
       <c r="J144" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="K144" s="19">
-        <f>K143 * (0.55/2.29)/1.12</f>
-        <v>0.12866500311915158</v>
+        <f>K142 * (0.26/(47/39))/0.53</f>
+        <v>0.11804897631473303</v>
       </c>
       <c r="L144" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="M144" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N144" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.25">
@@ -4360,55 +4372,76 @@
         <v>64</v>
       </c>
       <c r="J145" t="s">
+        <v>7</v>
+      </c>
+      <c r="K145" s="19">
+        <v>0.6</v>
+      </c>
+      <c r="L145" t="s">
+        <v>8</v>
+      </c>
+      <c r="M145" t="s">
+        <v>66</v>
+      </c>
+      <c r="N145" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>63</v>
+      </c>
+      <c r="C146" t="s">
+        <v>64</v>
+      </c>
+      <c r="J146" t="s">
+        <v>127</v>
+      </c>
+      <c r="K146" s="19">
+        <f>K145 * (0.55/2.29)/1.12</f>
+        <v>0.12866500311915158</v>
+      </c>
+      <c r="L146" t="s">
+        <v>130</v>
+      </c>
+      <c r="M146" t="s">
+        <v>132</v>
+      </c>
+      <c r="N146" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="147" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>63</v>
+      </c>
+      <c r="C147" t="s">
+        <v>64</v>
+      </c>
+      <c r="J147" t="s">
         <v>128</v>
       </c>
-      <c r="K145" s="19">
-        <f>K143 * (0.44/(47/39))/1.12</f>
+      <c r="K147" s="19">
+        <f>K145 * (0.44/(47/39))/1.12</f>
         <v>0.19559270516717325</v>
       </c>
-      <c r="L145" t="s">
+      <c r="L147" t="s">
         <v>131</v>
       </c>
-      <c r="M145" t="s">
+      <c r="M147" t="s">
         <v>133</v>
       </c>
-      <c r="N145" t="s">
+      <c r="N147" t="s">
         <v>134</v>
       </c>
     </row>
-    <row r="146" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F146" s="5"/>
-    </row>
-    <row r="147" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="13"/>
-      <c r="J147" s="6" t="s">
-        <v>102</v>
-      </c>
-      <c r="K147" s="18">
-        <v>0</v>
-      </c>
-      <c r="L147" s="18"/>
-      <c r="M147" s="18" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="148" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="13"/>
-      <c r="J148" s="6" t="s">
-        <v>106</v>
-      </c>
-      <c r="K148" s="18">
-        <v>0</v>
-      </c>
-      <c r="L148" s="18"/>
-      <c r="M148" s="18" t="s">
-        <v>122</v>
-      </c>
+    <row r="148" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F148" s="5"/>
     </row>
     <row r="149" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A149" s="13"/>
       <c r="J149" s="6" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="K149" s="18">
         <v>0</v>
@@ -4418,49 +4451,30 @@
         <v>122</v>
       </c>
     </row>
-    <row r="150" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A150" t="s">
-        <v>1</v>
-      </c>
-      <c r="D150" t="s">
-        <v>3</v>
-      </c>
-      <c r="F150" s="5"/>
-      <c r="J150" t="s">
-        <v>102</v>
-      </c>
-      <c r="K150">
-        <v>22.5</v>
-      </c>
-      <c r="L150" t="s">
-        <v>108</v>
-      </c>
-      <c r="M150" t="s">
-        <v>111</v>
-      </c>
-      <c r="N150" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="151" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A151" t="s">
-        <v>1</v>
-      </c>
-      <c r="D151" t="s">
-        <v>3</v>
-      </c>
-      <c r="F151" s="5"/>
-      <c r="J151" t="s">
+    <row r="150" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="13"/>
+      <c r="J150" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="K151">
-        <v>7.4</v>
-      </c>
-      <c r="L151" t="s">
-        <v>109</v>
-      </c>
-      <c r="N151" t="s">
-        <v>124</v>
+      <c r="K150" s="18">
+        <v>0</v>
+      </c>
+      <c r="L150" s="18"/>
+      <c r="M150" s="18" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="151" spans="1:14" s="12" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="13"/>
+      <c r="J151" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="K151" s="18">
+        <v>0</v>
+      </c>
+      <c r="L151" s="18"/>
+      <c r="M151" s="18" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.25">
@@ -4472,13 +4486,16 @@
       </c>
       <c r="F152" s="5"/>
       <c r="J152" t="s">
-        <v>107</v>
-      </c>
-      <c r="K152" s="17">
-        <v>2</v>
+        <v>102</v>
+      </c>
+      <c r="K152">
+        <v>22.5</v>
       </c>
       <c r="L152" t="s">
-        <v>110</v>
+        <v>108</v>
+      </c>
+      <c r="M152" t="s">
+        <v>111</v>
       </c>
       <c r="N152" t="s">
         <v>124</v>
@@ -4489,63 +4506,63 @@
         <v>1</v>
       </c>
       <c r="D153" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F153" s="5"/>
       <c r="J153" t="s">
+        <v>106</v>
+      </c>
+      <c r="K153">
+        <v>7.4</v>
+      </c>
+      <c r="L153" t="s">
+        <v>109</v>
+      </c>
+      <c r="N153" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>1</v>
+      </c>
+      <c r="D154" t="s">
+        <v>3</v>
+      </c>
+      <c r="F154" s="5"/>
+      <c r="J154" t="s">
+        <v>107</v>
+      </c>
+      <c r="K154" s="17">
+        <v>2</v>
+      </c>
+      <c r="L154" t="s">
+        <v>110</v>
+      </c>
+      <c r="N154" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>1</v>
+      </c>
+      <c r="D155" t="s">
+        <v>12</v>
+      </c>
+      <c r="F155" s="5"/>
+      <c r="J155" t="s">
         <v>102</v>
       </c>
-      <c r="K153">
+      <c r="K155">
         <f>23.1</f>
         <v>23.1</v>
       </c>
-      <c r="L153" t="s">
+      <c r="L155" t="s">
         <v>108</v>
       </c>
-      <c r="M153" t="s">
+      <c r="M155" t="s">
         <v>112</v>
-      </c>
-      <c r="N153" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="154" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A154" t="s">
-        <v>1</v>
-      </c>
-      <c r="D154" t="s">
-        <v>12</v>
-      </c>
-      <c r="F154" s="5"/>
-      <c r="J154" t="s">
-        <v>106</v>
-      </c>
-      <c r="K154">
-        <v>7.4</v>
-      </c>
-      <c r="L154" t="s">
-        <v>109</v>
-      </c>
-      <c r="N154" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="155" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A155" t="s">
-        <v>1</v>
-      </c>
-      <c r="D155" t="s">
-        <v>12</v>
-      </c>
-      <c r="F155" s="5"/>
-      <c r="J155" t="s">
-        <v>107</v>
-      </c>
-      <c r="K155" s="17">
-        <v>2</v>
-      </c>
-      <c r="L155" t="s">
-        <v>110</v>
       </c>
       <c r="N155" t="s">
         <v>124</v>
@@ -4556,20 +4573,17 @@
         <v>1</v>
       </c>
       <c r="D156" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F156" s="5"/>
       <c r="J156" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K156">
-        <v>26.4</v>
+        <v>7.4</v>
       </c>
       <c r="L156" t="s">
-        <v>108</v>
-      </c>
-      <c r="M156" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="N156" t="s">
         <v>124</v>
@@ -4580,17 +4594,17 @@
         <v>1</v>
       </c>
       <c r="D157" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F157" s="5"/>
       <c r="J157" t="s">
-        <v>106</v>
-      </c>
-      <c r="K157">
-        <v>6.85</v>
+        <v>107</v>
+      </c>
+      <c r="K157" s="17">
+        <v>2</v>
       </c>
       <c r="L157" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N157" t="s">
         <v>124</v>
@@ -4605,13 +4619,16 @@
       </c>
       <c r="F158" s="5"/>
       <c r="J158" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="K158">
-        <v>1.69</v>
+        <v>26.4</v>
       </c>
       <c r="L158" t="s">
-        <v>110</v>
+        <v>108</v>
+      </c>
+      <c r="M158" t="s">
+        <v>113</v>
       </c>
       <c r="N158" t="s">
         <v>124</v>
@@ -4622,20 +4639,17 @@
         <v>1</v>
       </c>
       <c r="D159" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F159" s="5"/>
       <c r="J159" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K159">
-        <v>27.04</v>
+        <v>6.85</v>
       </c>
       <c r="L159" t="s">
-        <v>108</v>
-      </c>
-      <c r="M159" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="N159" t="s">
         <v>124</v>
@@ -4646,17 +4660,17 @@
         <v>1</v>
       </c>
       <c r="D160" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="F160" s="5"/>
       <c r="J160" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K160">
-        <v>7.4</v>
+        <v>1.69</v>
       </c>
       <c r="L160" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N160" t="s">
         <v>124</v>
@@ -4671,13 +4685,16 @@
       </c>
       <c r="F161" s="5"/>
       <c r="J161" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="K161">
-        <v>1.91</v>
+        <v>27.04</v>
       </c>
       <c r="L161" t="s">
-        <v>110</v>
+        <v>108</v>
+      </c>
+      <c r="M161" t="s">
+        <v>115</v>
       </c>
       <c r="N161" t="s">
         <v>124</v>
@@ -4688,20 +4705,17 @@
         <v>1</v>
       </c>
       <c r="D162" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F162" s="5"/>
       <c r="J162" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K162">
-        <v>27.04</v>
+        <v>7.4</v>
       </c>
       <c r="L162" t="s">
-        <v>108</v>
-      </c>
-      <c r="M162" t="s">
-        <v>115</v>
+        <v>109</v>
       </c>
       <c r="N162" t="s">
         <v>124</v>
@@ -4712,17 +4726,17 @@
         <v>1</v>
       </c>
       <c r="D163" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F163" s="5"/>
       <c r="J163" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K163">
-        <v>7.4</v>
+        <v>1.91</v>
       </c>
       <c r="L163" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N163" t="s">
         <v>124</v>
@@ -4737,13 +4751,16 @@
       </c>
       <c r="F164" s="5"/>
       <c r="J164" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="K164">
-        <v>1.91</v>
+        <v>27.04</v>
       </c>
       <c r="L164" t="s">
-        <v>110</v>
+        <v>108</v>
+      </c>
+      <c r="M164" t="s">
+        <v>115</v>
       </c>
       <c r="N164" t="s">
         <v>124</v>
@@ -4754,20 +4771,17 @@
         <v>1</v>
       </c>
       <c r="D165" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F165" s="5"/>
       <c r="J165" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K165">
-        <v>25.28</v>
+        <v>7.4</v>
       </c>
       <c r="L165" t="s">
-        <v>108</v>
-      </c>
-      <c r="M165" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="N165" t="s">
         <v>124</v>
@@ -4778,17 +4792,17 @@
         <v>1</v>
       </c>
       <c r="D166" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F166" s="5"/>
       <c r="J166" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K166">
-        <v>7.4</v>
+        <v>1.91</v>
       </c>
       <c r="L166" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N166" t="s">
         <v>124</v>
@@ -4803,59 +4817,65 @@
       </c>
       <c r="F167" s="5"/>
       <c r="J167" t="s">
-        <v>107</v>
-      </c>
-      <c r="K167" s="17">
-        <v>2</v>
+        <v>102</v>
+      </c>
+      <c r="K167">
+        <v>25.28</v>
       </c>
       <c r="L167" t="s">
-        <v>110</v>
+        <v>108</v>
+      </c>
+      <c r="M167" t="s">
+        <v>114</v>
       </c>
       <c r="N167" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>1</v>
+      </c>
+      <c r="D168" t="s">
+        <v>17</v>
+      </c>
       <c r="F168" s="5"/>
+      <c r="J168" t="s">
+        <v>106</v>
+      </c>
+      <c r="K168">
+        <v>7.4</v>
+      </c>
+      <c r="L168" t="s">
+        <v>109</v>
+      </c>
+      <c r="N168" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>82</v>
+        <v>1</v>
+      </c>
+      <c r="D169" t="s">
+        <v>17</v>
       </c>
       <c r="F169" s="5"/>
       <c r="J169" t="s">
-        <v>102</v>
-      </c>
-      <c r="K169" s="5">
-        <v>25</v>
+        <v>107</v>
+      </c>
+      <c r="K169" s="17">
+        <v>2</v>
       </c>
       <c r="L169" t="s">
-        <v>108</v>
-      </c>
-      <c r="M169" t="s">
-        <v>125</v>
+        <v>110</v>
       </c>
       <c r="N169" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A170" t="s">
-        <v>82</v>
-      </c>
       <c r="F170" s="5"/>
-      <c r="J170" t="s">
-        <v>106</v>
-      </c>
-      <c r="K170" s="5">
-        <v>7.8</v>
-      </c>
-      <c r="L170" t="s">
-        <v>109</v>
-      </c>
-      <c r="N170" t="s">
-        <v>124</v>
-      </c>
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
@@ -4863,13 +4883,16 @@
       </c>
       <c r="F171" s="5"/>
       <c r="J171" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="K171" s="5">
-        <v>1.7</v>
+        <v>25</v>
       </c>
       <c r="L171" t="s">
-        <v>110</v>
+        <v>108</v>
+      </c>
+      <c r="M171" t="s">
+        <v>125</v>
       </c>
       <c r="N171" t="s">
         <v>124</v>
@@ -4879,21 +4902,15 @@
       <c r="A172" t="s">
         <v>82</v>
       </c>
-      <c r="D172" t="s">
-        <v>116</v>
-      </c>
       <c r="F172" s="5"/>
       <c r="J172" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K172" s="5">
-        <v>26.2</v>
+        <v>7.8</v>
       </c>
       <c r="L172" t="s">
-        <v>108</v>
-      </c>
-      <c r="M172" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="N172" t="s">
         <v>124</v>
@@ -4903,18 +4920,15 @@
       <c r="A173" t="s">
         <v>82</v>
       </c>
-      <c r="D173" t="s">
-        <v>116</v>
-      </c>
       <c r="F173" s="5"/>
       <c r="J173" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K173" s="5">
-        <v>5.2</v>
+        <v>1.7</v>
       </c>
       <c r="L173" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N173" t="s">
         <v>124</v>
@@ -4929,60 +4943,66 @@
       </c>
       <c r="F174" s="5"/>
       <c r="J174" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="K174" s="5">
-        <v>1.7</v>
+        <v>26.2</v>
       </c>
       <c r="L174" t="s">
-        <v>110</v>
+        <v>108</v>
+      </c>
+      <c r="M174" t="s">
+        <v>126</v>
       </c>
       <c r="N174" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>82</v>
+      </c>
+      <c r="D175" t="s">
+        <v>116</v>
+      </c>
       <c r="F175" s="5"/>
-      <c r="K175" s="5"/>
+      <c r="J175" t="s">
+        <v>106</v>
+      </c>
+      <c r="K175" s="5">
+        <v>5.2</v>
+      </c>
+      <c r="L175" t="s">
+        <v>109</v>
+      </c>
+      <c r="N175" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
-        <v>68</v>
+        <v>82</v>
+      </c>
+      <c r="D176" t="s">
+        <v>116</v>
       </c>
       <c r="F176" s="5"/>
       <c r="J176" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="K176" s="5">
-        <v>29.9</v>
+        <v>1.7</v>
       </c>
       <c r="L176" t="s">
-        <v>108</v>
-      </c>
-      <c r="M176" t="s">
-        <v>123</v>
+        <v>110</v>
       </c>
       <c r="N176" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A177" t="s">
-        <v>68</v>
-      </c>
       <c r="F177" s="5"/>
-      <c r="J177" t="s">
-        <v>106</v>
-      </c>
-      <c r="K177" s="5">
-        <v>7.5</v>
-      </c>
-      <c r="L177" t="s">
-        <v>109</v>
-      </c>
-      <c r="N177" t="s">
-        <v>124</v>
-      </c>
+      <c r="K177" s="5"/>
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
@@ -4990,66 +5010,60 @@
       </c>
       <c r="F178" s="5"/>
       <c r="J178" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="K178" s="5">
-        <v>2</v>
+        <v>29.9</v>
       </c>
       <c r="L178" t="s">
-        <v>110</v>
+        <v>108</v>
+      </c>
+      <c r="M178" t="s">
+        <v>123</v>
       </c>
       <c r="N178" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A179" t="s">
+        <v>68</v>
+      </c>
       <c r="F179" s="5"/>
-      <c r="K179" s="17"/>
+      <c r="J179" t="s">
+        <v>106</v>
+      </c>
+      <c r="K179" s="5">
+        <v>7.5</v>
+      </c>
+      <c r="L179" t="s">
+        <v>109</v>
+      </c>
+      <c r="N179" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>43</v>
-      </c>
-      <c r="D180" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="F180" s="5"/>
       <c r="J180" t="s">
-        <v>102</v>
-      </c>
-      <c r="K180">
-        <v>25</v>
+        <v>107</v>
+      </c>
+      <c r="K180" s="5">
+        <v>2</v>
       </c>
       <c r="L180" t="s">
-        <v>108</v>
-      </c>
-      <c r="M180" t="s">
-        <v>117</v>
+        <v>110</v>
       </c>
       <c r="N180" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A181" t="s">
-        <v>43</v>
-      </c>
-      <c r="D181" t="s">
-        <v>50</v>
-      </c>
       <c r="F181" s="5"/>
-      <c r="J181" t="s">
-        <v>106</v>
-      </c>
-      <c r="K181">
-        <v>5.35</v>
-      </c>
-      <c r="L181" t="s">
-        <v>109</v>
-      </c>
-      <c r="N181" t="s">
-        <v>124</v>
-      </c>
+      <c r="K181" s="17"/>
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
@@ -5060,13 +5074,16 @@
       </c>
       <c r="F182" s="5"/>
       <c r="J182" t="s">
-        <v>107</v>
-      </c>
-      <c r="K182" s="17">
-        <v>2.08</v>
+        <v>102</v>
+      </c>
+      <c r="K182">
+        <v>25</v>
       </c>
       <c r="L182" t="s">
-        <v>110</v>
+        <v>108</v>
+      </c>
+      <c r="M182" t="s">
+        <v>117</v>
       </c>
       <c r="N182" t="s">
         <v>124</v>
@@ -5077,19 +5094,17 @@
         <v>43</v>
       </c>
       <c r="D183" t="s">
-        <v>53</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="F183" s="5"/>
       <c r="J183" t="s">
-        <v>102</v>
-      </c>
-      <c r="K183" s="17">
-        <v>24.9</v>
+        <v>106</v>
+      </c>
+      <c r="K183">
+        <v>5.35</v>
       </c>
       <c r="L183" t="s">
-        <v>108</v>
-      </c>
-      <c r="M183" t="s">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="N183" t="s">
         <v>124</v>
@@ -5100,16 +5115,17 @@
         <v>43</v>
       </c>
       <c r="D184" t="s">
-        <v>53</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="F184" s="5"/>
       <c r="J184" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K184" s="17">
-        <v>5.35</v>
+        <v>2.08</v>
       </c>
       <c r="L184" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N184" t="s">
         <v>124</v>
@@ -5123,13 +5139,16 @@
         <v>53</v>
       </c>
       <c r="J185" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="K185" s="17">
-        <v>2.25</v>
+        <v>24.9</v>
       </c>
       <c r="L185" t="s">
-        <v>110</v>
+        <v>108</v>
+      </c>
+      <c r="M185" t="s">
+        <v>118</v>
       </c>
       <c r="N185" t="s">
         <v>124</v>
@@ -5140,19 +5159,16 @@
         <v>43</v>
       </c>
       <c r="D186" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J186" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K186" s="17">
-        <v>25</v>
+        <v>5.35</v>
       </c>
       <c r="L186" t="s">
-        <v>108</v>
-      </c>
-      <c r="M186" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="N186" t="s">
         <v>124</v>
@@ -5163,16 +5179,16 @@
         <v>43</v>
       </c>
       <c r="D187" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="J187" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K187" s="17">
-        <v>5.35</v>
+        <v>2.25</v>
       </c>
       <c r="L187" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N187" t="s">
         <v>124</v>
@@ -5186,13 +5202,16 @@
         <v>51</v>
       </c>
       <c r="J188" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="K188" s="17">
-        <v>2.04</v>
+        <v>25</v>
       </c>
       <c r="L188" t="s">
-        <v>110</v>
+        <v>108</v>
+      </c>
+      <c r="M188" t="s">
+        <v>119</v>
       </c>
       <c r="N188" t="s">
         <v>124</v>
@@ -5203,20 +5222,16 @@
         <v>43</v>
       </c>
       <c r="D189" t="s">
-        <v>52</v>
-      </c>
-      <c r="F189" s="5"/>
+        <v>51</v>
+      </c>
       <c r="J189" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K189" s="17">
-        <v>23.1</v>
+        <v>5.35</v>
       </c>
       <c r="L189" t="s">
-        <v>108</v>
-      </c>
-      <c r="M189" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="N189" t="s">
         <v>124</v>
@@ -5227,17 +5242,16 @@
         <v>43</v>
       </c>
       <c r="D190" t="s">
-        <v>52</v>
-      </c>
-      <c r="F190" s="5"/>
+        <v>51</v>
+      </c>
       <c r="J190" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K190" s="17">
-        <v>5.36</v>
+        <v>2.04</v>
       </c>
       <c r="L190" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N190" t="s">
         <v>124</v>
@@ -5252,13 +5266,16 @@
       </c>
       <c r="F191" s="5"/>
       <c r="J191" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="K191" s="17">
-        <v>2.64</v>
+        <v>23.1</v>
       </c>
       <c r="L191" t="s">
-        <v>110</v>
+        <v>108</v>
+      </c>
+      <c r="M191" t="s">
+        <v>120</v>
       </c>
       <c r="N191" t="s">
         <v>124</v>
@@ -5268,18 +5285,18 @@
       <c r="A192" t="s">
         <v>43</v>
       </c>
+      <c r="D192" t="s">
+        <v>52</v>
+      </c>
       <c r="F192" s="5"/>
       <c r="J192" t="s">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="K192" s="17">
-        <v>25</v>
+        <v>5.36</v>
       </c>
       <c r="L192" t="s">
-        <v>108</v>
-      </c>
-      <c r="M192" t="s">
-        <v>121</v>
+        <v>109</v>
       </c>
       <c r="N192" t="s">
         <v>124</v>
@@ -5289,15 +5306,18 @@
       <c r="A193" t="s">
         <v>43</v>
       </c>
+      <c r="D193" t="s">
+        <v>52</v>
+      </c>
       <c r="F193" s="5"/>
       <c r="J193" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K193" s="17">
-        <v>5.36</v>
+        <v>2.64</v>
       </c>
       <c r="L193" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N193" t="s">
         <v>124</v>
@@ -5309,50 +5329,65 @@
       </c>
       <c r="F194" s="5"/>
       <c r="J194" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="K194" s="17">
-        <v>2.2799999999999998</v>
+        <v>25</v>
       </c>
       <c r="L194" t="s">
-        <v>110</v>
+        <v>108</v>
+      </c>
+      <c r="M194" t="s">
+        <v>121</v>
       </c>
       <c r="N194" t="s">
         <v>124</v>
       </c>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A195" t="s">
+        <v>43</v>
+      </c>
       <c r="F195" s="5"/>
-      <c r="K195" s="17"/>
+      <c r="J195" t="s">
+        <v>106</v>
+      </c>
+      <c r="K195" s="17">
+        <v>5.36</v>
+      </c>
+      <c r="L195" t="s">
+        <v>109</v>
+      </c>
+      <c r="N195" t="s">
+        <v>124</v>
+      </c>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A196" t="s">
+        <v>43</v>
+      </c>
       <c r="F196" s="5"/>
-      <c r="J196" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="K196" s="20">
-        <v>0</v>
-      </c>
-      <c r="L196" s="6" t="s">
-        <v>122</v>
+      <c r="J196" t="s">
+        <v>107</v>
+      </c>
+      <c r="K196" s="17">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="L196" t="s">
+        <v>110</v>
+      </c>
+      <c r="N196" t="s">
+        <v>124</v>
       </c>
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F197" s="5"/>
-      <c r="J197" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="K197" s="20">
-        <v>0</v>
-      </c>
-      <c r="L197" s="6" t="s">
-        <v>122</v>
-      </c>
+      <c r="K197" s="17"/>
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F198" s="5"/>
       <c r="J198" s="6" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="K198" s="20">
         <v>0</v>
@@ -5362,44 +5397,27 @@
       </c>
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E199" t="s">
-        <v>146</v>
-      </c>
       <c r="F199" s="5"/>
-      <c r="J199" t="s">
-        <v>137</v>
-      </c>
-      <c r="K199" s="19">
-        <f>5.49/1.035</f>
-        <v>5.304347826086957</v>
-      </c>
-      <c r="L199" t="s">
-        <v>138</v>
-      </c>
-      <c r="M199" t="s">
-        <v>144</v>
-      </c>
-      <c r="N199" t="s">
-        <v>145</v>
+      <c r="J199" s="6" t="s">
+        <v>142</v>
+      </c>
+      <c r="K199" s="20">
+        <v>0</v>
+      </c>
+      <c r="L199" s="6" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E200" t="s">
-        <v>146</v>
-      </c>
       <c r="F200" s="5"/>
-      <c r="J200" t="s">
-        <v>142</v>
-      </c>
-      <c r="K200" s="19">
-        <f>0.97/1.035</f>
-        <v>0.9371980676328503</v>
-      </c>
-      <c r="L200" t="s">
-        <v>139</v>
-      </c>
-      <c r="N200" t="s">
-        <v>145</v>
+      <c r="J200" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="K200" s="20">
+        <v>0</v>
+      </c>
+      <c r="L200" s="6" t="s">
+        <v>122</v>
       </c>
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.25">
@@ -5408,67 +5426,84 @@
       </c>
       <c r="F201" s="5"/>
       <c r="J201" t="s">
+        <v>137</v>
+      </c>
+      <c r="K201" s="19">
+        <f>5.49/1.035</f>
+        <v>5.304347826086957</v>
+      </c>
+      <c r="L201" t="s">
+        <v>138</v>
+      </c>
+      <c r="M201" t="s">
+        <v>144</v>
+      </c>
+      <c r="N201" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="E202" t="s">
+        <v>146</v>
+      </c>
+      <c r="F202" s="5"/>
+      <c r="J202" t="s">
+        <v>142</v>
+      </c>
+      <c r="K202" s="19">
+        <f>0.97/1.035</f>
+        <v>0.9371980676328503</v>
+      </c>
+      <c r="L202" t="s">
+        <v>139</v>
+      </c>
+      <c r="N202" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="E203" t="s">
+        <v>146</v>
+      </c>
+      <c r="F203" s="5"/>
+      <c r="J203" t="s">
         <v>143</v>
       </c>
-      <c r="K201" s="19">
+      <c r="K203" s="19">
         <f>1.6/1.035</f>
         <v>1.5458937198067635</v>
       </c>
-      <c r="L201" t="s">
+      <c r="L203" t="s">
         <v>140</v>
       </c>
-      <c r="N201" t="s">
+      <c r="N203" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="202" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F202" s="5"/>
-    </row>
-    <row r="203" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A203" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="B203" s="15"/>
-      <c r="C203" s="15"/>
-      <c r="D203" s="15"/>
-      <c r="E203" s="15"/>
-      <c r="F203" s="16"/>
-      <c r="G203" s="15"/>
-      <c r="H203" s="15"/>
-      <c r="I203" s="15"/>
-      <c r="J203" s="15"/>
-      <c r="K203" s="15"/>
-      <c r="L203" s="15"/>
-      <c r="M203" s="15"/>
-      <c r="N203" s="15"/>
-    </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J204" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K204" s="1">
-        <v>0</v>
-      </c>
-      <c r="L204" s="1"/>
-      <c r="M204" s="1" t="s">
-        <v>62</v>
-      </c>
+      <c r="F204" s="5"/>
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J205" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="K205" s="1">
-        <v>0</v>
-      </c>
-      <c r="L205" s="1"/>
-      <c r="M205" s="1" t="s">
-        <v>62</v>
-      </c>
+      <c r="A205" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="B205" s="15"/>
+      <c r="C205" s="15"/>
+      <c r="D205" s="15"/>
+      <c r="E205" s="15"/>
+      <c r="F205" s="16"/>
+      <c r="G205" s="15"/>
+      <c r="H205" s="15"/>
+      <c r="I205" s="15"/>
+      <c r="J205" s="15"/>
+      <c r="K205" s="15"/>
+      <c r="L205" s="15"/>
+      <c r="M205" s="15"/>
+      <c r="N205" s="15"/>
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.25">
       <c r="J206" s="1" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="K206" s="1">
         <v>0</v>
@@ -5479,49 +5514,27 @@
       </c>
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A207" t="s">
-        <v>1</v>
-      </c>
-      <c r="F207" t="s">
-        <v>24</v>
-      </c>
-      <c r="H207" t="s">
-        <v>27</v>
-      </c>
-      <c r="J207" t="s">
-        <v>28</v>
-      </c>
-      <c r="K207">
-        <v>4</v>
-      </c>
-      <c r="L207" t="s">
-        <v>72</v>
-      </c>
-      <c r="N207" t="s">
-        <v>22</v>
+      <c r="J207" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="K207" s="1">
+        <v>0</v>
+      </c>
+      <c r="L207" s="1"/>
+      <c r="M207" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A208" t="s">
-        <v>1</v>
-      </c>
-      <c r="F208" t="s">
-        <v>25</v>
-      </c>
-      <c r="H208" t="s">
-        <v>27</v>
-      </c>
-      <c r="J208" t="s">
-        <v>28</v>
-      </c>
-      <c r="K208">
-        <v>4</v>
-      </c>
-      <c r="L208" t="s">
-        <v>72</v>
-      </c>
-      <c r="N208" t="s">
-        <v>22</v>
+      <c r="J208" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K208" s="1">
+        <v>0</v>
+      </c>
+      <c r="L208" s="1"/>
+      <c r="M208" s="1" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.25">
@@ -5529,7 +5542,7 @@
         <v>1</v>
       </c>
       <c r="F209" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H209" t="s">
         <v>27</v>
@@ -5538,7 +5551,7 @@
         <v>28</v>
       </c>
       <c r="K209">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="L209" t="s">
         <v>72</v>
@@ -5549,10 +5562,10 @@
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="F210" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H210" t="s">
         <v>27</v>
@@ -5561,7 +5574,7 @@
         <v>28</v>
       </c>
       <c r="K210">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="L210" t="s">
         <v>72</v>
@@ -5572,10 +5585,10 @@
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>43</v>
+        <v>1</v>
       </c>
       <c r="F211" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H211" t="s">
         <v>27</v>
@@ -5584,7 +5597,7 @@
         <v>28</v>
       </c>
       <c r="K211">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="L211" t="s">
         <v>72</v>
@@ -5598,7 +5611,7 @@
         <v>43</v>
       </c>
       <c r="F212" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H212" t="s">
         <v>27</v>
@@ -5607,7 +5620,7 @@
         <v>28</v>
       </c>
       <c r="K212">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="L212" t="s">
         <v>72</v>
@@ -5618,13 +5631,10 @@
     </row>
     <row r="213" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
-        <v>63</v>
-      </c>
-      <c r="C213" t="s">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="F213" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H213" t="s">
         <v>27</v>
@@ -5633,7 +5643,7 @@
         <v>28</v>
       </c>
       <c r="K213">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L213" t="s">
         <v>72</v>
@@ -5644,13 +5654,10 @@
     </row>
     <row r="214" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
-        <v>63</v>
-      </c>
-      <c r="C214" t="s">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="F214" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H214" t="s">
         <v>27</v>
@@ -5659,7 +5666,7 @@
         <v>28</v>
       </c>
       <c r="K214">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="L214" t="s">
         <v>72</v>
@@ -5676,7 +5683,7 @@
         <v>83</v>
       </c>
       <c r="F215" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H215" t="s">
         <v>27</v>
@@ -5685,7 +5692,7 @@
         <v>28</v>
       </c>
       <c r="K215">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="L215" t="s">
         <v>72</v>
@@ -5699,13 +5706,10 @@
         <v>63</v>
       </c>
       <c r="C216" t="s">
-        <v>64</v>
-      </c>
-      <c r="D216" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="F216" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H216" t="s">
         <v>27</v>
@@ -5728,10 +5732,10 @@
         <v>63</v>
       </c>
       <c r="C217" t="s">
-        <v>64</v>
+        <v>83</v>
       </c>
       <c r="F217" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H217" t="s">
         <v>27</v>
@@ -5740,13 +5744,10 @@
         <v>28</v>
       </c>
       <c r="K217">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="L217" t="s">
         <v>72</v>
-      </c>
-      <c r="M217" t="s">
-        <v>73</v>
       </c>
       <c r="N217" t="s">
         <v>22</v>
@@ -5759,8 +5760,11 @@
       <c r="C218" t="s">
         <v>64</v>
       </c>
+      <c r="D218" t="s">
+        <v>65</v>
+      </c>
       <c r="F218" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H218" t="s">
         <v>27</v>
@@ -5773,9 +5777,6 @@
       </c>
       <c r="L218" t="s">
         <v>72</v>
-      </c>
-      <c r="M218" t="s">
-        <v>73</v>
       </c>
       <c r="N218" t="s">
         <v>22</v>
@@ -5789,7 +5790,7 @@
         <v>64</v>
       </c>
       <c r="F219" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H219" t="s">
         <v>27</v>
@@ -5798,7 +5799,7 @@
         <v>28</v>
       </c>
       <c r="K219">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="L219" t="s">
         <v>72</v>
@@ -5811,61 +5812,61 @@
       </c>
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A220" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B220" s="1"/>
-      <c r="C220" s="1"/>
-      <c r="D220" s="1"/>
-      <c r="E220" s="1"/>
-      <c r="F220" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G220" s="1"/>
-      <c r="H220" s="1" t="s">
+      <c r="A220" t="s">
+        <v>63</v>
+      </c>
+      <c r="C220" t="s">
+        <v>64</v>
+      </c>
+      <c r="F220" t="s">
+        <v>25</v>
+      </c>
+      <c r="H220" t="s">
         <v>27</v>
       </c>
-      <c r="I220" s="1"/>
-      <c r="J220" s="1" t="s">
+      <c r="J220" t="s">
         <v>28</v>
       </c>
-      <c r="K220" s="1">
-        <v>4</v>
-      </c>
-      <c r="L220" s="1" t="s">
+      <c r="K220">
+        <v>10</v>
+      </c>
+      <c r="L220" t="s">
         <v>72</v>
       </c>
-      <c r="M220" s="1" t="s">
-        <v>69</v>
+      <c r="M220" t="s">
+        <v>73</v>
+      </c>
+      <c r="N220" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A221" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B221" s="1"/>
-      <c r="C221" s="1"/>
-      <c r="D221" s="1"/>
-      <c r="E221" s="1"/>
-      <c r="F221" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G221" s="1"/>
-      <c r="H221" s="1" t="s">
+      <c r="A221" t="s">
+        <v>63</v>
+      </c>
+      <c r="C221" t="s">
+        <v>64</v>
+      </c>
+      <c r="F221" t="s">
+        <v>26</v>
+      </c>
+      <c r="H221" t="s">
         <v>27</v>
       </c>
-      <c r="I221" s="1"/>
-      <c r="J221" s="1" t="s">
+      <c r="J221" t="s">
         <v>28</v>
       </c>
-      <c r="K221" s="1">
-        <v>4</v>
-      </c>
-      <c r="L221" s="1" t="s">
+      <c r="K221">
+        <v>35</v>
+      </c>
+      <c r="L221" t="s">
         <v>72</v>
       </c>
-      <c r="M221" s="1" t="s">
-        <v>69</v>
+      <c r="M221" t="s">
+        <v>73</v>
+      </c>
+      <c r="N221" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.25">
@@ -5877,7 +5878,7 @@
       <c r="D222" s="1"/>
       <c r="E222" s="1"/>
       <c r="F222" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G222" s="1"/>
       <c r="H222" s="1" t="s">
@@ -5888,7 +5889,7 @@
         <v>28</v>
       </c>
       <c r="K222" s="1">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="L222" s="1" t="s">
         <v>72</v>
@@ -5898,69 +5899,69 @@
       </c>
     </row>
     <row r="223" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A223" t="s">
-        <v>1</v>
-      </c>
-      <c r="F223" t="s">
-        <v>24</v>
-      </c>
-      <c r="H223" t="s">
+      <c r="A223" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B223" s="1"/>
+      <c r="C223" s="1"/>
+      <c r="D223" s="1"/>
+      <c r="E223" s="1"/>
+      <c r="F223" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G223" s="1"/>
+      <c r="H223" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J223" t="s">
-        <v>29</v>
-      </c>
-      <c r="K223">
-        <v>3</v>
-      </c>
-      <c r="L223" t="s">
+      <c r="I223" s="1"/>
+      <c r="J223" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K223" s="1">
+        <v>4</v>
+      </c>
+      <c r="L223" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="N223" t="s">
-        <v>22</v>
+      <c r="M223" s="1" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="224" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A224" t="s">
-        <v>1</v>
-      </c>
-      <c r="C224" t="s">
-        <v>2</v>
-      </c>
-      <c r="D224" t="s">
-        <v>3</v>
-      </c>
-      <c r="F224" t="s">
-        <v>25</v>
-      </c>
-      <c r="H224" t="s">
+      <c r="A224" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B224" s="1"/>
+      <c r="C224" s="1"/>
+      <c r="D224" s="1"/>
+      <c r="E224" s="1"/>
+      <c r="F224" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G224" s="1"/>
+      <c r="H224" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J224" t="s">
-        <v>29</v>
-      </c>
-      <c r="K224">
-        <v>18</v>
-      </c>
-      <c r="L224" t="s">
+      <c r="I224" s="1"/>
+      <c r="J224" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="K224" s="1">
+        <v>20</v>
+      </c>
+      <c r="L224" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="N224" t="s">
-        <v>22</v>
+      <c r="M224" s="1" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="225" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>1</v>
       </c>
-      <c r="C225" t="s">
-        <v>9</v>
-      </c>
-      <c r="D225" t="s">
-        <v>3</v>
-      </c>
       <c r="F225" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H225" t="s">
         <v>27</v>
@@ -5969,7 +5970,7 @@
         <v>29</v>
       </c>
       <c r="K225">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="L225" t="s">
         <v>72</v>
@@ -5982,8 +5983,11 @@
       <c r="A226" t="s">
         <v>1</v>
       </c>
+      <c r="C226" t="s">
+        <v>2</v>
+      </c>
       <c r="D226" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F226" t="s">
         <v>25</v>
@@ -6008,8 +6012,11 @@
       <c r="A227" t="s">
         <v>1</v>
       </c>
+      <c r="C227" t="s">
+        <v>9</v>
+      </c>
       <c r="D227" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F227" t="s">
         <v>25</v>
@@ -6021,7 +6028,7 @@
         <v>29</v>
       </c>
       <c r="K227">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L227" t="s">
         <v>72</v>
@@ -6035,7 +6042,7 @@
         <v>1</v>
       </c>
       <c r="D228" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F228" t="s">
         <v>25</v>
@@ -6047,7 +6054,7 @@
         <v>29</v>
       </c>
       <c r="K228">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L228" t="s">
         <v>72</v>
@@ -6061,7 +6068,7 @@
         <v>1</v>
       </c>
       <c r="D229" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F229" t="s">
         <v>25</v>
@@ -6073,7 +6080,7 @@
         <v>29</v>
       </c>
       <c r="K229">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L229" t="s">
         <v>72</v>
@@ -6087,7 +6094,7 @@
         <v>1</v>
       </c>
       <c r="D230" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F230" t="s">
         <v>25</v>
@@ -6104,9 +6111,6 @@
       <c r="L230" t="s">
         <v>72</v>
       </c>
-      <c r="M230" t="s">
-        <v>18</v>
-      </c>
       <c r="N230" t="s">
         <v>22</v>
       </c>
@@ -6115,8 +6119,11 @@
       <c r="A231" t="s">
         <v>1</v>
       </c>
+      <c r="D231" t="s">
+        <v>16</v>
+      </c>
       <c r="F231" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="H231" t="s">
         <v>27</v>
@@ -6125,7 +6132,7 @@
         <v>29</v>
       </c>
       <c r="K231">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="L231" t="s">
         <v>72</v>
@@ -6135,61 +6142,55 @@
       </c>
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A232" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B232" s="1"/>
-      <c r="C232" s="1"/>
-      <c r="D232" s="1"/>
-      <c r="E232" s="1"/>
-      <c r="F232" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G232" s="1"/>
-      <c r="H232" s="1" t="s">
+      <c r="A232" t="s">
+        <v>1</v>
+      </c>
+      <c r="D232" t="s">
+        <v>17</v>
+      </c>
+      <c r="F232" t="s">
+        <v>25</v>
+      </c>
+      <c r="H232" t="s">
         <v>27</v>
       </c>
-      <c r="I232" s="1"/>
-      <c r="J232" s="1" t="s">
+      <c r="J232" t="s">
         <v>29</v>
       </c>
-      <c r="K232" s="1">
-        <v>3</v>
-      </c>
-      <c r="L232" s="1" t="s">
+      <c r="K232">
+        <v>17</v>
+      </c>
+      <c r="L232" t="s">
         <v>72</v>
       </c>
-      <c r="M232" s="1" t="s">
-        <v>69</v>
+      <c r="M232" t="s">
+        <v>18</v>
+      </c>
+      <c r="N232" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A233" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B233" s="1"/>
-      <c r="C233" s="1"/>
-      <c r="D233" s="1"/>
-      <c r="E233" s="1"/>
-      <c r="F233" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="G233" s="1"/>
-      <c r="H233" s="1" t="s">
+      <c r="A233" t="s">
+        <v>1</v>
+      </c>
+      <c r="F233" t="s">
+        <v>26</v>
+      </c>
+      <c r="H233" t="s">
         <v>27</v>
       </c>
-      <c r="I233" s="1"/>
-      <c r="J233" s="1" t="s">
+      <c r="J233" t="s">
         <v>29</v>
       </c>
-      <c r="K233" s="1">
-        <v>17</v>
-      </c>
-      <c r="L233" s="1" t="s">
+      <c r="K233">
+        <v>30</v>
+      </c>
+      <c r="L233" t="s">
         <v>72</v>
       </c>
-      <c r="M233" s="1" t="s">
-        <v>70</v>
+      <c r="N233" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.25">
@@ -6201,7 +6202,7 @@
       <c r="D234" s="1"/>
       <c r="E234" s="1"/>
       <c r="F234" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G234" s="1"/>
       <c r="H234" s="1" t="s">
@@ -6212,7 +6213,7 @@
         <v>29</v>
       </c>
       <c r="K234" s="1">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="L234" s="1" t="s">
         <v>72</v>
@@ -6222,49 +6223,61 @@
       </c>
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A235" t="s">
-        <v>43</v>
-      </c>
-      <c r="F235" t="s">
-        <v>24</v>
-      </c>
-      <c r="H235" t="s">
+      <c r="A235" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B235" s="1"/>
+      <c r="C235" s="1"/>
+      <c r="D235" s="1"/>
+      <c r="E235" s="1"/>
+      <c r="F235" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G235" s="1"/>
+      <c r="H235" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J235" t="s">
+      <c r="I235" s="1"/>
+      <c r="J235" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K235">
-        <v>4</v>
-      </c>
-      <c r="L235" t="s">
+      <c r="K235" s="1">
+        <v>17</v>
+      </c>
+      <c r="L235" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="N235" t="s">
-        <v>22</v>
+      <c r="M235" s="1" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A236" t="s">
-        <v>43</v>
-      </c>
-      <c r="F236" t="s">
-        <v>25</v>
-      </c>
-      <c r="H236" t="s">
+      <c r="A236" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B236" s="1"/>
+      <c r="C236" s="1"/>
+      <c r="D236" s="1"/>
+      <c r="E236" s="1"/>
+      <c r="F236" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="G236" s="1"/>
+      <c r="H236" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="J236" t="s">
+      <c r="I236" s="1"/>
+      <c r="J236" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="K236">
-        <v>18</v>
-      </c>
-      <c r="L236" t="s">
+      <c r="K236" s="1">
+        <v>30</v>
+      </c>
+      <c r="L236" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="N236" t="s">
-        <v>22</v>
+      <c r="M236" s="1" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.25">
@@ -6272,7 +6285,7 @@
         <v>43</v>
       </c>
       <c r="F237" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H237" t="s">
         <v>27</v>
@@ -6281,7 +6294,7 @@
         <v>29</v>
       </c>
       <c r="K237">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="L237" t="s">
         <v>72</v>
@@ -6292,13 +6305,10 @@
     </row>
     <row r="238" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>63</v>
-      </c>
-      <c r="C238" t="s">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="F238" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H238" t="s">
         <v>27</v>
@@ -6307,7 +6317,7 @@
         <v>29</v>
       </c>
       <c r="K238">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="L238" t="s">
         <v>72</v>
@@ -6318,13 +6328,10 @@
     </row>
     <row r="239" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>63</v>
-      </c>
-      <c r="C239" t="s">
-        <v>83</v>
+        <v>43</v>
       </c>
       <c r="F239" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H239" t="s">
         <v>27</v>
@@ -6333,7 +6340,7 @@
         <v>29</v>
       </c>
       <c r="K239">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="L239" t="s">
         <v>72</v>
@@ -6350,7 +6357,7 @@
         <v>83</v>
       </c>
       <c r="F240" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H240" t="s">
         <v>27</v>
@@ -6359,7 +6366,7 @@
         <v>29</v>
       </c>
       <c r="K240">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="L240" t="s">
         <v>72</v>
@@ -6373,10 +6380,7 @@
         <v>63</v>
       </c>
       <c r="C241" t="s">
-        <v>64</v>
-      </c>
-      <c r="D241" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="F241" t="s">
         <v>25</v>
@@ -6388,7 +6392,7 @@
         <v>29</v>
       </c>
       <c r="K241">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="L241" t="s">
         <v>72</v>
@@ -6402,10 +6406,7 @@
         <v>63</v>
       </c>
       <c r="C242" t="s">
-        <v>64</v>
-      </c>
-      <c r="D242" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="F242" t="s">
         <v>26</v>
@@ -6417,7 +6418,7 @@
         <v>29</v>
       </c>
       <c r="K242">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L242" t="s">
         <v>72</v>
@@ -6433,8 +6434,11 @@
       <c r="C243" t="s">
         <v>64</v>
       </c>
+      <c r="D243" t="s">
+        <v>65</v>
+      </c>
       <c r="F243" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H243" t="s">
         <v>27</v>
@@ -6443,13 +6447,10 @@
         <v>29</v>
       </c>
       <c r="K243">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L243" t="s">
         <v>72</v>
-      </c>
-      <c r="M243" t="s">
-        <v>73</v>
       </c>
       <c r="N243" t="s">
         <v>22</v>
@@ -6462,8 +6463,11 @@
       <c r="C244" t="s">
         <v>64</v>
       </c>
+      <c r="D244" t="s">
+        <v>65</v>
+      </c>
       <c r="F244" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H244" t="s">
         <v>27</v>
@@ -6472,13 +6476,10 @@
         <v>29</v>
       </c>
       <c r="K244">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="L244" t="s">
         <v>72</v>
-      </c>
-      <c r="M244" t="s">
-        <v>73</v>
       </c>
       <c r="N244" t="s">
         <v>22</v>
@@ -6492,7 +6493,7 @@
         <v>64</v>
       </c>
       <c r="F245" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H245" t="s">
         <v>27</v>
@@ -6501,7 +6502,7 @@
         <v>29</v>
       </c>
       <c r="K245">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="L245" t="s">
         <v>72</v>
@@ -6514,40 +6515,58 @@
       </c>
     </row>
     <row r="246" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A246" t="s">
+        <v>63</v>
+      </c>
+      <c r="C246" t="s">
+        <v>64</v>
+      </c>
       <c r="F246" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H246" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J246" t="s">
         <v>29</v>
       </c>
       <c r="K246">
-        <v>0.01</v>
+        <v>12</v>
       </c>
       <c r="L246" t="s">
-        <v>74</v>
+        <v>72</v>
+      </c>
+      <c r="M246" t="s">
+        <v>73</v>
       </c>
       <c r="N246" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="247" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A247" t="s">
+        <v>63</v>
+      </c>
+      <c r="C247" t="s">
+        <v>64</v>
+      </c>
       <c r="F247" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H247" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="J247" t="s">
         <v>29</v>
       </c>
       <c r="K247">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L247" t="s">
-        <v>74</v>
+        <v>72</v>
+      </c>
+      <c r="M247" t="s">
+        <v>73</v>
       </c>
       <c r="N247" t="s">
         <v>22</v>
@@ -6555,7 +6574,7 @@
     </row>
     <row r="248" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F248" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H248" t="s">
         <v>30</v>
@@ -6564,7 +6583,7 @@
         <v>29</v>
       </c>
       <c r="K248">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="L248" t="s">
         <v>74</v>
@@ -6575,19 +6594,19 @@
     </row>
     <row r="249" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F249" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H249" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J249" t="s">
         <v>29</v>
       </c>
       <c r="K249">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L249" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N249" t="s">
         <v>22</v>
@@ -6595,19 +6614,19 @@
     </row>
     <row r="250" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F250" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H250" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J250" t="s">
         <v>29</v>
       </c>
       <c r="K250">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="L250" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N250" t="s">
         <v>22</v>
@@ -6615,7 +6634,7 @@
     </row>
     <row r="251" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F251" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H251" t="s">
         <v>31</v>
@@ -6624,7 +6643,7 @@
         <v>29</v>
       </c>
       <c r="K251">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L251" t="s">
         <v>72</v>
@@ -6635,19 +6654,19 @@
     </row>
     <row r="252" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F252" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H252" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J252" t="s">
         <v>29</v>
       </c>
       <c r="K252">
-        <v>0.3</v>
+        <v>0.5</v>
       </c>
       <c r="L252" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="N252" t="s">
         <v>22</v>
@@ -6655,19 +6674,19 @@
     </row>
     <row r="253" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F253" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H253" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J253" t="s">
         <v>29</v>
       </c>
       <c r="K253">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="L253" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="N253" t="s">
         <v>22</v>
@@ -6675,7 +6694,7 @@
     </row>
     <row r="254" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F254" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="H254" t="s">
         <v>32</v>
@@ -6684,7 +6703,7 @@
         <v>29</v>
       </c>
       <c r="K254">
-        <v>30</v>
+        <v>0.3</v>
       </c>
       <c r="L254" t="s">
         <v>74</v>
@@ -6694,69 +6713,57 @@
       </c>
     </row>
     <row r="255" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A255" t="s">
-        <v>1</v>
-      </c>
       <c r="F255" t="s">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="H255" t="s">
+        <v>32</v>
       </c>
       <c r="J255" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="K255">
-        <v>60</v>
+        <v>30</v>
       </c>
       <c r="L255" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N255" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
     </row>
     <row r="256" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A256" t="s">
-        <v>1</v>
-      </c>
-      <c r="C256" t="s">
-        <v>2</v>
-      </c>
-      <c r="D256" t="s">
-        <v>3</v>
-      </c>
       <c r="F256" t="s">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="H256" t="s">
+        <v>32</v>
       </c>
       <c r="J256" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="K256">
-        <v>51</v>
+        <v>30</v>
       </c>
       <c r="L256" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="N256" t="s">
-        <v>71</v>
+        <v>22</v>
       </c>
     </row>
     <row r="257" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>1</v>
       </c>
-      <c r="C257" t="s">
-        <v>9</v>
-      </c>
-      <c r="D257" t="s">
-        <v>3</v>
-      </c>
       <c r="F257" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J257" t="s">
         <v>33</v>
       </c>
       <c r="K257">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="L257" t="s">
         <v>72</v>
@@ -6769,8 +6776,11 @@
       <c r="A258" t="s">
         <v>1</v>
       </c>
+      <c r="C258" t="s">
+        <v>2</v>
+      </c>
       <c r="D258" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="F258" t="s">
         <v>25</v>
@@ -6792,8 +6802,11 @@
       <c r="A259" t="s">
         <v>1</v>
       </c>
+      <c r="C259" t="s">
+        <v>9</v>
+      </c>
       <c r="D259" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F259" t="s">
         <v>25</v>
@@ -6802,7 +6815,7 @@
         <v>33</v>
       </c>
       <c r="K259">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="L259" t="s">
         <v>72</v>
@@ -6816,7 +6829,7 @@
         <v>1</v>
       </c>
       <c r="D260" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F260" t="s">
         <v>25</v>
@@ -6825,7 +6838,7 @@
         <v>33</v>
       </c>
       <c r="K260">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L260" t="s">
         <v>72</v>
@@ -6839,7 +6852,7 @@
         <v>1</v>
       </c>
       <c r="D261" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F261" t="s">
         <v>25</v>
@@ -6848,7 +6861,7 @@
         <v>33</v>
       </c>
       <c r="K261">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L261" t="s">
         <v>72</v>
@@ -6862,7 +6875,7 @@
         <v>1</v>
       </c>
       <c r="D262" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F262" t="s">
         <v>25</v>
@@ -6876,22 +6889,25 @@
       <c r="L262" t="s">
         <v>72</v>
       </c>
-      <c r="M262" t="s">
-        <v>18</v>
+      <c r="N262" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="263" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>1</v>
       </c>
+      <c r="D263" t="s">
+        <v>16</v>
+      </c>
       <c r="F263" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J263" t="s">
         <v>33</v>
       </c>
       <c r="K263">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="L263" t="s">
         <v>72</v>
@@ -6901,67 +6917,54 @@
       </c>
     </row>
     <row r="264" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A264" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="F264" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="G264" s="5"/>
-      <c r="H264" s="5"/>
-      <c r="I264" s="5"/>
-      <c r="J264" s="5" t="s">
+      <c r="A264" t="s">
+        <v>1</v>
+      </c>
+      <c r="D264" t="s">
+        <v>17</v>
+      </c>
+      <c r="F264" t="s">
+        <v>25</v>
+      </c>
+      <c r="J264" t="s">
         <v>33</v>
       </c>
-      <c r="K264" s="5">
-        <v>60</v>
-      </c>
-      <c r="L264" s="5" t="s">
+      <c r="K264">
+        <v>52</v>
+      </c>
+      <c r="L264" t="s">
         <v>72</v>
       </c>
-      <c r="M264" s="1"/>
-      <c r="N264" t="s">
-        <v>75</v>
+      <c r="M264" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="265" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A265" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B265" s="5"/>
-      <c r="C265" s="5"/>
-      <c r="D265" s="5"/>
-      <c r="E265" s="5"/>
-      <c r="F265" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G265" s="5"/>
-      <c r="H265" s="5"/>
-      <c r="I265" s="5"/>
-      <c r="J265" s="5" t="s">
+      <c r="A265" t="s">
+        <v>1</v>
+      </c>
+      <c r="F265" t="s">
+        <v>26</v>
+      </c>
+      <c r="J265" t="s">
         <v>33</v>
       </c>
-      <c r="K265" s="5">
-        <v>24</v>
+      <c r="K265">
+        <v>10</v>
       </c>
       <c r="L265" t="s">
         <v>72</v>
       </c>
-      <c r="M265" s="1"/>
       <c r="N265" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="266" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A266" s="5" t="s">
-        <v>68</v>
-      </c>
-      <c r="B266" s="5"/>
-      <c r="C266" s="5"/>
-      <c r="D266" s="5"/>
-      <c r="E266" s="5"/>
+      <c r="A266" s="1" t="s">
+        <v>1</v>
+      </c>
       <c r="F266" s="5" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G266" s="5"/>
       <c r="H266" s="5"/>
@@ -6970,14 +6973,14 @@
         <v>33</v>
       </c>
       <c r="K266" s="5">
-        <v>25</v>
-      </c>
-      <c r="L266" t="s">
+        <v>60</v>
+      </c>
+      <c r="L266" s="5" t="s">
         <v>72</v>
       </c>
       <c r="M266" s="1"/>
       <c r="N266" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
     </row>
     <row r="267" spans="1:14" x14ac:dyDescent="0.25">
@@ -6989,7 +6992,7 @@
       <c r="D267" s="5"/>
       <c r="E267" s="5"/>
       <c r="F267" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G267" s="5"/>
       <c r="H267" s="5"/>
@@ -6998,7 +7001,7 @@
         <v>33</v>
       </c>
       <c r="K267" s="5">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="L267" t="s">
         <v>72</v>
@@ -7017,7 +7020,7 @@
       <c r="D268" s="5"/>
       <c r="E268" s="5"/>
       <c r="F268" s="5" t="s">
-        <v>19</v>
+        <v>25</v>
       </c>
       <c r="G268" s="5"/>
       <c r="H268" s="5"/>
@@ -7026,28 +7029,26 @@
         <v>33</v>
       </c>
       <c r="K268" s="5">
-        <v>60</v>
-      </c>
-      <c r="L268" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L268" t="s">
         <v>72</v>
       </c>
       <c r="M268" s="1"/>
       <c r="N268" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="269" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A269" s="5" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B269" s="5"/>
-      <c r="C269" s="5" t="s">
-        <v>83</v>
-      </c>
+      <c r="C269" s="5"/>
       <c r="D269" s="5"/>
       <c r="E269" s="5"/>
       <c r="F269" s="5" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="G269" s="5"/>
       <c r="H269" s="5"/>
@@ -7056,25 +7057,26 @@
         <v>33</v>
       </c>
       <c r="K269" s="5">
-        <v>75</v>
-      </c>
-      <c r="L269" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="L269" t="s">
         <v>72</v>
       </c>
       <c r="M269" s="1"/>
+      <c r="N269" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="270" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A270" s="5" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B270" s="5"/>
-      <c r="C270" s="5" t="s">
-        <v>83</v>
-      </c>
+      <c r="C270" s="5"/>
       <c r="D270" s="5"/>
       <c r="E270" s="5"/>
       <c r="F270" s="5" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="G270" s="5"/>
       <c r="H270" s="5"/>
@@ -7089,6 +7091,9 @@
         <v>72</v>
       </c>
       <c r="M270" s="1"/>
+      <c r="N270" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="271" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A271" s="5" t="s">
@@ -7101,7 +7106,7 @@
       <c r="D271" s="5"/>
       <c r="E271" s="5"/>
       <c r="F271" s="5" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G271" s="5"/>
       <c r="H271" s="5"/>
@@ -7110,7 +7115,7 @@
         <v>33</v>
       </c>
       <c r="K271" s="5">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="L271" s="5" t="s">
         <v>72</v>
@@ -7118,27 +7123,31 @@
       <c r="M271" s="1"/>
     </row>
     <row r="272" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A272" t="s">
+      <c r="A272" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="C272" t="s">
-        <v>64</v>
-      </c>
-      <c r="D272" t="s">
-        <v>65</v>
-      </c>
+      <c r="B272" s="5"/>
+      <c r="C272" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="D272" s="5"/>
+      <c r="E272" s="5"/>
+      <c r="F272" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G272" s="5"/>
+      <c r="H272" s="5"/>
+      <c r="I272" s="5"/>
       <c r="J272" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="K272">
-        <v>40</v>
+      <c r="K272" s="5">
+        <v>60</v>
       </c>
       <c r="L272" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="N272" t="s">
-        <v>71</v>
-      </c>
+      <c r="M272" s="1"/>
     </row>
     <row r="273" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A273" s="5" t="s">
@@ -7146,46 +7155,48 @@
       </c>
       <c r="B273" s="5"/>
       <c r="C273" s="5" t="s">
-        <v>64</v>
-      </c>
+        <v>83</v>
+      </c>
+      <c r="D273" s="5"/>
+      <c r="E273" s="5"/>
       <c r="F273" s="5" t="s">
-        <v>24</v>
-      </c>
+        <v>26</v>
+      </c>
+      <c r="G273" s="5"/>
+      <c r="H273" s="5"/>
+      <c r="I273" s="5"/>
       <c r="J273" s="5" t="s">
         <v>33</v>
       </c>
       <c r="K273" s="5">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c r="L273" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="M273" t="s">
-        <v>73</v>
-      </c>
+      <c r="M273" s="1"/>
     </row>
     <row r="274" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A274" s="5" t="s">
+      <c r="A274" t="s">
         <v>63</v>
       </c>
-      <c r="B274" s="5"/>
-      <c r="C274" s="5" t="s">
+      <c r="C274" t="s">
         <v>64</v>
       </c>
-      <c r="F274" s="5" t="s">
-        <v>25</v>
+      <c r="D274" t="s">
+        <v>65</v>
       </c>
       <c r="J274" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="K274" s="5">
-        <v>60</v>
+      <c r="K274">
+        <v>40</v>
       </c>
       <c r="L274" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="M274" t="s">
-        <v>73</v>
+      <c r="N274" t="s">
+        <v>71</v>
       </c>
     </row>
     <row r="275" spans="1:14" x14ac:dyDescent="0.25">
@@ -7196,19 +7207,14 @@
       <c r="C275" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="D275" s="1"/>
-      <c r="E275" s="1"/>
       <c r="F275" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="G275" s="1"/>
-      <c r="H275" s="1"/>
-      <c r="I275" s="1"/>
+        <v>24</v>
+      </c>
       <c r="J275" s="5" t="s">
         <v>33</v>
       </c>
       <c r="K275" s="5">
-        <v>40</v>
+        <v>75</v>
       </c>
       <c r="L275" s="5" t="s">
         <v>72</v>
@@ -7218,43 +7224,56 @@
       </c>
     </row>
     <row r="276" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A276" t="s">
-        <v>43</v>
-      </c>
-      <c r="F276" t="s">
-        <v>24</v>
-      </c>
-      <c r="J276" t="s">
+      <c r="A276" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B276" s="5"/>
+      <c r="C276" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="F276" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="J276" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="K276">
-        <v>70</v>
-      </c>
-      <c r="L276" t="s">
+      <c r="K276" s="5">
+        <v>60</v>
+      </c>
+      <c r="L276" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="N276" t="s">
-        <v>71</v>
+      <c r="M276" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="277" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A277" t="s">
-        <v>43</v>
-      </c>
-      <c r="F277" t="s">
-        <v>25</v>
-      </c>
-      <c r="J277" t="s">
+      <c r="A277" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="B277" s="5"/>
+      <c r="C277" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D277" s="1"/>
+      <c r="E277" s="1"/>
+      <c r="F277" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G277" s="1"/>
+      <c r="H277" s="1"/>
+      <c r="I277" s="1"/>
+      <c r="J277" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="K277">
-        <v>51</v>
-      </c>
-      <c r="L277" t="s">
+      <c r="K277" s="5">
+        <v>40</v>
+      </c>
+      <c r="L277" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="N277" t="s">
-        <v>71</v>
+      <c r="M277" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="278" spans="1:14" x14ac:dyDescent="0.25">
@@ -7262,13 +7281,13 @@
         <v>43</v>
       </c>
       <c r="F278" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="J278" t="s">
         <v>33</v>
       </c>
       <c r="K278">
-        <v>10</v>
+        <v>70</v>
       </c>
       <c r="L278" t="s">
         <v>72</v>
@@ -7277,107 +7296,87 @@
         <v>71</v>
       </c>
     </row>
-    <row r="281" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A281" s="11" t="s">
+    <row r="279" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A279" t="s">
+        <v>43</v>
+      </c>
+      <c r="F279" t="s">
+        <v>25</v>
+      </c>
+      <c r="J279" t="s">
+        <v>33</v>
+      </c>
+      <c r="K279">
+        <v>51</v>
+      </c>
+      <c r="L279" t="s">
+        <v>72</v>
+      </c>
+      <c r="N279" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="280" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>43</v>
+      </c>
+      <c r="F280" t="s">
+        <v>26</v>
+      </c>
+      <c r="J280" t="s">
+        <v>33</v>
+      </c>
+      <c r="K280">
+        <v>10</v>
+      </c>
+      <c r="L280" t="s">
+        <v>72</v>
+      </c>
+      <c r="N280" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="283" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A283" s="11" t="s">
         <v>96</v>
       </c>
-      <c r="B281" s="8"/>
-      <c r="C281" s="8"/>
-      <c r="D281" s="8"/>
-      <c r="E281" s="8"/>
-      <c r="F281" s="8"/>
-      <c r="G281" s="8"/>
-      <c r="H281" s="8"/>
-      <c r="I281" s="8"/>
-      <c r="J281" s="8"/>
-      <c r="K281" s="8"/>
-      <c r="L281" s="8"/>
-      <c r="M281" s="8"/>
-      <c r="N281" s="8"/>
-    </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A282" s="8"/>
-      <c r="B282" s="8"/>
-      <c r="C282" s="8"/>
-      <c r="D282" s="8"/>
-      <c r="E282" s="8"/>
-      <c r="F282" s="8"/>
-      <c r="G282" s="8"/>
-      <c r="H282" s="8"/>
-      <c r="I282" s="8"/>
-      <c r="J282" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="K282" s="9">
-        <v>0</v>
-      </c>
-      <c r="L282" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="M282" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="N282" s="8"/>
-    </row>
-    <row r="283" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A283" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B283" s="9"/>
-      <c r="C283" s="9" t="s">
-        <v>2</v>
-      </c>
-      <c r="D283" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E283" s="9"/>
-      <c r="F283" s="9"/>
-      <c r="G283" s="9"/>
-      <c r="H283" s="9"/>
-      <c r="I283" s="9"/>
-      <c r="J283" s="9" t="s">
-        <v>4</v>
-      </c>
-      <c r="K283" s="9">
-        <v>5.39</v>
-      </c>
-      <c r="L283" s="9" t="s">
-        <v>5</v>
-      </c>
-      <c r="M283" s="9"/>
-      <c r="N283" s="9" t="s">
-        <v>6</v>
-      </c>
+      <c r="B283" s="8"/>
+      <c r="C283" s="8"/>
+      <c r="D283" s="8"/>
+      <c r="E283" s="8"/>
+      <c r="F283" s="8"/>
+      <c r="G283" s="8"/>
+      <c r="H283" s="8"/>
+      <c r="I283" s="8"/>
+      <c r="J283" s="8"/>
+      <c r="K283" s="8"/>
+      <c r="L283" s="8"/>
+      <c r="M283" s="8"/>
+      <c r="N283" s="8"/>
     </row>
     <row r="284" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A284" s="9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B284" s="9"/>
-      <c r="C284" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="D284" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="E284" s="9"/>
-      <c r="F284" s="9"/>
-      <c r="G284" s="9"/>
-      <c r="H284" s="9"/>
-      <c r="I284" s="9"/>
+      <c r="A284" s="8"/>
+      <c r="B284" s="8"/>
+      <c r="C284" s="8"/>
+      <c r="D284" s="8"/>
+      <c r="E284" s="8"/>
+      <c r="F284" s="8"/>
+      <c r="G284" s="8"/>
+      <c r="H284" s="8"/>
+      <c r="I284" s="8"/>
       <c r="J284" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="K284" s="10">
-        <v>2.2999999999999998</v>
+      <c r="K284" s="9">
+        <v>0</v>
       </c>
       <c r="L284" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="M284" s="9"/>
-      <c r="N284" s="9" t="s">
-        <v>10</v>
-      </c>
+      <c r="M284" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="N284" s="8"/>
     </row>
     <row r="285" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A285" s="9" t="s">
@@ -7385,30 +7384,28 @@
       </c>
       <c r="B285" s="9"/>
       <c r="C285" s="9" t="s">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D285" s="9" t="s">
         <v>3</v>
       </c>
       <c r="E285" s="9"/>
-      <c r="F285" s="9" t="s">
-        <v>19</v>
-      </c>
+      <c r="F285" s="9"/>
       <c r="G285" s="9"/>
       <c r="H285" s="9"/>
       <c r="I285" s="9"/>
       <c r="J285" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="K285" s="10">
-        <v>3.17</v>
+      <c r="K285" s="9">
+        <v>5.39</v>
       </c>
       <c r="L285" s="9" t="s">
         <v>5</v>
       </c>
       <c r="M285" s="9"/>
       <c r="N285" s="9" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
     <row r="286" spans="1:14" x14ac:dyDescent="0.25">
@@ -7416,9 +7413,11 @@
         <v>1</v>
       </c>
       <c r="B286" s="9"/>
-      <c r="C286" s="9"/>
+      <c r="C286" s="9" t="s">
+        <v>9</v>
+      </c>
       <c r="D286" s="9" t="s">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="E286" s="9"/>
       <c r="F286" s="9"/>
@@ -7428,8 +7427,8 @@
       <c r="J286" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="K286" s="9">
-        <v>2.2599999999999998</v>
+      <c r="K286" s="10">
+        <v>2.2999999999999998</v>
       </c>
       <c r="L286" s="9" t="s">
         <v>5</v>
@@ -7444,27 +7443,29 @@
         <v>1</v>
       </c>
       <c r="B287" s="9"/>
-      <c r="C287" s="9"/>
+      <c r="C287" s="9" t="s">
+        <v>9</v>
+      </c>
       <c r="D287" s="9" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="E287" s="9"/>
-      <c r="F287" s="9"/>
+      <c r="F287" s="9" t="s">
+        <v>19</v>
+      </c>
       <c r="G287" s="9"/>
       <c r="H287" s="9"/>
       <c r="I287" s="9"/>
       <c r="J287" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="K287" s="9">
-        <v>0.79</v>
+      <c r="K287" s="10">
+        <v>3.17</v>
       </c>
       <c r="L287" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="M287" s="9" t="s">
-        <v>14</v>
-      </c>
+      <c r="M287" s="9"/>
       <c r="N287" s="9" t="s">
         <v>10</v>
       </c>
@@ -7476,7 +7477,7 @@
       <c r="B288" s="9"/>
       <c r="C288" s="9"/>
       <c r="D288" s="9" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E288" s="9"/>
       <c r="F288" s="9"/>
@@ -7504,7 +7505,7 @@
       <c r="B289" s="9"/>
       <c r="C289" s="9"/>
       <c r="D289" s="9" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E289" s="9"/>
       <c r="F289" s="9"/>
@@ -7515,12 +7516,14 @@
         <v>4</v>
       </c>
       <c r="K289" s="9">
-        <v>2.2599999999999998</v>
+        <v>0.79</v>
       </c>
       <c r="L289" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="M289" s="9"/>
+      <c r="M289" s="9" t="s">
+        <v>14</v>
+      </c>
       <c r="N289" s="9" t="s">
         <v>10</v>
       </c>
@@ -7532,7 +7535,7 @@
       <c r="B290" s="9"/>
       <c r="C290" s="9"/>
       <c r="D290" s="9" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E290" s="9"/>
       <c r="F290" s="9"/>
@@ -7548,20 +7551,20 @@
       <c r="L290" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="M290" s="9" t="s">
-        <v>18</v>
-      </c>
+      <c r="M290" s="9"/>
       <c r="N290" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="291" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A291" s="9" t="s">
-        <v>82</v>
+        <v>1</v>
       </c>
       <c r="B291" s="9"/>
       <c r="C291" s="9"/>
-      <c r="D291" s="9"/>
+      <c r="D291" s="9" t="s">
+        <v>15</v>
+      </c>
       <c r="E291" s="9"/>
       <c r="F291" s="9"/>
       <c r="G291" s="9"/>
@@ -7571,23 +7574,25 @@
         <v>4</v>
       </c>
       <c r="K291" s="9">
-        <v>0.4</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="L291" s="9" t="s">
         <v>5</v>
       </c>
       <c r="M291" s="9"/>
       <c r="N291" s="9" t="s">
-        <v>95</v>
+        <v>10</v>
       </c>
     </row>
     <row r="292" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A292" s="9" t="s">
-        <v>68</v>
+        <v>1</v>
       </c>
       <c r="B292" s="9"/>
       <c r="C292" s="9"/>
-      <c r="D292" s="9"/>
+      <c r="D292" s="9" t="s">
+        <v>17</v>
+      </c>
       <c r="E292" s="9"/>
       <c r="F292" s="9"/>
       <c r="G292" s="9"/>
@@ -7597,25 +7602,25 @@
         <v>4</v>
       </c>
       <c r="K292" s="9">
-        <v>2.13</v>
+        <v>2.2599999999999998</v>
       </c>
       <c r="L292" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="M292" s="9"/>
+      <c r="M292" s="9" t="s">
+        <v>18</v>
+      </c>
       <c r="N292" s="9" t="s">
-        <v>95</v>
+        <v>10</v>
       </c>
     </row>
     <row r="293" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A293" s="9" t="s">
-        <v>43</v>
+        <v>82</v>
       </c>
       <c r="B293" s="9"/>
       <c r="C293" s="9"/>
-      <c r="D293" s="9" t="s">
-        <v>50</v>
-      </c>
+      <c r="D293" s="9"/>
       <c r="E293" s="9"/>
       <c r="F293" s="9"/>
       <c r="G293" s="9"/>
@@ -7625,25 +7630,23 @@
         <v>4</v>
       </c>
       <c r="K293" s="9">
-        <v>0.69</v>
+        <v>0.4</v>
       </c>
       <c r="L293" s="9" t="s">
         <v>5</v>
       </c>
       <c r="M293" s="9"/>
       <c r="N293" s="9" t="s">
-        <v>10</v>
+        <v>95</v>
       </c>
     </row>
     <row r="294" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A294" s="9" t="s">
-        <v>43</v>
+        <v>68</v>
       </c>
       <c r="B294" s="9"/>
       <c r="C294" s="9"/>
-      <c r="D294" s="9" t="s">
-        <v>51</v>
-      </c>
+      <c r="D294" s="9"/>
       <c r="E294" s="9"/>
       <c r="F294" s="9"/>
       <c r="G294" s="9"/>
@@ -7653,14 +7656,14 @@
         <v>4</v>
       </c>
       <c r="K294" s="9">
-        <v>0.45</v>
+        <v>2.13</v>
       </c>
       <c r="L294" s="9" t="s">
         <v>5</v>
       </c>
       <c r="M294" s="9"/>
       <c r="N294" s="9" t="s">
-        <v>10</v>
+        <v>95</v>
       </c>
     </row>
     <row r="295" spans="1:14" x14ac:dyDescent="0.25">
@@ -7670,7 +7673,7 @@
       <c r="B295" s="9"/>
       <c r="C295" s="9"/>
       <c r="D295" s="9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E295" s="9"/>
       <c r="F295" s="9"/>
@@ -7681,7 +7684,7 @@
         <v>4</v>
       </c>
       <c r="K295" s="9">
-        <v>4.3999999999999997E-2</v>
+        <v>0.69</v>
       </c>
       <c r="L295" s="9" t="s">
         <v>5</v>
@@ -7698,7 +7701,7 @@
       <c r="B296" s="9"/>
       <c r="C296" s="9"/>
       <c r="D296" s="9" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="E296" s="9"/>
       <c r="F296" s="9"/>
@@ -7709,14 +7712,12 @@
         <v>4</v>
       </c>
       <c r="K296" s="9">
-        <v>0.69</v>
+        <v>0.45</v>
       </c>
       <c r="L296" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="M296" s="9" t="s">
-        <v>76</v>
-      </c>
+      <c r="M296" s="9"/>
       <c r="N296" s="9" t="s">
         <v>10</v>
       </c>
@@ -7728,7 +7729,7 @@
       <c r="B297" s="9"/>
       <c r="C297" s="9"/>
       <c r="D297" s="9" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E297" s="9"/>
       <c r="F297" s="9"/>
@@ -7739,7 +7740,7 @@
         <v>4</v>
       </c>
       <c r="K297" s="9">
-        <v>0.37</v>
+        <v>4.3999999999999997E-2</v>
       </c>
       <c r="L297" s="9" t="s">
         <v>5</v>
@@ -7756,7 +7757,7 @@
       <c r="B298" s="9"/>
       <c r="C298" s="9"/>
       <c r="D298" s="9" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="E298" s="9"/>
       <c r="F298" s="9"/>
@@ -7767,24 +7768,26 @@
         <v>4</v>
       </c>
       <c r="K298" s="9">
-        <v>0.37</v>
+        <v>0.69</v>
       </c>
       <c r="L298" s="9" t="s">
         <v>5</v>
       </c>
-      <c r="M298" s="9"/>
+      <c r="M298" s="9" t="s">
+        <v>76</v>
+      </c>
       <c r="N298" s="9" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="299" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A299" s="9" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="B299" s="9"/>
       <c r="C299" s="9"/>
       <c r="D299" s="9" t="s">
-        <v>64</v>
+        <v>44</v>
       </c>
       <c r="E299" s="9"/>
       <c r="F299" s="9"/>
@@ -7795,24 +7798,24 @@
         <v>4</v>
       </c>
       <c r="K299" s="9">
-        <v>0.01</v>
+        <v>0.37</v>
       </c>
       <c r="L299" s="9" t="s">
         <v>5</v>
       </c>
       <c r="M299" s="9"/>
       <c r="N299" s="9" t="s">
-        <v>95</v>
+        <v>10</v>
       </c>
     </row>
     <row r="300" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A300" s="9" t="s">
-        <v>63</v>
+        <v>43</v>
       </c>
       <c r="B300" s="9"/>
       <c r="C300" s="9"/>
       <c r="D300" s="9" t="s">
-        <v>83</v>
+        <v>45</v>
       </c>
       <c r="E300" s="9"/>
       <c r="F300" s="9"/>
@@ -7823,86 +7826,90 @@
         <v>4</v>
       </c>
       <c r="K300" s="9">
-        <v>0.02</v>
+        <v>0.37</v>
       </c>
       <c r="L300" s="9" t="s">
         <v>5</v>
       </c>
       <c r="M300" s="9"/>
       <c r="N300" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="301" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A301" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B301" s="9"/>
+      <c r="C301" s="9"/>
+      <c r="D301" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="E301" s="9"/>
+      <c r="F301" s="9"/>
+      <c r="G301" s="9"/>
+      <c r="H301" s="9"/>
+      <c r="I301" s="9"/>
+      <c r="J301" s="9" t="s">
+        <v>4</v>
+      </c>
+      <c r="K301" s="9">
+        <v>0.01</v>
+      </c>
+      <c r="L301" s="9" t="s">
+        <v>5</v>
+      </c>
+      <c r="M301" s="9"/>
+      <c r="N301" s="9" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="301" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A301" s="8"/>
-      <c r="B301" s="8"/>
-      <c r="C301" s="8"/>
-      <c r="D301" s="8"/>
-      <c r="E301" s="8"/>
-      <c r="F301" s="8"/>
-      <c r="G301" s="8"/>
-      <c r="H301" s="8"/>
-      <c r="I301" s="8"/>
-      <c r="J301" s="8"/>
-      <c r="K301" s="8"/>
-      <c r="L301" s="8"/>
-      <c r="M301" s="8"/>
-      <c r="N301" s="8"/>
-    </row>
     <row r="302" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A302" s="9"/>
+      <c r="A302" s="9" t="s">
+        <v>63</v>
+      </c>
       <c r="B302" s="9"/>
       <c r="C302" s="9"/>
-      <c r="D302" s="9"/>
+      <c r="D302" s="9" t="s">
+        <v>83</v>
+      </c>
       <c r="E302" s="9"/>
       <c r="F302" s="9"/>
       <c r="G302" s="9"/>
       <c r="H302" s="9"/>
       <c r="I302" s="9"/>
       <c r="J302" s="9" t="s">
-        <v>81</v>
+        <v>4</v>
       </c>
       <c r="K302" s="9">
-        <v>0</v>
+        <v>0.02</v>
       </c>
       <c r="L302" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="M302" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="N302" s="9"/>
+        <v>5</v>
+      </c>
+      <c r="M302" s="9"/>
+      <c r="N302" s="9" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="303" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A303" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="B303" s="9"/>
-      <c r="C303" s="9"/>
-      <c r="D303" s="9"/>
-      <c r="E303" s="9"/>
-      <c r="F303" s="9"/>
-      <c r="G303" s="9"/>
-      <c r="H303" s="9"/>
-      <c r="I303" s="9"/>
-      <c r="J303" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="K303" s="9">
-        <v>1.56</v>
-      </c>
-      <c r="L303" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="M303" s="9"/>
-      <c r="N303" s="9" t="s">
-        <v>86</v>
-      </c>
+      <c r="A303" s="8"/>
+      <c r="B303" s="8"/>
+      <c r="C303" s="8"/>
+      <c r="D303" s="8"/>
+      <c r="E303" s="8"/>
+      <c r="F303" s="8"/>
+      <c r="G303" s="8"/>
+      <c r="H303" s="8"/>
+      <c r="I303" s="8"/>
+      <c r="J303" s="8"/>
+      <c r="K303" s="8"/>
+      <c r="L303" s="8"/>
+      <c r="M303" s="8"/>
+      <c r="N303" s="8"/>
     </row>
     <row r="304" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A304" s="9" t="s">
-        <v>82</v>
-      </c>
+      <c r="A304" s="9"/>
       <c r="B304" s="9"/>
       <c r="C304" s="9"/>
       <c r="D304" s="9"/>
@@ -7915,24 +7922,22 @@
         <v>81</v>
       </c>
       <c r="K304" s="9">
-        <v>0.19</v>
+        <v>0</v>
       </c>
       <c r="L304" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="M304" s="9"/>
-      <c r="N304" s="9" t="s">
-        <v>86</v>
-      </c>
+      <c r="M304" s="9" t="s">
+        <v>79</v>
+      </c>
+      <c r="N304" s="9"/>
     </row>
     <row r="305" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A305" s="9" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="B305" s="9"/>
-      <c r="C305" s="9" t="s">
-        <v>64</v>
-      </c>
+      <c r="C305" s="9"/>
       <c r="D305" s="9"/>
       <c r="E305" s="9"/>
       <c r="F305" s="9"/>
@@ -7943,7 +7948,7 @@
         <v>81</v>
       </c>
       <c r="K305" s="9">
-        <v>0.02</v>
+        <v>1.56</v>
       </c>
       <c r="L305" s="9" t="s">
         <v>80</v>
@@ -7955,12 +7960,10 @@
     </row>
     <row r="306" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A306" s="9" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="B306" s="9"/>
-      <c r="C306" s="9" t="s">
-        <v>83</v>
-      </c>
+      <c r="C306" s="9"/>
       <c r="D306" s="9"/>
       <c r="E306" s="9"/>
       <c r="F306" s="9"/>
@@ -7971,7 +7974,7 @@
         <v>81</v>
       </c>
       <c r="K306" s="9">
-        <v>0.03</v>
+        <v>0.19</v>
       </c>
       <c r="L306" s="9" t="s">
         <v>80</v>
@@ -7981,8 +7984,64 @@
         <v>86</v>
       </c>
     </row>
-    <row r="309" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K309" s="7"/>
+    <row r="307" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A307" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B307" s="9"/>
+      <c r="C307" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D307" s="9"/>
+      <c r="E307" s="9"/>
+      <c r="F307" s="9"/>
+      <c r="G307" s="9"/>
+      <c r="H307" s="9"/>
+      <c r="I307" s="9"/>
+      <c r="J307" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K307" s="9">
+        <v>0.02</v>
+      </c>
+      <c r="L307" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="M307" s="9"/>
+      <c r="N307" s="9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="308" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A308" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="B308" s="9"/>
+      <c r="C308" s="9" t="s">
+        <v>83</v>
+      </c>
+      <c r="D308" s="9"/>
+      <c r="E308" s="9"/>
+      <c r="F308" s="9"/>
+      <c r="G308" s="9"/>
+      <c r="H308" s="9"/>
+      <c r="I308" s="9"/>
+      <c r="J308" s="9" t="s">
+        <v>81</v>
+      </c>
+      <c r="K308" s="9">
+        <v>0.03</v>
+      </c>
+      <c r="L308" s="9" t="s">
+        <v>80</v>
+      </c>
+      <c r="M308" s="9"/>
+      <c r="N308" s="9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="311" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K311" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/data/default/ManureMgmt.xlsx
+++ b/data/default/ManureMgmt.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1655" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1681" uniqueCount="196">
   <si>
     <t>value</t>
   </si>
@@ -603,6 +603,12 @@
   </si>
   <si>
     <t>Swedish IIR 2023, Table 5-10</t>
+  </si>
+  <si>
+    <t>Included in grown animals</t>
+  </si>
+  <si>
+    <t>Statistics Netherlands 2012, Table 3.40</t>
   </si>
 </sst>
 </file>
@@ -1357,26 +1363,8 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="10"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="10"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="10"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="36" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1392,6 +1380,24 @@
     </xf>
     <xf numFmtId="0" fontId="25" fillId="36" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="9"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="10"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="10"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="10"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1740,7 +1746,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N308"/>
+  <dimension ref="A1:N314"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
@@ -4750,16 +4756,13 @@
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
-        <v>52</v>
-      </c>
-      <c r="C147" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J147" t="s">
         <v>5</v>
       </c>
-      <c r="K147" s="17">
-        <v>0.6</v>
+      <c r="K147" s="15">
+        <v>14</v>
       </c>
       <c r="L147" t="s">
         <v>6</v>
@@ -4770,127 +4773,95 @@
     </row>
     <row r="148" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
-        <v>52</v>
-      </c>
-      <c r="C148" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J148" t="s">
         <v>105</v>
       </c>
-      <c r="K148" s="17">
-        <f>K147 * (0.39/2.29)/0.75</f>
-        <v>0.13624454148471615</v>
+      <c r="K148" s="15">
+        <f>K147 * (4.8/2.29)/14.4</f>
+        <v>2.0378457059679769</v>
       </c>
       <c r="L148" t="s">
         <v>108</v>
       </c>
-      <c r="M148" t="s">
-        <v>110</v>
-      </c>
       <c r="N148" t="s">
-        <v>113</v>
+        <v>195</v>
       </c>
     </row>
     <row r="149" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
-        <v>52</v>
-      </c>
-      <c r="C149" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J149" t="s">
         <v>106</v>
       </c>
-      <c r="K149" s="17">
-        <f>K147 * (0.33/(47/39))/0.75</f>
-        <v>0.21906382978723404</v>
+      <c r="K149" s="15">
+        <f>K147 * (25.2/(47/39))/14.4</f>
+        <v>20.329787234042556</v>
       </c>
       <c r="L149" t="s">
         <v>109</v>
       </c>
-      <c r="M149" t="s">
-        <v>111</v>
-      </c>
       <c r="N149" t="s">
-        <v>113</v>
+        <v>195</v>
       </c>
     </row>
     <row r="150" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
-        <v>52</v>
-      </c>
-      <c r="C150" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D150" t="s">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="J150" t="s">
         <v>5</v>
       </c>
-      <c r="K150">
-        <v>0.28999999999999998</v>
+      <c r="K150" s="15">
+        <v>0</v>
       </c>
       <c r="L150" t="s">
         <v>6</v>
       </c>
+      <c r="M150" t="s">
+        <v>194</v>
+      </c>
       <c r="N150" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="151" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
-        <v>52</v>
-      </c>
-      <c r="C151" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D151" t="s">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="J151" t="s">
         <v>105</v>
       </c>
-      <c r="K151" s="17">
-        <f>K150 * (0.19/2.29)/0.53</f>
-        <v>4.5398368624866105E-2</v>
+      <c r="K151" s="15">
+        <v>0</v>
       </c>
       <c r="L151" t="s">
         <v>108</v>
       </c>
-      <c r="M151" t="s">
-        <v>110</v>
-      </c>
-      <c r="N151" t="s">
-        <v>107</v>
-      </c>
     </row>
     <row r="152" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
-        <v>52</v>
-      </c>
-      <c r="C152" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="D152" t="s">
-        <v>54</v>
+        <v>94</v>
       </c>
       <c r="J152" t="s">
         <v>106</v>
       </c>
-      <c r="K152" s="17">
-        <f>K150 * (0.26/(47/39))/0.53</f>
-        <v>0.11804897631473303</v>
+      <c r="K152" s="15">
+        <v>0</v>
       </c>
       <c r="L152" t="s">
         <v>109</v>
-      </c>
-      <c r="M152" t="s">
-        <v>111</v>
-      </c>
-      <c r="N152" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="153" spans="1:14" x14ac:dyDescent="0.25">
@@ -4898,7 +4869,7 @@
         <v>52</v>
       </c>
       <c r="C153" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="J153" t="s">
         <v>5</v>
@@ -4908,9 +4879,6 @@
       </c>
       <c r="L153" t="s">
         <v>6</v>
-      </c>
-      <c r="M153" t="s">
-        <v>55</v>
       </c>
       <c r="N153" t="s">
         <v>8</v>
@@ -4921,14 +4889,14 @@
         <v>52</v>
       </c>
       <c r="C154" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="J154" t="s">
         <v>105</v>
       </c>
       <c r="K154" s="17">
-        <f>K153 * (0.55/2.29)/1.12</f>
-        <v>0.12866500311915158</v>
+        <f>K153 * (0.39/2.29)/0.75</f>
+        <v>0.13624454148471615</v>
       </c>
       <c r="L154" t="s">
         <v>108</v>
@@ -4937,7 +4905,7 @@
         <v>110</v>
       </c>
       <c r="N154" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="155" spans="1:14" x14ac:dyDescent="0.25">
@@ -4945,14 +4913,14 @@
         <v>52</v>
       </c>
       <c r="C155" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="J155" t="s">
         <v>106</v>
       </c>
       <c r="K155" s="17">
-        <f>K153 * (0.44/(47/39))/1.12</f>
-        <v>0.19559270516717325</v>
+        <f>K153 * (0.33/(47/39))/0.75</f>
+        <v>0.21906382978723404</v>
       </c>
       <c r="L155" t="s">
         <v>109</v>
@@ -4961,182 +4929,197 @@
         <v>111</v>
       </c>
       <c r="N155" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="156" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F156" s="5"/>
-    </row>
-    <row r="157" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="11"/>
-      <c r="J157" s="6" t="s">
-        <v>80</v>
-      </c>
-      <c r="K157" s="16">
-        <v>0</v>
-      </c>
-      <c r="L157" s="16"/>
-      <c r="M157" s="16" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="158" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="11"/>
-      <c r="J158" s="6" t="s">
-        <v>84</v>
-      </c>
-      <c r="K158" s="16">
-        <v>0</v>
-      </c>
-      <c r="L158" s="16"/>
-      <c r="M158" s="16" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="159" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="11"/>
-      <c r="J159" s="6" t="s">
-        <v>85</v>
-      </c>
-      <c r="K159" s="16">
-        <v>0</v>
-      </c>
-      <c r="L159" s="16"/>
-      <c r="M159" s="16" t="s">
-        <v>100</v>
+      <c r="A156" t="s">
+        <v>52</v>
+      </c>
+      <c r="C156" t="s">
+        <v>53</v>
+      </c>
+      <c r="D156" t="s">
+        <v>54</v>
+      </c>
+      <c r="J156" t="s">
+        <v>5</v>
+      </c>
+      <c r="K156">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="L156" t="s">
+        <v>6</v>
+      </c>
+      <c r="N156" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="157" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>52</v>
+      </c>
+      <c r="C157" t="s">
+        <v>53</v>
+      </c>
+      <c r="D157" t="s">
+        <v>54</v>
+      </c>
+      <c r="J157" t="s">
+        <v>105</v>
+      </c>
+      <c r="K157" s="17">
+        <f>K156 * (0.19/2.29)/0.53</f>
+        <v>4.5398368624866105E-2</v>
+      </c>
+      <c r="L157" t="s">
+        <v>108</v>
+      </c>
+      <c r="M157" t="s">
+        <v>110</v>
+      </c>
+      <c r="N157" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="158" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>52</v>
+      </c>
+      <c r="C158" t="s">
+        <v>53</v>
+      </c>
+      <c r="D158" t="s">
+        <v>54</v>
+      </c>
+      <c r="J158" t="s">
+        <v>106</v>
+      </c>
+      <c r="K158" s="17">
+        <f>K156 * (0.26/(47/39))/0.53</f>
+        <v>0.11804897631473303</v>
+      </c>
+      <c r="L158" t="s">
+        <v>109</v>
+      </c>
+      <c r="M158" t="s">
+        <v>111</v>
+      </c>
+      <c r="N158" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="159" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>52</v>
+      </c>
+      <c r="C159" t="s">
+        <v>53</v>
+      </c>
+      <c r="J159" t="s">
+        <v>5</v>
+      </c>
+      <c r="K159" s="17">
+        <v>0.6</v>
+      </c>
+      <c r="L159" t="s">
+        <v>6</v>
+      </c>
+      <c r="M159" t="s">
+        <v>55</v>
+      </c>
+      <c r="N159" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="160" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
-        <v>1</v>
-      </c>
-      <c r="D160" t="s">
-        <v>3</v>
-      </c>
-      <c r="F160" s="5"/>
+        <v>52</v>
+      </c>
+      <c r="C160" t="s">
+        <v>53</v>
+      </c>
       <c r="J160" t="s">
-        <v>80</v>
-      </c>
-      <c r="K160">
-        <v>22.5</v>
+        <v>105</v>
+      </c>
+      <c r="K160" s="17">
+        <f>K159 * (0.55/2.29)/1.12</f>
+        <v>0.12866500311915158</v>
       </c>
       <c r="L160" t="s">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="M160" t="s">
-        <v>89</v>
+        <v>110</v>
       </c>
       <c r="N160" t="s">
-        <v>102</v>
+        <v>112</v>
       </c>
     </row>
     <row r="161" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
-        <v>1</v>
-      </c>
-      <c r="D161" t="s">
-        <v>3</v>
-      </c>
-      <c r="F161" s="5"/>
+        <v>52</v>
+      </c>
+      <c r="C161" t="s">
+        <v>53</v>
+      </c>
       <c r="J161" t="s">
+        <v>106</v>
+      </c>
+      <c r="K161" s="17">
+        <f>K159 * (0.44/(47/39))/1.12</f>
+        <v>0.19559270516717325</v>
+      </c>
+      <c r="L161" t="s">
+        <v>109</v>
+      </c>
+      <c r="M161" t="s">
+        <v>111</v>
+      </c>
+      <c r="N161" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F162" s="5"/>
+    </row>
+    <row r="163" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A163" s="11"/>
+      <c r="J163" s="6" t="s">
+        <v>80</v>
+      </c>
+      <c r="K163" s="16">
+        <v>0</v>
+      </c>
+      <c r="L163" s="16"/>
+      <c r="M163" s="16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="164" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A164" s="11"/>
+      <c r="J164" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="K161">
-        <v>7.4</v>
-      </c>
-      <c r="L161" t="s">
-        <v>87</v>
-      </c>
-      <c r="N161" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="162" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A162" t="s">
-        <v>1</v>
-      </c>
-      <c r="D162" t="s">
-        <v>3</v>
-      </c>
-      <c r="F162" s="5"/>
-      <c r="J162" t="s">
+      <c r="K164" s="16">
+        <v>0</v>
+      </c>
+      <c r="L164" s="16"/>
+      <c r="M164" s="16" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="165" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="11"/>
+      <c r="J165" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="K162" s="15">
-        <v>2</v>
-      </c>
-      <c r="L162" t="s">
-        <v>88</v>
-      </c>
-      <c r="N162" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="163" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A163" t="s">
-        <v>1</v>
-      </c>
-      <c r="D163" t="s">
-        <v>9</v>
-      </c>
-      <c r="F163" s="5"/>
-      <c r="J163" t="s">
-        <v>80</v>
-      </c>
-      <c r="K163">
-        <f>23.1</f>
-        <v>23.1</v>
-      </c>
-      <c r="L163" t="s">
-        <v>86</v>
-      </c>
-      <c r="M163" t="s">
-        <v>90</v>
-      </c>
-      <c r="N163" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="164" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A164" t="s">
-        <v>1</v>
-      </c>
-      <c r="D164" t="s">
-        <v>9</v>
-      </c>
-      <c r="F164" s="5"/>
-      <c r="J164" t="s">
-        <v>84</v>
-      </c>
-      <c r="K164">
-        <v>7.4</v>
-      </c>
-      <c r="L164" t="s">
-        <v>87</v>
-      </c>
-      <c r="N164" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="165" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A165" t="s">
-        <v>1</v>
-      </c>
-      <c r="D165" t="s">
-        <v>9</v>
-      </c>
-      <c r="F165" s="5"/>
-      <c r="J165" t="s">
-        <v>85</v>
-      </c>
-      <c r="K165" s="15">
-        <v>2</v>
-      </c>
-      <c r="L165" t="s">
-        <v>88</v>
-      </c>
-      <c r="N165" t="s">
-        <v>102</v>
+      <c r="K165" s="16">
+        <v>0</v>
+      </c>
+      <c r="L165" s="16"/>
+      <c r="M165" s="16" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.25">
@@ -5144,20 +5127,20 @@
         <v>1</v>
       </c>
       <c r="D166" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F166" s="5"/>
       <c r="J166" t="s">
         <v>80</v>
       </c>
       <c r="K166">
-        <v>26.4</v>
+        <v>22.5</v>
       </c>
       <c r="L166" t="s">
         <v>86</v>
       </c>
       <c r="M166" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="N166" t="s">
         <v>102</v>
@@ -5168,14 +5151,14 @@
         <v>1</v>
       </c>
       <c r="D167" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F167" s="5"/>
       <c r="J167" t="s">
         <v>84</v>
       </c>
       <c r="K167">
-        <v>6.85</v>
+        <v>7.4</v>
       </c>
       <c r="L167" t="s">
         <v>87</v>
@@ -5189,14 +5172,14 @@
         <v>1</v>
       </c>
       <c r="D168" t="s">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="F168" s="5"/>
       <c r="J168" t="s">
         <v>85</v>
       </c>
-      <c r="K168">
-        <v>1.69</v>
+      <c r="K168" s="15">
+        <v>2</v>
       </c>
       <c r="L168" t="s">
         <v>88</v>
@@ -5210,20 +5193,21 @@
         <v>1</v>
       </c>
       <c r="D169" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F169" s="5"/>
       <c r="J169" t="s">
         <v>80</v>
       </c>
       <c r="K169">
-        <v>27.04</v>
+        <f>23.1</f>
+        <v>23.1</v>
       </c>
       <c r="L169" t="s">
         <v>86</v>
       </c>
       <c r="M169" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="N169" t="s">
         <v>102</v>
@@ -5234,7 +5218,7 @@
         <v>1</v>
       </c>
       <c r="D170" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F170" s="5"/>
       <c r="J170" t="s">
@@ -5255,14 +5239,14 @@
         <v>1</v>
       </c>
       <c r="D171" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F171" s="5"/>
       <c r="J171" t="s">
         <v>85</v>
       </c>
-      <c r="K171">
-        <v>1.91</v>
+      <c r="K171" s="15">
+        <v>2</v>
       </c>
       <c r="L171" t="s">
         <v>88</v>
@@ -5276,20 +5260,20 @@
         <v>1</v>
       </c>
       <c r="D172" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F172" s="5"/>
       <c r="J172" t="s">
         <v>80</v>
       </c>
       <c r="K172">
-        <v>27.04</v>
+        <v>26.4</v>
       </c>
       <c r="L172" t="s">
         <v>86</v>
       </c>
       <c r="M172" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="N172" t="s">
         <v>102</v>
@@ -5300,14 +5284,14 @@
         <v>1</v>
       </c>
       <c r="D173" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F173" s="5"/>
       <c r="J173" t="s">
         <v>84</v>
       </c>
       <c r="K173">
-        <v>7.4</v>
+        <v>6.85</v>
       </c>
       <c r="L173" t="s">
         <v>87</v>
@@ -5321,14 +5305,14 @@
         <v>1</v>
       </c>
       <c r="D174" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F174" s="5"/>
       <c r="J174" t="s">
         <v>85</v>
       </c>
       <c r="K174">
-        <v>1.91</v>
+        <v>1.69</v>
       </c>
       <c r="L174" t="s">
         <v>88</v>
@@ -5342,20 +5326,20 @@
         <v>1</v>
       </c>
       <c r="D175" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F175" s="5"/>
       <c r="J175" t="s">
         <v>80</v>
       </c>
       <c r="K175">
-        <v>25.28</v>
+        <v>27.04</v>
       </c>
       <c r="L175" t="s">
         <v>86</v>
       </c>
       <c r="M175" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N175" t="s">
         <v>102</v>
@@ -5366,7 +5350,7 @@
         <v>1</v>
       </c>
       <c r="D176" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F176" s="5"/>
       <c r="J176" t="s">
@@ -5387,14 +5371,14 @@
         <v>1</v>
       </c>
       <c r="D177" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F177" s="5"/>
       <c r="J177" t="s">
         <v>85</v>
       </c>
-      <c r="K177" s="15">
-        <v>2</v>
+      <c r="K177">
+        <v>1.91</v>
       </c>
       <c r="L177" t="s">
         <v>88</v>
@@ -5404,24 +5388,45 @@
       </c>
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A178" t="s">
+        <v>1</v>
+      </c>
+      <c r="D178" t="s">
+        <v>12</v>
+      </c>
       <c r="F178" s="5"/>
+      <c r="J178" t="s">
+        <v>80</v>
+      </c>
+      <c r="K178">
+        <v>27.04</v>
+      </c>
+      <c r="L178" t="s">
+        <v>86</v>
+      </c>
+      <c r="M178" t="s">
+        <v>93</v>
+      </c>
+      <c r="N178" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
-        <v>62</v>
+        <v>1</v>
+      </c>
+      <c r="D179" t="s">
+        <v>12</v>
       </c>
       <c r="F179" s="5"/>
       <c r="J179" t="s">
-        <v>80</v>
-      </c>
-      <c r="K179" s="5">
-        <v>25</v>
+        <v>84</v>
+      </c>
+      <c r="K179">
+        <v>7.4</v>
       </c>
       <c r="L179" t="s">
-        <v>86</v>
-      </c>
-      <c r="M179" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="N179" t="s">
         <v>102</v>
@@ -5429,17 +5434,20 @@
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
-        <v>62</v>
+        <v>1</v>
+      </c>
+      <c r="D180" t="s">
+        <v>12</v>
       </c>
       <c r="F180" s="5"/>
       <c r="J180" t="s">
-        <v>84</v>
-      </c>
-      <c r="K180" s="5">
-        <v>7.8</v>
+        <v>85</v>
+      </c>
+      <c r="K180">
+        <v>1.91</v>
       </c>
       <c r="L180" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N180" t="s">
         <v>102</v>
@@ -5447,17 +5455,23 @@
     </row>
     <row r="181" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
-        <v>62</v>
+        <v>1</v>
+      </c>
+      <c r="D181" t="s">
+        <v>13</v>
       </c>
       <c r="F181" s="5"/>
       <c r="J181" t="s">
-        <v>85</v>
-      </c>
-      <c r="K181" s="5">
-        <v>1.7</v>
+        <v>80</v>
+      </c>
+      <c r="K181">
+        <v>25.28</v>
       </c>
       <c r="L181" t="s">
-        <v>88</v>
+        <v>86</v>
+      </c>
+      <c r="M181" t="s">
+        <v>92</v>
       </c>
       <c r="N181" t="s">
         <v>102</v>
@@ -5465,23 +5479,20 @@
     </row>
     <row r="182" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="D182" t="s">
-        <v>94</v>
+        <v>13</v>
       </c>
       <c r="F182" s="5"/>
       <c r="J182" t="s">
-        <v>80</v>
-      </c>
-      <c r="K182" s="5">
-        <v>26.2</v>
+        <v>84</v>
+      </c>
+      <c r="K182">
+        <v>7.4</v>
       </c>
       <c r="L182" t="s">
-        <v>86</v>
-      </c>
-      <c r="M182" t="s">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="N182" t="s">
         <v>102</v>
@@ -5489,66 +5500,62 @@
     </row>
     <row r="183" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
-        <v>62</v>
+        <v>1</v>
       </c>
       <c r="D183" t="s">
-        <v>94</v>
+        <v>13</v>
       </c>
       <c r="F183" s="5"/>
       <c r="J183" t="s">
-        <v>84</v>
-      </c>
-      <c r="K183" s="5">
-        <v>5.2</v>
+        <v>85</v>
+      </c>
+      <c r="K183" s="15">
+        <v>2</v>
       </c>
       <c r="L183" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N183" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A184" t="s">
+      <c r="F184" s="5"/>
+    </row>
+    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A185" t="s">
         <v>62</v>
       </c>
-      <c r="D184" t="s">
-        <v>94</v>
-      </c>
-      <c r="F184" s="5"/>
-      <c r="J184" t="s">
-        <v>85</v>
-      </c>
-      <c r="K184" s="5">
-        <v>1.7</v>
-      </c>
-      <c r="L184" t="s">
-        <v>88</v>
-      </c>
-      <c r="N184" t="s">
+      <c r="F185" s="5"/>
+      <c r="J185" t="s">
+        <v>80</v>
+      </c>
+      <c r="K185" s="5">
+        <v>25</v>
+      </c>
+      <c r="L185" t="s">
+        <v>86</v>
+      </c>
+      <c r="M185" t="s">
+        <v>103</v>
+      </c>
+      <c r="N185" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="185" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F185" s="5"/>
-      <c r="K185" s="5"/>
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F186" s="5"/>
       <c r="J186" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="K186" s="5">
-        <v>29.9</v>
+        <v>7.8</v>
       </c>
       <c r="L186" t="s">
-        <v>86</v>
-      </c>
-      <c r="M186" t="s">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="N186" t="s">
         <v>102</v>
@@ -5556,17 +5563,17 @@
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
       <c r="F187" s="5"/>
       <c r="J187" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K187" s="5">
-        <v>7.5</v>
+        <v>1.7</v>
       </c>
       <c r="L187" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N187" t="s">
         <v>102</v>
@@ -5574,87 +5581,90 @@
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
-        <v>56</v>
+        <v>62</v>
+      </c>
+      <c r="D188" t="s">
+        <v>94</v>
       </c>
       <c r="F188" s="5"/>
       <c r="J188" t="s">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="K188" s="5">
-        <v>2</v>
+        <v>26.2</v>
       </c>
       <c r="L188" t="s">
-        <v>88</v>
+        <v>86</v>
+      </c>
+      <c r="M188" t="s">
+        <v>104</v>
       </c>
       <c r="N188" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A189" t="s">
+        <v>62</v>
+      </c>
+      <c r="D189" t="s">
+        <v>94</v>
+      </c>
       <c r="F189" s="5"/>
-      <c r="K189" s="15"/>
+      <c r="J189" t="s">
+        <v>84</v>
+      </c>
+      <c r="K189" s="5">
+        <v>5.2</v>
+      </c>
+      <c r="L189" t="s">
+        <v>87</v>
+      </c>
+      <c r="N189" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
-        <v>37</v>
+        <v>62</v>
       </c>
       <c r="D190" t="s">
-        <v>42</v>
+        <v>94</v>
       </c>
       <c r="F190" s="5"/>
       <c r="J190" t="s">
-        <v>80</v>
-      </c>
-      <c r="K190">
-        <v>25</v>
+        <v>85</v>
+      </c>
+      <c r="K190" s="5">
+        <v>1.7</v>
       </c>
       <c r="L190" t="s">
-        <v>86</v>
-      </c>
-      <c r="M190" t="s">
-        <v>95</v>
+        <v>88</v>
       </c>
       <c r="N190" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A191" t="s">
-        <v>37</v>
-      </c>
-      <c r="D191" t="s">
-        <v>42</v>
-      </c>
       <c r="F191" s="5"/>
-      <c r="J191" t="s">
-        <v>84</v>
-      </c>
-      <c r="K191">
-        <v>5.35</v>
-      </c>
-      <c r="L191" t="s">
-        <v>87</v>
-      </c>
-      <c r="N191" t="s">
-        <v>102</v>
-      </c>
+      <c r="K191" s="5"/>
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
-        <v>37</v>
-      </c>
-      <c r="D192" t="s">
-        <v>42</v>
+        <v>56</v>
       </c>
       <c r="F192" s="5"/>
       <c r="J192" t="s">
-        <v>85</v>
-      </c>
-      <c r="K192" s="15">
-        <v>2.08</v>
+        <v>80</v>
+      </c>
+      <c r="K192" s="5">
+        <v>29.9</v>
       </c>
       <c r="L192" t="s">
-        <v>88</v>
+        <v>86</v>
+      </c>
+      <c r="M192" t="s">
+        <v>101</v>
       </c>
       <c r="N192" t="s">
         <v>102</v>
@@ -5662,22 +5672,17 @@
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
-        <v>37</v>
-      </c>
-      <c r="D193" t="s">
-        <v>45</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="F193" s="5"/>
       <c r="J193" t="s">
-        <v>80</v>
-      </c>
-      <c r="K193" s="15">
-        <v>24.9</v>
+        <v>84</v>
+      </c>
+      <c r="K193" s="5">
+        <v>7.5</v>
       </c>
       <c r="L193" t="s">
-        <v>86</v>
-      </c>
-      <c r="M193" t="s">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="N193" t="s">
         <v>102</v>
@@ -5685,62 +5690,45 @@
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
-        <v>37</v>
-      </c>
-      <c r="D194" t="s">
-        <v>45</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="F194" s="5"/>
       <c r="J194" t="s">
-        <v>84</v>
-      </c>
-      <c r="K194" s="15">
-        <v>5.35</v>
+        <v>85</v>
+      </c>
+      <c r="K194" s="5">
+        <v>2</v>
       </c>
       <c r="L194" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N194" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A195" t="s">
-        <v>37</v>
-      </c>
-      <c r="D195" t="s">
-        <v>45</v>
-      </c>
-      <c r="J195" t="s">
-        <v>85</v>
-      </c>
-      <c r="K195" s="15">
-        <v>2.25</v>
-      </c>
-      <c r="L195" t="s">
-        <v>88</v>
-      </c>
-      <c r="N195" t="s">
-        <v>102</v>
-      </c>
+      <c r="F195" s="5"/>
+      <c r="K195" s="15"/>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>37</v>
       </c>
       <c r="D196" t="s">
-        <v>43</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F196" s="5"/>
       <c r="J196" t="s">
         <v>80</v>
       </c>
-      <c r="K196" s="15">
+      <c r="K196">
         <v>25</v>
       </c>
       <c r="L196" t="s">
         <v>86</v>
       </c>
       <c r="M196" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="N196" t="s">
         <v>102</v>
@@ -5751,12 +5739,13 @@
         <v>37</v>
       </c>
       <c r="D197" t="s">
-        <v>43</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F197" s="5"/>
       <c r="J197" t="s">
         <v>84</v>
       </c>
-      <c r="K197" s="15">
+      <c r="K197">
         <v>5.35</v>
       </c>
       <c r="L197" t="s">
@@ -5771,13 +5760,14 @@
         <v>37</v>
       </c>
       <c r="D198" t="s">
-        <v>43</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="F198" s="5"/>
       <c r="J198" t="s">
         <v>85</v>
       </c>
       <c r="K198" s="15">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="L198" t="s">
         <v>88</v>
@@ -5791,20 +5781,19 @@
         <v>37</v>
       </c>
       <c r="D199" t="s">
-        <v>44</v>
-      </c>
-      <c r="F199" s="5"/>
+        <v>45</v>
+      </c>
       <c r="J199" t="s">
         <v>80</v>
       </c>
       <c r="K199" s="15">
-        <v>23.1</v>
+        <v>24.9</v>
       </c>
       <c r="L199" t="s">
         <v>86</v>
       </c>
       <c r="M199" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="N199" t="s">
         <v>102</v>
@@ -5815,14 +5804,13 @@
         <v>37</v>
       </c>
       <c r="D200" t="s">
-        <v>44</v>
-      </c>
-      <c r="F200" s="5"/>
+        <v>45</v>
+      </c>
       <c r="J200" t="s">
         <v>84</v>
       </c>
       <c r="K200" s="15">
-        <v>5.36</v>
+        <v>5.35</v>
       </c>
       <c r="L200" t="s">
         <v>87</v>
@@ -5836,14 +5824,13 @@
         <v>37</v>
       </c>
       <c r="D201" t="s">
-        <v>44</v>
-      </c>
-      <c r="F201" s="5"/>
+        <v>45</v>
+      </c>
       <c r="J201" t="s">
         <v>85</v>
       </c>
       <c r="K201" s="15">
-        <v>2.64</v>
+        <v>2.25</v>
       </c>
       <c r="L201" t="s">
         <v>88</v>
@@ -5856,7 +5843,9 @@
       <c r="A202" t="s">
         <v>37</v>
       </c>
-      <c r="F202" s="5"/>
+      <c r="D202" t="s">
+        <v>43</v>
+      </c>
       <c r="J202" t="s">
         <v>80</v>
       </c>
@@ -5867,7 +5856,7 @@
         <v>86</v>
       </c>
       <c r="M202" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="N202" t="s">
         <v>102</v>
@@ -5877,12 +5866,14 @@
       <c r="A203" t="s">
         <v>37</v>
       </c>
-      <c r="F203" s="5"/>
+      <c r="D203" t="s">
+        <v>43</v>
+      </c>
       <c r="J203" t="s">
         <v>84</v>
       </c>
       <c r="K203" s="15">
-        <v>5.36</v>
+        <v>5.35</v>
       </c>
       <c r="L203" t="s">
         <v>87</v>
@@ -5895,12 +5886,14 @@
       <c r="A204" t="s">
         <v>37</v>
       </c>
-      <c r="F204" s="5"/>
+      <c r="D204" t="s">
+        <v>43</v>
+      </c>
       <c r="J204" t="s">
         <v>85</v>
       </c>
       <c r="K204" s="15">
-        <v>2.2799999999999998</v>
+        <v>2.04</v>
       </c>
       <c r="L204" t="s">
         <v>88</v>
@@ -5910,423 +5903,373 @@
       </c>
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>37</v>
+      </c>
+      <c r="D205" t="s">
+        <v>44</v>
+      </c>
       <c r="F205" s="5"/>
-      <c r="K205" s="15"/>
+      <c r="J205" t="s">
+        <v>80</v>
+      </c>
+      <c r="K205" s="15">
+        <v>23.1</v>
+      </c>
+      <c r="L205" t="s">
+        <v>86</v>
+      </c>
+      <c r="M205" t="s">
+        <v>98</v>
+      </c>
+      <c r="N205" t="s">
+        <v>102</v>
+      </c>
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>37</v>
+      </c>
+      <c r="D206" t="s">
+        <v>44</v>
+      </c>
       <c r="F206" s="5"/>
-      <c r="J206" s="6" t="s">
-        <v>115</v>
-      </c>
-      <c r="K206" s="18">
-        <v>0</v>
-      </c>
-      <c r="L206" s="6" t="s">
-        <v>100</v>
+      <c r="J206" t="s">
+        <v>84</v>
+      </c>
+      <c r="K206" s="15">
+        <v>5.36</v>
+      </c>
+      <c r="L206" t="s">
+        <v>87</v>
+      </c>
+      <c r="N206" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>37</v>
+      </c>
+      <c r="D207" t="s">
+        <v>44</v>
+      </c>
       <c r="F207" s="5"/>
-      <c r="J207" s="6" t="s">
-        <v>120</v>
-      </c>
-      <c r="K207" s="18">
-        <v>0</v>
-      </c>
-      <c r="L207" s="6" t="s">
-        <v>100</v>
+      <c r="J207" t="s">
+        <v>85</v>
+      </c>
+      <c r="K207" s="15">
+        <v>2.64</v>
+      </c>
+      <c r="L207" t="s">
+        <v>88</v>
+      </c>
+      <c r="N207" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
+        <v>37</v>
+      </c>
       <c r="F208" s="5"/>
-      <c r="J208" s="6" t="s">
-        <v>121</v>
-      </c>
-      <c r="K208" s="18">
-        <v>0</v>
-      </c>
-      <c r="L208" s="6" t="s">
-        <v>100</v>
+      <c r="J208" t="s">
+        <v>80</v>
+      </c>
+      <c r="K208" s="15">
+        <v>25</v>
+      </c>
+      <c r="L208" t="s">
+        <v>86</v>
+      </c>
+      <c r="M208" t="s">
+        <v>99</v>
+      </c>
+      <c r="N208" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E209" t="s">
-        <v>124</v>
+      <c r="A209" t="s">
+        <v>37</v>
       </c>
       <c r="F209" s="5"/>
       <c r="J209" t="s">
+        <v>84</v>
+      </c>
+      <c r="K209" s="15">
+        <v>5.36</v>
+      </c>
+      <c r="L209" t="s">
+        <v>87</v>
+      </c>
+      <c r="N209" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="210" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A210" t="s">
+        <v>37</v>
+      </c>
+      <c r="F210" s="5"/>
+      <c r="J210" t="s">
+        <v>85</v>
+      </c>
+      <c r="K210" s="15">
+        <v>2.2799999999999998</v>
+      </c>
+      <c r="L210" t="s">
+        <v>88</v>
+      </c>
+      <c r="N210" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="211" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F211" s="5"/>
+      <c r="K211" s="15"/>
+    </row>
+    <row r="212" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F212" s="5"/>
+      <c r="J212" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="K209" s="17">
+      <c r="K212" s="18">
+        <v>0</v>
+      </c>
+      <c r="L212" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="213" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F213" s="5"/>
+      <c r="J213" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="K213" s="18">
+        <v>0</v>
+      </c>
+      <c r="L213" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="214" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F214" s="5"/>
+      <c r="J214" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="K214" s="18">
+        <v>0</v>
+      </c>
+      <c r="L214" s="6" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="215" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="E215" t="s">
+        <v>124</v>
+      </c>
+      <c r="F215" s="5"/>
+      <c r="J215" t="s">
+        <v>115</v>
+      </c>
+      <c r="K215" s="17">
         <f>5.49/1.035</f>
         <v>5.304347826086957</v>
       </c>
-      <c r="L209" t="s">
+      <c r="L215" t="s">
         <v>116</v>
       </c>
-      <c r="M209" t="s">
+      <c r="M215" t="s">
         <v>122</v>
       </c>
-      <c r="N209" t="s">
+      <c r="N215" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="210" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E210" t="s">
+    <row r="216" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="E216" t="s">
         <v>124</v>
       </c>
-      <c r="F210" s="5"/>
-      <c r="J210" t="s">
+      <c r="F216" s="5"/>
+      <c r="J216" t="s">
         <v>120</v>
       </c>
-      <c r="K210" s="17">
+      <c r="K216" s="17">
         <f>0.97/1.035</f>
         <v>0.9371980676328503</v>
       </c>
-      <c r="L210" t="s">
+      <c r="L216" t="s">
         <v>117</v>
       </c>
-      <c r="N210" t="s">
+      <c r="N216" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="211" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="E211" t="s">
+    <row r="217" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="E217" t="s">
         <v>124</v>
       </c>
-      <c r="F211" s="5"/>
-      <c r="J211" t="s">
+      <c r="F217" s="5"/>
+      <c r="J217" t="s">
         <v>121</v>
       </c>
-      <c r="K211" s="17">
+      <c r="K217" s="17">
         <f>1.6/1.035</f>
         <v>1.5458937198067635</v>
       </c>
-      <c r="L211" t="s">
+      <c r="L217" t="s">
         <v>118</v>
       </c>
-      <c r="N211" t="s">
+      <c r="N217" t="s">
         <v>123</v>
       </c>
     </row>
-    <row r="212" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F212" s="5"/>
-    </row>
-    <row r="213" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A213" s="12" t="s">
+    <row r="218" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F218" s="5"/>
+    </row>
+    <row r="219" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A219" s="12" t="s">
         <v>139</v>
       </c>
-      <c r="B213" s="13"/>
-      <c r="C213" s="13"/>
-      <c r="D213" s="13"/>
-      <c r="E213" s="13"/>
-      <c r="F213" s="14"/>
-      <c r="G213" s="13"/>
-      <c r="H213" s="13"/>
-      <c r="I213" s="13"/>
-      <c r="J213" s="13"/>
-      <c r="K213" s="13"/>
-      <c r="L213" s="13"/>
-      <c r="M213" s="13"/>
-      <c r="N213" s="13"/>
-    </row>
-    <row r="214" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A214" s="53" t="s">
+      <c r="B219" s="13"/>
+      <c r="C219" s="13"/>
+      <c r="D219" s="13"/>
+      <c r="E219" s="13"/>
+      <c r="F219" s="14"/>
+      <c r="G219" s="13"/>
+      <c r="H219" s="13"/>
+      <c r="I219" s="13"/>
+      <c r="J219" s="13"/>
+      <c r="K219" s="13"/>
+      <c r="L219" s="13"/>
+      <c r="M219" s="13"/>
+      <c r="N219" s="13"/>
+    </row>
+    <row r="220" spans="1:14" s="10" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A220" s="53" t="s">
         <v>187</v>
       </c>
-      <c r="F214" s="52"/>
-    </row>
-    <row r="215" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J215" s="1" t="s">
+      <c r="F220" s="52"/>
+    </row>
+    <row r="221" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J221" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K215" s="1">
-        <v>0</v>
-      </c>
-      <c r="L215" s="1"/>
-      <c r="M215" s="1" t="s">
+      <c r="K221" s="1">
+        <v>0</v>
+      </c>
+      <c r="L221" s="1"/>
+      <c r="M221" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="216" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J216" s="1" t="s">
+    <row r="222" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J222" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="K216" s="1">
-        <v>0</v>
-      </c>
-      <c r="L216" s="1"/>
-      <c r="M216" s="1" t="s">
+      <c r="K222" s="1">
+        <v>0</v>
+      </c>
+      <c r="L222" s="1"/>
+      <c r="M222" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="217" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="J217" s="1" t="s">
+    <row r="223" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="J223" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="K217" s="1">
-        <v>0</v>
-      </c>
-      <c r="L217" s="1"/>
-      <c r="M217" s="1" t="s">
+      <c r="K223" s="1">
+        <v>0</v>
+      </c>
+      <c r="L223" s="1"/>
+      <c r="M223" s="1" t="s">
         <v>51</v>
       </c>
     </row>
-    <row r="218" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A218" s="54"/>
-      <c r="J218" s="1"/>
-      <c r="K218" s="1"/>
-      <c r="L218" s="1"/>
-      <c r="M218" s="1"/>
-    </row>
-    <row r="219" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A219" t="s">
-        <v>1</v>
-      </c>
-      <c r="F219" t="s">
+    <row r="224" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A224" s="54"/>
+      <c r="J224" s="1"/>
+      <c r="K224" s="1"/>
+      <c r="L224" s="1"/>
+      <c r="M224" s="1"/>
+    </row>
+    <row r="225" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
+        <v>1</v>
+      </c>
+      <c r="F225" t="s">
         <v>18</v>
       </c>
-      <c r="H219" t="s">
+      <c r="H225" t="s">
         <v>21</v>
       </c>
-      <c r="J219" t="s">
+      <c r="J225" t="s">
         <v>22</v>
       </c>
-      <c r="K219">
+      <c r="K225">
         <v>4</v>
       </c>
-      <c r="L219" t="s">
+      <c r="L225" t="s">
         <v>57</v>
       </c>
-      <c r="N219" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="220" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A220" t="s">
-        <v>1</v>
-      </c>
-      <c r="F220" t="s">
-        <v>19</v>
-      </c>
-      <c r="H220" t="s">
-        <v>21</v>
-      </c>
-      <c r="J220" t="s">
-        <v>22</v>
-      </c>
-      <c r="K220">
-        <v>4</v>
-      </c>
-      <c r="L220" t="s">
-        <v>57</v>
-      </c>
-      <c r="N220" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="221" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A221" t="s">
-        <v>1</v>
-      </c>
-      <c r="F221" t="s">
-        <v>20</v>
-      </c>
-      <c r="H221" t="s">
-        <v>21</v>
-      </c>
-      <c r="J221" t="s">
-        <v>22</v>
-      </c>
-      <c r="K221">
-        <v>20</v>
-      </c>
-      <c r="L221" t="s">
-        <v>57</v>
-      </c>
-      <c r="N221" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="222" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A222" t="s">
-        <v>1</v>
-      </c>
-      <c r="F222" t="s">
-        <v>185</v>
-      </c>
-      <c r="H222" t="s">
-        <v>21</v>
-      </c>
-      <c r="J222" t="s">
-        <v>22</v>
-      </c>
-      <c r="K222">
-        <v>4</v>
-      </c>
-      <c r="L222" t="s">
-        <v>57</v>
-      </c>
-      <c r="N222" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="223" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A223" s="44" t="s">
-        <v>56</v>
-      </c>
-      <c r="B223" s="44"/>
-      <c r="C223" s="44"/>
-      <c r="D223" s="44"/>
-      <c r="E223" s="44"/>
-      <c r="F223" s="44" t="s">
-        <v>19</v>
-      </c>
-      <c r="G223" s="44"/>
-      <c r="H223" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="I223" s="44"/>
-      <c r="J223" s="44" t="s">
-        <v>22</v>
-      </c>
-      <c r="K223" s="44">
-        <v>4</v>
-      </c>
-      <c r="L223" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="M223" s="1"/>
-      <c r="N223" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="224" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A224" s="44" t="s">
-        <v>56</v>
-      </c>
-      <c r="B224" s="44"/>
-      <c r="C224" s="44"/>
-      <c r="D224" s="44"/>
-      <c r="E224" s="44"/>
-      <c r="F224" s="44" t="s">
-        <v>20</v>
-      </c>
-      <c r="G224" s="44"/>
-      <c r="H224" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="I224" s="44"/>
-      <c r="J224" s="44" t="s">
-        <v>22</v>
-      </c>
-      <c r="K224" s="44">
-        <v>15</v>
-      </c>
-      <c r="L224" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="M224" s="1"/>
-      <c r="N224" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="225" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A225" s="44" t="s">
-        <v>56</v>
-      </c>
-      <c r="B225" s="44"/>
-      <c r="C225" s="44"/>
-      <c r="D225" s="44"/>
-      <c r="E225" s="44"/>
-      <c r="F225" s="44" t="s">
-        <v>177</v>
-      </c>
-      <c r="G225" s="44"/>
-      <c r="H225" s="44" t="s">
-        <v>21</v>
-      </c>
-      <c r="I225" s="44"/>
-      <c r="J225" s="44" t="s">
-        <v>22</v>
-      </c>
-      <c r="K225" s="44">
-        <v>4</v>
-      </c>
-      <c r="L225" s="44" t="s">
-        <v>57</v>
-      </c>
-      <c r="M225" s="1"/>
       <c r="N225" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A226" s="44" t="s">
-        <v>62</v>
-      </c>
-      <c r="B226" s="44"/>
-      <c r="C226" s="44"/>
-      <c r="D226" s="44"/>
-      <c r="E226" s="44"/>
+      <c r="A226" t="s">
+        <v>1</v>
+      </c>
       <c r="F226" t="s">
         <v>19</v>
       </c>
-      <c r="G226" s="44"/>
-      <c r="H226" s="44" t="s">
+      <c r="H226" t="s">
         <v>21</v>
       </c>
-      <c r="I226" s="44"/>
-      <c r="J226" s="44" t="s">
+      <c r="J226" t="s">
         <v>22</v>
       </c>
-      <c r="K226" s="44">
+      <c r="K226">
         <v>4</v>
       </c>
-      <c r="L226" s="44" t="s">
+      <c r="L226" t="s">
         <v>57</v>
       </c>
-      <c r="M226" s="1"/>
       <c r="N226" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A227" s="44" t="s">
-        <v>62</v>
-      </c>
-      <c r="B227" s="44"/>
-      <c r="C227" s="44"/>
-      <c r="D227" s="44"/>
-      <c r="E227" s="44"/>
+      <c r="A227" t="s">
+        <v>1</v>
+      </c>
       <c r="F227" t="s">
         <v>20</v>
       </c>
-      <c r="G227" s="44"/>
-      <c r="H227" s="44" t="s">
+      <c r="H227" t="s">
         <v>21</v>
       </c>
-      <c r="I227" s="44"/>
-      <c r="J227" s="44" t="s">
+      <c r="J227" t="s">
         <v>22</v>
       </c>
-      <c r="K227" s="44">
-        <v>15</v>
-      </c>
-      <c r="L227" s="44" t="s">
+      <c r="K227">
+        <v>20</v>
+      </c>
+      <c r="L227" t="s">
         <v>57</v>
       </c>
-      <c r="M227" s="1"/>
       <c r="N227" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="F228" t="s">
-        <v>18</v>
+        <v>185</v>
       </c>
       <c r="H228" t="s">
         <v>21</v>
@@ -6335,7 +6278,7 @@
         <v>22</v>
       </c>
       <c r="K228">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="L228" t="s">
         <v>57</v>
@@ -6345,126 +6288,161 @@
       </c>
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A229" t="s">
-        <v>37</v>
-      </c>
-      <c r="F229" t="s">
+      <c r="A229" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="B229" s="44"/>
+      <c r="C229" s="44"/>
+      <c r="D229" s="44"/>
+      <c r="E229" s="44"/>
+      <c r="F229" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="H229" t="s">
+      <c r="G229" s="44"/>
+      <c r="H229" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="J229" t="s">
+      <c r="I229" s="44"/>
+      <c r="J229" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="K229">
-        <v>10</v>
-      </c>
-      <c r="L229" t="s">
+      <c r="K229" s="44">
+        <v>4</v>
+      </c>
+      <c r="L229" s="44" t="s">
         <v>57</v>
       </c>
+      <c r="M229" s="1"/>
       <c r="N229" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="230" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A230" t="s">
-        <v>37</v>
-      </c>
-      <c r="F230" t="s">
+      <c r="A230" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="B230" s="44"/>
+      <c r="C230" s="44"/>
+      <c r="D230" s="44"/>
+      <c r="E230" s="44"/>
+      <c r="F230" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="H230" t="s">
+      <c r="G230" s="44"/>
+      <c r="H230" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="J230" t="s">
+      <c r="I230" s="44"/>
+      <c r="J230" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="K230">
-        <v>25</v>
-      </c>
-      <c r="L230" t="s">
+      <c r="K230" s="44">
+        <v>15</v>
+      </c>
+      <c r="L230" s="44" t="s">
         <v>57</v>
       </c>
+      <c r="M230" s="1"/>
       <c r="N230" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A231" t="s">
-        <v>37</v>
-      </c>
-      <c r="F231" t="s">
-        <v>185</v>
-      </c>
-      <c r="H231" t="s">
+      <c r="A231" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="B231" s="44"/>
+      <c r="C231" s="44"/>
+      <c r="D231" s="44"/>
+      <c r="E231" s="44"/>
+      <c r="F231" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="G231" s="44"/>
+      <c r="H231" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="J231" t="s">
+      <c r="I231" s="44"/>
+      <c r="J231" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="K231">
-        <v>14</v>
-      </c>
-      <c r="L231" t="s">
+      <c r="K231" s="44">
+        <v>4</v>
+      </c>
+      <c r="L231" s="44" t="s">
         <v>57</v>
       </c>
+      <c r="M231" s="1"/>
       <c r="N231" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A232" t="s">
-        <v>52</v>
-      </c>
+      <c r="A232" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="B232" s="44"/>
+      <c r="C232" s="44"/>
+      <c r="D232" s="44"/>
+      <c r="E232" s="44"/>
       <c r="F232" t="s">
-        <v>18</v>
-      </c>
-      <c r="H232" t="s">
+        <v>19</v>
+      </c>
+      <c r="G232" s="44"/>
+      <c r="H232" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="J232" t="s">
+      <c r="I232" s="44"/>
+      <c r="J232" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="K232">
-        <v>10</v>
-      </c>
-      <c r="L232" t="s">
+      <c r="K232" s="44">
+        <v>4</v>
+      </c>
+      <c r="L232" s="44" t="s">
         <v>57</v>
       </c>
+      <c r="M232" s="1"/>
       <c r="N232" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A233" t="s">
-        <v>52</v>
-      </c>
+      <c r="A233" s="44" t="s">
+        <v>62</v>
+      </c>
+      <c r="B233" s="44"/>
+      <c r="C233" s="44"/>
+      <c r="D233" s="44"/>
+      <c r="E233" s="44"/>
       <c r="F233" t="s">
-        <v>19</v>
-      </c>
-      <c r="H233" t="s">
+        <v>20</v>
+      </c>
+      <c r="G233" s="44"/>
+      <c r="H233" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="J233" t="s">
+      <c r="I233" s="44"/>
+      <c r="J233" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="K233">
-        <v>10</v>
-      </c>
-      <c r="L233" t="s">
+      <c r="K233" s="44">
+        <v>15</v>
+      </c>
+      <c r="L233" s="44" t="s">
         <v>57</v>
       </c>
+      <c r="M233" s="1"/>
       <c r="N233" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="F234" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H234" t="s">
         <v>21</v>
@@ -6473,7 +6451,7 @@
         <v>22</v>
       </c>
       <c r="K234">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="L234" t="s">
         <v>57</v>
@@ -6484,16 +6462,10 @@
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
-        <v>52</v>
-      </c>
-      <c r="C235" t="s">
-        <v>63</v>
-      </c>
-      <c r="D235" t="s">
-        <v>186</v>
+        <v>37</v>
       </c>
       <c r="F235" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H235" t="s">
         <v>21</v>
@@ -6502,7 +6474,7 @@
         <v>22</v>
       </c>
       <c r="K235">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="L235" t="s">
         <v>57</v>
@@ -6513,13 +6485,7 @@
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
-        <v>52</v>
-      </c>
-      <c r="C236" t="s">
-        <v>53</v>
-      </c>
-      <c r="D236" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F236" t="s">
         <v>20</v>
@@ -6531,7 +6497,7 @@
         <v>22</v>
       </c>
       <c r="K236">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="L236" t="s">
         <v>57</v>
@@ -6541,23 +6507,31 @@
       </c>
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A237" s="1"/>
-      <c r="B237" s="1"/>
-      <c r="C237" s="1"/>
-      <c r="D237" s="1"/>
-      <c r="E237" s="1"/>
-      <c r="F237" s="1"/>
-      <c r="G237" s="1"/>
-      <c r="H237" s="1"/>
-      <c r="I237" s="1"/>
-      <c r="J237" s="1"/>
-      <c r="K237" s="1"/>
-      <c r="L237" s="1"/>
-      <c r="M237" s="1"/>
+      <c r="A237" t="s">
+        <v>37</v>
+      </c>
+      <c r="F237" t="s">
+        <v>185</v>
+      </c>
+      <c r="H237" t="s">
+        <v>21</v>
+      </c>
+      <c r="J237" t="s">
+        <v>22</v>
+      </c>
+      <c r="K237">
+        <v>14</v>
+      </c>
+      <c r="L237" t="s">
+        <v>57</v>
+      </c>
+      <c r="N237" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="238" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
-        <v>1</v>
+        <v>52</v>
       </c>
       <c r="F238" t="s">
         <v>18</v>
@@ -6566,27 +6540,21 @@
         <v>21</v>
       </c>
       <c r="J238" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K238">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="L238" t="s">
         <v>57</v>
       </c>
       <c r="N238" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="239" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A239" t="s">
-        <v>1</v>
-      </c>
-      <c r="C239" t="s">
-        <v>2</v>
-      </c>
-      <c r="D239" t="s">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="F239" t="s">
         <v>19</v>
@@ -6595,134 +6563,120 @@
         <v>21</v>
       </c>
       <c r="J239" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K239">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="L239" t="s">
         <v>57</v>
       </c>
       <c r="N239" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="240" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A240" t="s">
-        <v>1</v>
-      </c>
-      <c r="C240" t="s">
-        <v>7</v>
-      </c>
-      <c r="D240" t="s">
-        <v>3</v>
+        <v>52</v>
       </c>
       <c r="F240" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H240" t="s">
         <v>21</v>
       </c>
       <c r="J240" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K240">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="L240" t="s">
         <v>57</v>
       </c>
       <c r="N240" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="241" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A241" t="s">
-        <v>1</v>
+        <v>52</v>
+      </c>
+      <c r="C241" t="s">
+        <v>63</v>
       </c>
       <c r="D241" t="s">
-        <v>9</v>
+        <v>186</v>
       </c>
       <c r="F241" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H241" t="s">
         <v>21</v>
       </c>
       <c r="J241" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K241">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="L241" t="s">
         <v>57</v>
       </c>
       <c r="N241" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="242" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A242" t="s">
-        <v>1</v>
+        <v>52</v>
+      </c>
+      <c r="C242" t="s">
+        <v>53</v>
       </c>
       <c r="D242" t="s">
-        <v>10</v>
+        <v>54</v>
       </c>
       <c r="F242" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H242" t="s">
         <v>21</v>
       </c>
       <c r="J242" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K242">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="L242" t="s">
         <v>57</v>
       </c>
       <c r="N242" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
     </row>
     <row r="243" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A243" t="s">
-        <v>1</v>
-      </c>
-      <c r="D243" t="s">
-        <v>11</v>
-      </c>
-      <c r="F243" t="s">
-        <v>19</v>
-      </c>
-      <c r="H243" t="s">
-        <v>21</v>
-      </c>
-      <c r="J243" t="s">
-        <v>23</v>
-      </c>
-      <c r="K243">
-        <v>17</v>
-      </c>
-      <c r="L243" t="s">
-        <v>57</v>
-      </c>
-      <c r="N243" t="s">
-        <v>183</v>
-      </c>
+      <c r="A243" s="1"/>
+      <c r="B243" s="1"/>
+      <c r="C243" s="1"/>
+      <c r="D243" s="1"/>
+      <c r="E243" s="1"/>
+      <c r="F243" s="1"/>
+      <c r="G243" s="1"/>
+      <c r="H243" s="1"/>
+      <c r="I243" s="1"/>
+      <c r="J243" s="1"/>
+      <c r="K243" s="1"/>
+      <c r="L243" s="1"/>
+      <c r="M243" s="1"/>
     </row>
     <row r="244" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>1</v>
       </c>
-      <c r="D244" t="s">
-        <v>12</v>
-      </c>
       <c r="F244" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H244" t="s">
         <v>21</v>
@@ -6731,7 +6685,7 @@
         <v>23</v>
       </c>
       <c r="K244">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="L244" t="s">
         <v>57</v>
@@ -6744,8 +6698,11 @@
       <c r="A245" t="s">
         <v>1</v>
       </c>
+      <c r="C245" t="s">
+        <v>2</v>
+      </c>
       <c r="D245" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F245" t="s">
         <v>19</v>
@@ -6757,14 +6714,11 @@
         <v>23</v>
       </c>
       <c r="K245">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L245" t="s">
         <v>57</v>
       </c>
-      <c r="M245" t="s">
-        <v>14</v>
-      </c>
       <c r="N245" t="s">
         <v>183</v>
       </c>
@@ -6773,8 +6727,14 @@
       <c r="A246" t="s">
         <v>1</v>
       </c>
+      <c r="C246" t="s">
+        <v>7</v>
+      </c>
+      <c r="D246" t="s">
+        <v>3</v>
+      </c>
       <c r="F246" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H246" t="s">
         <v>21</v>
@@ -6783,7 +6743,7 @@
         <v>23</v>
       </c>
       <c r="K246">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="L246" t="s">
         <v>57</v>
@@ -6796,8 +6756,11 @@
       <c r="A247" t="s">
         <v>1</v>
       </c>
+      <c r="D247" t="s">
+        <v>9</v>
+      </c>
       <c r="F247" t="s">
-        <v>185</v>
+        <v>19</v>
       </c>
       <c r="H247" t="s">
         <v>21</v>
@@ -6806,7 +6769,7 @@
         <v>23</v>
       </c>
       <c r="K247">
-        <v>2.75</v>
+        <v>18</v>
       </c>
       <c r="L247" t="s">
         <v>57</v>
@@ -6816,101 +6779,92 @@
       </c>
     </row>
     <row r="248" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A248" s="44" t="s">
-        <v>56</v>
-      </c>
-      <c r="B248" s="44"/>
-      <c r="C248" s="44"/>
-      <c r="D248" s="44"/>
-      <c r="E248" s="44"/>
-      <c r="F248" s="44" t="s">
+      <c r="A248" t="s">
+        <v>1</v>
+      </c>
+      <c r="D248" t="s">
+        <v>10</v>
+      </c>
+      <c r="F248" t="s">
         <v>19</v>
       </c>
-      <c r="G248" s="44"/>
-      <c r="H248" s="44" t="s">
+      <c r="H248" t="s">
         <v>21</v>
       </c>
-      <c r="I248" s="44"/>
-      <c r="J248" s="44" t="s">
+      <c r="J248" t="s">
         <v>23</v>
       </c>
-      <c r="K248" s="44">
-        <v>25</v>
-      </c>
-      <c r="L248" s="44" t="s">
+      <c r="K248">
+        <v>18</v>
+      </c>
+      <c r="L248" t="s">
         <v>57</v>
       </c>
-      <c r="M248" s="1"/>
       <c r="N248" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="249" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A249" s="44" t="s">
-        <v>56</v>
-      </c>
-      <c r="B249" s="44"/>
-      <c r="C249" s="44"/>
-      <c r="D249" s="44"/>
-      <c r="E249" s="44"/>
-      <c r="F249" s="44" t="s">
-        <v>20</v>
-      </c>
-      <c r="G249" s="44"/>
-      <c r="H249" s="44" t="s">
+      <c r="A249" t="s">
+        <v>1</v>
+      </c>
+      <c r="D249" t="s">
+        <v>11</v>
+      </c>
+      <c r="F249" t="s">
+        <v>19</v>
+      </c>
+      <c r="H249" t="s">
         <v>21</v>
       </c>
-      <c r="I249" s="44"/>
-      <c r="J249" s="44" t="s">
+      <c r="J249" t="s">
         <v>23</v>
       </c>
-      <c r="K249" s="44">
-        <v>33</v>
-      </c>
-      <c r="L249" s="44" t="s">
+      <c r="K249">
+        <v>17</v>
+      </c>
+      <c r="L249" t="s">
         <v>57</v>
       </c>
-      <c r="M249" s="1"/>
       <c r="N249" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="250" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A250" s="44" t="s">
-        <v>56</v>
-      </c>
-      <c r="B250" s="44"/>
-      <c r="C250" s="44"/>
-      <c r="D250" s="44"/>
-      <c r="E250" s="44"/>
-      <c r="F250" s="44" t="s">
-        <v>177</v>
-      </c>
-      <c r="G250" s="44"/>
-      <c r="H250" s="44" t="s">
+      <c r="A250" t="s">
+        <v>1</v>
+      </c>
+      <c r="D250" t="s">
+        <v>12</v>
+      </c>
+      <c r="F250" t="s">
+        <v>19</v>
+      </c>
+      <c r="H250" t="s">
         <v>21</v>
       </c>
-      <c r="I250" s="44"/>
-      <c r="J250" s="44" t="s">
+      <c r="J250" t="s">
         <v>23</v>
       </c>
-      <c r="K250" s="44">
-        <v>0.25</v>
-      </c>
-      <c r="L250" s="44" t="s">
+      <c r="K250">
+        <v>17</v>
+      </c>
+      <c r="L250" t="s">
         <v>57</v>
       </c>
-      <c r="M250" s="1"/>
       <c r="N250" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="251" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
-        <v>37</v>
+        <v>1</v>
+      </c>
+      <c r="D251" t="s">
+        <v>13</v>
       </c>
       <c r="F251" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H251" t="s">
         <v>21</v>
@@ -6919,21 +6873,24 @@
         <v>23</v>
       </c>
       <c r="K251">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="L251" t="s">
         <v>57</v>
       </c>
+      <c r="M251" t="s">
+        <v>14</v>
+      </c>
       <c r="N251" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="252" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A252" t="s">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="F252" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="H252" t="s">
         <v>21</v>
@@ -6942,7 +6899,7 @@
         <v>23</v>
       </c>
       <c r="K252">
-        <v>18</v>
+        <v>30</v>
       </c>
       <c r="L252" t="s">
         <v>57</v>
@@ -6953,10 +6910,10 @@
     </row>
     <row r="253" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
-        <v>37</v>
+        <v>1</v>
       </c>
       <c r="F253" t="s">
-        <v>20</v>
+        <v>185</v>
       </c>
       <c r="H253" t="s">
         <v>21</v>
@@ -6965,7 +6922,7 @@
         <v>23</v>
       </c>
       <c r="K253">
-        <v>30</v>
+        <v>2.75</v>
       </c>
       <c r="L253" t="s">
         <v>57</v>
@@ -6975,80 +6932,101 @@
       </c>
     </row>
     <row r="254" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A254" t="s">
-        <v>37</v>
-      </c>
-      <c r="F254" t="s">
-        <v>185</v>
-      </c>
-      <c r="H254" t="s">
+      <c r="A254" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="B254" s="44"/>
+      <c r="C254" s="44"/>
+      <c r="D254" s="44"/>
+      <c r="E254" s="44"/>
+      <c r="F254" s="44" t="s">
+        <v>19</v>
+      </c>
+      <c r="G254" s="44"/>
+      <c r="H254" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="J254" t="s">
+      <c r="I254" s="44"/>
+      <c r="J254" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="K254">
-        <v>2.75</v>
-      </c>
-      <c r="L254" t="s">
+      <c r="K254" s="44">
+        <v>25</v>
+      </c>
+      <c r="L254" s="44" t="s">
         <v>57</v>
       </c>
+      <c r="M254" s="1"/>
       <c r="N254" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="255" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A255" t="s">
-        <v>52</v>
-      </c>
-      <c r="F255" t="s">
-        <v>18</v>
-      </c>
-      <c r="H255" t="s">
+      <c r="A255" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="B255" s="44"/>
+      <c r="C255" s="44"/>
+      <c r="D255" s="44"/>
+      <c r="E255" s="44"/>
+      <c r="F255" s="44" t="s">
+        <v>20</v>
+      </c>
+      <c r="G255" s="44"/>
+      <c r="H255" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="J255" t="s">
+      <c r="I255" s="44"/>
+      <c r="J255" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="K255">
-        <v>4</v>
-      </c>
-      <c r="L255" t="s">
+      <c r="K255" s="44">
+        <v>33</v>
+      </c>
+      <c r="L255" s="44" t="s">
         <v>57</v>
       </c>
+      <c r="M255" s="1"/>
       <c r="N255" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="256" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A256" t="s">
-        <v>52</v>
-      </c>
-      <c r="F256" t="s">
-        <v>19</v>
-      </c>
-      <c r="H256" t="s">
+      <c r="A256" s="44" t="s">
+        <v>56</v>
+      </c>
+      <c r="B256" s="44"/>
+      <c r="C256" s="44"/>
+      <c r="D256" s="44"/>
+      <c r="E256" s="44"/>
+      <c r="F256" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="G256" s="44"/>
+      <c r="H256" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="J256" t="s">
+      <c r="I256" s="44"/>
+      <c r="J256" s="44" t="s">
         <v>23</v>
       </c>
-      <c r="K256">
-        <v>12</v>
-      </c>
-      <c r="L256" t="s">
+      <c r="K256" s="44">
+        <v>0.25</v>
+      </c>
+      <c r="L256" s="44" t="s">
         <v>57</v>
       </c>
+      <c r="M256" s="1"/>
       <c r="N256" t="s">
         <v>183</v>
       </c>
     </row>
     <row r="257" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
-        <v>52</v>
+        <v>37</v>
       </c>
       <c r="F257" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="H257" t="s">
         <v>21</v>
@@ -7057,7 +7035,7 @@
         <v>23</v>
       </c>
       <c r="K257">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="L257" t="s">
         <v>57</v>
@@ -7068,13 +7046,7 @@
     </row>
     <row r="258" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
-        <v>52</v>
-      </c>
-      <c r="C258" t="s">
-        <v>53</v>
-      </c>
-      <c r="D258" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F258" t="s">
         <v>19</v>
@@ -7086,7 +7058,7 @@
         <v>23</v>
       </c>
       <c r="K258">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="L258" t="s">
         <v>57</v>
@@ -7097,13 +7069,7 @@
     </row>
     <row r="259" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
-        <v>52</v>
-      </c>
-      <c r="C259" t="s">
-        <v>53</v>
-      </c>
-      <c r="D259" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="F259" t="s">
         <v>20</v>
@@ -7115,7 +7081,7 @@
         <v>23</v>
       </c>
       <c r="K259">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="L259" t="s">
         <v>57</v>
@@ -7124,132 +7090,182 @@
         <v>183</v>
       </c>
     </row>
+    <row r="260" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A260" t="s">
+        <v>37</v>
+      </c>
+      <c r="F260" t="s">
+        <v>185</v>
+      </c>
+      <c r="H260" t="s">
+        <v>21</v>
+      </c>
+      <c r="J260" t="s">
+        <v>23</v>
+      </c>
+      <c r="K260">
+        <v>2.75</v>
+      </c>
+      <c r="L260" t="s">
+        <v>57</v>
+      </c>
+      <c r="N260" t="s">
+        <v>183</v>
+      </c>
+    </row>
     <row r="261" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
+        <v>52</v>
+      </c>
       <c r="F261" t="s">
         <v>18</v>
       </c>
       <c r="H261" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J261" t="s">
         <v>23</v>
       </c>
       <c r="K261">
-        <v>0.01</v>
+        <v>4</v>
       </c>
       <c r="L261" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N261" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
     </row>
     <row r="262" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A262" t="s">
+        <v>52</v>
+      </c>
       <c r="F262" t="s">
         <v>19</v>
       </c>
       <c r="H262" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J262" t="s">
         <v>23</v>
       </c>
       <c r="K262">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="L262" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N262" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
     </row>
     <row r="263" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A263" t="s">
+        <v>52</v>
+      </c>
       <c r="F263" t="s">
         <v>20</v>
       </c>
       <c r="H263" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J263" t="s">
         <v>23</v>
       </c>
       <c r="K263">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="L263" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N263" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
     </row>
     <row r="264" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A264" t="s">
+        <v>52</v>
+      </c>
+      <c r="C264" t="s">
+        <v>53</v>
+      </c>
+      <c r="D264" t="s">
+        <v>54</v>
+      </c>
       <c r="F264" t="s">
-        <v>177</v>
+        <v>19</v>
       </c>
       <c r="H264" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="J264" t="s">
         <v>23</v>
       </c>
       <c r="K264">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L264" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="N264" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="266" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F266" t="s">
-        <v>18</v>
-      </c>
-      <c r="H266" t="s">
-        <v>25</v>
-      </c>
-      <c r="J266" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="265" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
+        <v>52</v>
+      </c>
+      <c r="C265" t="s">
+        <v>53</v>
+      </c>
+      <c r="D265" t="s">
+        <v>54</v>
+      </c>
+      <c r="F265" t="s">
+        <v>20</v>
+      </c>
+      <c r="H265" t="s">
+        <v>21</v>
+      </c>
+      <c r="J265" t="s">
         <v>23</v>
       </c>
-      <c r="K266">
-        <v>0.5</v>
-      </c>
-      <c r="L266" t="s">
+      <c r="K265">
+        <v>5</v>
+      </c>
+      <c r="L265" t="s">
         <v>57</v>
       </c>
-      <c r="N266" t="s">
-        <v>190</v>
+      <c r="N265" t="s">
+        <v>183</v>
       </c>
     </row>
     <row r="267" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F267" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H267" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J267" t="s">
         <v>23</v>
       </c>
       <c r="K267">
-        <v>0.5</v>
+        <v>0.01</v>
       </c>
       <c r="L267" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N267" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="268" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F268" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H268" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J268" t="s">
         <v>23</v>
@@ -7258,38 +7274,38 @@
         <v>1</v>
       </c>
       <c r="L268" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N268" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="269" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F269" t="s">
-        <v>185</v>
+        <v>20</v>
       </c>
       <c r="H269" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J269" t="s">
         <v>23</v>
       </c>
       <c r="K269">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L269" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N269" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="270" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F270" s="44" t="s">
+      <c r="F270" t="s">
         <v>177</v>
       </c>
       <c r="H270" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J270" t="s">
         <v>23</v>
@@ -7298,10 +7314,10 @@
         <v>1</v>
       </c>
       <c r="L270" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N270" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="272" spans="1:14" x14ac:dyDescent="0.25">
@@ -7309,22 +7325,19 @@
         <v>18</v>
       </c>
       <c r="H272" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J272" t="s">
         <v>23</v>
       </c>
       <c r="K272">
-        <v>0.31</v>
+        <v>0.5</v>
       </c>
       <c r="L272" t="s">
-        <v>58</v>
-      </c>
-      <c r="M272" t="s">
-        <v>189</v>
+        <v>57</v>
       </c>
       <c r="N272" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="273" spans="1:14" x14ac:dyDescent="0.25">
@@ -7332,22 +7345,19 @@
         <v>19</v>
       </c>
       <c r="H273" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J273" t="s">
         <v>23</v>
       </c>
       <c r="K273">
-        <v>31</v>
+        <v>0.5</v>
       </c>
       <c r="L273" t="s">
-        <v>58</v>
-      </c>
-      <c r="M273" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="N273" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="274" spans="1:14" x14ac:dyDescent="0.25">
@@ -7355,203 +7365,165 @@
         <v>20</v>
       </c>
       <c r="H274" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J274" t="s">
         <v>23</v>
       </c>
       <c r="K274">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="L274" t="s">
-        <v>58</v>
-      </c>
-      <c r="M274" t="s">
-        <v>19</v>
+        <v>57</v>
       </c>
       <c r="N274" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="275" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F275" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="H275" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="J275" t="s">
         <v>23</v>
       </c>
       <c r="K275">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="L275" t="s">
+        <v>57</v>
+      </c>
+      <c r="N275" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="276" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F276" s="44" t="s">
+        <v>177</v>
+      </c>
+      <c r="H276" t="s">
+        <v>25</v>
+      </c>
+      <c r="J276" t="s">
+        <v>23</v>
+      </c>
+      <c r="K276">
+        <v>1</v>
+      </c>
+      <c r="L276" t="s">
+        <v>57</v>
+      </c>
+      <c r="N276" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="278" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F278" t="s">
+        <v>18</v>
+      </c>
+      <c r="H278" t="s">
+        <v>26</v>
+      </c>
+      <c r="J278" t="s">
+        <v>23</v>
+      </c>
+      <c r="K278">
+        <v>0.31</v>
+      </c>
+      <c r="L278" t="s">
         <v>58</v>
       </c>
-      <c r="M275" t="s">
-        <v>19</v>
-      </c>
-      <c r="N275" t="s">
+      <c r="M278" t="s">
+        <v>189</v>
+      </c>
+      <c r="N278" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="277" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A277" t="s">
-        <v>1</v>
-      </c>
-      <c r="F277" t="s">
-        <v>18</v>
-      </c>
-      <c r="J277" t="s">
-        <v>27</v>
-      </c>
-      <c r="K277">
-        <v>60</v>
-      </c>
-      <c r="L277" t="s">
-        <v>57</v>
-      </c>
-      <c r="N277" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="278" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A278" t="s">
-        <v>1</v>
-      </c>
-      <c r="C278" t="s">
-        <v>2</v>
-      </c>
-      <c r="D278" t="s">
-        <v>3</v>
-      </c>
-      <c r="F278" t="s">
-        <v>19</v>
-      </c>
-      <c r="J278" t="s">
-        <v>27</v>
-      </c>
-      <c r="K278">
-        <v>51</v>
-      </c>
-      <c r="L278" t="s">
-        <v>57</v>
-      </c>
-      <c r="N278" t="s">
-        <v>193</v>
-      </c>
-    </row>
     <row r="279" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A279" t="s">
-        <v>1</v>
-      </c>
-      <c r="C279" t="s">
-        <v>7</v>
-      </c>
-      <c r="D279" t="s">
-        <v>3</v>
-      </c>
       <c r="F279" t="s">
         <v>19</v>
       </c>
+      <c r="H279" t="s">
+        <v>26</v>
+      </c>
       <c r="J279" t="s">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="K279">
-        <v>52</v>
+        <v>31</v>
       </c>
       <c r="L279" t="s">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="M279" t="s">
+        <v>19</v>
       </c>
       <c r="N279" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
     </row>
     <row r="280" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A280" t="s">
-        <v>1</v>
-      </c>
-      <c r="D280" t="s">
-        <v>9</v>
-      </c>
       <c r="F280" t="s">
+        <v>20</v>
+      </c>
+      <c r="H280" t="s">
+        <v>26</v>
+      </c>
+      <c r="J280" t="s">
+        <v>23</v>
+      </c>
+      <c r="K280">
+        <v>31</v>
+      </c>
+      <c r="L280" t="s">
+        <v>58</v>
+      </c>
+      <c r="M280" t="s">
         <v>19</v>
       </c>
-      <c r="J280" t="s">
-        <v>27</v>
-      </c>
-      <c r="K280">
-        <v>51</v>
-      </c>
-      <c r="L280" t="s">
-        <v>57</v>
-      </c>
       <c r="N280" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
     </row>
     <row r="281" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A281" t="s">
-        <v>1</v>
-      </c>
-      <c r="D281" t="s">
-        <v>10</v>
-      </c>
       <c r="F281" t="s">
+        <v>177</v>
+      </c>
+      <c r="H281" t="s">
+        <v>26</v>
+      </c>
+      <c r="J281" t="s">
+        <v>23</v>
+      </c>
+      <c r="K281">
+        <v>31</v>
+      </c>
+      <c r="L281" t="s">
+        <v>58</v>
+      </c>
+      <c r="M281" t="s">
         <v>19</v>
       </c>
-      <c r="J281" t="s">
-        <v>27</v>
-      </c>
-      <c r="K281">
-        <v>51</v>
-      </c>
-      <c r="L281" t="s">
-        <v>57</v>
-      </c>
       <c r="N281" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="282" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A282" t="s">
-        <v>1</v>
-      </c>
-      <c r="D282" t="s">
-        <v>11</v>
-      </c>
-      <c r="F282" t="s">
-        <v>19</v>
-      </c>
-      <c r="J282" t="s">
-        <v>27</v>
-      </c>
-      <c r="K282">
-        <v>52</v>
-      </c>
-      <c r="L282" t="s">
-        <v>57</v>
-      </c>
-      <c r="N282" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
     </row>
     <row r="283" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>1</v>
       </c>
-      <c r="D283" t="s">
-        <v>12</v>
-      </c>
       <c r="F283" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J283" t="s">
         <v>27</v>
       </c>
       <c r="K283">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="L283" t="s">
         <v>57</v>
@@ -7564,8 +7536,11 @@
       <c r="A284" t="s">
         <v>1</v>
       </c>
+      <c r="C284" t="s">
+        <v>2</v>
+      </c>
       <c r="D284" t="s">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="F284" t="s">
         <v>19</v>
@@ -7574,27 +7549,33 @@
         <v>27</v>
       </c>
       <c r="K284">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="L284" t="s">
         <v>57</v>
       </c>
-      <c r="M284" t="s">
-        <v>14</v>
+      <c r="N284" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="285" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>1</v>
       </c>
+      <c r="C285" t="s">
+        <v>7</v>
+      </c>
+      <c r="D285" t="s">
+        <v>3</v>
+      </c>
       <c r="F285" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="J285" t="s">
         <v>27</v>
       </c>
       <c r="K285">
-        <v>10</v>
+        <v>52</v>
       </c>
       <c r="L285" t="s">
         <v>57</v>
@@ -7607,14 +7588,17 @@
       <c r="A286" t="s">
         <v>1</v>
       </c>
+      <c r="D286" t="s">
+        <v>9</v>
+      </c>
       <c r="F286" t="s">
-        <v>185</v>
+        <v>19</v>
       </c>
       <c r="J286" t="s">
         <v>27</v>
       </c>
       <c r="K286">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="L286" t="s">
         <v>57</v>
@@ -7624,179 +7608,143 @@
       </c>
     </row>
     <row r="287" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A287" s="44" t="s">
-        <v>1</v>
-      </c>
-      <c r="F287" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="G287" s="5"/>
-      <c r="H287" s="5"/>
-      <c r="I287" s="5"/>
-      <c r="J287" s="5" t="s">
+      <c r="A287" t="s">
+        <v>1</v>
+      </c>
+      <c r="D287" t="s">
+        <v>10</v>
+      </c>
+      <c r="F287" t="s">
+        <v>19</v>
+      </c>
+      <c r="J287" t="s">
         <v>27</v>
       </c>
-      <c r="K287" s="5">
-        <v>60</v>
-      </c>
-      <c r="L287" s="5" t="s">
+      <c r="K287">
+        <v>51</v>
+      </c>
+      <c r="L287" t="s">
         <v>57</v>
       </c>
-      <c r="M287" s="1"/>
       <c r="N287" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="288" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A288" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B288" s="5"/>
-      <c r="C288" s="5"/>
-      <c r="D288" s="5"/>
-      <c r="E288" s="5"/>
-      <c r="F288" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G288" s="5"/>
-      <c r="H288" s="5"/>
-      <c r="I288" s="5"/>
-      <c r="J288" s="5" t="s">
+      <c r="A288" t="s">
+        <v>1</v>
+      </c>
+      <c r="D288" t="s">
+        <v>11</v>
+      </c>
+      <c r="F288" t="s">
+        <v>19</v>
+      </c>
+      <c r="J288" t="s">
         <v>27</v>
       </c>
-      <c r="K288" s="5">
-        <v>24</v>
+      <c r="K288">
+        <v>52</v>
       </c>
       <c r="L288" t="s">
         <v>57</v>
       </c>
-      <c r="M288" s="1"/>
       <c r="N288" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="289" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A289" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B289" s="5"/>
-      <c r="C289" s="5"/>
-      <c r="D289" s="5"/>
-      <c r="E289" s="5"/>
-      <c r="F289" s="5" t="s">
+      <c r="A289" t="s">
+        <v>1</v>
+      </c>
+      <c r="D289" t="s">
+        <v>12</v>
+      </c>
+      <c r="F289" t="s">
         <v>19</v>
       </c>
-      <c r="G289" s="5"/>
-      <c r="H289" s="5"/>
-      <c r="I289" s="5"/>
-      <c r="J289" s="5" t="s">
+      <c r="J289" t="s">
         <v>27</v>
       </c>
-      <c r="K289" s="5">
-        <v>25</v>
+      <c r="K289">
+        <v>52</v>
       </c>
       <c r="L289" t="s">
         <v>57</v>
       </c>
-      <c r="M289" s="1"/>
       <c r="N289" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="290" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A290" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B290" s="5"/>
-      <c r="C290" s="5"/>
-      <c r="D290" s="5"/>
-      <c r="E290" s="5"/>
-      <c r="F290" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G290" s="5"/>
-      <c r="H290" s="5"/>
-      <c r="I290" s="5"/>
-      <c r="J290" s="5" t="s">
+      <c r="A290" t="s">
+        <v>1</v>
+      </c>
+      <c r="D290" t="s">
+        <v>13</v>
+      </c>
+      <c r="F290" t="s">
+        <v>19</v>
+      </c>
+      <c r="J290" t="s">
         <v>27</v>
       </c>
-      <c r="K290" s="5">
-        <v>10</v>
+      <c r="K290">
+        <v>52</v>
       </c>
       <c r="L290" t="s">
         <v>57</v>
       </c>
-      <c r="M290" s="1"/>
-      <c r="N290" t="s">
-        <v>193</v>
+      <c r="M290" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="291" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A291" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B291" s="5"/>
-      <c r="C291" s="5"/>
-      <c r="D291" s="5"/>
-      <c r="E291" s="5"/>
-      <c r="F291" s="5" t="s">
-        <v>177</v>
-      </c>
-      <c r="G291" s="5"/>
-      <c r="H291" s="5"/>
-      <c r="I291" s="5"/>
-      <c r="J291" s="5" t="s">
+      <c r="A291" t="s">
+        <v>1</v>
+      </c>
+      <c r="F291" t="s">
+        <v>20</v>
+      </c>
+      <c r="J291" t="s">
         <v>27</v>
       </c>
-      <c r="K291" s="5">
-        <v>25</v>
+      <c r="K291">
+        <v>10</v>
       </c>
       <c r="L291" t="s">
         <v>57</v>
       </c>
-      <c r="M291" s="1"/>
       <c r="N291" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="292" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A292" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="B292" s="5"/>
-      <c r="C292" s="5"/>
-      <c r="D292" s="5"/>
-      <c r="E292" s="5"/>
-      <c r="F292" s="5" t="s">
+      <c r="A292" t="s">
+        <v>1</v>
+      </c>
+      <c r="F292" t="s">
+        <v>185</v>
+      </c>
+      <c r="J292" t="s">
+        <v>27</v>
+      </c>
+      <c r="K292">
+        <v>60</v>
+      </c>
+      <c r="L292" t="s">
+        <v>57</v>
+      </c>
+      <c r="N292" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="293" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A293" s="44" t="s">
+        <v>1</v>
+      </c>
+      <c r="F293" s="5" t="s">
         <v>15</v>
-      </c>
-      <c r="G292" s="5"/>
-      <c r="H292" s="5"/>
-      <c r="I292" s="5"/>
-      <c r="J292" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="K292" s="5">
-        <v>60</v>
-      </c>
-      <c r="L292" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="M292" s="1"/>
-      <c r="N292" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="293" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A293" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="B293" s="5"/>
-      <c r="C293" s="5"/>
-      <c r="D293" s="5"/>
-      <c r="E293" s="5"/>
-      <c r="F293" s="5" t="s">
-        <v>18</v>
       </c>
       <c r="G293" s="5"/>
       <c r="H293" s="5"/>
@@ -7805,26 +7753,26 @@
         <v>27</v>
       </c>
       <c r="K293" s="5">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="L293" s="5" t="s">
         <v>57</v>
       </c>
       <c r="M293" s="1"/>
       <c r="N293" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="294" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A294" s="5" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B294" s="5"/>
       <c r="C294" s="5"/>
       <c r="D294" s="5"/>
       <c r="E294" s="5"/>
       <c r="F294" s="5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G294" s="5"/>
       <c r="H294" s="5"/>
@@ -7833,9 +7781,9 @@
         <v>27</v>
       </c>
       <c r="K294" s="5">
-        <v>25</v>
-      </c>
-      <c r="L294" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L294" t="s">
         <v>57</v>
       </c>
       <c r="M294" s="1"/>
@@ -7845,14 +7793,14 @@
     </row>
     <row r="295" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A295" s="5" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B295" s="5"/>
       <c r="C295" s="5"/>
       <c r="D295" s="5"/>
       <c r="E295" s="5"/>
       <c r="F295" s="5" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="G295" s="5"/>
       <c r="H295" s="5"/>
@@ -7861,106 +7809,138 @@
         <v>27</v>
       </c>
       <c r="K295" s="5">
-        <v>50</v>
-      </c>
-      <c r="L295" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="L295" t="s">
         <v>57</v>
       </c>
       <c r="M295" s="1"/>
       <c r="N295" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
     </row>
     <row r="296" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A296" t="s">
-        <v>37</v>
-      </c>
-      <c r="F296" t="s">
-        <v>18</v>
-      </c>
-      <c r="J296" t="s">
+      <c r="A296" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B296" s="5"/>
+      <c r="C296" s="5"/>
+      <c r="D296" s="5"/>
+      <c r="E296" s="5"/>
+      <c r="F296" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G296" s="5"/>
+      <c r="H296" s="5"/>
+      <c r="I296" s="5"/>
+      <c r="J296" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="K296">
-        <v>70</v>
+      <c r="K296" s="5">
+        <v>10</v>
       </c>
       <c r="L296" t="s">
         <v>57</v>
       </c>
+      <c r="M296" s="1"/>
       <c r="N296" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="297" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A297" t="s">
-        <v>37</v>
-      </c>
-      <c r="F297" t="s">
-        <v>19</v>
-      </c>
-      <c r="J297" t="s">
+      <c r="A297" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B297" s="5"/>
+      <c r="C297" s="5"/>
+      <c r="D297" s="5"/>
+      <c r="E297" s="5"/>
+      <c r="F297" s="5" t="s">
+        <v>177</v>
+      </c>
+      <c r="G297" s="5"/>
+      <c r="H297" s="5"/>
+      <c r="I297" s="5"/>
+      <c r="J297" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="K297">
-        <v>51</v>
+      <c r="K297" s="5">
+        <v>25</v>
       </c>
       <c r="L297" t="s">
         <v>57</v>
       </c>
+      <c r="M297" s="1"/>
       <c r="N297" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="298" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A298" t="s">
-        <v>37</v>
-      </c>
-      <c r="F298" t="s">
-        <v>20</v>
-      </c>
-      <c r="J298" t="s">
+      <c r="A298" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="B298" s="5"/>
+      <c r="C298" s="5"/>
+      <c r="D298" s="5"/>
+      <c r="E298" s="5"/>
+      <c r="F298" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="G298" s="5"/>
+      <c r="H298" s="5"/>
+      <c r="I298" s="5"/>
+      <c r="J298" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="K298">
-        <v>10</v>
-      </c>
-      <c r="L298" t="s">
+      <c r="K298" s="5">
+        <v>60</v>
+      </c>
+      <c r="L298" s="5" t="s">
         <v>57</v>
       </c>
+      <c r="M298" s="1"/>
       <c r="N298" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="299" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A299" t="s">
-        <v>37</v>
-      </c>
-      <c r="F299" t="s">
-        <v>185</v>
-      </c>
-      <c r="J299" t="s">
+      <c r="A299" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="B299" s="5"/>
+      <c r="C299" s="5"/>
+      <c r="D299" s="5"/>
+      <c r="E299" s="5"/>
+      <c r="F299" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G299" s="5"/>
+      <c r="H299" s="5"/>
+      <c r="I299" s="5"/>
+      <c r="J299" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="K299">
-        <v>70</v>
-      </c>
-      <c r="L299" t="s">
+      <c r="K299" s="5">
+        <v>25</v>
+      </c>
+      <c r="L299" s="5" t="s">
         <v>57</v>
       </c>
+      <c r="M299" s="1"/>
       <c r="N299" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="300" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A300" s="5" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B300" s="5"/>
       <c r="C300" s="5"/>
       <c r="D300" s="5"/>
       <c r="E300" s="5"/>
       <c r="F300" s="5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G300" s="5"/>
       <c r="H300" s="5"/>
@@ -7969,7 +7949,7 @@
         <v>27</v>
       </c>
       <c r="K300" s="5">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="L300" s="5" t="s">
         <v>57</v>
@@ -7981,14 +7961,14 @@
     </row>
     <row r="301" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A301" s="5" t="s">
-        <v>52</v>
+        <v>62</v>
       </c>
       <c r="B301" s="5"/>
       <c r="C301" s="5"/>
       <c r="D301" s="5"/>
       <c r="E301" s="5"/>
       <c r="F301" s="5" t="s">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G301" s="5"/>
       <c r="H301" s="5"/>
@@ -7997,64 +7977,50 @@
         <v>27</v>
       </c>
       <c r="K301" s="5">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="L301" s="5" t="s">
         <v>57</v>
       </c>
       <c r="M301" s="1"/>
       <c r="N301" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="302" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A302" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B302" s="5"/>
-      <c r="C302" s="5"/>
-      <c r="D302" s="5"/>
-      <c r="E302" s="5"/>
-      <c r="F302" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G302" s="5"/>
-      <c r="H302" s="5"/>
-      <c r="I302" s="5"/>
-      <c r="J302" s="5" t="s">
+      <c r="A302" t="s">
+        <v>37</v>
+      </c>
+      <c r="F302" t="s">
+        <v>18</v>
+      </c>
+      <c r="J302" t="s">
         <v>27</v>
       </c>
-      <c r="K302" s="5">
-        <v>40</v>
-      </c>
-      <c r="L302" s="5" t="s">
+      <c r="K302">
+        <v>70</v>
+      </c>
+      <c r="L302" t="s">
         <v>57</v>
       </c>
-      <c r="M302" s="1"/>
       <c r="N302" t="s">
         <v>193</v>
       </c>
     </row>
     <row r="303" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
-        <v>52</v>
-      </c>
-      <c r="C303" t="s">
-        <v>53</v>
-      </c>
-      <c r="D303" t="s">
-        <v>54</v>
-      </c>
-      <c r="F303" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="J303" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F303" t="s">
+        <v>19</v>
+      </c>
+      <c r="J303" t="s">
         <v>27</v>
       </c>
       <c r="K303">
-        <v>40</v>
-      </c>
-      <c r="L303" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="L303" t="s">
         <v>57</v>
       </c>
       <c r="N303" t="s">
@@ -8063,24 +8029,18 @@
     </row>
     <row r="304" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
-        <v>52</v>
-      </c>
-      <c r="C304" t="s">
-        <v>53</v>
-      </c>
-      <c r="D304" t="s">
-        <v>54</v>
-      </c>
-      <c r="F304" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="J304" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F304" t="s">
+        <v>20</v>
+      </c>
+      <c r="J304" t="s">
         <v>27</v>
       </c>
-      <c r="K304" s="5">
-        <v>40</v>
-      </c>
-      <c r="L304" s="5" t="s">
+      <c r="K304">
+        <v>10</v>
+      </c>
+      <c r="L304" t="s">
         <v>57</v>
       </c>
       <c r="N304" t="s">
@@ -8089,32 +8049,188 @@
     </row>
     <row r="305" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A305" t="s">
-        <v>52</v>
-      </c>
-      <c r="C305" t="s">
-        <v>53</v>
-      </c>
-      <c r="D305" t="s">
-        <v>54</v>
-      </c>
-      <c r="F305" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="J305" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="F305" t="s">
+        <v>185</v>
+      </c>
+      <c r="J305" t="s">
         <v>27</v>
       </c>
-      <c r="K305" s="5">
-        <v>40</v>
-      </c>
-      <c r="L305" s="5" t="s">
+      <c r="K305">
+        <v>70</v>
+      </c>
+      <c r="L305" t="s">
         <v>57</v>
       </c>
       <c r="N305" t="s">
         <v>193</v>
       </c>
     </row>
+    <row r="306" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A306" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B306" s="5"/>
+      <c r="C306" s="5"/>
+      <c r="D306" s="5"/>
+      <c r="E306" s="5"/>
+      <c r="F306" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G306" s="5"/>
+      <c r="H306" s="5"/>
+      <c r="I306" s="5"/>
+      <c r="J306" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K306" s="5">
+        <v>75</v>
+      </c>
+      <c r="L306" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="M306" s="1"/>
+      <c r="N306" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="307" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A307" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B307" s="5"/>
+      <c r="C307" s="5"/>
+      <c r="D307" s="5"/>
+      <c r="E307" s="5"/>
+      <c r="F307" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="G307" s="5"/>
+      <c r="H307" s="5"/>
+      <c r="I307" s="5"/>
+      <c r="J307" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K307" s="5">
+        <v>60</v>
+      </c>
+      <c r="L307" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="M307" s="1"/>
+      <c r="N307" t="s">
+        <v>193</v>
+      </c>
+    </row>
     <row r="308" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="K308" s="7"/>
+      <c r="A308" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B308" s="5"/>
+      <c r="C308" s="5"/>
+      <c r="D308" s="5"/>
+      <c r="E308" s="5"/>
+      <c r="F308" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G308" s="5"/>
+      <c r="H308" s="5"/>
+      <c r="I308" s="5"/>
+      <c r="J308" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K308" s="5">
+        <v>40</v>
+      </c>
+      <c r="L308" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="M308" s="1"/>
+      <c r="N308" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="309" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A309" t="s">
+        <v>52</v>
+      </c>
+      <c r="C309" t="s">
+        <v>53</v>
+      </c>
+      <c r="D309" t="s">
+        <v>54</v>
+      </c>
+      <c r="F309" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="J309" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K309">
+        <v>40</v>
+      </c>
+      <c r="L309" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="N309" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="310" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A310" t="s">
+        <v>52</v>
+      </c>
+      <c r="C310" t="s">
+        <v>53</v>
+      </c>
+      <c r="D310" t="s">
+        <v>54</v>
+      </c>
+      <c r="F310" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="J310" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K310" s="5">
+        <v>40</v>
+      </c>
+      <c r="L310" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="N310" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="311" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A311" t="s">
+        <v>52</v>
+      </c>
+      <c r="C311" t="s">
+        <v>53</v>
+      </c>
+      <c r="D311" t="s">
+        <v>54</v>
+      </c>
+      <c r="F311" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="J311" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="K311" s="5">
+        <v>40</v>
+      </c>
+      <c r="L311" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="N311" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="314" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="K314" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -9174,20 +9290,20 @@
       </c>
     </row>
     <row r="16" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B16" s="60" t="s">
+      <c r="B16" s="55" t="s">
         <v>152</v>
       </c>
-      <c r="C16" s="60"/>
-      <c r="D16" s="60"/>
-      <c r="E16" s="60"/>
-      <c r="F16" s="60"/>
-      <c r="G16" s="60"/>
-      <c r="H16" s="60"/>
-      <c r="I16" s="60"/>
-      <c r="J16" s="60"/>
-      <c r="K16" s="60"/>
-      <c r="L16" s="60"/>
-      <c r="M16" s="60"/>
+      <c r="C16" s="55"/>
+      <c r="D16" s="55"/>
+      <c r="E16" s="55"/>
+      <c r="F16" s="55"/>
+      <c r="G16" s="55"/>
+      <c r="H16" s="55"/>
+      <c r="I16" s="55"/>
+      <c r="J16" s="55"/>
+      <c r="K16" s="55"/>
+      <c r="L16" s="55"/>
+      <c r="M16" s="55"/>
     </row>
     <row r="17" spans="2:13" ht="33" x14ac:dyDescent="0.25">
       <c r="B17" s="28" t="s">
@@ -10012,23 +10128,23 @@
       <c r="M40" s="27"/>
     </row>
     <row r="42" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B42" s="60" t="s">
+      <c r="B42" s="55" t="s">
         <v>167</v>
       </c>
-      <c r="C42" s="60"/>
-      <c r="D42" s="60"/>
-      <c r="E42" s="60"/>
-      <c r="F42" s="60"/>
-      <c r="G42" s="60"/>
-      <c r="H42" s="60"/>
-      <c r="I42" s="60"/>
-      <c r="J42" s="60"/>
-      <c r="K42" s="60"/>
-      <c r="L42" s="60"/>
-      <c r="M42" s="60"/>
-      <c r="N42" s="60"/>
-      <c r="O42" s="60"/>
-      <c r="P42" s="60"/>
+      <c r="C42" s="55"/>
+      <c r="D42" s="55"/>
+      <c r="E42" s="55"/>
+      <c r="F42" s="55"/>
+      <c r="G42" s="55"/>
+      <c r="H42" s="55"/>
+      <c r="I42" s="55"/>
+      <c r="J42" s="55"/>
+      <c r="K42" s="55"/>
+      <c r="L42" s="55"/>
+      <c r="M42" s="55"/>
+      <c r="N42" s="55"/>
+      <c r="O42" s="55"/>
+      <c r="P42" s="55"/>
     </row>
     <row r="43" spans="2:16" ht="44.25" x14ac:dyDescent="0.25">
       <c r="B43" s="38" t="s">
@@ -10996,43 +11112,43 @@
       <c r="N66" s="27"/>
     </row>
     <row r="68" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="60" t="s">
+      <c r="B68" s="55" t="s">
         <v>160</v>
       </c>
-      <c r="C68" s="60"/>
-      <c r="D68" s="60"/>
-      <c r="E68" s="60"/>
-      <c r="F68" s="60"/>
-      <c r="G68" s="60"/>
-      <c r="H68" s="60"/>
-      <c r="I68" s="60"/>
-      <c r="J68" s="60"/>
-      <c r="K68" s="60"/>
-      <c r="L68" s="60"/>
-      <c r="M68" s="60"/>
+      <c r="C68" s="55"/>
+      <c r="D68" s="55"/>
+      <c r="E68" s="55"/>
+      <c r="F68" s="55"/>
+      <c r="G68" s="55"/>
+      <c r="H68" s="55"/>
+      <c r="I68" s="55"/>
+      <c r="J68" s="55"/>
+      <c r="K68" s="55"/>
+      <c r="L68" s="55"/>
+      <c r="M68" s="55"/>
     </row>
     <row r="69" spans="2:14" ht="24" x14ac:dyDescent="0.25">
-      <c r="B69" s="62" t="s">
+      <c r="B69" s="56" t="s">
         <v>141</v>
       </c>
-      <c r="C69" s="64" t="s">
+      <c r="C69" s="58" t="s">
         <v>161</v>
       </c>
-      <c r="D69" s="65"/>
-      <c r="E69" s="65"/>
-      <c r="F69" s="65"/>
-      <c r="G69" s="65"/>
-      <c r="H69" s="65"/>
-      <c r="I69" s="65"/>
-      <c r="J69" s="65"/>
-      <c r="K69" s="66"/>
+      <c r="D69" s="59"/>
+      <c r="E69" s="59"/>
+      <c r="F69" s="59"/>
+      <c r="G69" s="59"/>
+      <c r="H69" s="59"/>
+      <c r="I69" s="59"/>
+      <c r="J69" s="59"/>
+      <c r="K69" s="60"/>
       <c r="L69" s="33" t="s">
         <v>162</v>
       </c>
       <c r="M69" s="34"/>
     </row>
     <row r="70" spans="2:14" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="B70" s="63"/>
+      <c r="B70" s="57"/>
       <c r="C70" s="23" t="s">
         <v>142</v>
       </c>
@@ -11451,22 +11567,22 @@
       <c r="L82" s="61"/>
     </row>
     <row r="83" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B83" s="55"/>
-      <c r="C83" s="57" t="s">
+      <c r="B83" s="62"/>
+      <c r="C83" s="64" t="s">
         <v>165</v>
       </c>
-      <c r="D83" s="58"/>
-      <c r="E83" s="58"/>
-      <c r="F83" s="58"/>
-      <c r="G83" s="58"/>
-      <c r="H83" s="58"/>
-      <c r="I83" s="58"/>
-      <c r="J83" s="58"/>
-      <c r="K83" s="59"/>
+      <c r="D83" s="65"/>
+      <c r="E83" s="65"/>
+      <c r="F83" s="65"/>
+      <c r="G83" s="65"/>
+      <c r="H83" s="65"/>
+      <c r="I83" s="65"/>
+      <c r="J83" s="65"/>
+      <c r="K83" s="66"/>
       <c r="L83" s="27"/>
     </row>
     <row r="84" spans="2:12" ht="42" x14ac:dyDescent="0.25">
-      <c r="B84" s="56"/>
+      <c r="B84" s="63"/>
       <c r="C84" s="36" t="s">
         <v>142</v>
       </c>
@@ -11836,16 +11952,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B83:B84"/>
+    <mergeCell ref="C83:K83"/>
+    <mergeCell ref="B42:P42"/>
+    <mergeCell ref="B55:N55"/>
+    <mergeCell ref="B29:M29"/>
     <mergeCell ref="B16:M16"/>
     <mergeCell ref="B68:M68"/>
     <mergeCell ref="B69:B70"/>
     <mergeCell ref="C69:K69"/>
     <mergeCell ref="B82:L82"/>
-    <mergeCell ref="B83:B84"/>
-    <mergeCell ref="C83:K83"/>
-    <mergeCell ref="B42:P42"/>
-    <mergeCell ref="B55:N55"/>
-    <mergeCell ref="B29:M29"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data/default/ManureMgmt.xlsx
+++ b/data/default/ManureMgmt.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jnka0003\Documents\#1 Projekt\MISTRA Food Futures WP5\CIBUSmod Food Systems Model\CIBUSmod\data\default\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jnka0003\Git repos\CIBUSmod\data\default\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1830" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1829" uniqueCount="204">
   <si>
     <t>value</t>
   </si>
@@ -173,9 +173,6 @@
     <t>f_element</t>
   </si>
   <si>
-    <t>fallback OK?</t>
-  </si>
-  <si>
     <t>poultry</t>
   </si>
   <si>
@@ -633,6 +630,9 @@
   </si>
   <si>
     <t>Share of manure to anaerobic digestion treated in co-digesters</t>
+  </si>
+  <si>
+    <t>loss_storage_of_TAN</t>
   </si>
 </sst>
 </file>
@@ -1400,26 +1400,11 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="10"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="10"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="36" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="10"/>
-    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="36" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1436,9 +1421,24 @@
     <xf numFmtId="0" fontId="25" fillId="36" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="9"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="10"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="10"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="36" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="10"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1770,12 +1770,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -1786,7 +1786,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:N338"/>
+  <dimension ref="A1:N339"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
@@ -1815,7 +1815,7 @@
         <v>30</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>31</v>
@@ -1827,7 +1827,7 @@
         <v>32</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="J1" s="4" t="s">
         <v>33</v>
@@ -1847,7 +1847,7 @@
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B2" s="3"/>
       <c r="C2" s="3"/>
@@ -1887,7 +1887,7 @@
         <v>17</v>
       </c>
       <c r="N3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
@@ -1914,7 +1914,7 @@
         <v>17</v>
       </c>
       <c r="N4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
@@ -1941,7 +1941,7 @@
         <v>17</v>
       </c>
       <c r="N5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
@@ -1955,7 +1955,7 @@
         <v>3</v>
       </c>
       <c r="F6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J6" t="s">
         <v>16</v>
@@ -1968,7 +1968,7 @@
         <v>17</v>
       </c>
       <c r="N6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
@@ -1982,7 +1982,7 @@
         <v>3</v>
       </c>
       <c r="F7" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J7" t="s">
         <v>16</v>
@@ -1995,7 +1995,7 @@
         <v>17</v>
       </c>
       <c r="N7" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -2022,7 +2022,7 @@
         <v>17</v>
       </c>
       <c r="N8" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -2049,7 +2049,7 @@
         <v>17</v>
       </c>
       <c r="N9" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -2076,7 +2076,7 @@
         <v>17</v>
       </c>
       <c r="N10" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
@@ -2090,7 +2090,7 @@
         <v>3</v>
       </c>
       <c r="F11" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J11" t="s">
         <v>16</v>
@@ -2103,7 +2103,7 @@
         <v>17</v>
       </c>
       <c r="N11" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -2117,7 +2117,7 @@
         <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J12" t="s">
         <v>16</v>
@@ -2130,7 +2130,7 @@
         <v>17</v>
       </c>
       <c r="N12" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
@@ -2154,7 +2154,7 @@
         <v>17</v>
       </c>
       <c r="N13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -2178,7 +2178,7 @@
         <v>17</v>
       </c>
       <c r="N14" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
@@ -2202,7 +2202,7 @@
         <v>17</v>
       </c>
       <c r="N15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
@@ -2213,7 +2213,7 @@
         <v>9</v>
       </c>
       <c r="F16" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J16" t="s">
         <v>16</v>
@@ -2226,7 +2226,7 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
@@ -2237,7 +2237,7 @@
         <v>9</v>
       </c>
       <c r="F17" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J17" t="s">
         <v>16</v>
@@ -2250,7 +2250,7 @@
         <v>17</v>
       </c>
       <c r="N17" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
@@ -2274,7 +2274,7 @@
         <v>17</v>
       </c>
       <c r="N18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
@@ -2298,7 +2298,7 @@
         <v>17</v>
       </c>
       <c r="N19" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
@@ -2322,7 +2322,7 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
@@ -2333,7 +2333,7 @@
         <v>11</v>
       </c>
       <c r="F21" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J21" t="s">
         <v>16</v>
@@ -2346,7 +2346,7 @@
         <v>17</v>
       </c>
       <c r="N21" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
@@ -2357,7 +2357,7 @@
         <v>11</v>
       </c>
       <c r="F22" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J22" t="s">
         <v>16</v>
@@ -2370,7 +2370,7 @@
         <v>17</v>
       </c>
       <c r="N22" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
@@ -2394,7 +2394,7 @@
         <v>17</v>
       </c>
       <c r="N23" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
@@ -2418,7 +2418,7 @@
         <v>17</v>
       </c>
       <c r="N24" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
@@ -2442,7 +2442,7 @@
         <v>17</v>
       </c>
       <c r="N25" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
@@ -2453,7 +2453,7 @@
         <v>12</v>
       </c>
       <c r="F26" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J26" t="s">
         <v>16</v>
@@ -2466,7 +2466,7 @@
         <v>17</v>
       </c>
       <c r="N26" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
@@ -2477,7 +2477,7 @@
         <v>12</v>
       </c>
       <c r="F27" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J27" t="s">
         <v>16</v>
@@ -2490,7 +2490,7 @@
         <v>17</v>
       </c>
       <c r="N27" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
@@ -2514,7 +2514,7 @@
         <v>17</v>
       </c>
       <c r="N28" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
@@ -2538,7 +2538,7 @@
         <v>17</v>
       </c>
       <c r="N29" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
@@ -2562,7 +2562,7 @@
         <v>17</v>
       </c>
       <c r="N30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
@@ -2573,7 +2573,7 @@
         <v>10</v>
       </c>
       <c r="F31" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J31" t="s">
         <v>16</v>
@@ -2586,7 +2586,7 @@
         <v>17</v>
       </c>
       <c r="N31" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
@@ -2597,7 +2597,7 @@
         <v>10</v>
       </c>
       <c r="F32" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J32" t="s">
         <v>16</v>
@@ -2610,7 +2610,7 @@
         <v>17</v>
       </c>
       <c r="N32" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
@@ -2634,7 +2634,7 @@
         <v>17</v>
       </c>
       <c r="N33" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
@@ -2658,7 +2658,7 @@
         <v>17</v>
       </c>
       <c r="N34" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
@@ -2682,7 +2682,7 @@
         <v>17</v>
       </c>
       <c r="N35" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
@@ -2693,7 +2693,7 @@
         <v>13</v>
       </c>
       <c r="F36" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J36" t="s">
         <v>16</v>
@@ -2706,7 +2706,7 @@
         <v>17</v>
       </c>
       <c r="N36" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
@@ -2717,7 +2717,7 @@
         <v>13</v>
       </c>
       <c r="F37" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J37" t="s">
         <v>16</v>
@@ -2730,12 +2730,12 @@
         <v>17</v>
       </c>
       <c r="N37" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F38" t="s">
         <v>18</v>
@@ -2751,12 +2751,12 @@
         <v>17</v>
       </c>
       <c r="N38" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F39" t="s">
         <v>19</v>
@@ -2772,12 +2772,12 @@
         <v>17</v>
       </c>
       <c r="N39" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F40" t="s">
         <v>20</v>
@@ -2793,15 +2793,15 @@
         <v>17</v>
       </c>
       <c r="N40" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F41" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J41" t="s">
         <v>16</v>
@@ -2814,15 +2814,15 @@
         <v>17</v>
       </c>
       <c r="N41" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F42" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J42" t="s">
         <v>16</v>
@@ -2835,12 +2835,12 @@
         <v>17</v>
       </c>
       <c r="N42" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F43" t="s">
         <v>18</v>
@@ -2856,12 +2856,12 @@
         <v>17</v>
       </c>
       <c r="N43" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F44" t="s">
         <v>19</v>
@@ -2877,12 +2877,12 @@
         <v>17</v>
       </c>
       <c r="N44" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F45" t="s">
         <v>20</v>
@@ -2898,15 +2898,15 @@
         <v>17</v>
       </c>
       <c r="N45" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F46" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J46" t="s">
         <v>16</v>
@@ -2919,15 +2919,15 @@
         <v>17</v>
       </c>
       <c r="N46" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F47" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J47" t="s">
         <v>16</v>
@@ -2940,7 +2940,7 @@
         <v>17</v>
       </c>
       <c r="N47" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
@@ -2961,7 +2961,7 @@
         <v>17</v>
       </c>
       <c r="N48" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
@@ -2982,7 +2982,7 @@
         <v>17</v>
       </c>
       <c r="N49" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
@@ -3003,7 +3003,7 @@
         <v>17</v>
       </c>
       <c r="N50" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
@@ -3011,7 +3011,7 @@
         <v>37</v>
       </c>
       <c r="F51" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J51" t="s">
         <v>16</v>
@@ -3024,7 +3024,7 @@
         <v>17</v>
       </c>
       <c r="N51" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
@@ -3032,7 +3032,7 @@
         <v>37</v>
       </c>
       <c r="F52" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J52" t="s">
         <v>16</v>
@@ -3045,7 +3045,7 @@
         <v>17</v>
       </c>
       <c r="N52" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
@@ -3069,7 +3069,7 @@
         <v>17</v>
       </c>
       <c r="N53" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
@@ -3093,7 +3093,7 @@
         <v>17</v>
       </c>
       <c r="N54" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
@@ -3117,7 +3117,7 @@
         <v>17</v>
       </c>
       <c r="N55" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
@@ -3128,7 +3128,7 @@
         <v>38</v>
       </c>
       <c r="F56" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J56" t="s">
         <v>16</v>
@@ -3141,7 +3141,7 @@
         <v>17</v>
       </c>
       <c r="N56" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
@@ -3152,7 +3152,7 @@
         <v>38</v>
       </c>
       <c r="F57" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J57" t="s">
         <v>16</v>
@@ -3165,7 +3165,7 @@
         <v>17</v>
       </c>
       <c r="N57" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
@@ -3189,7 +3189,7 @@
         <v>17</v>
       </c>
       <c r="N58" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
@@ -3213,7 +3213,7 @@
         <v>17</v>
       </c>
       <c r="N59" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
@@ -3237,7 +3237,7 @@
         <v>17</v>
       </c>
       <c r="N60" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
@@ -3248,7 +3248,7 @@
         <v>39</v>
       </c>
       <c r="F61" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J61" t="s">
         <v>16</v>
@@ -3261,7 +3261,7 @@
         <v>17</v>
       </c>
       <c r="N61" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
@@ -3272,7 +3272,7 @@
         <v>39</v>
       </c>
       <c r="F62" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J62" t="s">
         <v>16</v>
@@ -3285,12 +3285,12 @@
         <v>17</v>
       </c>
       <c r="N62" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F63" t="s">
         <v>18</v>
@@ -3306,12 +3306,12 @@
         <v>17</v>
       </c>
       <c r="N63" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F64" t="s">
         <v>19</v>
@@ -3327,12 +3327,12 @@
         <v>17</v>
       </c>
       <c r="N64" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F65" t="s">
         <v>20</v>
@@ -3348,15 +3348,15 @@
         <v>17</v>
       </c>
       <c r="N65" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F66" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J66" t="s">
         <v>16</v>
@@ -3369,15 +3369,15 @@
         <v>17</v>
       </c>
       <c r="N66" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F67" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J67" t="s">
         <v>16</v>
@@ -3390,18 +3390,18 @@
         <v>17</v>
       </c>
       <c r="N67" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
+        <v>50</v>
+      </c>
+      <c r="C68" t="s">
         <v>51</v>
       </c>
-      <c r="C68" t="s">
+      <c r="D68" t="s">
         <v>52</v>
-      </c>
-      <c r="D68" t="s">
-        <v>53</v>
       </c>
       <c r="F68" t="s">
         <v>18</v>
@@ -3417,18 +3417,18 @@
         <v>17</v>
       </c>
       <c r="N68" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
+        <v>50</v>
+      </c>
+      <c r="C69" t="s">
         <v>51</v>
       </c>
-      <c r="C69" t="s">
+      <c r="D69" t="s">
         <v>52</v>
-      </c>
-      <c r="D69" t="s">
-        <v>53</v>
       </c>
       <c r="F69" t="s">
         <v>19</v>
@@ -3444,18 +3444,18 @@
         <v>17</v>
       </c>
       <c r="N69" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
+        <v>50</v>
+      </c>
+      <c r="C70" t="s">
         <v>51</v>
       </c>
-      <c r="C70" t="s">
+      <c r="D70" t="s">
         <v>52</v>
-      </c>
-      <c r="D70" t="s">
-        <v>53</v>
       </c>
       <c r="F70" t="s">
         <v>20</v>
@@ -3471,21 +3471,21 @@
         <v>17</v>
       </c>
       <c r="N70" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
+        <v>50</v>
+      </c>
+      <c r="C71" t="s">
         <v>51</v>
       </c>
-      <c r="C71" t="s">
+      <c r="D71" t="s">
         <v>52</v>
       </c>
-      <c r="D71" t="s">
-        <v>53</v>
-      </c>
       <c r="F71" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J71" t="s">
         <v>16</v>
@@ -3498,21 +3498,21 @@
         <v>17</v>
       </c>
       <c r="N71" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
+        <v>50</v>
+      </c>
+      <c r="C72" t="s">
         <v>51</v>
       </c>
-      <c r="C72" t="s">
+      <c r="D72" t="s">
         <v>52</v>
       </c>
-      <c r="D72" t="s">
-        <v>53</v>
-      </c>
       <c r="F72" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J72" t="s">
         <v>16</v>
@@ -3525,22 +3525,22 @@
         <v>17</v>
       </c>
       <c r="N72" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A74" s="68" t="s">
-        <v>202</v>
+      <c r="A74" s="56" t="s">
+        <v>201</v>
       </c>
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A75" s="68" t="s">
-        <v>200</v>
+      <c r="A75" s="56" t="s">
+        <v>199</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="J76" s="6" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K76" s="6">
         <v>0</v>
@@ -3549,7 +3549,7 @@
         <v>17</v>
       </c>
       <c r="M76" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
@@ -3563,10 +3563,10 @@
         <v>3</v>
       </c>
       <c r="F77" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J77" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K77" s="44">
         <f>INDEX(MMS!$S$16:$AF$16,MATCH(A77&amp;C77&amp;D77,MMS!$S$8:$AF$8,0))</f>
@@ -3576,10 +3576,10 @@
         <v>17</v>
       </c>
       <c r="M77" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="N77" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
@@ -3593,10 +3593,10 @@
         <v>3</v>
       </c>
       <c r="F78" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J78" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K78" s="44">
         <f>INDEX(MMS!$S$16:$AF$16,MATCH(A78&amp;C78&amp;D78,MMS!$S$8:$AF$8,0))</f>
@@ -3614,10 +3614,10 @@
         <v>9</v>
       </c>
       <c r="F79" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J79" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K79" s="44">
         <f>INDEX(MMS!$S$16:$AF$16,MATCH(A79&amp;C79&amp;D79,MMS!$S$8:$AF$8,0))</f>
@@ -3635,10 +3635,10 @@
         <v>11</v>
       </c>
       <c r="F80" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J80" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K80" s="44">
         <f>INDEX(MMS!$S$16:$AF$16,MATCH(A80&amp;C80&amp;D80,MMS!$S$8:$AF$8,0))</f>
@@ -3656,10 +3656,10 @@
         <v>12</v>
       </c>
       <c r="F81" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J81" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K81" s="44">
         <f>INDEX(MMS!$S$16:$AF$16,MATCH(A81&amp;C81&amp;D81,MMS!$S$8:$AF$8,0))</f>
@@ -3677,10 +3677,10 @@
         <v>10</v>
       </c>
       <c r="F82" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J82" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K82" s="44">
         <f>INDEX(MMS!$S$16:$AF$16,MATCH(A82&amp;C82&amp;D82,MMS!$S$8:$AF$8,0))</f>
@@ -3698,10 +3698,10 @@
         <v>13</v>
       </c>
       <c r="F83" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J83" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K83" s="44">
         <f>INDEX(MMS!$S$16:$AF$16,MATCH(A83&amp;C83&amp;D83,MMS!$S$8:$AF$8,0))</f>
@@ -3713,13 +3713,13 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F84" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J84" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K84" s="44">
         <f>INDEX(MMS!$S$16:$AF$16,MATCH(A84&amp;C84&amp;D84,MMS!$S$8:$AF$8,0))</f>
@@ -3731,13 +3731,13 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F85" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J85" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K85" s="44">
         <f>INDEX(MMS!$S$16:$AF$16,MATCH(A85&amp;C85&amp;D85,MMS!$S$8:$AF$8,0))</f>
@@ -3752,10 +3752,10 @@
         <v>37</v>
       </c>
       <c r="F86" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J86" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K86" s="44">
         <f>INDEX(MMS!$S$16:$AF$16,MATCH(A86&amp;C86&amp;D86,MMS!$S$8:$AF$8,0))</f>
@@ -3773,10 +3773,10 @@
         <v>38</v>
       </c>
       <c r="F87" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J87" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K87" s="44">
         <f>INDEX(MMS!$S$16:$AF$16,MATCH(A87&amp;C87&amp;D87,MMS!$S$8:$AF$8,0))</f>
@@ -3794,10 +3794,10 @@
         <v>39</v>
       </c>
       <c r="F88" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J88" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K88" s="44">
         <f>INDEX(MMS!$S$16:$AF$16,MATCH(A88&amp;C88&amp;D88,MMS!$S$8:$AF$8,0))</f>
@@ -3809,13 +3809,13 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F89" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J89" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K89" s="44">
         <f>INDEX(MMS!$S$16:$AF$16,MATCH(A89&amp;C89&amp;D89,MMS!$S$8:$AF$8,0))</f>
@@ -3827,19 +3827,19 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
+        <v>50</v>
+      </c>
+      <c r="C90" t="s">
         <v>51</v>
       </c>
-      <c r="C90" t="s">
+      <c r="D90" t="s">
         <v>52</v>
       </c>
-      <c r="D90" t="s">
-        <v>53</v>
-      </c>
       <c r="F90" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J90" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="K90" s="44">
         <f>INDEX(MMS!$S$16:$AF$16,MATCH(A90&amp;C90&amp;D90,MMS!$S$8:$AF$8,0))</f>
@@ -3857,7 +3857,7 @@
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="J92" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="K92" s="1">
         <v>0</v>
@@ -3866,12 +3866,12 @@
         <v>17</v>
       </c>
       <c r="M92" s="1" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -3884,20 +3884,20 @@
       <c r="J94" s="2"/>
       <c r="K94" s="2"/>
       <c r="L94" s="18" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="M94" s="2"/>
       <c r="N94" s="2"/>
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="J96" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K96">
         <v>0</v>
       </c>
       <c r="M96" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
@@ -3911,17 +3911,17 @@
         <v>3</v>
       </c>
       <c r="I98" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J98" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K98" s="16">
         <f>1.5*0.85</f>
         <v>1.2749999999999999</v>
       </c>
       <c r="N98" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
@@ -3935,17 +3935,17 @@
         <v>3</v>
       </c>
       <c r="I99" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J99" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K99" s="16">
         <f>5.5*0.85</f>
         <v>4.6749999999999998</v>
       </c>
       <c r="N99" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
@@ -3956,17 +3956,17 @@
         <v>10</v>
       </c>
       <c r="I100" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J100" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K100" s="16">
         <f>5*0.85</f>
         <v>4.25</v>
       </c>
       <c r="N100" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
@@ -3977,17 +3977,17 @@
         <v>9</v>
       </c>
       <c r="I101" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J101" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K101" s="16">
         <f>3.5*0.85</f>
         <v>2.9750000000000001</v>
       </c>
       <c r="N101" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
@@ -3998,17 +3998,17 @@
         <v>11</v>
       </c>
       <c r="I102" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J102" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K102" s="16">
         <f>K101</f>
         <v>2.9750000000000001</v>
       </c>
       <c r="N102" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
@@ -4019,17 +4019,17 @@
         <v>12</v>
       </c>
       <c r="I103" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J103" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K103" s="16">
         <f>K101</f>
         <v>2.9750000000000001</v>
       </c>
       <c r="N103" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="104" spans="1:14" x14ac:dyDescent="0.25">
@@ -4040,17 +4040,17 @@
         <v>13</v>
       </c>
       <c r="I104" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J104" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K104" s="16">
         <f>K101</f>
         <v>2.9750000000000001</v>
       </c>
       <c r="N104" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.25">
@@ -4058,20 +4058,20 @@
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="I106" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J106" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K106" s="16">
         <f>6*0.85</f>
         <v>5.0999999999999996</v>
       </c>
       <c r="N106" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.25">
@@ -4079,26 +4079,26 @@
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D108" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="I108" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J108" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K108" s="16">
         <f>100/(365.25/2)*0.85</f>
         <v>0.4654346338124572</v>
       </c>
       <c r="M108" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="N108" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.25">
@@ -4112,17 +4112,17 @@
         <v>41</v>
       </c>
       <c r="I110" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J110" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K110" s="16">
         <f>1.5*0.85</f>
         <v>1.2749999999999999</v>
       </c>
       <c r="N110" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.25">
@@ -4133,10 +4133,10 @@
         <v>42</v>
       </c>
       <c r="I111" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J111" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K111" s="19">
         <v>0</v>
@@ -4150,17 +4150,17 @@
         <v>44</v>
       </c>
       <c r="I112" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J112" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K112" s="20">
         <f>K114</f>
         <v>5.9500000000000004E-2</v>
       </c>
       <c r="M112" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.25">
@@ -4171,19 +4171,19 @@
         <v>43</v>
       </c>
       <c r="I113" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J113" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K113" s="16">
         <v>0</v>
       </c>
       <c r="M113" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="N113" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="114" spans="1:14" x14ac:dyDescent="0.25">
@@ -4194,17 +4194,17 @@
         <v>38</v>
       </c>
       <c r="I114" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J114" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K114" s="16">
         <f>0.07*0.85</f>
         <v>5.9500000000000004E-2</v>
       </c>
       <c r="N114" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="115" spans="1:14" x14ac:dyDescent="0.25">
@@ -4215,10 +4215,10 @@
         <v>39</v>
       </c>
       <c r="I115" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J115" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="K115" s="20">
         <f>K114</f>
@@ -4230,10 +4230,10 @@
     </row>
     <row r="117" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C117" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="K117" s="20"/>
     </row>
@@ -4242,10 +4242,10 @@
     </row>
     <row r="119" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
+        <v>50</v>
+      </c>
+      <c r="C119" t="s">
         <v>51</v>
-      </c>
-      <c r="C119" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="120" spans="1:14" x14ac:dyDescent="0.25">
@@ -4274,7 +4274,7 @@
     </row>
     <row r="122" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A122" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B122" s="12"/>
       <c r="C122" s="12"/>
@@ -4292,19 +4292,19 @@
     </row>
     <row r="123" spans="1:14" x14ac:dyDescent="0.25">
       <c r="J123" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K123" s="5">
         <v>0.04</v>
       </c>
       <c r="L123" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="M123" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="M123" s="5" t="s">
-        <v>72</v>
-      </c>
       <c r="N123" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="124" spans="1:14" x14ac:dyDescent="0.25">
@@ -4312,16 +4312,16 @@
         <v>37</v>
       </c>
       <c r="J124" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K124" s="5">
         <v>0.02</v>
       </c>
       <c r="L124" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="N124" s="5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="125" spans="1:14" x14ac:dyDescent="0.25">
@@ -4333,7 +4333,7 @@
     </row>
     <row r="126" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A126" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B126" s="12"/>
       <c r="C126" s="12"/>
@@ -4351,16 +4351,16 @@
     </row>
     <row r="127" spans="1:14" x14ac:dyDescent="0.25">
       <c r="J127" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="K127" s="6">
+        <v>0</v>
+      </c>
+      <c r="L127" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="K127" s="6">
-        <v>0</v>
-      </c>
-      <c r="L127" s="6" t="s">
+      <c r="M127" s="6" t="s">
         <v>59</v>
-      </c>
-      <c r="M127" s="6" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="128" spans="1:14" x14ac:dyDescent="0.25">
@@ -4374,16 +4374,16 @@
         <v>3</v>
       </c>
       <c r="J128" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K128">
         <v>0.24</v>
       </c>
       <c r="L128" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N128" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="129" spans="1:14" x14ac:dyDescent="0.25">
@@ -4391,50 +4391,50 @@
         <v>1</v>
       </c>
       <c r="J129" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K129">
         <v>0.18</v>
       </c>
       <c r="L129" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N129" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="130" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J130" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K130">
         <v>0.19</v>
       </c>
       <c r="L130" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N130" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="131" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J131" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K131">
         <v>0.3</v>
       </c>
       <c r="L131" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N131" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="132" spans="1:14" x14ac:dyDescent="0.25">
@@ -4442,56 +4442,56 @@
         <v>37</v>
       </c>
       <c r="J132" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K132">
         <v>0.45</v>
       </c>
       <c r="L132" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N132" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="133" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
+        <v>50</v>
+      </c>
+      <c r="C133" t="s">
         <v>51</v>
       </c>
-      <c r="C133" t="s">
-        <v>52</v>
-      </c>
       <c r="J133" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K133">
         <v>0.36</v>
       </c>
       <c r="L133" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N133" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="134" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C134" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J134" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K134">
         <v>0.39</v>
       </c>
       <c r="L134" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="N134" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="136" spans="1:14" x14ac:dyDescent="0.25">
@@ -4499,16 +4499,16 @@
         <v>15</v>
       </c>
       <c r="J136" t="s">
+        <v>62</v>
+      </c>
+      <c r="K136">
+        <v>1</v>
+      </c>
+      <c r="L136" t="s">
         <v>63</v>
       </c>
-      <c r="K136">
-        <v>1</v>
-      </c>
-      <c r="L136" t="s">
+      <c r="N136" t="s">
         <v>64</v>
-      </c>
-      <c r="N136" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="137" spans="1:14" x14ac:dyDescent="0.25">
@@ -4516,16 +4516,16 @@
         <v>18</v>
       </c>
       <c r="J137" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K137">
         <v>3.5</v>
       </c>
       <c r="L137" t="s">
+        <v>63</v>
+      </c>
+      <c r="N137" t="s">
         <v>64</v>
-      </c>
-      <c r="N137" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="138" spans="1:14" x14ac:dyDescent="0.25">
@@ -4533,16 +4533,16 @@
         <v>19</v>
       </c>
       <c r="J138" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K138">
         <v>2</v>
       </c>
       <c r="L138" t="s">
+        <v>63</v>
+      </c>
+      <c r="N138" t="s">
         <v>64</v>
-      </c>
-      <c r="N138" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="139" spans="1:14" x14ac:dyDescent="0.25">
@@ -4550,50 +4550,50 @@
         <v>20</v>
       </c>
       <c r="J139" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K139">
         <v>17</v>
       </c>
       <c r="L139" t="s">
+        <v>63</v>
+      </c>
+      <c r="N139" t="s">
         <v>64</v>
-      </c>
-      <c r="N139" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="140" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F140" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="J140" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K140">
         <v>0.5</v>
       </c>
       <c r="L140" t="s">
+        <v>63</v>
+      </c>
+      <c r="N140" t="s">
         <v>64</v>
-      </c>
-      <c r="N140" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="141" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F141" s="5" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J141" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="K141">
         <v>10.7</v>
       </c>
       <c r="L141" t="s">
+        <v>63</v>
+      </c>
+      <c r="N141" t="s">
         <v>64</v>
-      </c>
-      <c r="N141" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="142" spans="1:14" x14ac:dyDescent="0.25">
@@ -4601,7 +4601,7 @@
     </row>
     <row r="143" spans="1:14" x14ac:dyDescent="0.25">
       <c r="J143" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="K143">
         <v>55</v>
@@ -4610,16 +4610,16 @@
         <v>17</v>
       </c>
       <c r="M143" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="N143" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="144" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F144" s="5"/>
       <c r="J144" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K144">
         <v>10</v>
@@ -4628,10 +4628,10 @@
         <v>17</v>
       </c>
       <c r="M144" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N144" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="145" spans="1:14" x14ac:dyDescent="0.25">
@@ -4639,7 +4639,7 @@
         <v>15</v>
       </c>
       <c r="J145" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="K145">
         <v>0</v>
@@ -4650,7 +4650,7 @@
     </row>
     <row r="147" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
@@ -4668,7 +4668,7 @@
     </row>
     <row r="148" spans="1:14" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A148" s="11" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B148" s="12"/>
       <c r="C148" s="12"/>
@@ -5064,7 +5064,7 @@
     </row>
     <row r="162" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J162" t="s">
         <v>5</v>
@@ -5081,49 +5081,49 @@
     </row>
     <row r="163" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J163" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K163" s="14">
         <f>K162 * (6.4/2.29)/16</f>
         <v>8.3842794759825345</v>
       </c>
       <c r="L163" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M163" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N163" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="164" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="J164" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K164" s="14">
         <f>K162 * (15.9/(47/39))/16</f>
         <v>39.58085106382979</v>
       </c>
       <c r="L164" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M164" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N164" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="165" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J165" t="s">
         <v>5</v>
@@ -5140,46 +5140,46 @@
     </row>
     <row r="166" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J166" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K166" s="14">
         <f>K165 * (4.8/2.29)/14.4</f>
         <v>2.0378457059679769</v>
       </c>
       <c r="L166" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="N166" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="167" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J167" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K167" s="14">
         <f>K165 * (25.2/(47/39))/14.4</f>
         <v>20.329787234042556</v>
       </c>
       <c r="L167" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="N167" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="168" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D168" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J168" t="s">
         <v>5</v>
@@ -5191,7 +5191,7 @@
         <v>6</v>
       </c>
       <c r="M168" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="N168" t="s">
         <v>8</v>
@@ -5199,44 +5199,44 @@
     </row>
     <row r="169" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D169" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J169" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K169" s="14">
         <v>0</v>
       </c>
       <c r="L169" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="170" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D170" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="J170" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K170" s="14">
         <v>0</v>
       </c>
       <c r="L170" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="171" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C171" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J171" t="s">
         <v>5</v>
@@ -5253,61 +5253,61 @@
     </row>
     <row r="172" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C172" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J172" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K172" s="16">
         <f>K171 * (0.39/2.29)/0.75</f>
         <v>0.13624454148471615</v>
       </c>
       <c r="L172" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M172" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N172" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="173" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C173" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="J173" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K173" s="16">
         <f>K171 * (0.33/(47/39))/0.75</f>
         <v>0.21906382978723404</v>
       </c>
       <c r="L173" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M173" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N173" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="174" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
+        <v>50</v>
+      </c>
+      <c r="C174" t="s">
         <v>51</v>
       </c>
-      <c r="C174" t="s">
+      <c r="D174" t="s">
         <v>52</v>
-      </c>
-      <c r="D174" t="s">
-        <v>53</v>
       </c>
       <c r="J174" t="s">
         <v>5</v>
@@ -5324,64 +5324,64 @@
     </row>
     <row r="175" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
+        <v>50</v>
+      </c>
+      <c r="C175" t="s">
         <v>51</v>
       </c>
-      <c r="C175" t="s">
+      <c r="D175" t="s">
         <v>52</v>
       </c>
-      <c r="D175" t="s">
-        <v>53</v>
-      </c>
       <c r="J175" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K175" s="16">
         <f>K174 * (0.19/2.29)/0.53</f>
         <v>4.5398368624866105E-2</v>
       </c>
       <c r="L175" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M175" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N175" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="176" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
+        <v>50</v>
+      </c>
+      <c r="C176" t="s">
         <v>51</v>
       </c>
-      <c r="C176" t="s">
+      <c r="D176" t="s">
         <v>52</v>
       </c>
-      <c r="D176" t="s">
-        <v>53</v>
-      </c>
       <c r="J176" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K176" s="16">
         <f>K174 * (0.26/(47/39))/0.53</f>
         <v>0.11804897631473303</v>
       </c>
       <c r="L176" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M176" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="N176" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="177" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
+        <v>50</v>
+      </c>
+      <c r="C177" t="s">
         <v>51</v>
-      </c>
-      <c r="C177" t="s">
-        <v>52</v>
       </c>
       <c r="J177" t="s">
         <v>5</v>
@@ -5393,7 +5393,7 @@
         <v>6</v>
       </c>
       <c r="M177" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="N177" t="s">
         <v>8</v>
@@ -5401,50 +5401,50 @@
     </row>
     <row r="178" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
+        <v>50</v>
+      </c>
+      <c r="C178" t="s">
         <v>51</v>
       </c>
-      <c r="C178" t="s">
-        <v>52</v>
-      </c>
       <c r="J178" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K178" s="16">
         <f>K177 * (0.55/2.29)/1.12</f>
         <v>0.12866500311915158</v>
       </c>
       <c r="L178" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="M178" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="N178" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="179" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
+        <v>50</v>
+      </c>
+      <c r="C179" t="s">
         <v>51</v>
       </c>
-      <c r="C179" t="s">
-        <v>52</v>
-      </c>
       <c r="J179" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="K179" s="16">
         <f>K177 * (0.44/(47/39))/1.12</f>
         <v>0.19559270516717325</v>
       </c>
       <c r="L179" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="M179" t="s">
+        <v>109</v>
+      </c>
+      <c r="N179" t="s">
         <v>110</v>
-      </c>
-      <c r="N179" t="s">
-        <v>111</v>
       </c>
     </row>
     <row r="180" spans="1:14" x14ac:dyDescent="0.25">
@@ -5453,40 +5453,40 @@
     <row r="181" spans="1:14" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A181" s="10"/>
       <c r="J181" s="6" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K181" s="15">
         <v>0</v>
       </c>
       <c r="L181" s="15"/>
       <c r="M181" s="15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="182" spans="1:14" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A182" s="10"/>
       <c r="J182" s="6" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K182" s="15">
         <v>0</v>
       </c>
       <c r="L182" s="15"/>
       <c r="M182" s="15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="183" spans="1:14" s="9" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A183" s="10"/>
       <c r="J183" s="6" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K183" s="15">
         <v>0</v>
       </c>
       <c r="L183" s="15"/>
       <c r="M183" s="15" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="184" spans="1:14" x14ac:dyDescent="0.25">
@@ -5498,19 +5498,19 @@
       </c>
       <c r="F184" s="5"/>
       <c r="J184" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K184">
         <v>22.5</v>
       </c>
       <c r="L184" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M184" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N184" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="185" spans="1:14" x14ac:dyDescent="0.25">
@@ -5522,16 +5522,16 @@
       </c>
       <c r="F185" s="5"/>
       <c r="J185" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K185">
         <v>7.4</v>
       </c>
       <c r="L185" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N185" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="186" spans="1:14" x14ac:dyDescent="0.25">
@@ -5543,16 +5543,16 @@
       </c>
       <c r="F186" s="5"/>
       <c r="J186" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K186" s="14">
         <v>2</v>
       </c>
       <c r="L186" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N186" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="187" spans="1:14" x14ac:dyDescent="0.25">
@@ -5564,20 +5564,20 @@
       </c>
       <c r="F187" s="5"/>
       <c r="J187" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K187">
         <f>23.1</f>
         <v>23.1</v>
       </c>
       <c r="L187" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M187" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="N187" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="188" spans="1:14" x14ac:dyDescent="0.25">
@@ -5589,16 +5589,16 @@
       </c>
       <c r="F188" s="5"/>
       <c r="J188" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K188">
         <v>7.4</v>
       </c>
       <c r="L188" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N188" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="189" spans="1:14" x14ac:dyDescent="0.25">
@@ -5610,16 +5610,16 @@
       </c>
       <c r="F189" s="5"/>
       <c r="J189" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K189" s="14">
         <v>2</v>
       </c>
       <c r="L189" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N189" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="190" spans="1:14" x14ac:dyDescent="0.25">
@@ -5631,19 +5631,19 @@
       </c>
       <c r="F190" s="5"/>
       <c r="J190" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K190">
         <v>26.4</v>
       </c>
       <c r="L190" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M190" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="N190" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="191" spans="1:14" x14ac:dyDescent="0.25">
@@ -5655,16 +5655,16 @@
       </c>
       <c r="F191" s="5"/>
       <c r="J191" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K191">
         <v>6.85</v>
       </c>
       <c r="L191" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N191" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="192" spans="1:14" x14ac:dyDescent="0.25">
@@ -5676,16 +5676,16 @@
       </c>
       <c r="F192" s="5"/>
       <c r="J192" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K192">
         <v>1.69</v>
       </c>
       <c r="L192" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N192" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="193" spans="1:14" x14ac:dyDescent="0.25">
@@ -5697,19 +5697,19 @@
       </c>
       <c r="F193" s="5"/>
       <c r="J193" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K193">
         <v>27.04</v>
       </c>
       <c r="L193" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M193" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N193" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="194" spans="1:14" x14ac:dyDescent="0.25">
@@ -5721,16 +5721,16 @@
       </c>
       <c r="F194" s="5"/>
       <c r="J194" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K194">
         <v>7.4</v>
       </c>
       <c r="L194" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N194" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="195" spans="1:14" x14ac:dyDescent="0.25">
@@ -5742,16 +5742,16 @@
       </c>
       <c r="F195" s="5"/>
       <c r="J195" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K195">
         <v>1.91</v>
       </c>
       <c r="L195" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N195" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="196" spans="1:14" x14ac:dyDescent="0.25">
@@ -5763,19 +5763,19 @@
       </c>
       <c r="F196" s="5"/>
       <c r="J196" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K196">
         <v>27.04</v>
       </c>
       <c r="L196" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M196" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="N196" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="197" spans="1:14" x14ac:dyDescent="0.25">
@@ -5787,16 +5787,16 @@
       </c>
       <c r="F197" s="5"/>
       <c r="J197" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K197">
         <v>7.4</v>
       </c>
       <c r="L197" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N197" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="198" spans="1:14" x14ac:dyDescent="0.25">
@@ -5808,16 +5808,16 @@
       </c>
       <c r="F198" s="5"/>
       <c r="J198" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K198">
         <v>1.91</v>
       </c>
       <c r="L198" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N198" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="199" spans="1:14" x14ac:dyDescent="0.25">
@@ -5829,19 +5829,19 @@
       </c>
       <c r="F199" s="5"/>
       <c r="J199" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K199">
         <v>25.28</v>
       </c>
       <c r="L199" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M199" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="N199" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="200" spans="1:14" x14ac:dyDescent="0.25">
@@ -5853,16 +5853,16 @@
       </c>
       <c r="F200" s="5"/>
       <c r="J200" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K200">
         <v>7.4</v>
       </c>
       <c r="L200" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N200" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="201" spans="1:14" x14ac:dyDescent="0.25">
@@ -5874,16 +5874,16 @@
       </c>
       <c r="F201" s="5"/>
       <c r="J201" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K201" s="14">
         <v>2</v>
       </c>
       <c r="L201" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N201" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="202" spans="1:14" x14ac:dyDescent="0.25">
@@ -5891,125 +5891,125 @@
     </row>
     <row r="203" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F203" s="5"/>
       <c r="J203" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K203" s="5">
         <v>25</v>
       </c>
       <c r="L203" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M203" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="N203" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="204" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F204" s="5"/>
       <c r="J204" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K204" s="5">
         <v>7.8</v>
       </c>
       <c r="L204" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N204" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="205" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F205" s="5"/>
       <c r="J205" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K205" s="5">
         <v>1.7</v>
       </c>
       <c r="L205" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N205" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="206" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D206" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F206" s="5"/>
       <c r="J206" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K206" s="5">
         <v>26.2</v>
       </c>
       <c r="L206" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M206" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="N206" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="207" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D207" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F207" s="5"/>
       <c r="J207" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K207" s="5">
         <v>5.2</v>
       </c>
       <c r="L207" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N207" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="208" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D208" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F208" s="5"/>
       <c r="J208" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K208" s="5">
         <v>1.7</v>
       </c>
       <c r="L208" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N208" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="209" spans="1:14" x14ac:dyDescent="0.25">
@@ -6018,59 +6018,59 @@
     </row>
     <row r="210" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F210" s="5"/>
       <c r="J210" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K210" s="5">
         <v>29.9</v>
       </c>
       <c r="L210" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M210" t="s">
+        <v>99</v>
+      </c>
+      <c r="N210" t="s">
         <v>100</v>
-      </c>
-      <c r="N210" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="211" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F211" s="5"/>
       <c r="J211" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K211" s="5">
         <v>7.5</v>
       </c>
       <c r="L211" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N211" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="212" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F212" s="5"/>
       <c r="J212" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K212" s="5">
         <v>2</v>
       </c>
       <c r="L212" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N212" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="213" spans="1:14" x14ac:dyDescent="0.25">
@@ -6086,19 +6086,19 @@
       </c>
       <c r="F214" s="5"/>
       <c r="J214" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K214">
         <v>25</v>
       </c>
       <c r="L214" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M214" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="N214" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="215" spans="1:14" x14ac:dyDescent="0.25">
@@ -6110,16 +6110,16 @@
       </c>
       <c r="F215" s="5"/>
       <c r="J215" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K215">
         <v>5.35</v>
       </c>
       <c r="L215" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N215" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="216" spans="1:14" x14ac:dyDescent="0.25">
@@ -6131,16 +6131,16 @@
       </c>
       <c r="F216" s="5"/>
       <c r="J216" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K216" s="14">
         <v>2.08</v>
       </c>
       <c r="L216" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N216" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="217" spans="1:14" x14ac:dyDescent="0.25">
@@ -6151,19 +6151,19 @@
         <v>44</v>
       </c>
       <c r="J217" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K217" s="14">
         <v>24.9</v>
       </c>
       <c r="L217" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M217" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="N217" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="218" spans="1:14" x14ac:dyDescent="0.25">
@@ -6174,16 +6174,16 @@
         <v>44</v>
       </c>
       <c r="J218" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K218" s="14">
         <v>5.35</v>
       </c>
       <c r="L218" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N218" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="219" spans="1:14" x14ac:dyDescent="0.25">
@@ -6194,16 +6194,16 @@
         <v>44</v>
       </c>
       <c r="J219" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K219" s="14">
         <v>2.25</v>
       </c>
       <c r="L219" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N219" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="220" spans="1:14" x14ac:dyDescent="0.25">
@@ -6214,19 +6214,19 @@
         <v>42</v>
       </c>
       <c r="J220" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K220" s="14">
         <v>25</v>
       </c>
       <c r="L220" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M220" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N220" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="221" spans="1:14" x14ac:dyDescent="0.25">
@@ -6237,16 +6237,16 @@
         <v>42</v>
       </c>
       <c r="J221" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K221" s="14">
         <v>5.35</v>
       </c>
       <c r="L221" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N221" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="222" spans="1:14" x14ac:dyDescent="0.25">
@@ -6257,16 +6257,16 @@
         <v>42</v>
       </c>
       <c r="J222" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K222" s="14">
         <v>2.04</v>
       </c>
       <c r="L222" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N222" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="223" spans="1:14" x14ac:dyDescent="0.25">
@@ -6278,19 +6278,19 @@
       </c>
       <c r="F223" s="5"/>
       <c r="J223" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K223" s="14">
         <v>23.1</v>
       </c>
       <c r="L223" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M223" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="N223" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="224" spans="1:14" x14ac:dyDescent="0.25">
@@ -6302,16 +6302,16 @@
       </c>
       <c r="F224" s="5"/>
       <c r="J224" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K224" s="14">
         <v>5.36</v>
       </c>
       <c r="L224" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N224" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="225" spans="1:14" x14ac:dyDescent="0.25">
@@ -6323,16 +6323,16 @@
       </c>
       <c r="F225" s="5"/>
       <c r="J225" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K225" s="14">
         <v>2.64</v>
       </c>
       <c r="L225" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N225" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="226" spans="1:14" x14ac:dyDescent="0.25">
@@ -6341,19 +6341,19 @@
       </c>
       <c r="F226" s="5"/>
       <c r="J226" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K226" s="14">
         <v>25</v>
       </c>
       <c r="L226" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="M226" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="N226" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="227" spans="1:14" x14ac:dyDescent="0.25">
@@ -6362,16 +6362,16 @@
       </c>
       <c r="F227" s="5"/>
       <c r="J227" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="K227" s="14">
         <v>5.36</v>
       </c>
       <c r="L227" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="N227" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="228" spans="1:14" x14ac:dyDescent="0.25">
@@ -6380,16 +6380,16 @@
       </c>
       <c r="F228" s="5"/>
       <c r="J228" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="K228" s="14">
         <v>2.2799999999999998</v>
       </c>
       <c r="L228" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="N228" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="229" spans="1:14" x14ac:dyDescent="0.25">
@@ -6399,97 +6399,97 @@
     <row r="230" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F230" s="5"/>
       <c r="J230" s="6" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K230" s="17">
         <v>0</v>
       </c>
       <c r="L230" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="231" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F231" s="5"/>
       <c r="J231" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K231" s="17">
         <v>0</v>
       </c>
       <c r="L231" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="232" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F232" s="5"/>
       <c r="J232" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K232" s="17">
         <v>0</v>
       </c>
       <c r="L232" s="6" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="233" spans="1:14" x14ac:dyDescent="0.25">
       <c r="E233" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F233" s="5"/>
       <c r="J233" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="K233" s="16">
         <f>5.49/1.035</f>
         <v>5.304347826086957</v>
       </c>
       <c r="L233" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M233" t="s">
+        <v>120</v>
+      </c>
+      <c r="N233" t="s">
         <v>121</v>
-      </c>
-      <c r="N233" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="234" spans="1:14" x14ac:dyDescent="0.25">
       <c r="E234" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F234" s="5"/>
       <c r="J234" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="K234" s="16">
         <f>0.97/1.035</f>
         <v>0.9371980676328503</v>
       </c>
       <c r="L234" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N234" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="235" spans="1:14" x14ac:dyDescent="0.25">
       <c r="E235" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F235" s="5"/>
       <c r="J235" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="K235" s="16">
         <f>1.6/1.035</f>
         <v>1.5458937198067635</v>
       </c>
       <c r="L235" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N235" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="236" spans="1:14" x14ac:dyDescent="0.25">
@@ -6498,7 +6498,7 @@
     </row>
     <row r="237" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A237" s="11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B237" s="12"/>
       <c r="C237" s="12"/>
@@ -6519,7 +6519,7 @@
     </row>
     <row r="239" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A239" s="52" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F239" s="5"/>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="L240" s="6"/>
       <c r="M240" s="6" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="241" spans="1:14" x14ac:dyDescent="0.25">
@@ -6550,10 +6550,10 @@
         <v>60</v>
       </c>
       <c r="L241" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N241" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="242" spans="1:14" x14ac:dyDescent="0.25">
@@ -6576,10 +6576,10 @@
         <v>51</v>
       </c>
       <c r="L242" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N242" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="243" spans="1:14" x14ac:dyDescent="0.25">
@@ -6602,10 +6602,10 @@
         <v>52</v>
       </c>
       <c r="L243" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N243" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="244" spans="1:14" x14ac:dyDescent="0.25">
@@ -6625,10 +6625,10 @@
         <v>51</v>
       </c>
       <c r="L244" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N244" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="245" spans="1:14" x14ac:dyDescent="0.25">
@@ -6648,10 +6648,10 @@
         <v>51</v>
       </c>
       <c r="L245" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N245" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="246" spans="1:14" x14ac:dyDescent="0.25">
@@ -6671,10 +6671,10 @@
         <v>52</v>
       </c>
       <c r="L246" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N246" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="247" spans="1:14" x14ac:dyDescent="0.25">
@@ -6694,10 +6694,10 @@
         <v>52</v>
       </c>
       <c r="L247" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N247" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="248" spans="1:14" x14ac:dyDescent="0.25">
@@ -6717,7 +6717,7 @@
         <v>52</v>
       </c>
       <c r="L248" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M248" t="s">
         <v>14</v>
@@ -6737,10 +6737,10 @@
         <v>10</v>
       </c>
       <c r="L249" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N249" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="250" spans="1:14" x14ac:dyDescent="0.25">
@@ -6748,7 +6748,7 @@
         <v>1</v>
       </c>
       <c r="F250" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J250" t="s">
         <v>27</v>
@@ -6757,10 +6757,10 @@
         <v>60</v>
       </c>
       <c r="L250" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N250" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="251" spans="1:14" x14ac:dyDescent="0.25">
@@ -6780,16 +6780,16 @@
         <v>60</v>
       </c>
       <c r="L251" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M251" s="1"/>
       <c r="N251" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="252" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A252" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B252" s="5"/>
       <c r="C252" s="5"/>
@@ -6808,16 +6808,16 @@
         <v>24</v>
       </c>
       <c r="L252" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M252" s="1"/>
       <c r="N252" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="253" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A253" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B253" s="5"/>
       <c r="C253" s="5"/>
@@ -6836,16 +6836,16 @@
         <v>25</v>
       </c>
       <c r="L253" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M253" s="1"/>
       <c r="N253" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="254" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A254" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B254" s="5"/>
       <c r="C254" s="5"/>
@@ -6864,23 +6864,23 @@
         <v>10</v>
       </c>
       <c r="L254" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M254" s="1"/>
       <c r="N254" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="255" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A255" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B255" s="5"/>
       <c r="C255" s="5"/>
       <c r="D255" s="5"/>
       <c r="E255" s="5"/>
       <c r="F255" s="5" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G255" s="5"/>
       <c r="H255" s="5"/>
@@ -6892,16 +6892,16 @@
         <v>25</v>
       </c>
       <c r="L255" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M255" s="1"/>
       <c r="N255" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="256" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A256" s="5" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B256" s="5"/>
       <c r="C256" s="5"/>
@@ -6920,16 +6920,16 @@
         <v>60</v>
       </c>
       <c r="L256" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M256" s="1"/>
       <c r="N256" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="257" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A257" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B257" s="5"/>
       <c r="C257" s="5"/>
@@ -6948,16 +6948,16 @@
         <v>25</v>
       </c>
       <c r="L257" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M257" s="1"/>
       <c r="N257" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="258" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A258" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B258" s="5"/>
       <c r="C258" s="5"/>
@@ -6976,16 +6976,16 @@
         <v>25</v>
       </c>
       <c r="L258" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M258" s="1"/>
       <c r="N258" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="259" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A259" s="5" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B259" s="5"/>
       <c r="C259" s="5"/>
@@ -7004,11 +7004,11 @@
         <v>50</v>
       </c>
       <c r="L259" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M259" s="1"/>
       <c r="N259" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="260" spans="1:14" x14ac:dyDescent="0.25">
@@ -7025,10 +7025,10 @@
         <v>70</v>
       </c>
       <c r="L260" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N260" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="261" spans="1:14" x14ac:dyDescent="0.25">
@@ -7045,10 +7045,10 @@
         <v>51</v>
       </c>
       <c r="L261" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N261" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="262" spans="1:14" x14ac:dyDescent="0.25">
@@ -7065,10 +7065,10 @@
         <v>10</v>
       </c>
       <c r="L262" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N262" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="263" spans="1:14" x14ac:dyDescent="0.25">
@@ -7076,7 +7076,7 @@
         <v>37</v>
       </c>
       <c r="F263" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="J263" t="s">
         <v>27</v>
@@ -7085,15 +7085,15 @@
         <v>70</v>
       </c>
       <c r="L263" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N263" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="264" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A264" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B264" s="5"/>
       <c r="C264" s="5"/>
@@ -7112,16 +7112,16 @@
         <v>75</v>
       </c>
       <c r="L264" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M264" s="1"/>
       <c r="N264" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="265" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A265" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B265" s="5"/>
       <c r="C265" s="5"/>
@@ -7140,16 +7140,16 @@
         <v>60</v>
       </c>
       <c r="L265" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M265" s="1"/>
       <c r="N265" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="266" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A266" s="5" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B266" s="5"/>
       <c r="C266" s="5"/>
@@ -7168,22 +7168,22 @@
         <v>40</v>
       </c>
       <c r="L266" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M266" s="1"/>
       <c r="N266" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="267" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
+        <v>50</v>
+      </c>
+      <c r="C267" t="s">
         <v>51</v>
       </c>
-      <c r="C267" t="s">
+      <c r="D267" t="s">
         <v>52</v>
-      </c>
-      <c r="D267" t="s">
-        <v>53</v>
       </c>
       <c r="F267" s="5" t="s">
         <v>18</v>
@@ -7195,21 +7195,21 @@
         <v>40</v>
       </c>
       <c r="L267" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N267" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="268" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
+        <v>50</v>
+      </c>
+      <c r="C268" t="s">
         <v>51</v>
       </c>
-      <c r="C268" t="s">
+      <c r="D268" t="s">
         <v>52</v>
-      </c>
-      <c r="D268" t="s">
-        <v>53</v>
       </c>
       <c r="F268" s="5" t="s">
         <v>19</v>
@@ -7221,21 +7221,21 @@
         <v>40</v>
       </c>
       <c r="L268" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N268" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="269" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
+        <v>50</v>
+      </c>
+      <c r="C269" t="s">
         <v>51</v>
       </c>
-      <c r="C269" t="s">
+      <c r="D269" t="s">
         <v>52</v>
-      </c>
-      <c r="D269" t="s">
-        <v>53</v>
       </c>
       <c r="F269" s="5" t="s">
         <v>20</v>
@@ -7247,10 +7247,10 @@
         <v>40</v>
       </c>
       <c r="L269" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N269" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
     </row>
     <row r="270" spans="1:14" x14ac:dyDescent="0.25">
@@ -7258,7 +7258,7 @@
     </row>
     <row r="271" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A271" s="11" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B271" s="12"/>
       <c r="C271" s="12"/>
@@ -7278,77 +7278,64 @@
       <c r="F272" s="51"/>
     </row>
     <row r="273" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G273" t="s">
-        <v>196</v>
-      </c>
-      <c r="J273" s="1" t="s">
+      <c r="G273" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H273" s="6"/>
+      <c r="I273" s="6"/>
+      <c r="J273" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="K273" s="1">
+      <c r="K273" s="6">
         <v>0</v>
       </c>
       <c r="L273" s="1"/>
-      <c r="M273" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="M273" s="1"/>
     </row>
     <row r="274" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G274" t="s">
-        <v>196</v>
-      </c>
-      <c r="J274" s="1" t="s">
+      <c r="G274" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="H274" s="6"/>
+      <c r="I274" s="6"/>
+      <c r="J274" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="K274" s="1">
+      <c r="K274" s="6">
         <v>0</v>
       </c>
       <c r="L274" s="1"/>
-      <c r="M274" s="1" t="s">
-        <v>50</v>
-      </c>
+      <c r="M274" s="1"/>
     </row>
     <row r="275" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A275" s="53"/>
-      <c r="J275" s="1"/>
-      <c r="K275" s="1"/>
+      <c r="G275" s="6"/>
+      <c r="H275" s="6"/>
+      <c r="I275" s="6"/>
+      <c r="J275" s="6" t="s">
+        <v>203</v>
+      </c>
+      <c r="K275" s="6">
+        <v>0</v>
+      </c>
       <c r="L275" s="1"/>
       <c r="M275" s="1"/>
     </row>
     <row r="276" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A276" t="s">
-        <v>1</v>
-      </c>
-      <c r="F276" t="s">
-        <v>18</v>
-      </c>
-      <c r="G276" t="s">
-        <v>196</v>
-      </c>
-      <c r="H276" t="s">
-        <v>21</v>
-      </c>
-      <c r="J276" t="s">
-        <v>22</v>
-      </c>
-      <c r="K276">
-        <v>4</v>
-      </c>
-      <c r="L276" t="s">
-        <v>56</v>
-      </c>
-      <c r="N276" t="s">
-        <v>180</v>
-      </c>
+      <c r="A276" s="53"/>
+      <c r="K276" s="1"/>
+      <c r="L276" s="1"/>
+      <c r="M276" s="1"/>
     </row>
     <row r="277" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>1</v>
       </c>
       <c r="F277" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G277" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H277" t="s">
         <v>21</v>
@@ -7360,10 +7347,10 @@
         <v>4</v>
       </c>
       <c r="L277" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N277" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="278" spans="1:14" x14ac:dyDescent="0.25">
@@ -7371,10 +7358,10 @@
         <v>1</v>
       </c>
       <c r="F278" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G278" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H278" t="s">
         <v>21</v>
@@ -7383,13 +7370,13 @@
         <v>22</v>
       </c>
       <c r="K278">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="L278" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N278" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="279" spans="1:14" x14ac:dyDescent="0.25">
@@ -7397,10 +7384,10 @@
         <v>1</v>
       </c>
       <c r="F279" t="s">
-        <v>183</v>
+        <v>20</v>
       </c>
       <c r="G279" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H279" t="s">
         <v>21</v>
@@ -7409,60 +7396,54 @@
         <v>22</v>
       </c>
       <c r="K279">
+        <v>20</v>
+      </c>
+      <c r="L279" t="s">
+        <v>55</v>
+      </c>
+      <c r="N279" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="280" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A280" t="s">
+        <v>1</v>
+      </c>
+      <c r="F280" t="s">
+        <v>182</v>
+      </c>
+      <c r="G280" t="s">
+        <v>195</v>
+      </c>
+      <c r="H280" t="s">
+        <v>21</v>
+      </c>
+      <c r="J280" t="s">
+        <v>22</v>
+      </c>
+      <c r="K280">
         <v>4</v>
       </c>
-      <c r="L279" t="s">
-        <v>56</v>
-      </c>
-      <c r="N279" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="280" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A280" s="43" t="s">
+      <c r="L280" t="s">
         <v>55</v>
       </c>
-      <c r="B280" s="43"/>
-      <c r="C280" s="43"/>
-      <c r="D280" s="43"/>
-      <c r="E280" s="43"/>
-      <c r="F280" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="G280" t="s">
-        <v>196</v>
-      </c>
-      <c r="H280" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="I280" s="43"/>
-      <c r="J280" s="43" t="s">
-        <v>22</v>
-      </c>
-      <c r="K280" s="43">
-        <v>4</v>
-      </c>
-      <c r="L280" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="M280" s="1"/>
       <c r="N280" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="281" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A281" s="43" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B281" s="43"/>
       <c r="C281" s="43"/>
       <c r="D281" s="43"/>
       <c r="E281" s="43"/>
       <c r="F281" s="43" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G281" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H281" s="43" t="s">
         <v>21</v>
@@ -7472,29 +7453,29 @@
         <v>22</v>
       </c>
       <c r="K281" s="43">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="L281" s="43" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M281" s="1"/>
       <c r="N281" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="282" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A282" s="43" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B282" s="43"/>
       <c r="C282" s="43"/>
       <c r="D282" s="43"/>
       <c r="E282" s="43"/>
       <c r="F282" s="43" t="s">
-        <v>175</v>
+        <v>20</v>
       </c>
       <c r="G282" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H282" s="43" t="s">
         <v>21</v>
@@ -7504,29 +7485,29 @@
         <v>22</v>
       </c>
       <c r="K282" s="43">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="L282" s="43" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M282" s="1"/>
       <c r="N282" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="283" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A283" s="43" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="B283" s="43"/>
       <c r="C283" s="43"/>
       <c r="D283" s="43"/>
       <c r="E283" s="43"/>
-      <c r="F283" t="s">
-        <v>19</v>
+      <c r="F283" s="43" t="s">
+        <v>174</v>
       </c>
       <c r="G283" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H283" s="43" t="s">
         <v>21</v>
@@ -7539,26 +7520,26 @@
         <v>4</v>
       </c>
       <c r="L283" s="43" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M283" s="1"/>
       <c r="N283" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="284" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A284" s="43" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B284" s="43"/>
       <c r="C284" s="43"/>
       <c r="D284" s="43"/>
       <c r="E284" s="43"/>
       <c r="F284" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G284" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H284" s="43" t="s">
         <v>21</v>
@@ -7568,40 +7549,46 @@
         <v>22</v>
       </c>
       <c r="K284" s="43">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="L284" s="43" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M284" s="1"/>
       <c r="N284" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="285" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A285" t="s">
-        <v>37</v>
-      </c>
+      <c r="A285" s="43" t="s">
+        <v>60</v>
+      </c>
+      <c r="B285" s="43"/>
+      <c r="C285" s="43"/>
+      <c r="D285" s="43"/>
+      <c r="E285" s="43"/>
       <c r="F285" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G285" t="s">
-        <v>196</v>
-      </c>
-      <c r="H285" t="s">
+        <v>195</v>
+      </c>
+      <c r="H285" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="J285" t="s">
+      <c r="I285" s="43"/>
+      <c r="J285" s="43" t="s">
         <v>22</v>
       </c>
-      <c r="K285">
-        <v>14</v>
-      </c>
-      <c r="L285" t="s">
-        <v>56</v>
-      </c>
+      <c r="K285" s="43">
+        <v>15</v>
+      </c>
+      <c r="L285" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="M285" s="1"/>
       <c r="N285" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="286" spans="1:14" x14ac:dyDescent="0.25">
@@ -7609,10 +7596,10 @@
         <v>37</v>
       </c>
       <c r="F286" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G286" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H286" t="s">
         <v>21</v>
@@ -7621,13 +7608,13 @@
         <v>22</v>
       </c>
       <c r="K286">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L286" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N286" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="287" spans="1:14" x14ac:dyDescent="0.25">
@@ -7635,10 +7622,10 @@
         <v>37</v>
       </c>
       <c r="F287" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G287" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H287" t="s">
         <v>21</v>
@@ -7647,13 +7634,13 @@
         <v>22</v>
       </c>
       <c r="K287">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="L287" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N287" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="288" spans="1:14" x14ac:dyDescent="0.25">
@@ -7661,10 +7648,10 @@
         <v>37</v>
       </c>
       <c r="F288" t="s">
-        <v>183</v>
+        <v>20</v>
       </c>
       <c r="G288" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H288" t="s">
         <v>21</v>
@@ -7673,24 +7660,24 @@
         <v>22</v>
       </c>
       <c r="K288">
-        <v>14</v>
+        <v>25</v>
       </c>
       <c r="L288" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N288" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="289" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="F289" t="s">
-        <v>18</v>
+        <v>182</v>
       </c>
       <c r="G289" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H289" t="s">
         <v>21</v>
@@ -7699,24 +7686,24 @@
         <v>22</v>
       </c>
       <c r="K289">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L289" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N289" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="290" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F290" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G290" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H290" t="s">
         <v>21</v>
@@ -7728,21 +7715,21 @@
         <v>10</v>
       </c>
       <c r="L290" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N290" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="291" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F291" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G291" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H291" t="s">
         <v>21</v>
@@ -7751,30 +7738,24 @@
         <v>22</v>
       </c>
       <c r="K291">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="L291" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N291" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="292" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>51</v>
-      </c>
-      <c r="C292" t="s">
-        <v>62</v>
-      </c>
-      <c r="D292" t="s">
-        <v>184</v>
+        <v>50</v>
       </c>
       <c r="F292" t="s">
         <v>20</v>
       </c>
       <c r="G292" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H292" t="s">
         <v>21</v>
@@ -7783,30 +7764,30 @@
         <v>22</v>
       </c>
       <c r="K292">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="L292" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N292" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="293" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C293" t="s">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="D293" t="s">
-        <v>53</v>
+        <v>183</v>
       </c>
       <c r="F293" t="s">
         <v>20</v>
       </c>
       <c r="G293" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H293" t="s">
         <v>21</v>
@@ -7815,71 +7796,71 @@
         <v>22</v>
       </c>
       <c r="K293">
+        <v>20</v>
+      </c>
+      <c r="L293" t="s">
+        <v>55</v>
+      </c>
+      <c r="N293" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="294" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A294" t="s">
+        <v>50</v>
+      </c>
+      <c r="C294" t="s">
+        <v>51</v>
+      </c>
+      <c r="D294" t="s">
+        <v>52</v>
+      </c>
+      <c r="F294" t="s">
+        <v>20</v>
+      </c>
+      <c r="G294" t="s">
+        <v>195</v>
+      </c>
+      <c r="H294" t="s">
+        <v>21</v>
+      </c>
+      <c r="J294" t="s">
+        <v>22</v>
+      </c>
+      <c r="K294">
         <v>10</v>
       </c>
-      <c r="L293" t="s">
-        <v>56</v>
-      </c>
-      <c r="N293" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="294" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A294" s="1"/>
-      <c r="B294" s="1"/>
-      <c r="C294" s="1"/>
-      <c r="D294" s="1"/>
-      <c r="E294" s="1"/>
-      <c r="F294" s="1"/>
-      <c r="G294" s="1"/>
-      <c r="H294" s="1"/>
-      <c r="I294" s="1"/>
-      <c r="J294" s="1"/>
-      <c r="K294" s="1"/>
-      <c r="L294" s="1"/>
-      <c r="M294" s="1"/>
+      <c r="L294" t="s">
+        <v>55</v>
+      </c>
+      <c r="N294" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="295" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A295" t="s">
-        <v>1</v>
-      </c>
-      <c r="F295" t="s">
-        <v>18</v>
-      </c>
-      <c r="G295" t="s">
-        <v>196</v>
-      </c>
-      <c r="H295" t="s">
-        <v>21</v>
-      </c>
-      <c r="J295" t="s">
-        <v>23</v>
-      </c>
-      <c r="K295">
-        <v>3</v>
-      </c>
-      <c r="L295" t="s">
-        <v>56</v>
-      </c>
-      <c r="N295" t="s">
-        <v>181</v>
-      </c>
+      <c r="A295" s="1"/>
+      <c r="B295" s="1"/>
+      <c r="C295" s="1"/>
+      <c r="D295" s="1"/>
+      <c r="E295" s="1"/>
+      <c r="F295" s="1"/>
+      <c r="G295" s="1"/>
+      <c r="H295" s="1"/>
+      <c r="I295" s="1"/>
+      <c r="J295" s="1"/>
+      <c r="K295" s="1"/>
+      <c r="L295" s="1"/>
+      <c r="M295" s="1"/>
     </row>
     <row r="296" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>1</v>
       </c>
-      <c r="C296" t="s">
-        <v>2</v>
-      </c>
-      <c r="D296" t="s">
-        <v>3</v>
-      </c>
       <c r="F296" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G296" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H296" t="s">
         <v>21</v>
@@ -7888,13 +7869,13 @@
         <v>23</v>
       </c>
       <c r="K296">
-        <v>18</v>
+        <v>3</v>
       </c>
       <c r="L296" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N296" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="297" spans="1:14" x14ac:dyDescent="0.25">
@@ -7902,7 +7883,7 @@
         <v>1</v>
       </c>
       <c r="C297" t="s">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="D297" t="s">
         <v>3</v>
@@ -7911,7 +7892,7 @@
         <v>19</v>
       </c>
       <c r="G297" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H297" t="s">
         <v>21</v>
@@ -7920,27 +7901,30 @@
         <v>23</v>
       </c>
       <c r="K297">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L297" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N297" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="298" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>1</v>
       </c>
+      <c r="C298" t="s">
+        <v>7</v>
+      </c>
       <c r="D298" t="s">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="F298" t="s">
         <v>19</v>
       </c>
       <c r="G298" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H298" t="s">
         <v>21</v>
@@ -7949,13 +7933,13 @@
         <v>23</v>
       </c>
       <c r="K298">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="L298" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N298" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="299" spans="1:14" x14ac:dyDescent="0.25">
@@ -7963,13 +7947,13 @@
         <v>1</v>
       </c>
       <c r="D299" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F299" t="s">
         <v>19</v>
       </c>
       <c r="G299" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H299" t="s">
         <v>21</v>
@@ -7981,10 +7965,10 @@
         <v>18</v>
       </c>
       <c r="L299" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N299" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="300" spans="1:14" x14ac:dyDescent="0.25">
@@ -7992,13 +7976,13 @@
         <v>1</v>
       </c>
       <c r="D300" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F300" t="s">
         <v>19</v>
       </c>
       <c r="G300" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H300" t="s">
         <v>21</v>
@@ -8007,13 +7991,13 @@
         <v>23</v>
       </c>
       <c r="K300">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L300" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N300" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="301" spans="1:14" x14ac:dyDescent="0.25">
@@ -8021,13 +8005,13 @@
         <v>1</v>
       </c>
       <c r="D301" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="F301" t="s">
         <v>19</v>
       </c>
       <c r="G301" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H301" t="s">
         <v>21</v>
@@ -8039,10 +8023,10 @@
         <v>17</v>
       </c>
       <c r="L301" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N301" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="302" spans="1:14" x14ac:dyDescent="0.25">
@@ -8050,13 +8034,13 @@
         <v>1</v>
       </c>
       <c r="D302" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F302" t="s">
         <v>19</v>
       </c>
       <c r="G302" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H302" t="s">
         <v>21</v>
@@ -8068,24 +8052,24 @@
         <v>17</v>
       </c>
       <c r="L302" t="s">
-        <v>56</v>
-      </c>
-      <c r="M302" t="s">
-        <v>14</v>
+        <v>55</v>
       </c>
       <c r="N302" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="303" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>1</v>
       </c>
+      <c r="D303" t="s">
+        <v>13</v>
+      </c>
       <c r="F303" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G303" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H303" t="s">
         <v>21</v>
@@ -8094,13 +8078,16 @@
         <v>23</v>
       </c>
       <c r="K303">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="L303" t="s">
-        <v>56</v>
+        <v>55</v>
+      </c>
+      <c r="M303" t="s">
+        <v>14</v>
       </c>
       <c r="N303" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="304" spans="1:14" x14ac:dyDescent="0.25">
@@ -8108,10 +8095,10 @@
         <v>1</v>
       </c>
       <c r="F304" t="s">
-        <v>183</v>
+        <v>20</v>
       </c>
       <c r="G304" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H304" t="s">
         <v>21</v>
@@ -8120,60 +8107,54 @@
         <v>23</v>
       </c>
       <c r="K304">
+        <v>30</v>
+      </c>
+      <c r="L304" t="s">
+        <v>55</v>
+      </c>
+      <c r="N304" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="305" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>1</v>
+      </c>
+      <c r="F305" t="s">
+        <v>182</v>
+      </c>
+      <c r="G305" t="s">
+        <v>195</v>
+      </c>
+      <c r="H305" t="s">
+        <v>21</v>
+      </c>
+      <c r="J305" t="s">
+        <v>23</v>
+      </c>
+      <c r="K305">
         <v>2.75</v>
       </c>
-      <c r="L304" t="s">
-        <v>56</v>
-      </c>
-      <c r="N304" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="305" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A305" s="43" t="s">
+      <c r="L305" t="s">
         <v>55</v>
       </c>
-      <c r="B305" s="43"/>
-      <c r="C305" s="43"/>
-      <c r="D305" s="43"/>
-      <c r="E305" s="43"/>
-      <c r="F305" s="43" t="s">
-        <v>19</v>
-      </c>
-      <c r="G305" t="s">
-        <v>196</v>
-      </c>
-      <c r="H305" s="43" t="s">
-        <v>21</v>
-      </c>
-      <c r="I305" s="43"/>
-      <c r="J305" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="K305" s="43">
-        <v>25</v>
-      </c>
-      <c r="L305" s="43" t="s">
-        <v>56</v>
-      </c>
-      <c r="M305" s="1"/>
       <c r="N305" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="306" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A306" s="43" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B306" s="43"/>
       <c r="C306" s="43"/>
       <c r="D306" s="43"/>
       <c r="E306" s="43"/>
       <c r="F306" s="43" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G306" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H306" s="43" t="s">
         <v>21</v>
@@ -8183,29 +8164,29 @@
         <v>23</v>
       </c>
       <c r="K306" s="43">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="L306" s="43" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M306" s="1"/>
       <c r="N306" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="307" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A307" s="43" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B307" s="43"/>
       <c r="C307" s="43"/>
       <c r="D307" s="43"/>
       <c r="E307" s="43"/>
       <c r="F307" s="43" t="s">
-        <v>175</v>
+        <v>20</v>
       </c>
       <c r="G307" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H307" s="43" t="s">
         <v>21</v>
@@ -8215,40 +8196,46 @@
         <v>23</v>
       </c>
       <c r="K307" s="43">
-        <v>0.25</v>
+        <v>33</v>
       </c>
       <c r="L307" s="43" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M307" s="1"/>
       <c r="N307" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="308" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A308" t="s">
-        <v>37</v>
-      </c>
-      <c r="F308" t="s">
-        <v>18</v>
+      <c r="A308" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="B308" s="43"/>
+      <c r="C308" s="43"/>
+      <c r="D308" s="43"/>
+      <c r="E308" s="43"/>
+      <c r="F308" s="43" t="s">
+        <v>174</v>
       </c>
       <c r="G308" t="s">
-        <v>196</v>
-      </c>
-      <c r="H308" t="s">
+        <v>195</v>
+      </c>
+      <c r="H308" s="43" t="s">
         <v>21</v>
       </c>
-      <c r="J308" t="s">
+      <c r="I308" s="43"/>
+      <c r="J308" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="K308">
-        <v>4</v>
-      </c>
-      <c r="L308" t="s">
-        <v>56</v>
-      </c>
+      <c r="K308" s="43">
+        <v>0.25</v>
+      </c>
+      <c r="L308" s="43" t="s">
+        <v>55</v>
+      </c>
+      <c r="M308" s="1"/>
       <c r="N308" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="309" spans="1:14" x14ac:dyDescent="0.25">
@@ -8256,10 +8243,10 @@
         <v>37</v>
       </c>
       <c r="F309" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G309" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H309" t="s">
         <v>21</v>
@@ -8268,13 +8255,13 @@
         <v>23</v>
       </c>
       <c r="K309">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="L309" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N309" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="310" spans="1:14" x14ac:dyDescent="0.25">
@@ -8282,10 +8269,10 @@
         <v>37</v>
       </c>
       <c r="F310" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G310" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H310" t="s">
         <v>21</v>
@@ -8294,13 +8281,13 @@
         <v>23</v>
       </c>
       <c r="K310">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="L310" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N310" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="311" spans="1:14" x14ac:dyDescent="0.25">
@@ -8308,10 +8295,10 @@
         <v>37</v>
       </c>
       <c r="F311" t="s">
-        <v>183</v>
+        <v>20</v>
       </c>
       <c r="G311" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H311" t="s">
         <v>21</v>
@@ -8320,24 +8307,24 @@
         <v>23</v>
       </c>
       <c r="K311">
-        <v>2.75</v>
+        <v>30</v>
       </c>
       <c r="L311" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N311" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="312" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="F312" t="s">
-        <v>18</v>
+        <v>182</v>
       </c>
       <c r="G312" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H312" t="s">
         <v>21</v>
@@ -8346,24 +8333,24 @@
         <v>23</v>
       </c>
       <c r="K312">
-        <v>4</v>
+        <v>2.75</v>
       </c>
       <c r="L312" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N312" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="313" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A313" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F313" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G313" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H313" t="s">
         <v>21</v>
@@ -8372,24 +8359,24 @@
         <v>23</v>
       </c>
       <c r="K313">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="L313" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N313" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="314" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F314" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G314" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H314" t="s">
         <v>21</v>
@@ -8398,30 +8385,24 @@
         <v>23</v>
       </c>
       <c r="K314">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="L314" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N314" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="315" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
-        <v>51</v>
-      </c>
-      <c r="C315" t="s">
-        <v>52</v>
-      </c>
-      <c r="D315" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F315" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G315" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H315" t="s">
         <v>21</v>
@@ -8430,30 +8411,30 @@
         <v>23</v>
       </c>
       <c r="K315">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="L315" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N315" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="316" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A316" t="s">
+        <v>50</v>
+      </c>
+      <c r="C316" t="s">
         <v>51</v>
       </c>
-      <c r="C316" t="s">
+      <c r="D316" t="s">
         <v>52</v>
       </c>
-      <c r="D316" t="s">
-        <v>53</v>
-      </c>
       <c r="F316" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G316" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H316" t="s">
         <v>21</v>
@@ -8465,133 +8446,142 @@
         <v>5</v>
       </c>
       <c r="L316" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N316" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="318" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F318" t="s">
-        <v>18</v>
-      </c>
-      <c r="G318" t="s">
-        <v>196</v>
-      </c>
-      <c r="H318" t="s">
-        <v>24</v>
-      </c>
-      <c r="J318" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="317" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A317" t="s">
+        <v>50</v>
+      </c>
+      <c r="C317" t="s">
+        <v>51</v>
+      </c>
+      <c r="D317" t="s">
+        <v>52</v>
+      </c>
+      <c r="F317" t="s">
+        <v>20</v>
+      </c>
+      <c r="G317" t="s">
+        <v>195</v>
+      </c>
+      <c r="H317" t="s">
+        <v>21</v>
+      </c>
+      <c r="J317" t="s">
         <v>23</v>
       </c>
-      <c r="K318">
-        <v>0.01</v>
-      </c>
-      <c r="L318" t="s">
-        <v>57</v>
-      </c>
-      <c r="N318" t="s">
-        <v>189</v>
+      <c r="K317">
+        <v>5</v>
+      </c>
+      <c r="L317" t="s">
+        <v>55</v>
+      </c>
+      <c r="N317" t="s">
+        <v>180</v>
       </c>
     </row>
     <row r="319" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F319" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G319" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H319" t="s">
         <v>24</v>
       </c>
       <c r="J319" t="s">
-        <v>23</v>
+        <v>203</v>
       </c>
       <c r="K319">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="L319" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N319" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="320" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F320" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G320" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H320" t="s">
         <v>24</v>
       </c>
       <c r="J320" t="s">
-        <v>23</v>
+        <v>203</v>
       </c>
       <c r="K320">
         <v>1</v>
       </c>
       <c r="L320" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N320" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="321" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F321" t="s">
-        <v>175</v>
+        <v>20</v>
       </c>
       <c r="G321" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H321" t="s">
         <v>24</v>
       </c>
       <c r="J321" t="s">
-        <v>23</v>
+        <v>203</v>
       </c>
       <c r="K321">
         <v>1</v>
       </c>
       <c r="L321" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="N321" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="323" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F323" t="s">
-        <v>18</v>
-      </c>
-      <c r="G323" t="s">
-        <v>196</v>
-      </c>
-      <c r="H323" t="s">
-        <v>25</v>
-      </c>
-      <c r="J323" t="s">
-        <v>23</v>
-      </c>
-      <c r="K323">
-        <v>0.5</v>
-      </c>
-      <c r="L323" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="322" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F322" t="s">
+        <v>174</v>
+      </c>
+      <c r="G322" t="s">
+        <v>195</v>
+      </c>
+      <c r="H322" t="s">
+        <v>24</v>
+      </c>
+      <c r="J322" t="s">
+        <v>203</v>
+      </c>
+      <c r="K322">
+        <v>1</v>
+      </c>
+      <c r="L322" t="s">
         <v>56</v>
       </c>
-      <c r="N323" t="s">
+      <c r="N322" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="324" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F324" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G324" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H324" t="s">
         <v>25</v>
@@ -8603,18 +8593,18 @@
         <v>0.5</v>
       </c>
       <c r="L324" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N324" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="325" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F325" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G325" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H325" t="s">
         <v>25</v>
@@ -8623,21 +8613,21 @@
         <v>23</v>
       </c>
       <c r="K325">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="L325" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N325" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="326" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F326" t="s">
-        <v>183</v>
+        <v>20</v>
       </c>
       <c r="G326" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H326" t="s">
         <v>25</v>
@@ -8646,21 +8636,21 @@
         <v>23</v>
       </c>
       <c r="K326">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L326" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N326" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="327" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F327" s="43" t="s">
-        <v>175</v>
+      <c r="F327" t="s">
+        <v>182</v>
       </c>
       <c r="G327" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H327" t="s">
         <v>25</v>
@@ -8669,147 +8659,156 @@
         <v>23</v>
       </c>
       <c r="K327">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L327" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="N327" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="329" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="F329" t="s">
-        <v>18</v>
-      </c>
-      <c r="G329" t="s">
-        <v>196</v>
-      </c>
-      <c r="H329" t="s">
-        <v>26</v>
-      </c>
-      <c r="J329" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="328" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F328" s="43" t="s">
+        <v>174</v>
+      </c>
+      <c r="G328" t="s">
+        <v>195</v>
+      </c>
+      <c r="H328" t="s">
+        <v>25</v>
+      </c>
+      <c r="J328" t="s">
         <v>23</v>
       </c>
-      <c r="K329">
-        <v>0.31</v>
-      </c>
-      <c r="L329" t="s">
-        <v>57</v>
-      </c>
-      <c r="M329" t="s">
+      <c r="K328">
+        <v>1</v>
+      </c>
+      <c r="L328" t="s">
+        <v>55</v>
+      </c>
+      <c r="N328" t="s">
         <v>187</v>
-      </c>
-      <c r="N329" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="330" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F330" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G330" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H330" t="s">
         <v>26</v>
       </c>
       <c r="J330" t="s">
-        <v>23</v>
+        <v>203</v>
       </c>
       <c r="K330">
-        <v>31</v>
+        <v>0.31</v>
       </c>
       <c r="L330" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M330" t="s">
-        <v>19</v>
+        <v>186</v>
       </c>
       <c r="N330" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="331" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F331" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G331" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H331" t="s">
         <v>26</v>
       </c>
       <c r="J331" t="s">
-        <v>23</v>
+        <v>203</v>
       </c>
       <c r="K331">
         <v>31</v>
       </c>
       <c r="L331" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M331" t="s">
         <v>19</v>
       </c>
       <c r="N331" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="332" spans="1:14" x14ac:dyDescent="0.25">
       <c r="F332" t="s">
-        <v>175</v>
+        <v>20</v>
       </c>
       <c r="G332" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H332" t="s">
         <v>26</v>
       </c>
       <c r="J332" t="s">
-        <v>23</v>
+        <v>203</v>
       </c>
       <c r="K332">
         <v>31</v>
       </c>
       <c r="L332" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="M332" t="s">
         <v>19</v>
       </c>
       <c r="N332" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="334" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A334" s="1" t="s">
-        <v>199</v>
+        <v>185</v>
+      </c>
+    </row>
+    <row r="333" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="F333" t="s">
+        <v>174</v>
+      </c>
+      <c r="G333" t="s">
+        <v>195</v>
+      </c>
+      <c r="H333" t="s">
+        <v>26</v>
+      </c>
+      <c r="J333" t="s">
+        <v>203</v>
+      </c>
+      <c r="K333">
+        <v>31</v>
+      </c>
+      <c r="L333" t="s">
+        <v>56</v>
+      </c>
+      <c r="M333" t="s">
+        <v>19</v>
+      </c>
+      <c r="N333" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="335" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="G335" t="s">
-        <v>197</v>
-      </c>
-      <c r="H335" t="s">
-        <v>197</v>
-      </c>
-      <c r="J335" t="s">
-        <v>22</v>
-      </c>
-      <c r="K335">
-        <v>0</v>
+      <c r="A335" s="1" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="336" spans="1:14" x14ac:dyDescent="0.25">
       <c r="G336" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H336" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J336" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K336">
         <v>0</v>
@@ -8817,29 +8816,43 @@
     </row>
     <row r="337" spans="7:11" x14ac:dyDescent="0.25">
       <c r="G337" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="H337" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="J337" t="s">
-        <v>22</v>
-      </c>
-      <c r="K337" s="44">
+        <v>23</v>
+      </c>
+      <c r="K337">
         <v>0</v>
       </c>
     </row>
     <row r="338" spans="7:11" x14ac:dyDescent="0.25">
       <c r="G338" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H338" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J338" t="s">
+        <v>22</v>
+      </c>
+      <c r="K338" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="339" spans="7:11" x14ac:dyDescent="0.25">
+      <c r="G339" t="s">
+        <v>197</v>
+      </c>
+      <c r="H339" t="s">
+        <v>197</v>
+      </c>
+      <c r="J339" t="s">
         <v>23</v>
       </c>
-      <c r="K338">
+      <c r="K339">
         <v>0</v>
       </c>
     </row>
@@ -8856,17 +8869,17 @@
   <sheetData>
     <row r="2" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="4" spans="2:32" x14ac:dyDescent="0.25">
       <c r="R4" s="4" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="5" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B5" s="46" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C5" s="47" t="s">
         <v>1</v>
@@ -8890,10 +8903,10 @@
         <v>1</v>
       </c>
       <c r="J5" s="47" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="K5" s="47" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L5" s="47" t="s">
         <v>37</v>
@@ -8905,13 +8918,13 @@
         <v>37</v>
       </c>
       <c r="O5" s="47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="P5" s="47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="R5" s="46" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="S5" s="47" t="s">
         <v>1</v>
@@ -8935,10 +8948,10 @@
         <v>1</v>
       </c>
       <c r="Z5" s="47" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="AA5" s="47" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AB5" s="47" t="s">
         <v>37</v>
@@ -8950,15 +8963,15 @@
         <v>37</v>
       </c>
       <c r="AE5" s="47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="AF5" s="47" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B6" s="46" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C6" s="47" t="s">
         <v>2</v>
@@ -8978,10 +8991,10 @@
       <c r="N6" s="47"/>
       <c r="O6" s="47"/>
       <c r="P6" s="47" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="R6" s="46" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="S6" s="47" t="s">
         <v>2</v>
@@ -9001,12 +9014,12 @@
       <c r="AD6" s="47"/>
       <c r="AE6" s="47"/>
       <c r="AF6" s="47" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B7" s="46" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C7" s="47" t="s">
         <v>3</v>
@@ -9040,10 +9053,10 @@
       </c>
       <c r="O7" s="47"/>
       <c r="P7" s="47" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="R7" s="46" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="S7" s="47" t="s">
         <v>3</v>
@@ -9077,7 +9090,7 @@
       </c>
       <c r="AE7" s="47"/>
       <c r="AF7" s="47" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="2:32" x14ac:dyDescent="0.25">
@@ -9136,7 +9149,7 @@
         <v>0</v>
       </c>
       <c r="R8" s="46" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="S8" s="50" t="str">
         <f>S5&amp;S6&amp;S7</f>
@@ -9364,7 +9377,7 @@
         <v>2.6666666666666665</v>
       </c>
       <c r="N10" s="45">
-        <f t="shared" ref="N10:N12" si="5">M10</f>
+        <f t="shared" ref="N10:N11" si="5">M10</f>
         <v>2.6666666666666665</v>
       </c>
       <c r="O10" s="44">
@@ -9557,7 +9570,7 @@
     </row>
     <row r="12" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B12" s="47" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C12" s="44">
         <f>C83+C97</f>
@@ -9612,7 +9625,7 @@
         <v>0</v>
       </c>
       <c r="R12" s="47" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="S12" s="44">
         <f t="shared" si="4"/>
@@ -9673,7 +9686,7 @@
     </row>
     <row r="13" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B13" s="47" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C13" s="44">
         <v>0</v>
@@ -9721,7 +9734,7 @@
         <v>0</v>
       </c>
       <c r="R13" s="47" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="S13" s="44">
         <f t="shared" si="4"/>
@@ -9782,7 +9795,7 @@
     </row>
     <row r="14" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B14" s="46" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="C14" s="49">
         <f>SUM(C8:C13)</f>
@@ -9841,7 +9854,7 @@
         <v>100</v>
       </c>
       <c r="R14" s="46" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="S14" s="49">
         <f>SUM(S9:S13)</f>
@@ -9901,8 +9914,8 @@
       </c>
     </row>
     <row r="15" spans="2:32" x14ac:dyDescent="0.25">
-      <c r="B15" s="67" t="s">
-        <v>163</v>
+      <c r="B15" s="55" t="s">
+        <v>162</v>
       </c>
       <c r="C15" s="49"/>
       <c r="D15" s="49"/>
@@ -9918,8 +9931,8 @@
       <c r="N15" s="49"/>
       <c r="O15" s="49"/>
       <c r="P15" s="49"/>
-      <c r="R15" s="67" t="s">
-        <v>163</v>
+      <c r="R15" s="55" t="s">
+        <v>162</v>
       </c>
       <c r="S15" s="49"/>
       <c r="T15" s="49"/>
@@ -9995,112 +10008,112 @@
       <c r="R16" s="48" t="s">
         <v>17</v>
       </c>
-      <c r="S16" s="66">
+      <c r="S16" s="54">
         <f>C16</f>
         <v>65.600000000000009</v>
       </c>
-      <c r="T16" s="66">
+      <c r="T16" s="54">
         <f t="shared" ref="T16:AF16" si="17">D16</f>
         <v>64.705882352941174</v>
       </c>
-      <c r="U16" s="66">
+      <c r="U16" s="54">
         <f t="shared" si="17"/>
         <v>65.517241379310349</v>
       </c>
-      <c r="V16" s="66">
+      <c r="V16" s="54">
         <f t="shared" si="17"/>
         <v>65.517241379310349</v>
       </c>
-      <c r="W16" s="66">
+      <c r="W16" s="54">
         <f t="shared" si="17"/>
         <v>65.517241379310349</v>
       </c>
-      <c r="X16" s="66">
+      <c r="X16" s="54">
         <f t="shared" si="17"/>
         <v>66.666666666666671</v>
       </c>
-      <c r="Y16" s="66">
+      <c r="Y16" s="54">
         <f t="shared" si="17"/>
         <v>66.666666666666671</v>
       </c>
-      <c r="Z16" s="66">
+      <c r="Z16" s="54">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AA16" s="66">
+      <c r="AA16" s="54">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AB16" s="66">
+      <c r="AB16" s="54">
         <f t="shared" si="17"/>
         <v>65.986394557823118</v>
       </c>
-      <c r="AC16" s="66">
+      <c r="AC16" s="54">
         <f t="shared" si="17"/>
         <v>65.93186372745491</v>
       </c>
-      <c r="AD16" s="66">
+      <c r="AD16" s="54">
         <f t="shared" si="17"/>
         <v>65.93186372745491</v>
       </c>
-      <c r="AE16" s="66">
+      <c r="AE16" s="54">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AF16" s="66">
+      <c r="AF16" s="54">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B19" s="59" t="s">
-        <v>150</v>
-      </c>
-      <c r="C19" s="59"/>
-      <c r="D19" s="59"/>
-      <c r="E19" s="59"/>
-      <c r="F19" s="59"/>
-      <c r="G19" s="59"/>
-      <c r="H19" s="59"/>
-      <c r="I19" s="59"/>
-      <c r="J19" s="59"/>
-      <c r="K19" s="59"/>
-      <c r="L19" s="59"/>
-      <c r="M19" s="59"/>
+      <c r="B19" s="57" t="s">
+        <v>149</v>
+      </c>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="57"/>
+      <c r="J19" s="57"/>
+      <c r="K19" s="57"/>
+      <c r="L19" s="57"/>
+      <c r="M19" s="57"/>
     </row>
     <row r="20" spans="2:13" ht="33" x14ac:dyDescent="0.25">
       <c r="B20" s="27" t="s">
+        <v>138</v>
+      </c>
+      <c r="C20" s="28" t="s">
         <v>139</v>
       </c>
-      <c r="C20" s="28" t="s">
+      <c r="D20" s="28" t="s">
         <v>140</v>
       </c>
-      <c r="D20" s="28" t="s">
+      <c r="E20" s="28" t="s">
         <v>141</v>
       </c>
-      <c r="E20" s="28" t="s">
+      <c r="F20" s="28" t="s">
         <v>142</v>
       </c>
-      <c r="F20" s="28" t="s">
+      <c r="G20" s="28" t="s">
         <v>143</v>
       </c>
-      <c r="G20" s="28" t="s">
-        <v>144</v>
-      </c>
       <c r="H20" s="28" t="s">
+        <v>150</v>
+      </c>
+      <c r="I20" s="28" t="s">
         <v>151</v>
       </c>
-      <c r="I20" s="28" t="s">
+      <c r="J20" s="28" t="s">
         <v>152</v>
       </c>
-      <c r="J20" s="28" t="s">
+      <c r="K20" s="28" t="s">
         <v>153</v>
       </c>
-      <c r="K20" s="28" t="s">
+      <c r="L20" s="28" t="s">
         <v>154</v>
-      </c>
-      <c r="L20" s="28" t="s">
-        <v>155</v>
       </c>
       <c r="M20" s="23"/>
     </row>
@@ -10124,7 +10137,7 @@
         <v>35</v>
       </c>
       <c r="H21" s="30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I21" s="31">
         <v>50</v>
@@ -10136,7 +10149,7 @@
         <v>50</v>
       </c>
       <c r="L21" s="30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M21" s="26"/>
     </row>
@@ -10160,7 +10173,7 @@
         <v>35</v>
       </c>
       <c r="H22" s="30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I22" s="31">
         <v>50</v>
@@ -10172,7 +10185,7 @@
         <v>50</v>
       </c>
       <c r="L22" s="30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M22" s="26"/>
     </row>
@@ -10196,7 +10209,7 @@
         <v>36.700000000000003</v>
       </c>
       <c r="H23" s="30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I23" s="31">
         <v>50</v>
@@ -10208,7 +10221,7 @@
         <v>50</v>
       </c>
       <c r="L23" s="30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M23" s="26"/>
     </row>
@@ -10232,7 +10245,7 @@
         <v>36.6</v>
       </c>
       <c r="H24" s="30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I24" s="31">
         <v>50</v>
@@ -10244,7 +10257,7 @@
         <v>50</v>
       </c>
       <c r="L24" s="30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M24" s="26"/>
     </row>
@@ -10268,7 +10281,7 @@
         <v>31.4</v>
       </c>
       <c r="H25" s="30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I25" s="31">
         <v>50</v>
@@ -10280,7 +10293,7 @@
         <v>50</v>
       </c>
       <c r="L25" s="30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M25" s="26"/>
     </row>
@@ -10304,7 +10317,7 @@
         <v>31.7</v>
       </c>
       <c r="H26" s="30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I26" s="31">
         <v>50</v>
@@ -10316,7 +10329,7 @@
         <v>50</v>
       </c>
       <c r="L26" s="30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M26" s="26"/>
     </row>
@@ -10340,7 +10353,7 @@
         <v>35.700000000000003</v>
       </c>
       <c r="H27" s="30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I27" s="31">
         <v>50</v>
@@ -10352,7 +10365,7 @@
         <v>50</v>
       </c>
       <c r="L27" s="30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M27" s="26"/>
     </row>
@@ -10376,7 +10389,7 @@
         <v>35.700000000000003</v>
       </c>
       <c r="H28" s="30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I28" s="31">
         <v>50</v>
@@ -10388,7 +10401,7 @@
         <v>50</v>
       </c>
       <c r="L28" s="30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M28" s="26"/>
     </row>
@@ -10412,7 +10425,7 @@
         <v>35.700000000000003</v>
       </c>
       <c r="H29" s="30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="I29" s="31">
         <v>50</v>
@@ -10424,13 +10437,13 @@
         <v>50</v>
       </c>
       <c r="L29" s="30" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="M29" s="26"/>
     </row>
     <row r="30" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B30" s="41" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C30" s="42">
         <f>AVERAGE(C26:C28)</f>
@@ -10469,54 +10482,54 @@
       <c r="M30" s="26"/>
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B32" s="60" t="s">
-        <v>138</v>
-      </c>
-      <c r="C32" s="60"/>
-      <c r="D32" s="60"/>
-      <c r="E32" s="60"/>
-      <c r="F32" s="60"/>
-      <c r="G32" s="60"/>
-      <c r="H32" s="60"/>
-      <c r="I32" s="60"/>
-      <c r="J32" s="60"/>
-      <c r="K32" s="60"/>
-      <c r="L32" s="60"/>
-      <c r="M32" s="60"/>
+      <c r="B32" s="63" t="s">
+        <v>137</v>
+      </c>
+      <c r="C32" s="63"/>
+      <c r="D32" s="63"/>
+      <c r="E32" s="63"/>
+      <c r="F32" s="63"/>
+      <c r="G32" s="63"/>
+      <c r="H32" s="63"/>
+      <c r="I32" s="63"/>
+      <c r="J32" s="63"/>
+      <c r="K32" s="63"/>
+      <c r="L32" s="63"/>
+      <c r="M32" s="63"/>
     </row>
     <row r="33" spans="2:16" ht="66.75" x14ac:dyDescent="0.25">
       <c r="B33" s="21" t="s">
+        <v>138</v>
+      </c>
+      <c r="C33" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="C33" s="22" t="s">
+      <c r="D33" s="22" t="s">
         <v>140</v>
       </c>
-      <c r="D33" s="22" t="s">
+      <c r="E33" s="22" t="s">
         <v>141</v>
       </c>
-      <c r="E33" s="22" t="s">
+      <c r="F33" s="22" t="s">
         <v>142</v>
       </c>
-      <c r="F33" s="22" t="s">
+      <c r="G33" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="G33" s="22" t="s">
+      <c r="H33" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="H33" s="22" t="s">
+      <c r="I33" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="I33" s="22" t="s">
+      <c r="J33" s="22" t="s">
         <v>146</v>
       </c>
-      <c r="J33" s="22" t="s">
+      <c r="K33" s="22" t="s">
         <v>147</v>
       </c>
-      <c r="K33" s="22" t="s">
+      <c r="L33" s="22" t="s">
         <v>148</v>
-      </c>
-      <c r="L33" s="22" t="s">
-        <v>149</v>
       </c>
       <c r="M33" s="23"/>
     </row>
@@ -10846,7 +10859,7 @@
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B43" s="41" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C43" s="42">
         <f>AVERAGE(C39:C41)</f>
@@ -10891,66 +10904,66 @@
       <c r="M43" s="26"/>
     </row>
     <row r="45" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B45" s="59" t="s">
-        <v>165</v>
-      </c>
-      <c r="C45" s="59"/>
-      <c r="D45" s="59"/>
-      <c r="E45" s="59"/>
-      <c r="F45" s="59"/>
-      <c r="G45" s="59"/>
-      <c r="H45" s="59"/>
-      <c r="I45" s="59"/>
-      <c r="J45" s="59"/>
-      <c r="K45" s="59"/>
-      <c r="L45" s="59"/>
-      <c r="M45" s="59"/>
-      <c r="N45" s="59"/>
-      <c r="O45" s="59"/>
-      <c r="P45" s="59"/>
+      <c r="B45" s="57" t="s">
+        <v>164</v>
+      </c>
+      <c r="C45" s="57"/>
+      <c r="D45" s="57"/>
+      <c r="E45" s="57"/>
+      <c r="F45" s="57"/>
+      <c r="G45" s="57"/>
+      <c r="H45" s="57"/>
+      <c r="I45" s="57"/>
+      <c r="J45" s="57"/>
+      <c r="K45" s="57"/>
+      <c r="L45" s="57"/>
+      <c r="M45" s="57"/>
+      <c r="N45" s="57"/>
+      <c r="O45" s="57"/>
+      <c r="P45" s="57"/>
     </row>
     <row r="46" spans="2:16" ht="44.25" x14ac:dyDescent="0.25">
       <c r="B46" s="37" t="s">
+        <v>138</v>
+      </c>
+      <c r="C46" s="38" t="s">
         <v>139</v>
       </c>
-      <c r="C46" s="38" t="s">
+      <c r="D46" s="38" t="s">
         <v>140</v>
       </c>
-      <c r="D46" s="38" t="s">
+      <c r="E46" s="38" t="s">
         <v>141</v>
       </c>
-      <c r="E46" s="38" t="s">
+      <c r="F46" s="38" t="s">
         <v>142</v>
       </c>
-      <c r="F46" s="38" t="s">
+      <c r="G46" s="38" t="s">
         <v>143</v>
       </c>
-      <c r="G46" s="38" t="s">
+      <c r="H46" s="38" t="s">
         <v>144</v>
       </c>
-      <c r="H46" s="38" t="s">
+      <c r="I46" s="38" t="s">
         <v>145</v>
       </c>
-      <c r="I46" s="38" t="s">
-        <v>146</v>
-      </c>
       <c r="J46" s="38" t="s">
+        <v>165</v>
+      </c>
+      <c r="K46" s="38" t="s">
+        <v>152</v>
+      </c>
+      <c r="L46" s="38" t="s">
         <v>166</v>
       </c>
-      <c r="K46" s="38" t="s">
+      <c r="M46" s="38" t="s">
         <v>153</v>
       </c>
-      <c r="L46" s="38" t="s">
+      <c r="N46" s="38" t="s">
+        <v>147</v>
+      </c>
+      <c r="O46" s="38" t="s">
         <v>167</v>
-      </c>
-      <c r="M46" s="38" t="s">
-        <v>154</v>
-      </c>
-      <c r="N46" s="38" t="s">
-        <v>148</v>
-      </c>
-      <c r="O46" s="38" t="s">
-        <v>168</v>
       </c>
       <c r="P46" s="23"/>
     </row>
@@ -11361,7 +11374,7 @@
     </row>
     <row r="56" spans="2:16" x14ac:dyDescent="0.25">
       <c r="B56" s="41" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C56" s="42">
         <f>AVERAGE(C52:C54)</f>
@@ -11418,58 +11431,58 @@
       <c r="P56" s="26"/>
     </row>
     <row r="58" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B58" s="60" t="s">
-        <v>169</v>
-      </c>
-      <c r="C58" s="60"/>
-      <c r="D58" s="60"/>
-      <c r="E58" s="60"/>
-      <c r="F58" s="60"/>
-      <c r="G58" s="60"/>
-      <c r="H58" s="60"/>
-      <c r="I58" s="60"/>
-      <c r="J58" s="60"/>
-      <c r="K58" s="60"/>
-      <c r="L58" s="60"/>
-      <c r="M58" s="60"/>
-      <c r="N58" s="60"/>
+      <c r="B58" s="63" t="s">
+        <v>168</v>
+      </c>
+      <c r="C58" s="63"/>
+      <c r="D58" s="63"/>
+      <c r="E58" s="63"/>
+      <c r="F58" s="63"/>
+      <c r="G58" s="63"/>
+      <c r="H58" s="63"/>
+      <c r="I58" s="63"/>
+      <c r="J58" s="63"/>
+      <c r="K58" s="63"/>
+      <c r="L58" s="63"/>
+      <c r="M58" s="63"/>
+      <c r="N58" s="63"/>
     </row>
     <row r="59" spans="2:16" ht="65.25" x14ac:dyDescent="0.25">
       <c r="B59" s="40" t="s">
+        <v>138</v>
+      </c>
+      <c r="C59" s="38" t="s">
         <v>139</v>
       </c>
-      <c r="C59" s="38" t="s">
+      <c r="D59" s="38" t="s">
         <v>140</v>
       </c>
-      <c r="D59" s="38" t="s">
+      <c r="E59" s="38" t="s">
         <v>141</v>
       </c>
-      <c r="E59" s="38" t="s">
+      <c r="F59" s="38" t="s">
         <v>142</v>
       </c>
-      <c r="F59" s="38" t="s">
+      <c r="G59" s="38" t="s">
         <v>143</v>
       </c>
-      <c r="G59" s="38" t="s">
+      <c r="H59" s="38" t="s">
         <v>144</v>
       </c>
-      <c r="H59" s="38" t="s">
+      <c r="I59" s="38" t="s">
         <v>145</v>
       </c>
-      <c r="I59" s="38" t="s">
-        <v>146</v>
-      </c>
       <c r="J59" s="38" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="K59" s="38" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="L59" s="38" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="M59" s="38" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="N59" s="23"/>
     </row>
@@ -11826,7 +11839,7 @@
     </row>
     <row r="69" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B69" s="41" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C69" s="42">
         <f>AVERAGE(C65:C67)</f>
@@ -11875,72 +11888,72 @@
       <c r="N69" s="26"/>
     </row>
     <row r="71" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="59" t="s">
+      <c r="B71" s="57" t="s">
+        <v>157</v>
+      </c>
+      <c r="C71" s="57"/>
+      <c r="D71" s="57"/>
+      <c r="E71" s="57"/>
+      <c r="F71" s="57"/>
+      <c r="G71" s="57"/>
+      <c r="H71" s="57"/>
+      <c r="I71" s="57"/>
+      <c r="J71" s="57"/>
+      <c r="K71" s="57"/>
+      <c r="L71" s="57"/>
+      <c r="M71" s="57"/>
+    </row>
+    <row r="72" spans="2:14" ht="24" x14ac:dyDescent="0.25">
+      <c r="B72" s="58" t="s">
+        <v>138</v>
+      </c>
+      <c r="C72" s="60" t="s">
         <v>158</v>
       </c>
-      <c r="C71" s="59"/>
-      <c r="D71" s="59"/>
-      <c r="E71" s="59"/>
-      <c r="F71" s="59"/>
-      <c r="G71" s="59"/>
-      <c r="H71" s="59"/>
-      <c r="I71" s="59"/>
-      <c r="J71" s="59"/>
-      <c r="K71" s="59"/>
-      <c r="L71" s="59"/>
-      <c r="M71" s="59"/>
-    </row>
-    <row r="72" spans="2:14" ht="24" x14ac:dyDescent="0.25">
-      <c r="B72" s="61" t="s">
+      <c r="D72" s="61"/>
+      <c r="E72" s="61"/>
+      <c r="F72" s="61"/>
+      <c r="G72" s="61"/>
+      <c r="H72" s="61"/>
+      <c r="I72" s="61"/>
+      <c r="J72" s="61"/>
+      <c r="K72" s="62"/>
+      <c r="L72" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="M72" s="33"/>
+    </row>
+    <row r="73" spans="2:14" ht="49.5" x14ac:dyDescent="0.25">
+      <c r="B73" s="59"/>
+      <c r="C73" s="22" t="s">
         <v>139</v>
       </c>
-      <c r="C72" s="63" t="s">
-        <v>159</v>
-      </c>
-      <c r="D72" s="64"/>
-      <c r="E72" s="64"/>
-      <c r="F72" s="64"/>
-      <c r="G72" s="64"/>
-      <c r="H72" s="64"/>
-      <c r="I72" s="64"/>
-      <c r="J72" s="64"/>
-      <c r="K72" s="65"/>
-      <c r="L72" s="32" t="s">
+      <c r="D73" s="34" t="s">
+        <v>140</v>
+      </c>
+      <c r="E73" s="34" t="s">
+        <v>141</v>
+      </c>
+      <c r="F73" s="34" t="s">
+        <v>142</v>
+      </c>
+      <c r="G73" s="34" t="s">
+        <v>143</v>
+      </c>
+      <c r="H73" s="22" t="s">
         <v>160</v>
       </c>
-      <c r="M72" s="33"/>
-    </row>
-    <row r="73" spans="2:14" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="B73" s="62"/>
-      <c r="C73" s="22" t="s">
-        <v>140</v>
-      </c>
-      <c r="D73" s="34" t="s">
-        <v>141</v>
-      </c>
-      <c r="E73" s="34" t="s">
-        <v>142</v>
-      </c>
-      <c r="F73" s="34" t="s">
-        <v>143</v>
-      </c>
-      <c r="G73" s="34" t="s">
+      <c r="I73" s="34" t="s">
         <v>144</v>
       </c>
-      <c r="H73" s="22" t="s">
-        <v>161</v>
-      </c>
-      <c r="I73" s="34" t="s">
+      <c r="J73" s="34" t="s">
         <v>145</v>
       </c>
-      <c r="J73" s="34" t="s">
-        <v>146</v>
-      </c>
       <c r="K73" s="22" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L73" s="22" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="M73" s="23"/>
     </row>
@@ -12270,7 +12283,7 @@
     </row>
     <row r="83" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B83" s="41" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C83" s="42">
         <f>AVERAGE(C79:C81)</f>
@@ -12315,63 +12328,63 @@
       <c r="M83" s="26"/>
     </row>
     <row r="85" spans="2:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B85" s="60" t="s">
+      <c r="B85" s="63" t="s">
+        <v>161</v>
+      </c>
+      <c r="C85" s="63"/>
+      <c r="D85" s="63"/>
+      <c r="E85" s="63"/>
+      <c r="F85" s="63"/>
+      <c r="G85" s="63"/>
+      <c r="H85" s="63"/>
+      <c r="I85" s="63"/>
+      <c r="J85" s="63"/>
+      <c r="K85" s="63"/>
+      <c r="L85" s="63"/>
+    </row>
+    <row r="86" spans="2:13" x14ac:dyDescent="0.25">
+      <c r="B86" s="64"/>
+      <c r="C86" s="66" t="s">
         <v>162</v>
       </c>
-      <c r="C85" s="60"/>
-      <c r="D85" s="60"/>
-      <c r="E85" s="60"/>
-      <c r="F85" s="60"/>
-      <c r="G85" s="60"/>
-      <c r="H85" s="60"/>
-      <c r="I85" s="60"/>
-      <c r="J85" s="60"/>
-      <c r="K85" s="60"/>
-      <c r="L85" s="60"/>
-    </row>
-    <row r="86" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B86" s="54"/>
-      <c r="C86" s="56" t="s">
+      <c r="D86" s="67"/>
+      <c r="E86" s="67"/>
+      <c r="F86" s="67"/>
+      <c r="G86" s="67"/>
+      <c r="H86" s="67"/>
+      <c r="I86" s="67"/>
+      <c r="J86" s="67"/>
+      <c r="K86" s="68"/>
+      <c r="L86" s="26"/>
+    </row>
+    <row r="87" spans="2:13" ht="42" x14ac:dyDescent="0.25">
+      <c r="B87" s="65"/>
+      <c r="C87" s="35" t="s">
+        <v>139</v>
+      </c>
+      <c r="D87" s="36" t="s">
+        <v>140</v>
+      </c>
+      <c r="E87" s="36" t="s">
+        <v>141</v>
+      </c>
+      <c r="F87" s="36" t="s">
+        <v>142</v>
+      </c>
+      <c r="G87" s="36" t="s">
+        <v>143</v>
+      </c>
+      <c r="H87" s="35" t="s">
+        <v>160</v>
+      </c>
+      <c r="I87" s="36" t="s">
         <v>163</v>
       </c>
-      <c r="D86" s="57"/>
-      <c r="E86" s="57"/>
-      <c r="F86" s="57"/>
-      <c r="G86" s="57"/>
-      <c r="H86" s="57"/>
-      <c r="I86" s="57"/>
-      <c r="J86" s="57"/>
-      <c r="K86" s="58"/>
-      <c r="L86" s="26"/>
-    </row>
-    <row r="87" spans="2:13" ht="42" x14ac:dyDescent="0.25">
-      <c r="B87" s="55"/>
-      <c r="C87" s="35" t="s">
-        <v>140</v>
-      </c>
-      <c r="D87" s="36" t="s">
-        <v>141</v>
-      </c>
-      <c r="E87" s="36" t="s">
-        <v>142</v>
-      </c>
-      <c r="F87" s="36" t="s">
-        <v>143</v>
-      </c>
-      <c r="G87" s="36" t="s">
-        <v>144</v>
-      </c>
-      <c r="H87" s="35" t="s">
-        <v>161</v>
-      </c>
-      <c r="I87" s="36" t="s">
-        <v>164</v>
-      </c>
       <c r="J87" s="36" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K87" s="35" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L87" s="23"/>
     </row>
@@ -12674,7 +12687,7 @@
     </row>
     <row r="97" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B97" s="41" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C97" s="42">
         <f>AVERAGE(C93:C95)</f>
@@ -12715,16 +12728,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="C86:K86"/>
+    <mergeCell ref="B45:P45"/>
+    <mergeCell ref="B58:N58"/>
+    <mergeCell ref="B32:M32"/>
     <mergeCell ref="B19:M19"/>
     <mergeCell ref="B71:M71"/>
     <mergeCell ref="B72:B73"/>
     <mergeCell ref="C72:K72"/>
     <mergeCell ref="B85:L85"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="C86:K86"/>
-    <mergeCell ref="B45:P45"/>
-    <mergeCell ref="B58:N58"/>
-    <mergeCell ref="B32:M32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data/default/ManureMgmt.xlsx
+++ b/data/default/ManureMgmt.xlsx
@@ -1,27 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jnka0003\Git repos\CIBUSmod\data\default\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E10BFD5-DF70-4A22-BAE4-C5B0B3E77FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19020" windowHeight="6705" activeTab="1"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="references" sheetId="2" r:id="rId1"/>
     <sheet name="default" sheetId="1" r:id="rId2"/>
     <sheet name="MMS" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1648" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1671" uniqueCount="212">
   <si>
     <t>value</t>
   </si>
@@ -654,12 +668,15 @@
   </si>
   <si>
     <t>Starting pig, ca. 10 weeks</t>
+  </si>
+  <si>
+    <t>OBS. Fel i källtabell (står 0,25% där)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
@@ -1323,7 +1340,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -1331,16 +1348,12 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="1" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="21" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="25" fillId="35" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1409,22 +1422,36 @@
     <xf numFmtId="164" fontId="23" fillId="36" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="top" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="16" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="27" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="10"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="10"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="10"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1441,25 +1468,6 @@
     <xf numFmtId="0" fontId="25" fillId="35" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="9"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="10"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="10"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="10"/>
-    </xf>
-    <xf numFmtId="2" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -1785,7 +1793,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -1806,8 +1814,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:O319"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:O322"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
@@ -1904,7 +1912,7 @@
       <c r="K3" t="s">
         <v>14</v>
       </c>
-      <c r="L3" s="42">
+      <c r="L3" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G3,MMS!$O$9:$O$13,0),MATCH(A3&amp;C3&amp;E3,MMS!$P$8:$Z$8,0))</f>
         <v>83.800623052959494</v>
       </c>
@@ -1931,7 +1939,7 @@
       <c r="K4" t="s">
         <v>14</v>
       </c>
-      <c r="L4" s="42">
+      <c r="L4" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G4,MMS!$O$9:$O$13,0),MATCH(A4&amp;C4&amp;E4,MMS!$P$8:$Z$8,0))</f>
         <v>9.3457943925233611</v>
       </c>
@@ -1958,7 +1966,7 @@
       <c r="K5" t="s">
         <v>14</v>
       </c>
-      <c r="L5" s="42">
+      <c r="L5" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G5,MMS!$O$9:$O$13,0),MATCH(A5&amp;C5&amp;E5,MMS!$P$8:$Z$8,0))</f>
         <v>1.2906097018246547</v>
       </c>
@@ -1985,7 +1993,7 @@
       <c r="K6" t="s">
         <v>14</v>
       </c>
-      <c r="L6" s="42">
+      <c r="L6" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G6,MMS!$O$9:$O$13,0),MATCH(A6&amp;C6&amp;E6,MMS!$P$8:$Z$8,0))</f>
         <v>5.562972852692476</v>
       </c>
@@ -2012,7 +2020,7 @@
       <c r="K7" t="s">
         <v>14</v>
       </c>
-      <c r="L7" s="42">
+      <c r="L7" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G7,MMS!$O$9:$O$13,0),MATCH(A7&amp;C7&amp;E7,MMS!$P$8:$Z$8,0))</f>
         <v>0</v>
       </c>
@@ -2039,7 +2047,7 @@
       <c r="K8" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="42">
+      <c r="L8" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G8,MMS!$O$9:$O$13,0),MATCH(A8&amp;C8&amp;E8,MMS!$P$8:$Z$8,0))</f>
         <v>22.222222222222225</v>
       </c>
@@ -2066,7 +2074,7 @@
       <c r="K9" t="s">
         <v>14</v>
       </c>
-      <c r="L9" s="42">
+      <c r="L9" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G9,MMS!$O$9:$O$13,0),MATCH(A9&amp;C9&amp;E9,MMS!$P$8:$Z$8,0))</f>
         <v>30.405405405405407</v>
       </c>
@@ -2093,7 +2101,7 @@
       <c r="K10" t="s">
         <v>14</v>
       </c>
-      <c r="L10" s="42">
+      <c r="L10" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G10,MMS!$O$9:$O$13,0),MATCH(A10&amp;C10&amp;E10,MMS!$P$8:$Z$8,0))</f>
         <v>44.819819819819827</v>
       </c>
@@ -2120,7 +2128,7 @@
       <c r="K11" t="s">
         <v>14</v>
       </c>
-      <c r="L11" s="42">
+      <c r="L11" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G11,MMS!$O$9:$O$13,0),MATCH(A11&amp;C11&amp;E11,MMS!$P$8:$Z$8,0))</f>
         <v>2.5525525525525525</v>
       </c>
@@ -2147,7 +2155,7 @@
       <c r="K12" t="s">
         <v>14</v>
       </c>
-      <c r="L12" s="42">
+      <c r="L12" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G12,MMS!$O$9:$O$13,0),MATCH(A12&amp;C12&amp;E12,MMS!$P$8:$Z$8,0))</f>
         <v>0</v>
       </c>
@@ -2171,7 +2179,7 @@
       <c r="K13" t="s">
         <v>14</v>
       </c>
-      <c r="L13" s="42">
+      <c r="L13" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G13,MMS!$O$9:$O$13,0),MATCH(A13&amp;C13&amp;E13,MMS!$P$8:$Z$8,0))</f>
         <v>25.355691056910569</v>
       </c>
@@ -2195,7 +2203,7 @@
       <c r="K14" t="s">
         <v>14</v>
       </c>
-      <c r="L14" s="42">
+      <c r="L14" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G14,MMS!$O$9:$O$13,0),MATCH(A14&amp;C14&amp;E14,MMS!$P$8:$Z$8,0))</f>
         <v>20.325203252032519</v>
       </c>
@@ -2219,7 +2227,7 @@
       <c r="K15" t="s">
         <v>14</v>
       </c>
-      <c r="L15" s="42">
+      <c r="L15" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G15,MMS!$O$9:$O$13,0),MATCH(A15&amp;C15&amp;E15,MMS!$P$8:$Z$8,0))</f>
         <v>51.575203252032523</v>
       </c>
@@ -2243,7 +2251,7 @@
       <c r="K16" t="s">
         <v>14</v>
       </c>
-      <c r="L16" s="42">
+      <c r="L16" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G16,MMS!$O$9:$O$13,0),MATCH(A16&amp;C16&amp;E16,MMS!$P$8:$Z$8,0))</f>
         <v>2.7439024390243896</v>
       </c>
@@ -2267,7 +2275,7 @@
       <c r="K17" t="s">
         <v>14</v>
       </c>
-      <c r="L17" s="42">
+      <c r="L17" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G17,MMS!$O$9:$O$13,0),MATCH(A17&amp;C17&amp;E17,MMS!$P$8:$Z$8,0))</f>
         <v>0</v>
       </c>
@@ -2291,7 +2299,7 @@
       <c r="K18" t="s">
         <v>14</v>
       </c>
-      <c r="L18" s="42">
+      <c r="L18" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G18,MMS!$O$9:$O$13,0),MATCH(A18&amp;C18&amp;E18,MMS!$P$8:$Z$8,0))</f>
         <v>50.379048931771194</v>
       </c>
@@ -2315,7 +2323,7 @@
       <c r="K19" t="s">
         <v>14</v>
       </c>
-      <c r="L19" s="42">
+      <c r="L19" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G19,MMS!$O$9:$O$13,0),MATCH(A19&amp;C19&amp;E19,MMS!$P$8:$Z$8,0))</f>
         <v>19.090282563749142</v>
       </c>
@@ -2339,7 +2347,7 @@
       <c r="K20" t="s">
         <v>14</v>
       </c>
-      <c r="L20" s="42">
+      <c r="L20" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G20,MMS!$O$9:$O$13,0),MATCH(A20&amp;C20&amp;E20,MMS!$P$8:$Z$8,0))</f>
         <v>26.533425223983464</v>
       </c>
@@ -2363,7 +2371,7 @@
       <c r="K21" t="s">
         <v>14</v>
       </c>
-      <c r="L21" s="42">
+      <c r="L21" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G21,MMS!$O$9:$O$13,0),MATCH(A21&amp;C21&amp;E21,MMS!$P$8:$Z$8,0))</f>
         <v>3.9972432804962108</v>
       </c>
@@ -2387,7 +2395,7 @@
       <c r="K22" t="s">
         <v>14</v>
       </c>
-      <c r="L22" s="42">
+      <c r="L22" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G22,MMS!$O$9:$O$13,0),MATCH(A22&amp;C22&amp;E22,MMS!$P$8:$Z$8,0))</f>
         <v>0</v>
       </c>
@@ -2411,7 +2419,7 @@
       <c r="K23" t="s">
         <v>14</v>
       </c>
-      <c r="L23" s="42">
+      <c r="L23" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G23,MMS!$O$9:$O$13,0),MATCH(A23&amp;C23&amp;E23,MMS!$P$8:$Z$8,0))</f>
         <v>44.83940042826552</v>
       </c>
@@ -2435,7 +2443,7 @@
       <c r="K24" t="s">
         <v>14</v>
       </c>
-      <c r="L24" s="42">
+      <c r="L24" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G24,MMS!$O$9:$O$13,0),MATCH(A24&amp;C24&amp;E24,MMS!$P$8:$Z$8,0))</f>
         <v>19.914346895074946</v>
       </c>
@@ -2459,7 +2467,7 @@
       <c r="K25" t="s">
         <v>14</v>
       </c>
-      <c r="L25" s="42">
+      <c r="L25" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G25,MMS!$O$9:$O$13,0),MATCH(A25&amp;C25&amp;E25,MMS!$P$8:$Z$8,0))</f>
         <v>31.520342612419693</v>
       </c>
@@ -2483,7 +2491,7 @@
       <c r="K26" t="s">
         <v>14</v>
       </c>
-      <c r="L26" s="42">
+      <c r="L26" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G26,MMS!$O$9:$O$13,0),MATCH(A26&amp;C26&amp;E26,MMS!$P$8:$Z$8,0))</f>
         <v>3.7259100642398284</v>
       </c>
@@ -2507,7 +2515,7 @@
       <c r="K27" t="s">
         <v>14</v>
       </c>
-      <c r="L27" s="42">
+      <c r="L27" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G27,MMS!$O$9:$O$13,0),MATCH(A27&amp;C27&amp;E27,MMS!$P$8:$Z$8,0))</f>
         <v>0</v>
       </c>
@@ -2528,7 +2536,7 @@
       <c r="K28" t="s">
         <v>14</v>
       </c>
-      <c r="L28" s="42">
+      <c r="L28" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G28,MMS!$O$9:$O$13,0),MATCH(A28&amp;C28&amp;E28,MMS!$P$8:$Z$8,0))</f>
         <v>0</v>
       </c>
@@ -2549,7 +2557,7 @@
       <c r="K29" t="s">
         <v>14</v>
       </c>
-      <c r="L29" s="42">
+      <c r="L29" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G29,MMS!$O$9:$O$13,0),MATCH(A29&amp;C29&amp;E29,MMS!$P$8:$Z$8,0))</f>
         <v>66</v>
       </c>
@@ -2570,7 +2578,7 @@
       <c r="K30" t="s">
         <v>14</v>
       </c>
-      <c r="L30" s="42">
+      <c r="L30" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G30,MMS!$O$9:$O$13,0),MATCH(A30&amp;C30&amp;E30,MMS!$P$8:$Z$8,0))</f>
         <v>4</v>
       </c>
@@ -2591,7 +2599,7 @@
       <c r="K31" t="s">
         <v>14</v>
       </c>
-      <c r="L31" s="42">
+      <c r="L31" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G31,MMS!$O$9:$O$13,0),MATCH(A31&amp;C31&amp;E31,MMS!$P$8:$Z$8,0))</f>
         <v>0</v>
       </c>
@@ -2612,7 +2620,7 @@
       <c r="K32" t="s">
         <v>14</v>
       </c>
-      <c r="L32" s="42">
+      <c r="L32" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G32,MMS!$O$9:$O$13,0),MATCH(A32&amp;C32&amp;E32,MMS!$P$8:$Z$8,0))</f>
         <v>30</v>
       </c>
@@ -2633,7 +2641,7 @@
       <c r="K33" t="s">
         <v>14</v>
       </c>
-      <c r="L33" s="42">
+      <c r="L33" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G33,MMS!$O$9:$O$13,0),MATCH(A33&amp;C33&amp;E33,MMS!$P$8:$Z$8,0))</f>
         <v>0</v>
       </c>
@@ -2654,7 +2662,7 @@
       <c r="K34" t="s">
         <v>14</v>
       </c>
-      <c r="L34" s="42">
+      <c r="L34" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G34,MMS!$O$9:$O$13,0),MATCH(A34&amp;C34&amp;E34,MMS!$P$8:$Z$8,0))</f>
         <v>100</v>
       </c>
@@ -2675,7 +2683,7 @@
       <c r="K35" t="s">
         <v>14</v>
       </c>
-      <c r="L35" s="42">
+      <c r="L35" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G35,MMS!$O$9:$O$13,0),MATCH(A35&amp;C35&amp;E35,MMS!$P$8:$Z$8,0))</f>
         <v>0</v>
       </c>
@@ -2696,7 +2704,7 @@
       <c r="K36" t="s">
         <v>14</v>
       </c>
-      <c r="L36" s="42">
+      <c r="L36" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G36,MMS!$O$9:$O$13,0),MATCH(A36&amp;C36&amp;E36,MMS!$P$8:$Z$8,0))</f>
         <v>0</v>
       </c>
@@ -2717,7 +2725,7 @@
       <c r="K37" t="s">
         <v>14</v>
       </c>
-      <c r="L37" s="42">
+      <c r="L37" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G37,MMS!$O$9:$O$13,0),MATCH(A37&amp;C37&amp;E37,MMS!$P$8:$Z$8,0))</f>
         <v>0</v>
       </c>
@@ -2738,7 +2746,7 @@
       <c r="K38" t="s">
         <v>14</v>
       </c>
-      <c r="L38" s="42">
+      <c r="L38" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G38,MMS!$O$9:$O$13,0),MATCH(A38&amp;C38&amp;E38,MMS!$P$8:$Z$8,0))</f>
         <v>47.115705235078359</v>
       </c>
@@ -2759,7 +2767,7 @@
       <c r="K39" t="s">
         <v>14</v>
       </c>
-      <c r="L39" s="42">
+      <c r="L39" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G39,MMS!$O$9:$O$13,0),MATCH(A39&amp;C39&amp;E39,MMS!$P$8:$Z$8,0))</f>
         <v>27.875958652884293</v>
       </c>
@@ -2780,7 +2788,7 @@
       <c r="K40" t="s">
         <v>14</v>
       </c>
-      <c r="L40" s="42">
+      <c r="L40" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G40,MMS!$O$9:$O$13,0),MATCH(A40&amp;C40&amp;E40,MMS!$P$8:$Z$8,0))</f>
         <v>15.205068356118707</v>
       </c>
@@ -2801,7 +2809,7 @@
       <c r="K41" t="s">
         <v>14</v>
       </c>
-      <c r="L41" s="42">
+      <c r="L41" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G41,MMS!$O$9:$O$13,0),MATCH(A41&amp;C41&amp;E41,MMS!$P$8:$Z$8,0))</f>
         <v>9.8032677559186379</v>
       </c>
@@ -2822,7 +2830,7 @@
       <c r="K42" t="s">
         <v>14</v>
       </c>
-      <c r="L42" s="42">
+      <c r="L42" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G42,MMS!$O$9:$O$13,0),MATCH(A42&amp;C42&amp;E42,MMS!$P$8:$Z$8,0))</f>
         <v>0</v>
       </c>
@@ -2846,7 +2854,7 @@
       <c r="K43" t="s">
         <v>14</v>
       </c>
-      <c r="L43" s="42">
+      <c r="L43" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G43,MMS!$O$9:$O$13,0),MATCH(A43&amp;C43&amp;E43,MMS!$P$8:$Z$8,0))</f>
         <v>79.533333333333317</v>
       </c>
@@ -2870,7 +2878,7 @@
       <c r="K44" t="s">
         <v>14</v>
       </c>
-      <c r="L44" s="42">
+      <c r="L44" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G44,MMS!$O$9:$O$13,0),MATCH(A44&amp;C44&amp;E44,MMS!$P$8:$Z$8,0))</f>
         <v>2.6666666666666656</v>
       </c>
@@ -2894,7 +2902,7 @@
       <c r="K45" t="s">
         <v>14</v>
       </c>
-      <c r="L45" s="42">
+      <c r="L45" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G45,MMS!$O$9:$O$13,0),MATCH(A45&amp;C45&amp;E45,MMS!$P$8:$Z$8,0))</f>
         <v>1.1666666666666663</v>
       </c>
@@ -2918,7 +2926,7 @@
       <c r="K46" t="s">
         <v>14</v>
       </c>
-      <c r="L46" s="42">
+      <c r="L46" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G46,MMS!$O$9:$O$13,0),MATCH(A46&amp;C46&amp;E46,MMS!$P$8:$Z$8,0))</f>
         <v>16.633333333333329</v>
       </c>
@@ -2942,7 +2950,7 @@
       <c r="K47" t="s">
         <v>14</v>
       </c>
-      <c r="L47" s="42">
+      <c r="L47" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G47,MMS!$O$9:$O$13,0),MATCH(A47&amp;C47&amp;E47,MMS!$P$8:$Z$8,0))</f>
         <v>0</v>
       </c>
@@ -2963,7 +2971,7 @@
       <c r="K48" t="s">
         <v>14</v>
       </c>
-      <c r="L48" s="42">
+      <c r="L48" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G48,MMS!$O$9:$O$13,0),MATCH(A48&amp;C48&amp;E48,MMS!$P$8:$Z$8,0))</f>
         <v>7.7000000000000011</v>
       </c>
@@ -2984,7 +2992,7 @@
       <c r="K49" t="s">
         <v>14</v>
       </c>
-      <c r="L49" s="42">
+      <c r="L49" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G49,MMS!$O$9:$O$13,0),MATCH(A49&amp;C49&amp;E49,MMS!$P$8:$Z$8,0))</f>
         <v>85.966666666666669</v>
       </c>
@@ -3005,7 +3013,7 @@
       <c r="K50" t="s">
         <v>14</v>
       </c>
-      <c r="L50" s="42">
+      <c r="L50" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G50,MMS!$O$9:$O$13,0),MATCH(A50&amp;C50&amp;E50,MMS!$P$8:$Z$8,0))</f>
         <v>6.3333333333333339</v>
       </c>
@@ -3026,7 +3034,7 @@
       <c r="K51" t="s">
         <v>14</v>
       </c>
-      <c r="L51" s="42">
+      <c r="L51" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G51,MMS!$O$9:$O$13,0),MATCH(A51&amp;C51&amp;E51,MMS!$P$8:$Z$8,0))</f>
         <v>0</v>
       </c>
@@ -3047,7 +3055,7 @@
       <c r="K52" t="s">
         <v>14</v>
       </c>
-      <c r="L52" s="42">
+      <c r="L52" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G52,MMS!$O$9:$O$13,0),MATCH(A52&amp;C52&amp;E52,MMS!$P$8:$Z$8,0))</f>
         <v>0</v>
       </c>
@@ -3071,7 +3079,7 @@
       <c r="K53" t="s">
         <v>14</v>
       </c>
-      <c r="L53" s="42">
+      <c r="L53" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G53,MMS!$O$9:$O$13,0),MATCH(A53&amp;C53&amp;E53,MMS!$P$8:$Z$8,0))</f>
         <v>0</v>
       </c>
@@ -3095,7 +3103,7 @@
       <c r="K54" t="s">
         <v>14</v>
       </c>
-      <c r="L54" s="42">
+      <c r="L54" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G54,MMS!$O$9:$O$13,0),MATCH(A54&amp;C54&amp;E54,MMS!$P$8:$Z$8,0))</f>
         <v>0</v>
       </c>
@@ -3119,7 +3127,7 @@
       <c r="K55" t="s">
         <v>14</v>
       </c>
-      <c r="L55" s="42">
+      <c r="L55" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G55,MMS!$O$9:$O$13,0),MATCH(A55&amp;C55&amp;E55,MMS!$P$8:$Z$8,0))</f>
         <v>100</v>
       </c>
@@ -3143,7 +3151,7 @@
       <c r="K56" t="s">
         <v>14</v>
       </c>
-      <c r="L56" s="42">
+      <c r="L56" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G56,MMS!$O$9:$O$13,0),MATCH(A56&amp;C56&amp;E56,MMS!$P$8:$Z$8,0))</f>
         <v>0</v>
       </c>
@@ -3167,7 +3175,7 @@
       <c r="K57" t="s">
         <v>14</v>
       </c>
-      <c r="L57" s="42">
+      <c r="L57" s="37">
         <f>INDEX(MMS!$P$9:$Z$13,MATCH(G57,MMS!$O$9:$O$13,0),MATCH(A57&amp;C57&amp;E57,MMS!$P$8:$Z$8,0))</f>
         <v>0</v>
       </c>
@@ -3179,12 +3187,12 @@
       </c>
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A59" s="53" t="s">
+      <c r="A59" s="44" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A60" s="53" t="s">
+      <c r="A60" s="44" t="s">
         <v>188</v>
       </c>
     </row>
@@ -3218,7 +3226,7 @@
       <c r="K62" t="s">
         <v>189</v>
       </c>
-      <c r="L62" s="42">
+      <c r="L62" s="37">
         <f>INDEX(MMS!$P$16:$Z$16,MATCH(A62&amp;C62&amp;E62,MMS!$P$8:$Z$8,0))</f>
         <v>65.600000000000009</v>
       </c>
@@ -3248,7 +3256,7 @@
       <c r="K63" t="s">
         <v>189</v>
       </c>
-      <c r="L63" s="42">
+      <c r="L63" s="37">
         <f>INDEX(MMS!$P$16:$Z$16,MATCH(A63&amp;C63&amp;E63,MMS!$P$8:$Z$8,0))</f>
         <v>64.705882352941174</v>
       </c>
@@ -3269,7 +3277,7 @@
       <c r="K64" t="s">
         <v>189</v>
       </c>
-      <c r="L64" s="42">
+      <c r="L64" s="37">
         <f>INDEX(MMS!$P$16:$Z$16,MATCH(A64&amp;C64&amp;E64,MMS!$P$8:$Z$8,0))</f>
         <v>66.666666666666671</v>
       </c>
@@ -3290,7 +3298,7 @@
       <c r="K65" t="s">
         <v>189</v>
       </c>
-      <c r="L65" s="42">
+      <c r="L65" s="37">
         <f>INDEX(MMS!$P$16:$Z$16,MATCH(A65&amp;C65&amp;E65,MMS!$P$8:$Z$8,0))</f>
         <v>65.517241379310349</v>
       </c>
@@ -3311,7 +3319,7 @@
       <c r="K66" t="s">
         <v>189</v>
       </c>
-      <c r="L66" s="42">
+      <c r="L66" s="37">
         <f>INDEX(MMS!$P$16:$Z$16,MATCH(A66&amp;C66&amp;E66,MMS!$P$8:$Z$8,0))</f>
         <v>65.517241379310349</v>
       </c>
@@ -3329,7 +3337,7 @@
       <c r="K67" t="s">
         <v>189</v>
       </c>
-      <c r="L67" s="42">
+      <c r="L67" s="37">
         <f>INDEX(MMS!$P$16:$Z$16,MATCH(A67&amp;C67&amp;E67,MMS!$P$8:$Z$8,0))</f>
         <v>0</v>
       </c>
@@ -3347,7 +3355,7 @@
       <c r="K68" t="s">
         <v>189</v>
       </c>
-      <c r="L68" s="42">
+      <c r="L68" s="37">
         <f>INDEX(MMS!$P$16:$Z$16,MATCH(A68&amp;C68&amp;E68,MMS!$P$8:$Z$8,0))</f>
         <v>0</v>
       </c>
@@ -3365,7 +3373,7 @@
       <c r="K69" t="s">
         <v>189</v>
       </c>
-      <c r="L69" s="42">
+      <c r="L69" s="37">
         <f>INDEX(MMS!$P$16:$Z$16,MATCH(A69&amp;C69&amp;E69,MMS!$P$8:$Z$8,0))</f>
         <v>65.986394557823118</v>
       </c>
@@ -3386,7 +3394,7 @@
       <c r="K70" t="s">
         <v>189</v>
       </c>
-      <c r="L70" s="42">
+      <c r="L70" s="37">
         <f>INDEX(MMS!$P$16:$Z$16,MATCH(A70&amp;C70&amp;E70,MMS!$P$8:$Z$8,0))</f>
         <v>65.93186372745491</v>
       </c>
@@ -3404,7 +3412,7 @@
       <c r="K71" t="s">
         <v>189</v>
       </c>
-      <c r="L71" s="42">
+      <c r="L71" s="37">
         <f>INDEX(MMS!$P$16:$Z$16,MATCH(A71&amp;C71&amp;E71,MMS!$P$8:$Z$8,0))</f>
         <v>0</v>
       </c>
@@ -3425,7 +3433,7 @@
       <c r="K72" t="s">
         <v>189</v>
       </c>
-      <c r="L72" s="42">
+      <c r="L72" s="37">
         <f>INDEX(MMS!$P$16:$Z$16,MATCH(A72&amp;C72&amp;E72,MMS!$P$8:$Z$8,0))</f>
         <v>0</v>
       </c>
@@ -3468,7 +3476,7 @@
       <c r="J76" s="2"/>
       <c r="K76" s="2"/>
       <c r="L76" s="2"/>
-      <c r="M76" s="16" t="s">
+      <c r="M76" s="3" t="s">
         <v>119</v>
       </c>
       <c r="N76" s="2"/>
@@ -3502,7 +3510,7 @@
       <c r="K80" t="s">
         <v>118</v>
       </c>
-      <c r="L80" s="14">
+      <c r="L80" s="11">
         <f>1.5*0.85</f>
         <v>1.2749999999999999</v>
       </c>
@@ -3526,7 +3534,7 @@
       <c r="K81" t="s">
         <v>118</v>
       </c>
-      <c r="L81" s="14">
+      <c r="L81" s="11">
         <f>5.5*0.85</f>
         <v>4.6749999999999998</v>
       </c>
@@ -3547,7 +3555,7 @@
       <c r="K82" t="s">
         <v>118</v>
       </c>
-      <c r="L82" s="14">
+      <c r="L82" s="11">
         <f>5*0.85</f>
         <v>4.25</v>
       </c>
@@ -3568,7 +3576,7 @@
       <c r="K83" t="s">
         <v>118</v>
       </c>
-      <c r="L83" s="14">
+      <c r="L83" s="11">
         <f>3.5*0.85</f>
         <v>2.9750000000000001</v>
       </c>
@@ -3589,7 +3597,7 @@
       <c r="K84" t="s">
         <v>118</v>
       </c>
-      <c r="L84" s="14">
+      <c r="L84" s="11">
         <f>L83</f>
         <v>2.9750000000000001</v>
       </c>
@@ -3598,7 +3606,7 @@
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="L85" s="14"/>
+      <c r="L85" s="11"/>
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
@@ -3610,7 +3618,7 @@
       <c r="K86" t="s">
         <v>118</v>
       </c>
-      <c r="L86" s="14">
+      <c r="L86" s="11">
         <f>6*0.85</f>
         <v>5.0999999999999996</v>
       </c>
@@ -3619,7 +3627,7 @@
       </c>
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="L87" s="14"/>
+      <c r="L87" s="11"/>
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
@@ -3634,7 +3642,7 @@
       <c r="K88" t="s">
         <v>118</v>
       </c>
-      <c r="L88" s="14">
+      <c r="L88" s="11">
         <f>100/(365.25/2)*0.85</f>
         <v>0.4654346338124572</v>
       </c>
@@ -3646,7 +3654,7 @@
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="L89" s="14"/>
+      <c r="L89" s="11"/>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
@@ -3661,7 +3669,7 @@
       <c r="K90" t="s">
         <v>118</v>
       </c>
-      <c r="L90" s="14">
+      <c r="L90" s="11">
         <f>1.5*0.85</f>
         <v>1.2749999999999999</v>
       </c>
@@ -3682,7 +3690,7 @@
       <c r="K91" t="s">
         <v>118</v>
       </c>
-      <c r="L91" s="17">
+      <c r="L91" s="13">
         <v>0</v>
       </c>
     </row>
@@ -3699,7 +3707,7 @@
       <c r="K92" t="s">
         <v>118</v>
       </c>
-      <c r="L92" s="18">
+      <c r="L92" s="14">
         <f>L94</f>
         <v>5.9500000000000004E-2</v>
       </c>
@@ -3720,7 +3728,7 @@
       <c r="K93" t="s">
         <v>118</v>
       </c>
-      <c r="L93" s="14">
+      <c r="L93" s="11">
         <v>0</v>
       </c>
       <c r="N93" t="s">
@@ -3743,7 +3751,7 @@
       <c r="K94" t="s">
         <v>118</v>
       </c>
-      <c r="L94" s="14">
+      <c r="L94" s="11">
         <f>0.07*0.85</f>
         <v>5.9500000000000004E-2</v>
       </c>
@@ -3764,13 +3772,13 @@
       <c r="K95" t="s">
         <v>118</v>
       </c>
-      <c r="L95" s="18">
+      <c r="L95" s="14">
         <f>L94</f>
         <v>5.9500000000000004E-2</v>
       </c>
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="L96" s="18"/>
+      <c r="L96" s="14"/>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
@@ -3779,7 +3787,7 @@
       <c r="C97" t="s">
         <v>55</v>
       </c>
-      <c r="L97" s="18"/>
+      <c r="L97" s="14"/>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
@@ -3815,23 +3823,23 @@
       <c r="O100" s="3"/>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A101" s="9" t="s">
+      <c r="A101" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B101" s="10"/>
-      <c r="C101" s="10"/>
-      <c r="D101" s="10"/>
-      <c r="E101" s="10"/>
-      <c r="F101" s="10"/>
-      <c r="G101" s="10"/>
-      <c r="H101" s="10"/>
-      <c r="I101" s="10"/>
-      <c r="J101" s="10"/>
-      <c r="K101" s="10"/>
-      <c r="L101" s="10"/>
-      <c r="M101" s="10"/>
-      <c r="N101" s="10"/>
-      <c r="O101" s="10"/>
+      <c r="B101" s="8"/>
+      <c r="C101" s="8"/>
+      <c r="D101" s="8"/>
+      <c r="E101" s="8"/>
+      <c r="F101" s="8"/>
+      <c r="G101" s="8"/>
+      <c r="H101" s="8"/>
+      <c r="I101" s="8"/>
+      <c r="J101" s="8"/>
+      <c r="K101" s="8"/>
+      <c r="L101" s="8"/>
+      <c r="M101" s="8"/>
+      <c r="N101" s="8"/>
+      <c r="O101" s="8"/>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K102" s="5" t="s">
@@ -3875,23 +3883,23 @@
       <c r="O104" s="5"/>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A105" s="9" t="s">
+      <c r="A105" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B105" s="10"/>
-      <c r="C105" s="10"/>
-      <c r="D105" s="10"/>
-      <c r="E105" s="10"/>
-      <c r="F105" s="10"/>
-      <c r="G105" s="11"/>
-      <c r="H105" s="10"/>
-      <c r="I105" s="10"/>
-      <c r="J105" s="10"/>
-      <c r="K105" s="10"/>
-      <c r="L105" s="10"/>
-      <c r="M105" s="10"/>
-      <c r="N105" s="10"/>
-      <c r="O105" s="10"/>
+      <c r="B105" s="8"/>
+      <c r="C105" s="8"/>
+      <c r="D105" s="8"/>
+      <c r="E105" s="8"/>
+      <c r="F105" s="8"/>
+      <c r="G105" s="9"/>
+      <c r="H105" s="8"/>
+      <c r="I105" s="8"/>
+      <c r="J105" s="8"/>
+      <c r="K105" s="8"/>
+      <c r="L105" s="8"/>
+      <c r="M105" s="8"/>
+      <c r="N105" s="8"/>
+      <c r="O105" s="8"/>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K106" s="6" t="s">
@@ -4280,24 +4288,24 @@
       <c r="N129" s="3"/>
       <c r="O129" s="3"/>
     </row>
-    <row r="130" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="9" t="s">
+    <row r="130" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A130" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="B130" s="10"/>
-      <c r="C130" s="10"/>
-      <c r="D130" s="10"/>
-      <c r="E130" s="10"/>
-      <c r="F130" s="10"/>
-      <c r="G130" s="10"/>
-      <c r="H130" s="10"/>
-      <c r="I130" s="10"/>
-      <c r="J130" s="10"/>
-      <c r="K130" s="10"/>
-      <c r="L130" s="10"/>
-      <c r="M130" s="10"/>
-      <c r="N130" s="10"/>
-      <c r="O130" s="10"/>
+      <c r="B130" s="8"/>
+      <c r="C130" s="8"/>
+      <c r="D130" s="8"/>
+      <c r="E130" s="8"/>
+      <c r="F130" s="8"/>
+      <c r="G130" s="8"/>
+      <c r="H130" s="8"/>
+      <c r="I130" s="8"/>
+      <c r="J130" s="8"/>
+      <c r="K130" s="8"/>
+      <c r="L130" s="8"/>
+      <c r="M130" s="8"/>
+      <c r="N130" s="8"/>
+      <c r="O130" s="8"/>
     </row>
     <row r="131" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
@@ -4323,7 +4331,7 @@
       <c r="K132" t="s">
         <v>97</v>
       </c>
-      <c r="L132" s="12">
+      <c r="L132" s="10">
         <f>L131 * (6.4/2.29)/16</f>
         <v>8.3842794759825345</v>
       </c>
@@ -4344,7 +4352,7 @@
       <c r="K133" t="s">
         <v>98</v>
       </c>
-      <c r="L133" s="12">
+      <c r="L133" s="10">
         <f>L131 * (15.9/(47/39))/16</f>
         <v>39.58085106382979</v>
       </c>
@@ -4365,7 +4373,7 @@
       <c r="K134" t="s">
         <v>4</v>
       </c>
-      <c r="L134" s="12">
+      <c r="L134" s="10">
         <v>14</v>
       </c>
       <c r="M134" t="s">
@@ -4382,7 +4390,7 @@
       <c r="K135" t="s">
         <v>97</v>
       </c>
-      <c r="L135" s="12">
+      <c r="L135" s="10">
         <f>L134 * (4.8/2.29)/14.4</f>
         <v>2.0378457059679769</v>
       </c>
@@ -4400,7 +4408,7 @@
       <c r="K136" t="s">
         <v>98</v>
       </c>
-      <c r="L136" s="12">
+      <c r="L136" s="10">
         <f>L134 * (25.2/(47/39))/14.4</f>
         <v>20.329787234042556</v>
       </c>
@@ -4421,7 +4429,7 @@
       <c r="K137" t="s">
         <v>4</v>
       </c>
-      <c r="L137" s="12">
+      <c r="L137" s="10">
         <v>0</v>
       </c>
       <c r="M137" t="s">
@@ -4444,7 +4452,7 @@
       <c r="K138" t="s">
         <v>97</v>
       </c>
-      <c r="L138" s="12">
+      <c r="L138" s="10">
         <v>0</v>
       </c>
       <c r="M138" t="s">
@@ -4461,7 +4469,7 @@
       <c r="K139" t="s">
         <v>98</v>
       </c>
-      <c r="L139" s="12">
+      <c r="L139" s="10">
         <v>0</v>
       </c>
       <c r="M139" t="s">
@@ -4478,7 +4486,7 @@
       <c r="K140" t="s">
         <v>4</v>
       </c>
-      <c r="L140" s="14">
+      <c r="L140" s="11">
         <v>0.6</v>
       </c>
       <c r="M140" t="s">
@@ -4498,7 +4506,7 @@
       <c r="K141" t="s">
         <v>97</v>
       </c>
-      <c r="L141" s="14">
+      <c r="L141" s="11">
         <f>L140 * (0.39/2.29)/0.75</f>
         <v>0.13624454148471615</v>
       </c>
@@ -4522,7 +4530,7 @@
       <c r="K142" t="s">
         <v>98</v>
       </c>
-      <c r="L142" s="14">
+      <c r="L142" s="11">
         <f>L140 * (0.33/(47/39))/0.75</f>
         <v>0.21906382978723404</v>
       </c>
@@ -4566,7 +4574,7 @@
       <c r="K144" t="s">
         <v>97</v>
       </c>
-      <c r="L144" s="14">
+      <c r="L144" s="11">
         <f>L143 * (0.19/2.29)/0.53</f>
         <v>4.5398368624866105E-2</v>
       </c>
@@ -4590,7 +4598,7 @@
       <c r="K145" t="s">
         <v>98</v>
       </c>
-      <c r="L145" s="14">
+      <c r="L145" s="11">
         <f>L143 * (0.26/(47/39))/0.53</f>
         <v>0.11804897631473303</v>
       </c>
@@ -4614,7 +4622,7 @@
       <c r="K146" t="s">
         <v>4</v>
       </c>
-      <c r="L146" s="14">
+      <c r="L146" s="11">
         <v>0.22</v>
       </c>
       <c r="M146" t="s">
@@ -4634,7 +4642,7 @@
       <c r="K147" t="s">
         <v>97</v>
       </c>
-      <c r="L147" s="67">
+      <c r="L147" s="46">
         <f>L146 * (0.17/2.29)/0.34</f>
         <v>4.8034934497816588E-2</v>
       </c>
@@ -4658,7 +4666,7 @@
       <c r="K148" t="s">
         <v>98</v>
       </c>
-      <c r="L148" s="67">
+      <c r="L148" s="46">
         <f>L146 * (0.14/(47/39))/0.34</f>
         <v>7.5168961201501877E-2</v>
       </c>
@@ -4675,42 +4683,42 @@
     <row r="149" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G149" s="5"/>
     </row>
-    <row r="150" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="8"/>
+    <row r="150" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A150" s="4"/>
       <c r="K150" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="L150" s="13">
-        <v>0</v>
-      </c>
-      <c r="M150" s="13"/>
-      <c r="N150" s="13" t="s">
+      <c r="L150" s="6">
+        <v>0</v>
+      </c>
+      <c r="M150" s="6"/>
+      <c r="N150" s="6" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="151" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="8"/>
+    <row r="151" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A151" s="4"/>
       <c r="K151" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="L151" s="13">
-        <v>0</v>
-      </c>
-      <c r="M151" s="13"/>
-      <c r="N151" s="13" t="s">
+      <c r="L151" s="6">
+        <v>0</v>
+      </c>
+      <c r="M151" s="6"/>
+      <c r="N151" s="6" t="s">
         <v>92</v>
       </c>
     </row>
-    <row r="152" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="8"/>
+    <row r="152" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A152" s="4"/>
       <c r="K152" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="L152" s="13">
-        <v>0</v>
-      </c>
-      <c r="M152" s="13"/>
-      <c r="N152" s="13" t="s">
+      <c r="L152" s="6">
+        <v>0</v>
+      </c>
+      <c r="M152" s="6"/>
+      <c r="N152" s="6" t="s">
         <v>92</v>
       </c>
     </row>
@@ -4770,7 +4778,7 @@
       <c r="K155" t="s">
         <v>77</v>
       </c>
-      <c r="L155" s="12">
+      <c r="L155" s="10">
         <v>2</v>
       </c>
       <c r="M155" t="s">
@@ -4854,14 +4862,14 @@
         <v>200</v>
       </c>
       <c r="G159" s="5"/>
-      <c r="K159" s="54" t="s">
+      <c r="K159" s="45" t="s">
         <v>72</v>
       </c>
-      <c r="L159" s="54">
+      <c r="L159" s="45">
         <f>L156</f>
         <v>26.4</v>
       </c>
-      <c r="M159" s="54" t="s">
+      <c r="M159" s="45" t="s">
         <v>78</v>
       </c>
     </row>
@@ -4873,14 +4881,14 @@
         <v>200</v>
       </c>
       <c r="G160" s="5"/>
-      <c r="K160" s="54" t="s">
+      <c r="K160" s="45" t="s">
         <v>76</v>
       </c>
-      <c r="L160" s="54">
+      <c r="L160" s="45">
         <f t="shared" ref="L160:L170" si="0">L157</f>
         <v>6.85</v>
       </c>
-      <c r="M160" s="54" t="s">
+      <c r="M160" s="45" t="s">
         <v>79</v>
       </c>
     </row>
@@ -4892,14 +4900,14 @@
         <v>200</v>
       </c>
       <c r="G161" s="5"/>
-      <c r="K161" s="54" t="s">
+      <c r="K161" s="45" t="s">
         <v>77</v>
       </c>
-      <c r="L161" s="54">
+      <c r="L161" s="45">
         <f t="shared" si="0"/>
         <v>1.69</v>
       </c>
-      <c r="M161" s="54" t="s">
+      <c r="M161" s="45" t="s">
         <v>80</v>
       </c>
     </row>
@@ -4911,14 +4919,14 @@
         <v>201</v>
       </c>
       <c r="G162" s="5"/>
-      <c r="K162" s="54" t="s">
+      <c r="K162" s="45" t="s">
         <v>72</v>
       </c>
-      <c r="L162" s="54">
+      <c r="L162" s="45">
         <f t="shared" si="0"/>
         <v>26.4</v>
       </c>
-      <c r="M162" s="54" t="s">
+      <c r="M162" s="45" t="s">
         <v>78</v>
       </c>
     </row>
@@ -4930,14 +4938,14 @@
         <v>201</v>
       </c>
       <c r="G163" s="5"/>
-      <c r="K163" s="54" t="s">
+      <c r="K163" s="45" t="s">
         <v>76</v>
       </c>
-      <c r="L163" s="54">
+      <c r="L163" s="45">
         <f t="shared" si="0"/>
         <v>6.85</v>
       </c>
-      <c r="M163" s="54" t="s">
+      <c r="M163" s="45" t="s">
         <v>79</v>
       </c>
     </row>
@@ -4949,14 +4957,14 @@
         <v>201</v>
       </c>
       <c r="G164" s="5"/>
-      <c r="K164" s="54" t="s">
+      <c r="K164" s="45" t="s">
         <v>77</v>
       </c>
-      <c r="L164" s="54">
+      <c r="L164" s="45">
         <f t="shared" si="0"/>
         <v>1.69</v>
       </c>
-      <c r="M164" s="54" t="s">
+      <c r="M164" s="45" t="s">
         <v>80</v>
       </c>
     </row>
@@ -4968,14 +4976,14 @@
         <v>202</v>
       </c>
       <c r="G165" s="5"/>
-      <c r="K165" s="54" t="s">
+      <c r="K165" s="45" t="s">
         <v>72</v>
       </c>
-      <c r="L165" s="54">
+      <c r="L165" s="45">
         <f t="shared" si="0"/>
         <v>26.4</v>
       </c>
-      <c r="M165" s="54" t="s">
+      <c r="M165" s="45" t="s">
         <v>78</v>
       </c>
     </row>
@@ -4987,14 +4995,14 @@
         <v>202</v>
       </c>
       <c r="G166" s="5"/>
-      <c r="K166" s="54" t="s">
+      <c r="K166" s="45" t="s">
         <v>76</v>
       </c>
-      <c r="L166" s="54">
+      <c r="L166" s="45">
         <f t="shared" si="0"/>
         <v>6.85</v>
       </c>
-      <c r="M166" s="54" t="s">
+      <c r="M166" s="45" t="s">
         <v>79</v>
       </c>
     </row>
@@ -5006,14 +5014,14 @@
         <v>202</v>
       </c>
       <c r="G167" s="5"/>
-      <c r="K167" s="54" t="s">
+      <c r="K167" s="45" t="s">
         <v>77</v>
       </c>
-      <c r="L167" s="54">
+      <c r="L167" s="45">
         <f t="shared" si="0"/>
         <v>1.69</v>
       </c>
-      <c r="M167" s="54" t="s">
+      <c r="M167" s="45" t="s">
         <v>80</v>
       </c>
     </row>
@@ -5025,14 +5033,14 @@
         <v>203</v>
       </c>
       <c r="G168" s="5"/>
-      <c r="K168" s="54" t="s">
+      <c r="K168" s="45" t="s">
         <v>72</v>
       </c>
-      <c r="L168" s="54">
+      <c r="L168" s="45">
         <f t="shared" si="0"/>
         <v>26.4</v>
       </c>
-      <c r="M168" s="54" t="s">
+      <c r="M168" s="45" t="s">
         <v>78</v>
       </c>
     </row>
@@ -5044,14 +5052,14 @@
         <v>203</v>
       </c>
       <c r="G169" s="5"/>
-      <c r="K169" s="54" t="s">
+      <c r="K169" s="45" t="s">
         <v>76</v>
       </c>
-      <c r="L169" s="54">
+      <c r="L169" s="45">
         <f t="shared" si="0"/>
         <v>6.85</v>
       </c>
-      <c r="M169" s="54" t="s">
+      <c r="M169" s="45" t="s">
         <v>79</v>
       </c>
     </row>
@@ -5063,14 +5071,14 @@
         <v>203</v>
       </c>
       <c r="G170" s="5"/>
-      <c r="K170" s="54" t="s">
+      <c r="K170" s="45" t="s">
         <v>77</v>
       </c>
-      <c r="L170" s="54">
+      <c r="L170" s="45">
         <f t="shared" si="0"/>
         <v>1.69</v>
       </c>
-      <c r="M170" s="54" t="s">
+      <c r="M170" s="45" t="s">
         <v>80</v>
       </c>
     </row>
@@ -5131,7 +5139,7 @@
       <c r="K173" t="s">
         <v>77</v>
       </c>
-      <c r="L173" s="12">
+      <c r="L173" s="10">
         <v>2</v>
       </c>
       <c r="M173" t="s">
@@ -5329,7 +5337,7 @@
       <c r="K182" t="s">
         <v>77</v>
       </c>
-      <c r="L182" s="12">
+      <c r="L182" s="10">
         <v>2</v>
       </c>
       <c r="M182" t="s">
@@ -5528,7 +5536,7 @@
     </row>
     <row r="194" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G194" s="5"/>
-      <c r="L194" s="12"/>
+      <c r="L194" s="10"/>
     </row>
     <row r="195" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
@@ -5541,7 +5549,7 @@
       <c r="K195" t="s">
         <v>72</v>
       </c>
-      <c r="L195" s="12">
+      <c r="L195" s="10">
         <v>25</v>
       </c>
       <c r="M195" t="s">
@@ -5586,7 +5594,7 @@
       <c r="K197" t="s">
         <v>77</v>
       </c>
-      <c r="L197" s="14">
+      <c r="L197" s="11">
         <v>2.08</v>
       </c>
       <c r="M197" t="s">
@@ -5606,7 +5614,7 @@
       <c r="K198" t="s">
         <v>72</v>
       </c>
-      <c r="L198" s="12">
+      <c r="L198" s="10">
         <v>24.9</v>
       </c>
       <c r="M198" t="s">
@@ -5629,7 +5637,7 @@
       <c r="K199" t="s">
         <v>76</v>
       </c>
-      <c r="L199" s="14">
+      <c r="L199" s="11">
         <v>5.35</v>
       </c>
       <c r="M199" t="s">
@@ -5649,7 +5657,7 @@
       <c r="K200" t="s">
         <v>77</v>
       </c>
-      <c r="L200" s="14">
+      <c r="L200" s="11">
         <v>2.25</v>
       </c>
       <c r="M200" t="s">
@@ -5669,7 +5677,7 @@
       <c r="K201" t="s">
         <v>72</v>
       </c>
-      <c r="L201" s="12">
+      <c r="L201" s="10">
         <v>25</v>
       </c>
       <c r="M201" t="s">
@@ -5692,7 +5700,7 @@
       <c r="K202" t="s">
         <v>76</v>
       </c>
-      <c r="L202" s="14">
+      <c r="L202" s="11">
         <v>5.35</v>
       </c>
       <c r="M202" t="s">
@@ -5712,7 +5720,7 @@
       <c r="K203" t="s">
         <v>77</v>
       </c>
-      <c r="L203" s="14">
+      <c r="L203" s="11">
         <v>2.04</v>
       </c>
       <c r="M203" t="s">
@@ -5733,7 +5741,7 @@
       <c r="K204" t="s">
         <v>72</v>
       </c>
-      <c r="L204" s="12">
+      <c r="L204" s="10">
         <v>23.1</v>
       </c>
       <c r="M204" t="s">
@@ -5757,7 +5765,7 @@
       <c r="K205" t="s">
         <v>76</v>
       </c>
-      <c r="L205" s="14">
+      <c r="L205" s="11">
         <v>5.36</v>
       </c>
       <c r="M205" t="s">
@@ -5778,7 +5786,7 @@
       <c r="K206" t="s">
         <v>77</v>
       </c>
-      <c r="L206" s="14">
+      <c r="L206" s="11">
         <v>2.64</v>
       </c>
       <c r="M206" t="s">
@@ -5799,7 +5807,7 @@
       <c r="K207" t="s">
         <v>72</v>
       </c>
-      <c r="L207" s="12">
+      <c r="L207" s="10">
         <v>24.8</v>
       </c>
       <c r="M207" t="s">
@@ -5823,7 +5831,7 @@
       <c r="K208" t="s">
         <v>76</v>
       </c>
-      <c r="L208" s="14">
+      <c r="L208" s="11">
         <v>5.32</v>
       </c>
       <c r="M208" t="s">
@@ -5844,7 +5852,7 @@
       <c r="K209" t="s">
         <v>77</v>
       </c>
-      <c r="L209" s="14">
+      <c r="L209" s="11">
         <v>2.42</v>
       </c>
       <c r="M209" t="s">
@@ -5865,7 +5873,7 @@
       <c r="K210" t="s">
         <v>72</v>
       </c>
-      <c r="L210" s="12">
+      <c r="L210" s="10">
         <v>25</v>
       </c>
       <c r="M210" t="s">
@@ -5889,7 +5897,7 @@
       <c r="K211" t="s">
         <v>76</v>
       </c>
-      <c r="L211" s="14">
+      <c r="L211" s="11">
         <v>5.36</v>
       </c>
       <c r="M211" t="s">
@@ -5910,7 +5918,7 @@
       <c r="K212" t="s">
         <v>77</v>
       </c>
-      <c r="L212" s="14">
+      <c r="L212" s="11">
         <v>2.2799999999999998</v>
       </c>
       <c r="M212" t="s">
@@ -5922,14 +5930,14 @@
     </row>
     <row r="213" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G213" s="5"/>
-      <c r="L213" s="12"/>
+      <c r="L213" s="10"/>
     </row>
     <row r="214" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G214" s="5"/>
       <c r="K214" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="L214" s="15">
+      <c r="L214" s="12">
         <v>0</v>
       </c>
       <c r="M214" s="6" t="s">
@@ -5941,7 +5949,7 @@
       <c r="K215" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="L215" s="15">
+      <c r="L215" s="12">
         <v>0</v>
       </c>
       <c r="M215" s="6" t="s">
@@ -5953,7 +5961,7 @@
       <c r="K216" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="L216" s="15">
+      <c r="L216" s="12">
         <v>0</v>
       </c>
       <c r="M216" s="6" t="s">
@@ -5968,7 +5976,7 @@
       <c r="K217" t="s">
         <v>106</v>
       </c>
-      <c r="L217" s="14">
+      <c r="L217" s="11">
         <f>5.49/1.035</f>
         <v>5.304347826086957</v>
       </c>
@@ -5990,7 +5998,7 @@
       <c r="K218" t="s">
         <v>111</v>
       </c>
-      <c r="L218" s="14">
+      <c r="L218" s="11">
         <f>0.97/1.035</f>
         <v>0.9371980676328503</v>
       </c>
@@ -6009,7 +6017,7 @@
       <c r="K219" t="s">
         <v>112</v>
       </c>
-      <c r="L219" s="14">
+      <c r="L219" s="11">
         <f>1.6/1.035</f>
         <v>1.5458937198067635</v>
       </c>
@@ -6022,32 +6030,32 @@
     </row>
     <row r="220" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G220" s="5"/>
-      <c r="L220" s="14"/>
+      <c r="L220" s="11"/>
     </row>
     <row r="221" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A221" s="9" t="s">
+      <c r="A221" s="7" t="s">
         <v>182</v>
       </c>
-      <c r="B221" s="10"/>
-      <c r="C221" s="10"/>
-      <c r="D221" s="10"/>
-      <c r="E221" s="10"/>
-      <c r="F221" s="10"/>
-      <c r="G221" s="11"/>
-      <c r="H221" s="10"/>
-      <c r="I221" s="10"/>
-      <c r="J221" s="10"/>
-      <c r="K221" s="10"/>
-      <c r="L221" s="10"/>
-      <c r="M221" s="10"/>
-      <c r="N221" s="10"/>
-      <c r="O221" s="10"/>
+      <c r="B221" s="8"/>
+      <c r="C221" s="8"/>
+      <c r="D221" s="8"/>
+      <c r="E221" s="8"/>
+      <c r="F221" s="8"/>
+      <c r="G221" s="9"/>
+      <c r="H221" s="8"/>
+      <c r="I221" s="8"/>
+      <c r="J221" s="8"/>
+      <c r="K221" s="8"/>
+      <c r="L221" s="8"/>
+      <c r="M221" s="8"/>
+      <c r="N221" s="8"/>
+      <c r="O221" s="8"/>
     </row>
     <row r="222" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G222" s="5"/>
     </row>
     <row r="223" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A223" s="49" t="s">
+      <c r="A223" t="s">
         <v>175</v>
       </c>
       <c r="G223" s="5"/>
@@ -6247,7 +6255,7 @@
       </c>
     </row>
     <row r="233" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A233" s="41" t="s">
+      <c r="A233" t="s">
         <v>1</v>
       </c>
       <c r="G233" s="5" t="s">
@@ -6742,26 +6750,26 @@
       <c r="G252" s="5"/>
     </row>
     <row r="253" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A253" s="9" t="s">
+      <c r="A253" s="7" t="s">
         <v>75</v>
       </c>
-      <c r="B253" s="10"/>
-      <c r="C253" s="10"/>
-      <c r="D253" s="10"/>
-      <c r="E253" s="10"/>
-      <c r="F253" s="10"/>
-      <c r="G253" s="11"/>
-      <c r="H253" s="10"/>
-      <c r="I253" s="10"/>
-      <c r="J253" s="10"/>
-      <c r="K253" s="10"/>
-      <c r="L253" s="10"/>
-      <c r="M253" s="10"/>
-      <c r="N253" s="10"/>
-      <c r="O253" s="10"/>
-    </row>
-    <row r="254" spans="1:15" s="7" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="G254" s="48"/>
+      <c r="B253" s="8"/>
+      <c r="C253" s="8"/>
+      <c r="D253" s="8"/>
+      <c r="E253" s="8"/>
+      <c r="F253" s="8"/>
+      <c r="G253" s="9"/>
+      <c r="H253" s="8"/>
+      <c r="I253" s="8"/>
+      <c r="J253" s="8"/>
+      <c r="K253" s="8"/>
+      <c r="L253" s="8"/>
+      <c r="M253" s="8"/>
+      <c r="N253" s="8"/>
+      <c r="O253" s="8"/>
+    </row>
+    <row r="254" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G254" s="5"/>
     </row>
     <row r="255" spans="1:15" x14ac:dyDescent="0.25">
       <c r="H255" s="6" t="s">
@@ -6794,7 +6802,7 @@
       <c r="N256" s="1"/>
     </row>
     <row r="257" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A257" s="50"/>
+      <c r="A257" s="42"/>
       <c r="H257" s="6"/>
       <c r="I257" s="6"/>
       <c r="J257" s="6"/>
@@ -6808,7 +6816,7 @@
       <c r="N257" s="1"/>
     </row>
     <row r="258" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A258" s="50"/>
+      <c r="A258" s="42"/>
       <c r="L258" s="1"/>
       <c r="M258" s="1"/>
       <c r="N258" s="1"/>
@@ -6918,31 +6926,25 @@
       </c>
     </row>
     <row r="263" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A263" s="41" t="s">
+      <c r="A263" t="s">
         <v>48</v>
       </c>
-      <c r="B263" s="41"/>
-      <c r="C263" s="41"/>
-      <c r="D263" s="41"/>
-      <c r="E263" s="41"/>
-      <c r="F263" s="41"/>
-      <c r="G263" s="41" t="s">
+      <c r="G263" t="s">
         <v>17</v>
       </c>
       <c r="H263" t="s">
         <v>184</v>
       </c>
-      <c r="I263" s="41" t="s">
+      <c r="I263" t="s">
         <v>19</v>
       </c>
-      <c r="J263" s="41"/>
-      <c r="K263" s="41" t="s">
+      <c r="K263" t="s">
         <v>20</v>
       </c>
-      <c r="L263" s="41">
+      <c r="L263">
         <v>4</v>
       </c>
-      <c r="M263" s="41" t="s">
+      <c r="M263" t="s">
         <v>49</v>
       </c>
       <c r="N263" s="1"/>
@@ -6951,31 +6953,25 @@
       </c>
     </row>
     <row r="264" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A264" s="41" t="s">
+      <c r="A264" t="s">
         <v>48</v>
       </c>
-      <c r="B264" s="41"/>
-      <c r="C264" s="41"/>
-      <c r="D264" s="41"/>
-      <c r="E264" s="41"/>
-      <c r="F264" s="41"/>
-      <c r="G264" s="41" t="s">
+      <c r="G264" t="s">
         <v>18</v>
       </c>
       <c r="H264" t="s">
         <v>184</v>
       </c>
-      <c r="I264" s="41" t="s">
+      <c r="I264" t="s">
         <v>19</v>
       </c>
-      <c r="J264" s="41"/>
-      <c r="K264" s="41" t="s">
+      <c r="K264" t="s">
         <v>20</v>
       </c>
-      <c r="L264" s="41">
+      <c r="L264">
         <v>15</v>
       </c>
-      <c r="M264" s="41" t="s">
+      <c r="M264" t="s">
         <v>49</v>
       </c>
       <c r="N264" s="1"/>
@@ -6984,31 +6980,25 @@
       </c>
     </row>
     <row r="265" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A265" s="41" t="s">
+      <c r="A265" t="s">
         <v>48</v>
       </c>
-      <c r="B265" s="41"/>
-      <c r="C265" s="41"/>
-      <c r="D265" s="41"/>
-      <c r="E265" s="41"/>
-      <c r="F265" s="41"/>
-      <c r="G265" s="41" t="s">
+      <c r="G265" t="s">
         <v>166</v>
       </c>
       <c r="H265" t="s">
         <v>184</v>
       </c>
-      <c r="I265" s="41" t="s">
+      <c r="I265" t="s">
         <v>19</v>
       </c>
-      <c r="J265" s="41"/>
-      <c r="K265" s="41" t="s">
+      <c r="K265" t="s">
         <v>20</v>
       </c>
-      <c r="L265" s="41">
+      <c r="L265">
         <v>4</v>
       </c>
-      <c r="M265" s="41" t="s">
+      <c r="M265" t="s">
         <v>49</v>
       </c>
       <c r="N265" s="1"/>
@@ -7017,31 +7007,25 @@
       </c>
     </row>
     <row r="266" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A266" s="41" t="s">
+      <c r="A266" t="s">
         <v>54</v>
       </c>
-      <c r="B266" s="41"/>
-      <c r="C266" s="41"/>
-      <c r="D266" s="41"/>
-      <c r="E266" s="41"/>
-      <c r="F266" s="41"/>
       <c r="G266" t="s">
         <v>17</v>
       </c>
       <c r="H266" t="s">
         <v>184</v>
       </c>
-      <c r="I266" s="41" t="s">
+      <c r="I266" t="s">
         <v>19</v>
       </c>
-      <c r="J266" s="41"/>
-      <c r="K266" s="41" t="s">
+      <c r="K266" t="s">
         <v>20</v>
       </c>
-      <c r="L266" s="41">
+      <c r="L266">
         <v>4</v>
       </c>
-      <c r="M266" s="41" t="s">
+      <c r="M266" t="s">
         <v>49</v>
       </c>
       <c r="N266" s="1"/>
@@ -7050,31 +7034,25 @@
       </c>
     </row>
     <row r="267" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A267" s="41" t="s">
+      <c r="A267" t="s">
         <v>54</v>
       </c>
-      <c r="B267" s="41"/>
-      <c r="C267" s="41"/>
-      <c r="D267" s="41"/>
-      <c r="E267" s="41"/>
-      <c r="F267" s="41"/>
       <c r="G267" t="s">
         <v>18</v>
       </c>
       <c r="H267" t="s">
         <v>184</v>
       </c>
-      <c r="I267" s="41" t="s">
+      <c r="I267" t="s">
         <v>19</v>
       </c>
-      <c r="J267" s="41"/>
-      <c r="K267" s="41" t="s">
+      <c r="K267" t="s">
         <v>20</v>
       </c>
-      <c r="L267" s="41">
+      <c r="L267">
         <v>15</v>
       </c>
-      <c r="M267" s="41" t="s">
+      <c r="M267" t="s">
         <v>49</v>
       </c>
       <c r="N267" s="1"/>
@@ -7568,31 +7546,25 @@
       </c>
     </row>
     <row r="286" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A286" s="41" t="s">
-        <v>48</v>
-      </c>
-      <c r="B286" s="41"/>
-      <c r="C286" s="41"/>
-      <c r="D286" s="41"/>
-      <c r="E286" s="41"/>
-      <c r="F286" s="41"/>
-      <c r="G286" s="41" t="s">
+      <c r="A286" t="s">
+        <v>54</v>
+      </c>
+      <c r="G286" t="s">
         <v>17</v>
       </c>
       <c r="H286" t="s">
         <v>184</v>
       </c>
-      <c r="I286" s="41" t="s">
+      <c r="I286" t="s">
         <v>19</v>
       </c>
-      <c r="J286" s="41"/>
-      <c r="K286" s="41" t="s">
+      <c r="K286" t="s">
         <v>21</v>
       </c>
-      <c r="L286" s="41">
+      <c r="L286">
         <v>25</v>
       </c>
-      <c r="M286" s="41" t="s">
+      <c r="M286" t="s">
         <v>49</v>
       </c>
       <c r="N286" s="1"/>
@@ -7601,31 +7573,25 @@
       </c>
     </row>
     <row r="287" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A287" s="41" t="s">
-        <v>48</v>
-      </c>
-      <c r="B287" s="41"/>
-      <c r="C287" s="41"/>
-      <c r="D287" s="41"/>
-      <c r="E287" s="41"/>
-      <c r="F287" s="41"/>
-      <c r="G287" s="41" t="s">
+      <c r="A287" t="s">
+        <v>54</v>
+      </c>
+      <c r="G287" t="s">
         <v>18</v>
       </c>
       <c r="H287" t="s">
         <v>184</v>
       </c>
-      <c r="I287" s="41" t="s">
+      <c r="I287" t="s">
         <v>19</v>
       </c>
-      <c r="J287" s="41"/>
-      <c r="K287" s="41" t="s">
+      <c r="K287" t="s">
         <v>21</v>
       </c>
-      <c r="L287" s="41">
+      <c r="L287">
         <v>33</v>
       </c>
-      <c r="M287" s="41" t="s">
+      <c r="M287" t="s">
         <v>49</v>
       </c>
       <c r="N287" s="1"/>
@@ -7634,44 +7600,40 @@
       </c>
     </row>
     <row r="288" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A288" s="41" t="s">
-        <v>48</v>
-      </c>
-      <c r="B288" s="41"/>
-      <c r="C288" s="41"/>
-      <c r="D288" s="41"/>
-      <c r="E288" s="41"/>
-      <c r="F288" s="41"/>
-      <c r="G288" s="41" t="s">
+      <c r="A288" t="s">
+        <v>54</v>
+      </c>
+      <c r="G288" t="s">
         <v>166</v>
       </c>
       <c r="H288" t="s">
         <v>184</v>
       </c>
-      <c r="I288" s="41" t="s">
+      <c r="I288" t="s">
         <v>19</v>
       </c>
-      <c r="J288" s="41"/>
-      <c r="K288" s="41" t="s">
+      <c r="K288" t="s">
         <v>21</v>
       </c>
-      <c r="L288" s="41">
-        <v>0.25</v>
-      </c>
-      <c r="M288" s="41" t="s">
+      <c r="L288" s="5">
+        <v>25</v>
+      </c>
+      <c r="M288" t="s">
         <v>49</v>
       </c>
-      <c r="N288" s="1"/>
+      <c r="N288" s="5" t="s">
+        <v>211</v>
+      </c>
       <c r="O288" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="289" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="G289" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H289" t="s">
         <v>184</v>
@@ -7683,21 +7645,22 @@
         <v>21</v>
       </c>
       <c r="L289">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="M289" t="s">
         <v>49</v>
       </c>
+      <c r="N289" s="1"/>
       <c r="O289" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="290" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="G290" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H290" t="s">
         <v>184</v>
@@ -7709,21 +7672,22 @@
         <v>21</v>
       </c>
       <c r="L290">
-        <v>18</v>
+        <v>33</v>
       </c>
       <c r="M290" t="s">
         <v>49</v>
       </c>
+      <c r="N290" s="1"/>
       <c r="O290" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="291" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="G291" t="s">
-        <v>18</v>
+        <v>166</v>
       </c>
       <c r="H291" t="s">
         <v>184</v>
@@ -7734,11 +7698,14 @@
       <c r="K291" t="s">
         <v>21</v>
       </c>
-      <c r="L291">
-        <v>30</v>
+      <c r="L291" s="5">
+        <v>25</v>
       </c>
       <c r="M291" t="s">
         <v>49</v>
+      </c>
+      <c r="N291" s="5" t="s">
+        <v>211</v>
       </c>
       <c r="O291" t="s">
         <v>172</v>
@@ -7749,7 +7716,7 @@
         <v>35</v>
       </c>
       <c r="G292" t="s">
-        <v>174</v>
+        <v>16</v>
       </c>
       <c r="H292" t="s">
         <v>184</v>
@@ -7761,7 +7728,7 @@
         <v>21</v>
       </c>
       <c r="L292">
-        <v>2.75</v>
+        <v>4</v>
       </c>
       <c r="M292" t="s">
         <v>49</v>
@@ -7772,10 +7739,10 @@
     </row>
     <row r="293" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="G293" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H293" t="s">
         <v>184</v>
@@ -7787,7 +7754,7 @@
         <v>21</v>
       </c>
       <c r="L293">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="M293" t="s">
         <v>49</v>
@@ -7798,10 +7765,10 @@
     </row>
     <row r="294" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="G294" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H294" t="s">
         <v>184</v>
@@ -7813,7 +7780,7 @@
         <v>21</v>
       </c>
       <c r="L294">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="M294" t="s">
         <v>49</v>
@@ -7824,10 +7791,10 @@
     </row>
     <row r="295" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="G295" t="s">
-        <v>18</v>
+        <v>174</v>
       </c>
       <c r="H295" t="s">
         <v>184</v>
@@ -7839,7 +7806,7 @@
         <v>21</v>
       </c>
       <c r="L295">
-        <v>20</v>
+        <v>2.75</v>
       </c>
       <c r="M295" t="s">
         <v>49</v>
@@ -7852,11 +7819,8 @@
       <c r="A296" t="s">
         <v>45</v>
       </c>
-      <c r="E296" t="s">
-        <v>47</v>
-      </c>
       <c r="G296" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H296" t="s">
         <v>184</v>
@@ -7868,7 +7832,7 @@
         <v>21</v>
       </c>
       <c r="L296">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="M296" t="s">
         <v>49</v>
@@ -7881,11 +7845,8 @@
       <c r="A297" t="s">
         <v>45</v>
       </c>
-      <c r="E297" t="s">
-        <v>47</v>
-      </c>
       <c r="G297" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H297" t="s">
         <v>184</v>
@@ -7897,7 +7858,7 @@
         <v>21</v>
       </c>
       <c r="L297">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="M297" t="s">
         <v>49</v>
@@ -7906,78 +7867,93 @@
         <v>172</v>
       </c>
     </row>
+    <row r="298" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A298" t="s">
+        <v>45</v>
+      </c>
+      <c r="G298" t="s">
+        <v>18</v>
+      </c>
+      <c r="H298" t="s">
+        <v>184</v>
+      </c>
+      <c r="I298" t="s">
+        <v>19</v>
+      </c>
+      <c r="K298" t="s">
+        <v>21</v>
+      </c>
+      <c r="L298">
+        <v>20</v>
+      </c>
+      <c r="M298" t="s">
+        <v>49</v>
+      </c>
+      <c r="O298" t="s">
+        <v>172</v>
+      </c>
+    </row>
     <row r="299" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A299" t="s">
+        <v>45</v>
+      </c>
+      <c r="E299" t="s">
+        <v>47</v>
+      </c>
       <c r="G299" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H299" t="s">
         <v>184</v>
       </c>
       <c r="I299" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K299" t="s">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="L299">
-        <v>0.01</v>
+        <v>5</v>
       </c>
       <c r="M299" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O299" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
     </row>
     <row r="300" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A300" t="s">
+        <v>45</v>
+      </c>
+      <c r="E300" t="s">
+        <v>47</v>
+      </c>
       <c r="G300" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H300" t="s">
         <v>184</v>
       </c>
       <c r="I300" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K300" t="s">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="L300">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M300" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O300" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="301" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="G301" t="s">
-        <v>18</v>
-      </c>
-      <c r="H301" t="s">
-        <v>184</v>
-      </c>
-      <c r="I301" t="s">
-        <v>22</v>
-      </c>
-      <c r="K301" t="s">
-        <v>192</v>
-      </c>
-      <c r="L301">
-        <v>1</v>
-      </c>
-      <c r="M301" t="s">
-        <v>50</v>
-      </c>
-      <c r="O301" t="s">
-        <v>179</v>
+        <v>172</v>
       </c>
     </row>
     <row r="302" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G302" t="s">
-        <v>166</v>
+        <v>16</v>
       </c>
       <c r="H302" t="s">
         <v>184</v>
@@ -7989,7 +7965,7 @@
         <v>192</v>
       </c>
       <c r="L302">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="M302" t="s">
         <v>50</v>
@@ -7998,78 +7974,78 @@
         <v>179</v>
       </c>
     </row>
+    <row r="303" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G303" t="s">
+        <v>17</v>
+      </c>
+      <c r="H303" t="s">
+        <v>184</v>
+      </c>
+      <c r="I303" t="s">
+        <v>22</v>
+      </c>
+      <c r="K303" t="s">
+        <v>192</v>
+      </c>
+      <c r="L303">
+        <v>1</v>
+      </c>
+      <c r="M303" t="s">
+        <v>50</v>
+      </c>
+      <c r="O303" t="s">
+        <v>179</v>
+      </c>
+    </row>
     <row r="304" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G304" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H304" t="s">
         <v>184</v>
       </c>
       <c r="I304" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K304" t="s">
-        <v>21</v>
+        <v>192</v>
       </c>
       <c r="L304">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M304" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O304" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="305" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G305" t="s">
-        <v>17</v>
+        <v>166</v>
       </c>
       <c r="H305" t="s">
         <v>184</v>
       </c>
       <c r="I305" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K305" t="s">
-        <v>21</v>
+        <v>192</v>
       </c>
       <c r="L305">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M305" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O305" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="306" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="G306" t="s">
-        <v>18</v>
-      </c>
-      <c r="H306" t="s">
-        <v>184</v>
-      </c>
-      <c r="I306" t="s">
-        <v>23</v>
-      </c>
-      <c r="K306" t="s">
-        <v>21</v>
-      </c>
-      <c r="L306">
-        <v>1</v>
-      </c>
-      <c r="M306" t="s">
-        <v>49</v>
-      </c>
-      <c r="O306" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
     </row>
     <row r="307" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G307" t="s">
-        <v>174</v>
+        <v>16</v>
       </c>
       <c r="H307" t="s">
         <v>184</v>
@@ -8081,7 +8057,7 @@
         <v>21</v>
       </c>
       <c r="L307">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M307" t="s">
         <v>49</v>
@@ -8091,8 +8067,8 @@
       </c>
     </row>
     <row r="308" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="G308" s="41" t="s">
-        <v>166</v>
+      <c r="G308" t="s">
+        <v>17</v>
       </c>
       <c r="H308" t="s">
         <v>184</v>
@@ -8104,7 +8080,7 @@
         <v>21</v>
       </c>
       <c r="L308">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M308" t="s">
         <v>49</v>
@@ -8113,87 +8089,78 @@
         <v>178</v>
       </c>
     </row>
+    <row r="309" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G309" t="s">
+        <v>18</v>
+      </c>
+      <c r="H309" t="s">
+        <v>184</v>
+      </c>
+      <c r="I309" t="s">
+        <v>23</v>
+      </c>
+      <c r="K309" t="s">
+        <v>21</v>
+      </c>
+      <c r="L309">
+        <v>1</v>
+      </c>
+      <c r="M309" t="s">
+        <v>49</v>
+      </c>
+      <c r="O309" t="s">
+        <v>178</v>
+      </c>
+    </row>
     <row r="310" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G310" t="s">
-        <v>16</v>
+        <v>174</v>
       </c>
       <c r="H310" t="s">
         <v>184</v>
       </c>
       <c r="I310" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K310" t="s">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="L310">
-        <v>0.31</v>
+        <v>0</v>
       </c>
       <c r="M310" t="s">
-        <v>50</v>
-      </c>
-      <c r="N310" t="s">
-        <v>177</v>
+        <v>49</v>
       </c>
       <c r="O310" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="311" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G311" t="s">
-        <v>17</v>
+        <v>166</v>
       </c>
       <c r="H311" t="s">
         <v>184</v>
       </c>
       <c r="I311" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K311" t="s">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="L311">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="M311" t="s">
-        <v>50</v>
-      </c>
-      <c r="N311" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="O311" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="312" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="G312" t="s">
-        <v>18</v>
-      </c>
-      <c r="H312" t="s">
-        <v>184</v>
-      </c>
-      <c r="I312" t="s">
-        <v>24</v>
-      </c>
-      <c r="K312" t="s">
-        <v>192</v>
-      </c>
-      <c r="L312">
-        <v>31</v>
-      </c>
-      <c r="M312" t="s">
-        <v>50</v>
-      </c>
-      <c r="N312" t="s">
-        <v>17</v>
-      </c>
-      <c r="O312" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
     </row>
     <row r="313" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G313" t="s">
-        <v>166</v>
+        <v>16</v>
       </c>
       <c r="H313" t="s">
         <v>184</v>
@@ -8205,76 +8172,154 @@
         <v>192</v>
       </c>
       <c r="L313">
-        <v>31</v>
+        <v>0.31</v>
       </c>
       <c r="M313" t="s">
         <v>50</v>
       </c>
       <c r="N313" t="s">
-        <v>17</v>
+        <v>177</v>
       </c>
       <c r="O313" t="s">
         <v>176</v>
       </c>
     </row>
+    <row r="314" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G314" t="s">
+        <v>17</v>
+      </c>
+      <c r="H314" t="s">
+        <v>184</v>
+      </c>
+      <c r="I314" t="s">
+        <v>24</v>
+      </c>
+      <c r="K314" t="s">
+        <v>192</v>
+      </c>
+      <c r="L314">
+        <v>31</v>
+      </c>
+      <c r="M314" t="s">
+        <v>50</v>
+      </c>
+      <c r="N314" t="s">
+        <v>17</v>
+      </c>
+      <c r="O314" t="s">
+        <v>176</v>
+      </c>
+    </row>
     <row r="315" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A315" s="1" t="s">
+      <c r="G315" t="s">
+        <v>18</v>
+      </c>
+      <c r="H315" t="s">
+        <v>184</v>
+      </c>
+      <c r="I315" t="s">
+        <v>24</v>
+      </c>
+      <c r="K315" t="s">
+        <v>192</v>
+      </c>
+      <c r="L315">
+        <v>31</v>
+      </c>
+      <c r="M315" t="s">
+        <v>50</v>
+      </c>
+      <c r="N315" t="s">
+        <v>17</v>
+      </c>
+      <c r="O315" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="316" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G316" t="s">
+        <v>166</v>
+      </c>
+      <c r="H316" t="s">
+        <v>184</v>
+      </c>
+      <c r="I316" t="s">
+        <v>24</v>
+      </c>
+      <c r="K316" t="s">
+        <v>192</v>
+      </c>
+      <c r="L316">
+        <v>31</v>
+      </c>
+      <c r="M316" t="s">
+        <v>50</v>
+      </c>
+      <c r="N316" t="s">
+        <v>17</v>
+      </c>
+      <c r="O316" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="318" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A318" s="1" t="s">
         <v>187</v>
-      </c>
-    </row>
-    <row r="316" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="H316" t="s">
-        <v>185</v>
-      </c>
-      <c r="I316" t="s">
-        <v>185</v>
-      </c>
-      <c r="K316" t="s">
-        <v>20</v>
-      </c>
-      <c r="L316">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="317" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="H317" t="s">
-        <v>185</v>
-      </c>
-      <c r="I317" t="s">
-        <v>185</v>
-      </c>
-      <c r="K317" t="s">
-        <v>21</v>
-      </c>
-      <c r="L317">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="318" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="H318" t="s">
-        <v>186</v>
-      </c>
-      <c r="I318" t="s">
-        <v>186</v>
-      </c>
-      <c r="K318" t="s">
-        <v>20</v>
-      </c>
-      <c r="L318" s="42">
-        <v>0</v>
       </c>
     </row>
     <row r="319" spans="1:15" x14ac:dyDescent="0.25">
       <c r="H319" t="s">
+        <v>185</v>
+      </c>
+      <c r="I319" t="s">
+        <v>185</v>
+      </c>
+      <c r="K319" t="s">
+        <v>20</v>
+      </c>
+      <c r="L319">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="320" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="H320" t="s">
+        <v>185</v>
+      </c>
+      <c r="I320" t="s">
+        <v>185</v>
+      </c>
+      <c r="K320" t="s">
+        <v>21</v>
+      </c>
+      <c r="L320">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="321" spans="8:12" x14ac:dyDescent="0.25">
+      <c r="H321" t="s">
         <v>186</v>
       </c>
-      <c r="I319" t="s">
+      <c r="I321" t="s">
         <v>186</v>
       </c>
-      <c r="K319" t="s">
+      <c r="K321" t="s">
+        <v>20</v>
+      </c>
+      <c r="L321" s="37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="322" spans="8:12" x14ac:dyDescent="0.25">
+      <c r="H322" t="s">
+        <v>186</v>
+      </c>
+      <c r="I322" t="s">
+        <v>186</v>
+      </c>
+      <c r="K322" t="s">
         <v>21</v>
       </c>
-      <c r="L319">
+      <c r="L322">
         <v>0</v>
       </c>
     </row>
@@ -8285,7 +8330,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="B2:Z97"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -8300,3644 +8345,3644 @@
       </c>
     </row>
     <row r="5" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B5" s="43" t="s">
+      <c r="B5" s="38" t="s">
         <v>164</v>
       </c>
-      <c r="C5" s="44" t="s">
+      <c r="C5" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="D5" s="44" t="s">
+      <c r="D5" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="E5" s="44" t="s">
+      <c r="E5" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="F5" s="44" t="s">
+      <c r="F5" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="G5" s="44" t="s">
+      <c r="G5" s="39" t="s">
         <v>1</v>
       </c>
-      <c r="H5" s="44" t="s">
+      <c r="H5" s="39" t="s">
         <v>48</v>
       </c>
-      <c r="I5" s="44" t="s">
+      <c r="I5" s="39" t="s">
         <v>54</v>
       </c>
-      <c r="J5" s="44" t="s">
+      <c r="J5" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="K5" s="44" t="s">
+      <c r="K5" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="L5" s="44" t="s">
+      <c r="L5" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="M5" s="44" t="s">
+      <c r="M5" s="39" t="s">
         <v>45</v>
       </c>
-      <c r="O5" s="43" t="s">
+      <c r="O5" s="38" t="s">
         <v>164</v>
       </c>
-      <c r="P5" s="44" t="str">
+      <c r="P5" s="39" t="str">
         <f t="shared" ref="P5:Z5" si="0">C5</f>
         <v>cattle</v>
       </c>
-      <c r="Q5" s="44" t="str">
+      <c r="Q5" s="39" t="str">
         <f t="shared" si="0"/>
         <v>cattle</v>
       </c>
-      <c r="R5" s="44" t="str">
+      <c r="R5" s="39" t="str">
         <f t="shared" si="0"/>
         <v>cattle</v>
       </c>
-      <c r="S5" s="44" t="str">
+      <c r="S5" s="39" t="str">
         <f t="shared" si="0"/>
         <v>cattle</v>
       </c>
-      <c r="T5" s="44" t="str">
+      <c r="T5" s="39" t="str">
         <f t="shared" si="0"/>
         <v>cattle</v>
       </c>
-      <c r="U5" s="44" t="str">
+      <c r="U5" s="39" t="str">
         <f t="shared" si="0"/>
         <v>horses</v>
       </c>
-      <c r="V5" s="44" t="str">
+      <c r="V5" s="39" t="str">
         <f t="shared" si="0"/>
         <v>sheep</v>
       </c>
-      <c r="W5" s="44" t="str">
+      <c r="W5" s="39" t="str">
         <f t="shared" si="0"/>
         <v>pigs</v>
       </c>
-      <c r="X5" s="44" t="str">
+      <c r="X5" s="39" t="str">
         <f t="shared" si="0"/>
         <v>pigs</v>
       </c>
-      <c r="Y5" s="44" t="str">
+      <c r="Y5" s="39" t="str">
         <f t="shared" si="0"/>
         <v>poultry</v>
       </c>
-      <c r="Z5" s="44" t="str">
+      <c r="Z5" s="39" t="str">
         <f t="shared" si="0"/>
         <v>poultry</v>
       </c>
     </row>
     <row r="6" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B6" s="43" t="s">
+      <c r="B6" s="38" t="s">
         <v>165</v>
       </c>
-      <c r="C6" s="44" t="s">
+      <c r="C6" s="39" t="s">
         <v>2</v>
       </c>
-      <c r="D6" s="44" t="s">
+      <c r="D6" s="39" t="s">
         <v>6</v>
       </c>
-      <c r="E6" s="44"/>
-      <c r="F6" s="44"/>
-      <c r="G6" s="44"/>
-      <c r="H6" s="44"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="44"/>
-      <c r="M6" s="44"/>
-      <c r="O6" s="43" t="s">
+      <c r="E6" s="39"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="39"/>
+      <c r="H6" s="39"/>
+      <c r="I6" s="39"/>
+      <c r="J6" s="39"/>
+      <c r="K6" s="39"/>
+      <c r="L6" s="39"/>
+      <c r="M6" s="39"/>
+      <c r="O6" s="38" t="s">
         <v>165</v>
       </c>
-      <c r="P6" s="44" t="str">
+      <c r="P6" s="39" t="str">
         <f>C6</f>
         <v>dairy</v>
       </c>
-      <c r="Q6" s="44" t="str">
+      <c r="Q6" s="39" t="str">
         <f>D6</f>
         <v>beef</v>
       </c>
-      <c r="R6" s="44"/>
-      <c r="S6" s="44"/>
-      <c r="T6" s="44"/>
-      <c r="U6" s="44"/>
-      <c r="V6" s="44"/>
-      <c r="W6" s="44"/>
-      <c r="X6" s="44"/>
-      <c r="Y6" s="44"/>
-      <c r="Z6" s="44"/>
+      <c r="R6" s="39"/>
+      <c r="S6" s="39"/>
+      <c r="T6" s="39"/>
+      <c r="U6" s="39"/>
+      <c r="V6" s="39"/>
+      <c r="W6" s="39"/>
+      <c r="X6" s="39"/>
+      <c r="Y6" s="39"/>
+      <c r="Z6" s="39"/>
     </row>
     <row r="7" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B7" s="43" t="s">
+      <c r="B7" s="38" t="s">
         <v>198</v>
       </c>
-      <c r="C7" s="44" t="s">
+      <c r="C7" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="44" t="s">
+      <c r="D7" s="39" t="s">
         <v>3</v>
       </c>
-      <c r="E7" s="44" t="s">
+      <c r="E7" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="44" t="s">
+      <c r="F7" s="39" t="s">
         <v>196</v>
       </c>
-      <c r="G7" s="44" t="s">
+      <c r="G7" s="39" t="s">
         <v>9</v>
       </c>
-      <c r="H7" s="44"/>
-      <c r="I7" s="44"/>
-      <c r="J7" s="44"/>
-      <c r="K7" s="44" t="s">
+      <c r="H7" s="39"/>
+      <c r="I7" s="39"/>
+      <c r="J7" s="39"/>
+      <c r="K7" s="39" t="s">
         <v>197</v>
       </c>
-      <c r="L7" s="44"/>
-      <c r="M7" s="44" t="s">
+      <c r="L7" s="39"/>
+      <c r="M7" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="O7" s="43" t="s">
+      <c r="O7" s="38" t="s">
         <v>198</v>
       </c>
-      <c r="P7" s="44" t="str">
+      <c r="P7" s="39" t="str">
         <f>C7</f>
         <v>cows</v>
       </c>
-      <c r="Q7" s="44" t="str">
+      <c r="Q7" s="39" t="str">
         <f>D7</f>
         <v>cows</v>
       </c>
-      <c r="R7" s="44" t="str">
+      <c r="R7" s="39" t="str">
         <f>E7</f>
         <v>heifers</v>
       </c>
-      <c r="S7" s="44" t="str">
+      <c r="S7" s="39" t="str">
         <f>F7</f>
         <v>bulls and steers</v>
       </c>
-      <c r="T7" s="44" t="str">
+      <c r="T7" s="39" t="str">
         <f>G7</f>
         <v>calves</v>
       </c>
-      <c r="U7" s="44"/>
-      <c r="V7" s="44"/>
-      <c r="W7" s="44"/>
-      <c r="X7" s="44" t="str">
+      <c r="U7" s="39"/>
+      <c r="V7" s="39"/>
+      <c r="W7" s="39"/>
+      <c r="X7" s="39" t="str">
         <f>K7</f>
         <v>pigs for meat</v>
       </c>
-      <c r="Y7" s="44"/>
-      <c r="Z7" s="44" t="str">
+      <c r="Y7" s="39"/>
+      <c r="Z7" s="39" t="str">
         <f>M7</f>
         <v>broilers</v>
       </c>
     </row>
     <row r="8" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B8" s="45" t="s">
+      <c r="B8" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="42">
+      <c r="C8" s="37">
         <f>C30</f>
         <v>25.033333333333331</v>
       </c>
-      <c r="D8" s="42">
+      <c r="D8" s="37">
         <f>D30</f>
         <v>55.633333333333333</v>
       </c>
-      <c r="E8" s="42">
+      <c r="E8" s="37">
         <f>E30</f>
         <v>51.70000000000001</v>
       </c>
-      <c r="F8" s="42">
+      <c r="F8" s="37">
         <f>F30</f>
         <v>22.133333333333336</v>
       </c>
-      <c r="G8" s="42">
+      <c r="G8" s="37">
         <f>G30</f>
         <v>34.366666666666667</v>
       </c>
-      <c r="H8" s="42">
+      <c r="H8" s="37">
         <f>K30</f>
         <v>50</v>
       </c>
-      <c r="I8" s="42">
+      <c r="I8" s="37">
         <f>I30</f>
         <v>50</v>
       </c>
-      <c r="J8" s="42">
-        <v>0</v>
-      </c>
-      <c r="K8" s="42">
-        <v>0</v>
-      </c>
-      <c r="L8" s="42">
-        <v>0</v>
-      </c>
-      <c r="M8" s="42">
-        <v>0</v>
-      </c>
-      <c r="O8" s="43" t="s">
+      <c r="J8" s="37">
+        <v>0</v>
+      </c>
+      <c r="K8" s="37">
+        <v>0</v>
+      </c>
+      <c r="L8" s="37">
+        <v>0</v>
+      </c>
+      <c r="M8" s="37">
+        <v>0</v>
+      </c>
+      <c r="O8" s="38" t="s">
         <v>173</v>
       </c>
-      <c r="P8" s="47" t="str">
+      <c r="P8" s="41" t="str">
         <f>P5&amp;P6&amp;P7</f>
         <v>cattledairycows</v>
       </c>
-      <c r="Q8" s="47" t="str">
+      <c r="Q8" s="41" t="str">
         <f t="shared" ref="Q8:R8" si="1">Q5&amp;Q6&amp;Q7</f>
         <v>cattlebeefcows</v>
       </c>
-      <c r="R8" s="47" t="str">
+      <c r="R8" s="41" t="str">
         <f t="shared" si="1"/>
         <v>cattleheifers</v>
       </c>
-      <c r="S8" s="47" t="str">
+      <c r="S8" s="41" t="str">
         <f>S5&amp;S6&amp;S7</f>
         <v>cattlebulls and steers</v>
       </c>
-      <c r="T8" s="47" t="str">
+      <c r="T8" s="41" t="str">
         <f>T5&amp;T6&amp;T7</f>
         <v>cattlecalves</v>
       </c>
-      <c r="U8" s="47" t="str">
+      <c r="U8" s="41" t="str">
         <f t="shared" ref="U8:X8" si="2">U5&amp;U6&amp;U7</f>
         <v>horses</v>
       </c>
-      <c r="V8" s="47" t="str">
+      <c r="V8" s="41" t="str">
         <f t="shared" si="2"/>
         <v>sheep</v>
       </c>
-      <c r="W8" s="47" t="str">
+      <c r="W8" s="41" t="str">
         <f t="shared" si="2"/>
         <v>pigs</v>
       </c>
-      <c r="X8" s="47" t="str">
+      <c r="X8" s="41" t="str">
         <f t="shared" si="2"/>
         <v>pigspigs for meat</v>
       </c>
-      <c r="Y8" s="47" t="str">
+      <c r="Y8" s="41" t="str">
         <f>Y5&amp;Y6&amp;Y7</f>
         <v>poultry</v>
       </c>
-      <c r="Z8" s="47" t="str">
+      <c r="Z8" s="41" t="str">
         <f>Z5&amp;Z6&amp;Z7</f>
         <v>poultrybroilers</v>
       </c>
     </row>
     <row r="9" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B9" s="44" t="s">
+      <c r="B9" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="C9" s="42">
+      <c r="C9" s="37">
         <f>C43</f>
         <v>62.766666666666673</v>
       </c>
-      <c r="D9" s="42">
+      <c r="D9" s="37">
         <f>D43</f>
         <v>9.8666666666666671</v>
       </c>
-      <c r="E9" s="42">
+      <c r="E9" s="37">
         <f>E43</f>
         <v>24.366666666666664</v>
       </c>
-      <c r="F9" s="42">
+      <c r="F9" s="37">
         <f>F43</f>
         <v>34.9</v>
       </c>
-      <c r="G9" s="42">
+      <c r="G9" s="37">
         <f>G43</f>
         <v>16.633333333333333</v>
       </c>
-      <c r="H9" s="42">
+      <c r="H9" s="37">
         <f>J43</f>
         <v>0</v>
       </c>
-      <c r="I9" s="42">
+      <c r="I9" s="37">
         <f>J43</f>
         <v>0</v>
       </c>
-      <c r="J9" s="42">
+      <c r="J9" s="37">
         <f>I43</f>
         <v>47.1</v>
       </c>
-      <c r="K9" s="42">
+      <c r="K9" s="37">
         <f>H43</f>
         <v>79.533333333333346</v>
       </c>
-      <c r="L9" s="42">
+      <c r="L9" s="37">
         <f>K43</f>
         <v>7.7</v>
       </c>
-      <c r="M9" s="42">
+      <c r="M9" s="37">
         <f>L43</f>
         <v>0</v>
       </c>
-      <c r="O9" s="44" t="s">
+      <c r="O9" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="P9" s="42">
+      <c r="P9" s="37">
         <f t="shared" ref="P9:Z13" si="3">C9/SUM(C$9:C$13)*100</f>
         <v>83.800623052959494</v>
       </c>
-      <c r="Q9" s="42">
+      <c r="Q9" s="37">
         <f t="shared" si="3"/>
         <v>22.222222222222225</v>
       </c>
-      <c r="R9" s="42">
+      <c r="R9" s="37">
         <f t="shared" si="3"/>
         <v>50.379048931771194</v>
       </c>
-      <c r="S9" s="42">
+      <c r="S9" s="37">
         <f t="shared" si="3"/>
         <v>44.83940042826552</v>
       </c>
-      <c r="T9" s="42">
+      <c r="T9" s="37">
         <f t="shared" si="3"/>
         <v>25.355691056910569</v>
       </c>
-      <c r="U9" s="42">
+      <c r="U9" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V9" s="42">
+      <c r="V9" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="W9" s="42">
+      <c r="W9" s="37">
         <f t="shared" si="3"/>
         <v>47.115705235078359</v>
       </c>
-      <c r="X9" s="42">
+      <c r="X9" s="37">
         <f t="shared" si="3"/>
         <v>79.533333333333317</v>
       </c>
-      <c r="Y9" s="42">
+      <c r="Y9" s="37">
         <f t="shared" si="3"/>
         <v>7.7000000000000011</v>
       </c>
-      <c r="Z9" s="42">
+      <c r="Z9" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="10" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B10" s="44" t="s">
+      <c r="B10" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="C10" s="42">
+      <c r="C10" s="37">
         <f>C56</f>
         <v>7</v>
       </c>
-      <c r="D10" s="42">
+      <c r="D10" s="37">
         <f>D56</f>
         <v>13.5</v>
       </c>
-      <c r="E10" s="42">
+      <c r="E10" s="37">
         <f>E56</f>
         <v>9.2333333333333343</v>
       </c>
-      <c r="F10" s="42">
+      <c r="F10" s="37">
         <f>F56</f>
         <v>15.5</v>
       </c>
-      <c r="G10" s="42">
+      <c r="G10" s="37">
         <f>G56</f>
         <v>13.333333333333334</v>
       </c>
-      <c r="H10" s="42">
+      <c r="H10" s="37">
         <f>M56</f>
         <v>33</v>
       </c>
-      <c r="I10" s="42">
+      <c r="I10" s="37">
         <f>J56</f>
         <v>50</v>
       </c>
-      <c r="J10" s="42">
+      <c r="J10" s="37">
         <f>I56</f>
         <v>27.866666666666664</v>
       </c>
-      <c r="K10" s="42">
+      <c r="K10" s="37">
         <f>H56</f>
         <v>2.6666666666666665</v>
       </c>
-      <c r="L10" s="42">
+      <c r="L10" s="37">
         <f>N56</f>
         <v>85.966666666666654</v>
       </c>
-      <c r="M10" s="42">
+      <c r="M10" s="37">
         <f>O56</f>
         <v>0</v>
       </c>
-      <c r="O10" s="44" t="s">
+      <c r="O10" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="P10" s="42">
+      <c r="P10" s="37">
         <f t="shared" si="3"/>
         <v>9.3457943925233611</v>
       </c>
-      <c r="Q10" s="42">
+      <c r="Q10" s="37">
         <f t="shared" si="3"/>
         <v>30.405405405405407</v>
       </c>
-      <c r="R10" s="42">
+      <c r="R10" s="37">
         <f t="shared" si="3"/>
         <v>19.090282563749142</v>
       </c>
-      <c r="S10" s="42">
+      <c r="S10" s="37">
         <f t="shared" si="3"/>
         <v>19.914346895074946</v>
       </c>
-      <c r="T10" s="42">
+      <c r="T10" s="37">
         <f t="shared" si="3"/>
         <v>20.325203252032519</v>
       </c>
-      <c r="U10" s="42">
+      <c r="U10" s="37">
         <f t="shared" si="3"/>
         <v>66</v>
       </c>
-      <c r="V10" s="42">
+      <c r="V10" s="37">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
-      <c r="W10" s="42">
+      <c r="W10" s="37">
         <f t="shared" si="3"/>
         <v>27.875958652884293</v>
       </c>
-      <c r="X10" s="42">
+      <c r="X10" s="37">
         <f t="shared" si="3"/>
         <v>2.6666666666666656</v>
       </c>
-      <c r="Y10" s="42">
+      <c r="Y10" s="37">
         <f t="shared" si="3"/>
         <v>85.966666666666669</v>
       </c>
-      <c r="Z10" s="42">
+      <c r="Z10" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="11" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B11" s="44" t="s">
+      <c r="B11" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="C11" s="42">
+      <c r="C11" s="37">
         <f>C69</f>
         <v>0.96666666666666667</v>
       </c>
-      <c r="D11" s="42">
+      <c r="D11" s="37">
         <f>D69</f>
         <v>19.900000000000002</v>
       </c>
-      <c r="E11" s="42">
+      <c r="E11" s="37">
         <f>E69</f>
         <v>12.833333333333334</v>
       </c>
-      <c r="F11" s="42">
+      <c r="F11" s="37">
         <f>F69</f>
         <v>24.533333333333331</v>
       </c>
-      <c r="G11" s="42">
+      <c r="G11" s="37">
         <f>G69</f>
         <v>33.833333333333336</v>
       </c>
-      <c r="H11" s="42">
+      <c r="H11" s="37">
         <f>K69</f>
         <v>2</v>
       </c>
-      <c r="I11" s="42">
+      <c r="I11" s="37">
         <f>J69</f>
         <v>0</v>
       </c>
-      <c r="J11" s="42">
+      <c r="J11" s="37">
         <f>I69</f>
         <v>15.200000000000001</v>
       </c>
-      <c r="K11" s="42">
+      <c r="K11" s="37">
         <f>H69</f>
         <v>1.1666666666666667</v>
       </c>
-      <c r="L11" s="42">
+      <c r="L11" s="37">
         <f>L69</f>
         <v>6.333333333333333</v>
       </c>
-      <c r="M11" s="42">
+      <c r="M11" s="37">
         <f>M69</f>
         <v>100</v>
       </c>
-      <c r="O11" s="44" t="s">
+      <c r="O11" s="39" t="s">
         <v>18</v>
       </c>
-      <c r="P11" s="42">
+      <c r="P11" s="37">
         <f t="shared" si="3"/>
         <v>1.2906097018246547</v>
       </c>
-      <c r="Q11" s="42">
+      <c r="Q11" s="37">
         <f t="shared" si="3"/>
         <v>44.819819819819827</v>
       </c>
-      <c r="R11" s="42">
+      <c r="R11" s="37">
         <f t="shared" si="3"/>
         <v>26.533425223983464</v>
       </c>
-      <c r="S11" s="42">
+      <c r="S11" s="37">
         <f t="shared" si="3"/>
         <v>31.520342612419693</v>
       </c>
-      <c r="T11" s="42">
+      <c r="T11" s="37">
         <f t="shared" si="3"/>
         <v>51.575203252032523</v>
       </c>
-      <c r="U11" s="42">
+      <c r="U11" s="37">
         <f t="shared" si="3"/>
         <v>4</v>
       </c>
-      <c r="V11" s="42">
+      <c r="V11" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="W11" s="42">
+      <c r="W11" s="37">
         <f t="shared" si="3"/>
         <v>15.205068356118707</v>
       </c>
-      <c r="X11" s="42">
+      <c r="X11" s="37">
         <f t="shared" si="3"/>
         <v>1.1666666666666663</v>
       </c>
-      <c r="Y11" s="42">
+      <c r="Y11" s="37">
         <f t="shared" si="3"/>
         <v>6.3333333333333339</v>
       </c>
-      <c r="Z11" s="42">
+      <c r="Z11" s="37">
         <f t="shared" si="3"/>
         <v>100</v>
       </c>
     </row>
     <row r="12" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B12" s="44" t="s">
+      <c r="B12" s="39" t="s">
         <v>174</v>
       </c>
-      <c r="C12" s="42">
+      <c r="C12" s="37">
         <f>C83+C97</f>
         <v>4.1666666666666661</v>
       </c>
-      <c r="D12" s="42">
+      <c r="D12" s="37">
         <f>D83+D97</f>
         <v>1.1333333333333333</v>
       </c>
-      <c r="E12" s="42">
+      <c r="E12" s="37">
         <f>E83+E97</f>
         <v>1.9333333333333336</v>
       </c>
-      <c r="F12" s="42">
+      <c r="F12" s="37">
         <f>F83+F97</f>
         <v>2.9000000000000004</v>
       </c>
-      <c r="G12" s="42">
+      <c r="G12" s="37">
         <f>G83+G97</f>
         <v>1.7999999999999998</v>
       </c>
-      <c r="H12" s="42">
-        <v>0</v>
-      </c>
-      <c r="I12" s="42">
-        <v>0</v>
-      </c>
-      <c r="J12" s="42">
+      <c r="H12" s="37">
+        <v>0</v>
+      </c>
+      <c r="I12" s="37">
+        <v>0</v>
+      </c>
+      <c r="J12" s="37">
         <f>J83+J97</f>
         <v>9.7999999999999989</v>
       </c>
-      <c r="K12" s="42">
+      <c r="K12" s="37">
         <f>I83+I97</f>
         <v>16.633333333333333</v>
       </c>
-      <c r="L12" s="42">
-        <v>0</v>
-      </c>
-      <c r="M12" s="42">
-        <v>0</v>
-      </c>
-      <c r="O12" s="44" t="s">
+      <c r="L12" s="37">
+        <v>0</v>
+      </c>
+      <c r="M12" s="37">
+        <v>0</v>
+      </c>
+      <c r="O12" s="39" t="s">
         <v>174</v>
       </c>
-      <c r="P12" s="42">
+      <c r="P12" s="37">
         <f t="shared" si="3"/>
         <v>5.562972852692476</v>
       </c>
-      <c r="Q12" s="42">
+      <c r="Q12" s="37">
         <f t="shared" si="3"/>
         <v>2.5525525525525525</v>
       </c>
-      <c r="R12" s="42">
+      <c r="R12" s="37">
         <f t="shared" si="3"/>
         <v>3.9972432804962108</v>
       </c>
-      <c r="S12" s="42">
+      <c r="S12" s="37">
         <f t="shared" si="3"/>
         <v>3.7259100642398284</v>
       </c>
-      <c r="T12" s="42">
+      <c r="T12" s="37">
         <f t="shared" si="3"/>
         <v>2.7439024390243896</v>
       </c>
-      <c r="U12" s="42">
+      <c r="U12" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="V12" s="42">
+      <c r="V12" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="W12" s="42">
+      <c r="W12" s="37">
         <f t="shared" si="3"/>
         <v>9.8032677559186379</v>
       </c>
-      <c r="X12" s="42">
+      <c r="X12" s="37">
         <f t="shared" si="3"/>
         <v>16.633333333333329</v>
       </c>
-      <c r="Y12" s="42">
+      <c r="Y12" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z12" s="42">
+      <c r="Z12" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B13" s="44" t="s">
+      <c r="B13" s="39" t="s">
         <v>166</v>
       </c>
-      <c r="C13" s="42">
-        <v>0</v>
-      </c>
-      <c r="D13" s="42">
-        <v>0</v>
-      </c>
-      <c r="E13" s="42">
-        <v>0</v>
-      </c>
-      <c r="F13" s="42">
-        <v>0</v>
-      </c>
-      <c r="G13" s="42">
-        <v>0</v>
-      </c>
-      <c r="H13" s="42">
+      <c r="C13" s="37">
+        <v>0</v>
+      </c>
+      <c r="D13" s="37">
+        <v>0</v>
+      </c>
+      <c r="E13" s="37">
+        <v>0</v>
+      </c>
+      <c r="F13" s="37">
+        <v>0</v>
+      </c>
+      <c r="G13" s="37">
+        <v>0</v>
+      </c>
+      <c r="H13" s="37">
         <f>L83</f>
         <v>15</v>
       </c>
-      <c r="I13" s="42">
-        <v>0</v>
-      </c>
-      <c r="J13" s="42">
-        <v>0</v>
-      </c>
-      <c r="K13" s="42">
-        <v>0</v>
-      </c>
-      <c r="L13" s="42">
-        <v>0</v>
-      </c>
-      <c r="M13" s="42">
-        <v>0</v>
-      </c>
-      <c r="O13" s="44" t="s">
+      <c r="I13" s="37">
+        <v>0</v>
+      </c>
+      <c r="J13" s="37">
+        <v>0</v>
+      </c>
+      <c r="K13" s="37">
+        <v>0</v>
+      </c>
+      <c r="L13" s="37">
+        <v>0</v>
+      </c>
+      <c r="M13" s="37">
+        <v>0</v>
+      </c>
+      <c r="O13" s="39" t="s">
         <v>166</v>
       </c>
-      <c r="P13" s="42">
+      <c r="P13" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Q13" s="42">
+      <c r="Q13" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="R13" s="42">
+      <c r="R13" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="S13" s="42">
+      <c r="S13" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T13" s="42">
+      <c r="T13" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U13" s="42">
+      <c r="U13" s="37">
         <f t="shared" si="3"/>
         <v>30</v>
       </c>
-      <c r="V13" s="42">
+      <c r="V13" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="W13" s="42">
+      <c r="W13" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="X13" s="42">
+      <c r="X13" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Y13" s="42">
+      <c r="Y13" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="Z13" s="42">
+      <c r="Z13" s="37">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B14" s="43" t="s">
+      <c r="B14" s="38" t="s">
         <v>167</v>
       </c>
-      <c r="C14" s="46">
+      <c r="C14" s="40">
         <f>SUM(C8:C13)</f>
         <v>99.933333333333351</v>
       </c>
-      <c r="D14" s="46">
+      <c r="D14" s="40">
         <f t="shared" ref="D14:E14" si="4">SUM(D8:D13)</f>
         <v>100.03333333333335</v>
       </c>
-      <c r="E14" s="46">
+      <c r="E14" s="40">
         <f t="shared" si="4"/>
         <v>100.06666666666668</v>
       </c>
-      <c r="F14" s="46">
+      <c r="F14" s="40">
         <f>SUM(F8:F13)</f>
         <v>99.966666666666669</v>
       </c>
-      <c r="G14" s="46">
+      <c r="G14" s="40">
         <f t="shared" ref="G14" si="5">SUM(G8:G13)</f>
         <v>99.966666666666654</v>
       </c>
-      <c r="H14" s="46">
+      <c r="H14" s="40">
         <f t="shared" ref="H14" si="6">SUM(H8:H13)</f>
         <v>100</v>
       </c>
-      <c r="I14" s="46">
+      <c r="I14" s="40">
         <f t="shared" ref="I14" si="7">SUM(I8:I13)</f>
         <v>100</v>
       </c>
-      <c r="J14" s="46">
+      <c r="J14" s="40">
         <f t="shared" ref="J14" si="8">SUM(J8:J13)</f>
         <v>99.966666666666669</v>
       </c>
-      <c r="K14" s="46">
+      <c r="K14" s="40">
         <f t="shared" ref="K14" si="9">SUM(K8:K13)</f>
         <v>100.00000000000003</v>
       </c>
-      <c r="L14" s="46">
+      <c r="L14" s="40">
         <f t="shared" ref="L14" si="10">SUM(L8:L13)</f>
         <v>99.999999999999986</v>
       </c>
-      <c r="M14" s="46">
+      <c r="M14" s="40">
         <f t="shared" ref="M14" si="11">SUM(M8:M13)</f>
         <v>100</v>
       </c>
-      <c r="O14" s="43" t="s">
+      <c r="O14" s="38" t="s">
         <v>167</v>
       </c>
-      <c r="P14" s="46">
+      <c r="P14" s="40">
         <f>SUM(P9:P13)</f>
         <v>99.999999999999986</v>
       </c>
-      <c r="Q14" s="46">
+      <c r="Q14" s="40">
         <f t="shared" ref="Q14:R14" si="12">SUM(Q9:Q13)</f>
         <v>100.00000000000001</v>
       </c>
-      <c r="R14" s="46">
+      <c r="R14" s="40">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="S14" s="46">
+      <c r="S14" s="40">
         <f>SUM(S9:S13)</f>
         <v>99.999999999999986</v>
       </c>
-      <c r="T14" s="46">
+      <c r="T14" s="40">
         <f>SUM(T9:T13)</f>
         <v>100</v>
       </c>
-      <c r="U14" s="46">
+      <c r="U14" s="40">
         <f t="shared" ref="U14:X14" si="13">SUM(U9:U13)</f>
         <v>100</v>
       </c>
-      <c r="V14" s="46">
+      <c r="V14" s="40">
         <f t="shared" si="13"/>
         <v>100</v>
       </c>
-      <c r="W14" s="46">
+      <c r="W14" s="40">
         <f t="shared" si="13"/>
         <v>100</v>
       </c>
-      <c r="X14" s="46">
+      <c r="X14" s="40">
         <f t="shared" si="13"/>
         <v>99.999999999999986</v>
       </c>
-      <c r="Y14" s="46">
+      <c r="Y14" s="40">
         <f>SUM(Y9:Y13)</f>
         <v>100</v>
       </c>
-      <c r="Z14" s="46">
+      <c r="Z14" s="40">
         <f>SUM(Z9:Z13)</f>
         <v>100</v>
       </c>
     </row>
     <row r="15" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B15" s="52" t="s">
+      <c r="B15" s="43" t="s">
         <v>155</v>
       </c>
-      <c r="C15" s="46"/>
-      <c r="D15" s="46"/>
-      <c r="E15" s="46"/>
-      <c r="F15" s="46"/>
-      <c r="G15" s="46"/>
-      <c r="H15" s="46"/>
-      <c r="I15" s="46"/>
-      <c r="J15" s="46"/>
-      <c r="K15" s="46"/>
-      <c r="L15" s="46"/>
-      <c r="M15" s="46"/>
-      <c r="O15" s="52" t="s">
+      <c r="C15" s="40"/>
+      <c r="D15" s="40"/>
+      <c r="E15" s="40"/>
+      <c r="F15" s="40"/>
+      <c r="G15" s="40"/>
+      <c r="H15" s="40"/>
+      <c r="I15" s="40"/>
+      <c r="J15" s="40"/>
+      <c r="K15" s="40"/>
+      <c r="L15" s="40"/>
+      <c r="M15" s="40"/>
+      <c r="O15" s="43" t="s">
         <v>155</v>
       </c>
-      <c r="P15" s="46"/>
-      <c r="Q15" s="46"/>
-      <c r="R15" s="46"/>
-      <c r="S15" s="46"/>
-      <c r="T15" s="46"/>
-      <c r="U15" s="46"/>
-      <c r="V15" s="46"/>
-      <c r="W15" s="46"/>
-      <c r="X15" s="46"/>
-      <c r="Y15" s="46"/>
-      <c r="Z15" s="46"/>
+      <c r="P15" s="40"/>
+      <c r="Q15" s="40"/>
+      <c r="R15" s="40"/>
+      <c r="S15" s="40"/>
+      <c r="T15" s="40"/>
+      <c r="U15" s="40"/>
+      <c r="V15" s="40"/>
+      <c r="W15" s="40"/>
+      <c r="X15" s="40"/>
+      <c r="Y15" s="40"/>
+      <c r="Z15" s="40"/>
     </row>
     <row r="16" spans="2:26" x14ac:dyDescent="0.25">
-      <c r="B16" s="45" t="s">
+      <c r="B16" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="42">
+      <c r="C16" s="37">
         <f>C97/(C83+C97)*100</f>
         <v>65.600000000000009</v>
       </c>
-      <c r="D16" s="42">
+      <c r="D16" s="37">
         <f>D97/(D83+D97)*100</f>
         <v>64.705882352941174</v>
       </c>
-      <c r="E16" s="42">
+      <c r="E16" s="37">
         <f>E97/(E83+E97)*100</f>
         <v>65.517241379310349</v>
       </c>
-      <c r="F16" s="42">
+      <c r="F16" s="37">
         <f>F97/(F83+F97)*100</f>
         <v>65.517241379310349</v>
       </c>
-      <c r="G16" s="42">
+      <c r="G16" s="37">
         <f>G97/(G83+G97)*100</f>
         <v>66.666666666666671</v>
       </c>
-      <c r="H16" s="42">
-        <v>0</v>
-      </c>
-      <c r="I16" s="42">
-        <v>0</v>
-      </c>
-      <c r="J16" s="42">
+      <c r="H16" s="37">
+        <v>0</v>
+      </c>
+      <c r="I16" s="37">
+        <v>0</v>
+      </c>
+      <c r="J16" s="37">
         <f>J97/(J83+J97)*100</f>
         <v>65.986394557823118</v>
       </c>
-      <c r="K16" s="42">
+      <c r="K16" s="37">
         <f>I97/(I83+I97)*100</f>
         <v>65.93186372745491</v>
       </c>
-      <c r="L16" s="42">
-        <v>0</v>
-      </c>
-      <c r="M16" s="42">
-        <v>0</v>
-      </c>
-      <c r="O16" s="45" t="s">
+      <c r="L16" s="37">
+        <v>0</v>
+      </c>
+      <c r="M16" s="37">
+        <v>0</v>
+      </c>
+      <c r="O16" s="39" t="s">
         <v>15</v>
       </c>
-      <c r="P16" s="51">
+      <c r="P16" s="37">
         <f t="shared" ref="P16:Z16" si="14">C16</f>
         <v>65.600000000000009</v>
       </c>
-      <c r="Q16" s="51">
+      <c r="Q16" s="37">
         <f t="shared" si="14"/>
         <v>64.705882352941174</v>
       </c>
-      <c r="R16" s="51">
+      <c r="R16" s="37">
         <f t="shared" si="14"/>
         <v>65.517241379310349</v>
       </c>
-      <c r="S16" s="51">
+      <c r="S16" s="37">
         <f t="shared" si="14"/>
         <v>65.517241379310349</v>
       </c>
-      <c r="T16" s="51">
+      <c r="T16" s="37">
         <f t="shared" si="14"/>
         <v>66.666666666666671</v>
       </c>
-      <c r="U16" s="51">
+      <c r="U16" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="V16" s="51">
+      <c r="V16" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="W16" s="51">
+      <c r="W16" s="37">
         <f>J16</f>
         <v>65.986394557823118</v>
       </c>
-      <c r="X16" s="51">
+      <c r="X16" s="37">
         <f t="shared" si="14"/>
         <v>65.93186372745491</v>
       </c>
-      <c r="Y16" s="51">
+      <c r="Y16" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
-      <c r="Z16" s="51">
+      <c r="Z16" s="37">
         <f t="shared" si="14"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B19" s="55" t="s">
+      <c r="B19" s="52" t="s">
         <v>142</v>
       </c>
-      <c r="C19" s="55"/>
-      <c r="D19" s="55"/>
-      <c r="E19" s="55"/>
-      <c r="F19" s="55"/>
-      <c r="G19" s="55"/>
-      <c r="H19" s="55"/>
-      <c r="I19" s="55"/>
-      <c r="J19" s="55"/>
-      <c r="K19" s="55"/>
-      <c r="L19" s="55"/>
-      <c r="M19" s="55"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="52"/>
+      <c r="G19" s="52"/>
+      <c r="H19" s="52"/>
+      <c r="I19" s="52"/>
+      <c r="J19" s="52"/>
+      <c r="K19" s="52"/>
+      <c r="L19" s="52"/>
+      <c r="M19" s="52"/>
     </row>
     <row r="20" spans="2:13" ht="33" x14ac:dyDescent="0.25">
-      <c r="B20" s="25" t="s">
+      <c r="B20" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="C20" s="26" t="s">
+      <c r="C20" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="D20" s="26" t="s">
+      <c r="D20" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="E20" s="26" t="s">
+      <c r="E20" s="22" t="s">
         <v>134</v>
       </c>
-      <c r="F20" s="26" t="s">
+      <c r="F20" s="22" t="s">
         <v>135</v>
       </c>
-      <c r="G20" s="26" t="s">
+      <c r="G20" s="22" t="s">
         <v>136</v>
       </c>
-      <c r="H20" s="26" t="s">
+      <c r="H20" s="22" t="s">
         <v>143</v>
       </c>
-      <c r="I20" s="26" t="s">
+      <c r="I20" s="22" t="s">
         <v>144</v>
       </c>
-      <c r="J20" s="26" t="s">
+      <c r="J20" s="22" t="s">
         <v>145</v>
       </c>
-      <c r="K20" s="26" t="s">
+      <c r="K20" s="22" t="s">
         <v>146</v>
       </c>
-      <c r="L20" s="26" t="s">
+      <c r="L20" s="22" t="s">
         <v>147</v>
       </c>
-      <c r="M20" s="21"/>
+      <c r="M20" s="17"/>
     </row>
     <row r="21" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B21" s="27">
+      <c r="B21" s="23">
         <v>1990</v>
       </c>
-      <c r="C21" s="23">
+      <c r="C21" s="19">
         <v>24.8</v>
       </c>
-      <c r="D21" s="23">
+      <c r="D21" s="19">
         <v>48.3</v>
       </c>
-      <c r="E21" s="23">
+      <c r="E21" s="19">
         <v>45.8</v>
       </c>
-      <c r="F21" s="23">
+      <c r="F21" s="19">
         <v>36.700000000000003</v>
       </c>
-      <c r="G21" s="23">
+      <c r="G21" s="19">
         <v>35</v>
       </c>
-      <c r="H21" s="28" t="s">
+      <c r="H21" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="I21" s="29">
+      <c r="I21" s="25">
         <v>50</v>
       </c>
-      <c r="J21" s="29">
+      <c r="J21" s="25">
         <v>100</v>
       </c>
-      <c r="K21" s="29">
+      <c r="K21" s="25">
         <v>50</v>
       </c>
-      <c r="L21" s="28" t="s">
+      <c r="L21" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="M21" s="24"/>
+      <c r="M21" s="20"/>
     </row>
     <row r="22" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B22" s="27">
+      <c r="B22" s="23">
         <v>1995</v>
       </c>
-      <c r="C22" s="23">
+      <c r="C22" s="19">
         <v>24.8</v>
       </c>
-      <c r="D22" s="23">
+      <c r="D22" s="19">
         <v>48.3</v>
       </c>
-      <c r="E22" s="23">
+      <c r="E22" s="19">
         <v>45.8</v>
       </c>
-      <c r="F22" s="23">
+      <c r="F22" s="19">
         <v>36.700000000000003</v>
       </c>
-      <c r="G22" s="23">
+      <c r="G22" s="19">
         <v>35</v>
       </c>
-      <c r="H22" s="28" t="s">
+      <c r="H22" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="I22" s="29">
+      <c r="I22" s="25">
         <v>50</v>
       </c>
-      <c r="J22" s="29">
+      <c r="J22" s="25">
         <v>100</v>
       </c>
-      <c r="K22" s="29">
+      <c r="K22" s="25">
         <v>50</v>
       </c>
-      <c r="L22" s="28" t="s">
+      <c r="L22" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="M22" s="24"/>
+      <c r="M22" s="20"/>
     </row>
     <row r="23" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B23" s="27">
+      <c r="B23" s="23">
         <v>2000</v>
       </c>
-      <c r="C23" s="23">
+      <c r="C23" s="19">
         <v>24.8</v>
       </c>
-      <c r="D23" s="23">
+      <c r="D23" s="19">
         <v>51.7</v>
       </c>
-      <c r="E23" s="23">
+      <c r="E23" s="19">
         <v>49.2</v>
       </c>
-      <c r="F23" s="23">
+      <c r="F23" s="19">
         <v>36.700000000000003</v>
       </c>
-      <c r="G23" s="23">
+      <c r="G23" s="19">
         <v>36.700000000000003</v>
       </c>
-      <c r="H23" s="28" t="s">
+      <c r="H23" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="I23" s="29">
+      <c r="I23" s="25">
         <v>50</v>
       </c>
-      <c r="J23" s="29">
+      <c r="J23" s="25">
         <v>100</v>
       </c>
-      <c r="K23" s="29">
+      <c r="K23" s="25">
         <v>50</v>
       </c>
-      <c r="L23" s="28" t="s">
+      <c r="L23" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="M23" s="24"/>
+      <c r="M23" s="20"/>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B24" s="27">
+      <c r="B24" s="23">
         <v>2005</v>
       </c>
-      <c r="C24" s="23">
+      <c r="C24" s="19">
         <v>26.1</v>
       </c>
-      <c r="D24" s="23">
+      <c r="D24" s="19">
         <v>58.9</v>
       </c>
-      <c r="E24" s="23">
+      <c r="E24" s="19">
         <v>53.7</v>
       </c>
-      <c r="F24" s="23">
+      <c r="F24" s="19">
         <v>30.2</v>
       </c>
-      <c r="G24" s="23">
+      <c r="G24" s="19">
         <v>36.6</v>
       </c>
-      <c r="H24" s="28" t="s">
+      <c r="H24" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="I24" s="29">
+      <c r="I24" s="25">
         <v>50</v>
       </c>
-      <c r="J24" s="29">
+      <c r="J24" s="25">
         <v>100</v>
       </c>
-      <c r="K24" s="29">
+      <c r="K24" s="25">
         <v>50</v>
       </c>
-      <c r="L24" s="28" t="s">
+      <c r="L24" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="M24" s="24"/>
+      <c r="M24" s="20"/>
     </row>
     <row r="25" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B25" s="27">
+      <c r="B25" s="23">
         <v>2010</v>
       </c>
-      <c r="C25" s="23">
+      <c r="C25" s="19">
         <v>25</v>
       </c>
-      <c r="D25" s="23">
+      <c r="D25" s="19">
         <v>54.1</v>
       </c>
-      <c r="E25" s="23">
+      <c r="E25" s="19">
         <v>51.7</v>
       </c>
-      <c r="F25" s="23">
+      <c r="F25" s="19">
         <v>26.4</v>
       </c>
-      <c r="G25" s="23">
+      <c r="G25" s="19">
         <v>31.4</v>
       </c>
-      <c r="H25" s="28" t="s">
+      <c r="H25" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="I25" s="29">
+      <c r="I25" s="25">
         <v>50</v>
       </c>
-      <c r="J25" s="29">
+      <c r="J25" s="25">
         <v>100</v>
       </c>
-      <c r="K25" s="29">
+      <c r="K25" s="25">
         <v>50</v>
       </c>
-      <c r="L25" s="28" t="s">
+      <c r="L25" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="M25" s="24"/>
+      <c r="M25" s="20"/>
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B26" s="27">
+      <c r="B26" s="23">
         <v>2015</v>
       </c>
-      <c r="C26" s="23">
+      <c r="C26" s="19">
         <v>24.5</v>
       </c>
-      <c r="D26" s="23">
+      <c r="D26" s="19">
         <v>52.1</v>
       </c>
-      <c r="E26" s="23">
+      <c r="E26" s="19">
         <v>49.7</v>
       </c>
-      <c r="F26" s="23">
+      <c r="F26" s="19">
         <v>18.600000000000001</v>
       </c>
-      <c r="G26" s="23">
+      <c r="G26" s="19">
         <v>31.7</v>
       </c>
-      <c r="H26" s="28" t="s">
+      <c r="H26" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="I26" s="29">
+      <c r="I26" s="25">
         <v>50</v>
       </c>
-      <c r="J26" s="29">
+      <c r="J26" s="25">
         <v>100</v>
       </c>
-      <c r="K26" s="29">
+      <c r="K26" s="25">
         <v>50</v>
       </c>
-      <c r="L26" s="28" t="s">
+      <c r="L26" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="M26" s="24"/>
+      <c r="M26" s="20"/>
     </row>
     <row r="27" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B27" s="27">
+      <c r="B27" s="23">
         <v>2019</v>
       </c>
-      <c r="C27" s="23">
+      <c r="C27" s="19">
         <v>25.3</v>
       </c>
-      <c r="D27" s="23">
+      <c r="D27" s="19">
         <v>57.4</v>
       </c>
-      <c r="E27" s="23">
+      <c r="E27" s="19">
         <v>52.7</v>
       </c>
-      <c r="F27" s="23">
+      <c r="F27" s="19">
         <v>23.9</v>
       </c>
-      <c r="G27" s="23">
+      <c r="G27" s="19">
         <v>35.700000000000003</v>
       </c>
-      <c r="H27" s="28" t="s">
+      <c r="H27" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="I27" s="29">
+      <c r="I27" s="25">
         <v>50</v>
       </c>
-      <c r="J27" s="29">
+      <c r="J27" s="25">
         <v>100</v>
       </c>
-      <c r="K27" s="29">
+      <c r="K27" s="25">
         <v>50</v>
       </c>
-      <c r="L27" s="28" t="s">
+      <c r="L27" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="M27" s="24"/>
+      <c r="M27" s="20"/>
     </row>
     <row r="28" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B28" s="27">
+      <c r="B28" s="23">
         <v>2020</v>
       </c>
-      <c r="C28" s="23">
+      <c r="C28" s="19">
         <v>25.3</v>
       </c>
-      <c r="D28" s="23">
+      <c r="D28" s="19">
         <v>57.4</v>
       </c>
-      <c r="E28" s="23">
+      <c r="E28" s="19">
         <v>52.7</v>
       </c>
-      <c r="F28" s="23">
+      <c r="F28" s="19">
         <v>23.9</v>
       </c>
-      <c r="G28" s="23">
+      <c r="G28" s="19">
         <v>35.700000000000003</v>
       </c>
-      <c r="H28" s="28" t="s">
+      <c r="H28" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="I28" s="29">
+      <c r="I28" s="25">
         <v>50</v>
       </c>
-      <c r="J28" s="29">
+      <c r="J28" s="25">
         <v>100</v>
       </c>
-      <c r="K28" s="29">
+      <c r="K28" s="25">
         <v>50</v>
       </c>
-      <c r="L28" s="28" t="s">
+      <c r="L28" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="M28" s="24"/>
+      <c r="M28" s="20"/>
     </row>
     <row r="29" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B29" s="27">
+      <c r="B29" s="23">
         <v>2021</v>
       </c>
-      <c r="C29" s="23">
+      <c r="C29" s="19">
         <v>25.3</v>
       </c>
-      <c r="D29" s="23">
+      <c r="D29" s="19">
         <v>57.4</v>
       </c>
-      <c r="E29" s="23">
+      <c r="E29" s="19">
         <v>52.7</v>
       </c>
-      <c r="F29" s="23">
+      <c r="F29" s="19">
         <v>23.9</v>
       </c>
-      <c r="G29" s="23">
+      <c r="G29" s="19">
         <v>35.700000000000003</v>
       </c>
-      <c r="H29" s="28" t="s">
+      <c r="H29" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="I29" s="29">
+      <c r="I29" s="25">
         <v>50</v>
       </c>
-      <c r="J29" s="29">
+      <c r="J29" s="25">
         <v>100</v>
       </c>
-      <c r="K29" s="29">
+      <c r="K29" s="25">
         <v>50</v>
       </c>
-      <c r="L29" s="28" t="s">
+      <c r="L29" s="24" t="s">
         <v>148</v>
       </c>
-      <c r="M29" s="24"/>
+      <c r="M29" s="20"/>
     </row>
     <row r="30" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B30" s="39" t="s">
+      <c r="B30" s="35" t="s">
         <v>163</v>
       </c>
-      <c r="C30" s="40">
+      <c r="C30" s="36">
         <f>AVERAGE(C26:C28)</f>
         <v>25.033333333333331</v>
       </c>
-      <c r="D30" s="40">
+      <c r="D30" s="36">
         <f t="shared" ref="D30:K30" si="15">AVERAGE(D26:D28)</f>
         <v>55.633333333333333</v>
       </c>
-      <c r="E30" s="40">
+      <c r="E30" s="36">
         <f t="shared" si="15"/>
         <v>51.70000000000001</v>
       </c>
-      <c r="F30" s="40">
+      <c r="F30" s="36">
         <f t="shared" si="15"/>
         <v>22.133333333333336</v>
       </c>
-      <c r="G30" s="40">
+      <c r="G30" s="36">
         <f t="shared" si="15"/>
         <v>34.366666666666667</v>
       </c>
-      <c r="H30" s="40"/>
-      <c r="I30" s="40">
+      <c r="H30" s="36"/>
+      <c r="I30" s="36">
         <f t="shared" si="15"/>
         <v>50</v>
       </c>
-      <c r="J30" s="40">
+      <c r="J30" s="36">
         <f t="shared" si="15"/>
         <v>100</v>
       </c>
-      <c r="K30" s="40">
+      <c r="K30" s="36">
         <f t="shared" si="15"/>
         <v>50</v>
       </c>
-      <c r="L30" s="40"/>
-      <c r="M30" s="24"/>
+      <c r="L30" s="36"/>
+      <c r="M30" s="20"/>
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B32" s="61" t="s">
+      <c r="B32" s="53" t="s">
         <v>130</v>
       </c>
-      <c r="C32" s="61"/>
-      <c r="D32" s="61"/>
-      <c r="E32" s="61"/>
-      <c r="F32" s="61"/>
-      <c r="G32" s="61"/>
-      <c r="H32" s="61"/>
-      <c r="I32" s="61"/>
-      <c r="J32" s="61"/>
-      <c r="K32" s="61"/>
-      <c r="L32" s="61"/>
-      <c r="M32" s="61"/>
+      <c r="C32" s="53"/>
+      <c r="D32" s="53"/>
+      <c r="E32" s="53"/>
+      <c r="F32" s="53"/>
+      <c r="G32" s="53"/>
+      <c r="H32" s="53"/>
+      <c r="I32" s="53"/>
+      <c r="J32" s="53"/>
+      <c r="K32" s="53"/>
+      <c r="L32" s="53"/>
+      <c r="M32" s="53"/>
     </row>
     <row r="33" spans="2:16" ht="65.25" x14ac:dyDescent="0.25">
-      <c r="B33" s="19" t="s">
+      <c r="B33" s="15" t="s">
         <v>131</v>
       </c>
-      <c r="C33" s="20" t="s">
+      <c r="C33" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="D33" s="20" t="s">
+      <c r="D33" s="16" t="s">
         <v>133</v>
       </c>
-      <c r="E33" s="20" t="s">
+      <c r="E33" s="16" t="s">
         <v>134</v>
       </c>
-      <c r="F33" s="20" t="s">
+      <c r="F33" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="G33" s="20" t="s">
+      <c r="G33" s="16" t="s">
         <v>136</v>
       </c>
-      <c r="H33" s="20" t="s">
+      <c r="H33" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="I33" s="20" t="s">
+      <c r="I33" s="16" t="s">
         <v>138</v>
       </c>
-      <c r="J33" s="20" t="s">
+      <c r="J33" s="16" t="s">
         <v>139</v>
       </c>
-      <c r="K33" s="20" t="s">
+      <c r="K33" s="16" t="s">
         <v>140</v>
       </c>
-      <c r="L33" s="20" t="s">
+      <c r="L33" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="M33" s="21"/>
+      <c r="M33" s="17"/>
     </row>
     <row r="34" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B34" s="22">
+      <c r="B34" s="18">
         <v>1990</v>
       </c>
-      <c r="C34" s="23">
+      <c r="C34" s="19">
         <v>22.6</v>
       </c>
-      <c r="D34" s="23">
+      <c r="D34" s="19">
         <v>15.5</v>
       </c>
-      <c r="E34" s="23">
+      <c r="E34" s="19">
         <v>16.3</v>
       </c>
-      <c r="F34" s="23">
+      <c r="F34" s="19">
         <v>19</v>
       </c>
-      <c r="G34" s="23">
+      <c r="G34" s="19">
         <v>19.5</v>
       </c>
-      <c r="H34" s="23">
+      <c r="H34" s="19">
         <v>44</v>
       </c>
-      <c r="I34" s="23">
+      <c r="I34" s="19">
         <v>44</v>
       </c>
-      <c r="J34" s="23">
-        <v>0</v>
-      </c>
-      <c r="K34" s="23">
+      <c r="J34" s="19">
+        <v>0</v>
+      </c>
+      <c r="K34" s="19">
         <v>25</v>
       </c>
-      <c r="L34" s="23">
-        <v>0</v>
-      </c>
-      <c r="M34" s="24"/>
+      <c r="L34" s="19">
+        <v>0</v>
+      </c>
+      <c r="M34" s="20"/>
     </row>
     <row r="35" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B35" s="22">
+      <c r="B35" s="18">
         <v>1995</v>
       </c>
-      <c r="C35" s="23">
+      <c r="C35" s="19">
         <v>30.6</v>
       </c>
-      <c r="D35" s="23">
+      <c r="D35" s="19">
         <v>21</v>
       </c>
-      <c r="E35" s="23">
+      <c r="E35" s="19">
         <v>22</v>
       </c>
-      <c r="F35" s="23">
+      <c r="F35" s="19">
         <v>25.8</v>
       </c>
-      <c r="G35" s="23">
+      <c r="G35" s="19">
         <v>26.5</v>
       </c>
-      <c r="H35" s="23">
+      <c r="H35" s="19">
         <v>63</v>
       </c>
-      <c r="I35" s="23">
+      <c r="I35" s="19">
         <v>63</v>
       </c>
-      <c r="J35" s="23">
-        <v>0</v>
-      </c>
-      <c r="K35" s="23">
+      <c r="J35" s="19">
+        <v>0</v>
+      </c>
+      <c r="K35" s="19">
         <v>25</v>
       </c>
-      <c r="L35" s="23">
-        <v>0</v>
-      </c>
-      <c r="M35" s="24"/>
+      <c r="L35" s="19">
+        <v>0</v>
+      </c>
+      <c r="M35" s="20"/>
     </row>
     <row r="36" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B36" s="22">
+      <c r="B36" s="18">
         <v>2000</v>
       </c>
-      <c r="C36" s="23">
+      <c r="C36" s="19">
         <v>39</v>
       </c>
-      <c r="D36" s="23">
+      <c r="D36" s="19">
         <v>12.5</v>
       </c>
-      <c r="E36" s="23">
+      <c r="E36" s="19">
         <v>13.2</v>
       </c>
-      <c r="F36" s="23">
+      <c r="F36" s="19">
         <v>16.399999999999999</v>
       </c>
-      <c r="G36" s="23">
+      <c r="G36" s="19">
         <v>16.399999999999999</v>
       </c>
-      <c r="H36" s="23">
+      <c r="H36" s="19">
         <v>80.5</v>
       </c>
-      <c r="I36" s="23">
+      <c r="I36" s="19">
         <v>25.8</v>
       </c>
-      <c r="J36" s="23">
-        <v>0</v>
-      </c>
-      <c r="K36" s="23">
+      <c r="J36" s="19">
+        <v>0</v>
+      </c>
+      <c r="K36" s="19">
         <v>25</v>
       </c>
-      <c r="L36" s="23">
-        <v>0</v>
-      </c>
-      <c r="M36" s="24"/>
+      <c r="L36" s="19">
+        <v>0</v>
+      </c>
+      <c r="M36" s="20"/>
     </row>
     <row r="37" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B37" s="22">
+      <c r="B37" s="18">
         <v>2005</v>
       </c>
-      <c r="C37" s="23">
+      <c r="C37" s="19">
         <v>50.8</v>
       </c>
-      <c r="D37" s="23">
+      <c r="D37" s="19">
         <v>5.9</v>
       </c>
-      <c r="E37" s="23">
+      <c r="E37" s="19">
         <v>19.600000000000001</v>
       </c>
-      <c r="F37" s="23">
+      <c r="F37" s="19">
         <v>22.5</v>
       </c>
-      <c r="G37" s="23">
+      <c r="G37" s="19">
         <v>18.899999999999999</v>
       </c>
-      <c r="H37" s="23">
+      <c r="H37" s="19">
         <v>91.3</v>
       </c>
-      <c r="I37" s="23">
+      <c r="I37" s="19">
         <v>31.8</v>
       </c>
-      <c r="J37" s="23">
-        <v>0</v>
-      </c>
-      <c r="K37" s="23">
+      <c r="J37" s="19">
+        <v>0</v>
+      </c>
+      <c r="K37" s="19">
         <v>20.8</v>
       </c>
-      <c r="L37" s="23">
-        <v>0</v>
-      </c>
-      <c r="M37" s="24"/>
+      <c r="L37" s="19">
+        <v>0</v>
+      </c>
+      <c r="M37" s="20"/>
     </row>
     <row r="38" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B38" s="22">
+      <c r="B38" s="18">
         <v>2010</v>
       </c>
-      <c r="C38" s="23">
+      <c r="C38" s="19">
         <v>57.1</v>
       </c>
-      <c r="D38" s="23">
+      <c r="D38" s="19">
         <v>11.2</v>
       </c>
-      <c r="E38" s="23">
+      <c r="E38" s="19">
         <v>22.3</v>
       </c>
-      <c r="F38" s="23">
+      <c r="F38" s="19">
         <v>28.6</v>
       </c>
-      <c r="G38" s="23">
+      <c r="G38" s="19">
         <v>16.8</v>
       </c>
-      <c r="H38" s="23">
+      <c r="H38" s="19">
         <v>91.3</v>
       </c>
-      <c r="I38" s="23">
+      <c r="I38" s="19">
         <v>60.4</v>
       </c>
-      <c r="J38" s="23">
-        <v>0</v>
-      </c>
-      <c r="K38" s="23">
+      <c r="J38" s="19">
+        <v>0</v>
+      </c>
+      <c r="K38" s="19">
         <v>12</v>
       </c>
-      <c r="L38" s="23">
-        <v>0</v>
-      </c>
-      <c r="M38" s="24"/>
+      <c r="L38" s="19">
+        <v>0</v>
+      </c>
+      <c r="M38" s="20"/>
     </row>
     <row r="39" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B39" s="22">
+      <c r="B39" s="18">
         <v>2015</v>
       </c>
-      <c r="C39" s="23">
+      <c r="C39" s="19">
         <v>60.4</v>
       </c>
-      <c r="D39" s="23">
+      <c r="D39" s="19">
         <v>10</v>
       </c>
-      <c r="E39" s="23">
+      <c r="E39" s="19">
         <v>24.9</v>
       </c>
-      <c r="F39" s="23">
+      <c r="F39" s="19">
         <v>31.4</v>
       </c>
-      <c r="G39" s="23">
+      <c r="G39" s="19">
         <v>16.100000000000001</v>
       </c>
-      <c r="H39" s="23">
+      <c r="H39" s="19">
         <v>81.400000000000006</v>
       </c>
-      <c r="I39" s="23">
+      <c r="I39" s="19">
         <v>49.7</v>
       </c>
-      <c r="J39" s="23">
-        <v>0</v>
-      </c>
-      <c r="K39" s="23">
+      <c r="J39" s="19">
+        <v>0</v>
+      </c>
+      <c r="K39" s="19">
         <v>9.3000000000000007</v>
       </c>
-      <c r="L39" s="23">
-        <v>0</v>
-      </c>
-      <c r="M39" s="24"/>
+      <c r="L39" s="19">
+        <v>0</v>
+      </c>
+      <c r="M39" s="20"/>
     </row>
     <row r="40" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B40" s="22">
+      <c r="B40" s="18">
         <v>2019</v>
       </c>
-      <c r="C40" s="23">
+      <c r="C40" s="19">
         <v>64.099999999999994</v>
       </c>
-      <c r="D40" s="23">
+      <c r="D40" s="19">
         <v>9.8000000000000007</v>
       </c>
-      <c r="E40" s="23">
+      <c r="E40" s="19">
         <v>24.2</v>
       </c>
-      <c r="F40" s="23">
+      <c r="F40" s="19">
         <v>36.700000000000003</v>
       </c>
-      <c r="G40" s="23">
+      <c r="G40" s="19">
         <v>16.899999999999999</v>
       </c>
-      <c r="H40" s="23">
+      <c r="H40" s="19">
         <v>78.900000000000006</v>
       </c>
-      <c r="I40" s="23">
+      <c r="I40" s="19">
         <v>46</v>
       </c>
-      <c r="J40" s="23">
-        <v>0</v>
-      </c>
-      <c r="K40" s="23">
+      <c r="J40" s="19">
+        <v>0</v>
+      </c>
+      <c r="K40" s="19">
         <v>6.9</v>
       </c>
-      <c r="L40" s="23">
-        <v>0</v>
-      </c>
-      <c r="M40" s="24"/>
+      <c r="L40" s="19">
+        <v>0</v>
+      </c>
+      <c r="M40" s="20"/>
     </row>
     <row r="41" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B41" s="22">
+      <c r="B41" s="18">
         <v>2020</v>
       </c>
-      <c r="C41" s="23">
+      <c r="C41" s="19">
         <v>63.8</v>
       </c>
-      <c r="D41" s="23">
+      <c r="D41" s="19">
         <v>9.8000000000000007</v>
       </c>
-      <c r="E41" s="23">
+      <c r="E41" s="19">
         <v>24</v>
       </c>
-      <c r="F41" s="23">
+      <c r="F41" s="19">
         <v>36.6</v>
       </c>
-      <c r="G41" s="23">
+      <c r="G41" s="19">
         <v>16.899999999999999</v>
       </c>
-      <c r="H41" s="23">
+      <c r="H41" s="19">
         <v>78.3</v>
       </c>
-      <c r="I41" s="23">
+      <c r="I41" s="19">
         <v>45.6</v>
       </c>
-      <c r="J41" s="23">
-        <v>0</v>
-      </c>
-      <c r="K41" s="23">
+      <c r="J41" s="19">
+        <v>0</v>
+      </c>
+      <c r="K41" s="19">
         <v>6.9</v>
       </c>
-      <c r="L41" s="23">
-        <v>0</v>
-      </c>
-      <c r="M41" s="24"/>
+      <c r="L41" s="19">
+        <v>0</v>
+      </c>
+      <c r="M41" s="20"/>
     </row>
     <row r="42" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B42" s="22">
+      <c r="B42" s="18">
         <v>2021</v>
       </c>
-      <c r="C42" s="23">
+      <c r="C42" s="19">
         <v>63.7</v>
       </c>
-      <c r="D42" s="23">
+      <c r="D42" s="19">
         <v>9.6999999999999993</v>
       </c>
-      <c r="E42" s="23">
+      <c r="E42" s="19">
         <v>24</v>
       </c>
-      <c r="F42" s="23">
+      <c r="F42" s="19">
         <v>36.5</v>
       </c>
-      <c r="G42" s="23">
+      <c r="G42" s="19">
         <v>16.8</v>
       </c>
-      <c r="H42" s="23">
+      <c r="H42" s="19">
         <v>77.8</v>
       </c>
-      <c r="I42" s="23">
+      <c r="I42" s="19">
         <v>45.4</v>
       </c>
-      <c r="J42" s="23">
-        <v>0</v>
-      </c>
-      <c r="K42" s="23">
+      <c r="J42" s="19">
+        <v>0</v>
+      </c>
+      <c r="K42" s="19">
         <v>6.9</v>
       </c>
-      <c r="L42" s="23">
-        <v>0</v>
-      </c>
-      <c r="M42" s="24"/>
+      <c r="L42" s="19">
+        <v>0</v>
+      </c>
+      <c r="M42" s="20"/>
     </row>
     <row r="43" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B43" s="39" t="s">
+      <c r="B43" s="35" t="s">
         <v>163</v>
       </c>
-      <c r="C43" s="40">
+      <c r="C43" s="36">
         <f>AVERAGE(C39:C41)</f>
         <v>62.766666666666673</v>
       </c>
-      <c r="D43" s="40">
+      <c r="D43" s="36">
         <f t="shared" ref="D43:L43" si="16">AVERAGE(D39:D41)</f>
         <v>9.8666666666666671</v>
       </c>
-      <c r="E43" s="40">
+      <c r="E43" s="36">
         <f t="shared" si="16"/>
         <v>24.366666666666664</v>
       </c>
-      <c r="F43" s="40">
+      <c r="F43" s="36">
         <f t="shared" si="16"/>
         <v>34.9</v>
       </c>
-      <c r="G43" s="40">
+      <c r="G43" s="36">
         <f t="shared" si="16"/>
         <v>16.633333333333333</v>
       </c>
-      <c r="H43" s="40">
+      <c r="H43" s="36">
         <f t="shared" si="16"/>
         <v>79.533333333333346</v>
       </c>
-      <c r="I43" s="40">
+      <c r="I43" s="36">
         <f t="shared" si="16"/>
         <v>47.1</v>
       </c>
-      <c r="J43" s="40">
+      <c r="J43" s="36">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="K43" s="40">
+      <c r="K43" s="36">
         <f t="shared" si="16"/>
         <v>7.7</v>
       </c>
-      <c r="L43" s="40">
+      <c r="L43" s="36">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="M43" s="24"/>
+      <c r="M43" s="20"/>
     </row>
     <row r="45" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B45" s="55" t="s">
+      <c r="B45" s="52" t="s">
         <v>157</v>
       </c>
-      <c r="C45" s="55"/>
-      <c r="D45" s="55"/>
-      <c r="E45" s="55"/>
-      <c r="F45" s="55"/>
-      <c r="G45" s="55"/>
-      <c r="H45" s="55"/>
-      <c r="I45" s="55"/>
-      <c r="J45" s="55"/>
-      <c r="K45" s="55"/>
-      <c r="L45" s="55"/>
-      <c r="M45" s="55"/>
-      <c r="N45" s="55"/>
-      <c r="O45" s="55"/>
-      <c r="P45" s="55"/>
+      <c r="C45" s="52"/>
+      <c r="D45" s="52"/>
+      <c r="E45" s="52"/>
+      <c r="F45" s="52"/>
+      <c r="G45" s="52"/>
+      <c r="H45" s="52"/>
+      <c r="I45" s="52"/>
+      <c r="J45" s="52"/>
+      <c r="K45" s="52"/>
+      <c r="L45" s="52"/>
+      <c r="M45" s="52"/>
+      <c r="N45" s="52"/>
+      <c r="O45" s="52"/>
+      <c r="P45" s="52"/>
     </row>
     <row r="46" spans="2:16" ht="44.25" x14ac:dyDescent="0.25">
-      <c r="B46" s="35" t="s">
+      <c r="B46" s="31" t="s">
         <v>131</v>
       </c>
-      <c r="C46" s="36" t="s">
+      <c r="C46" s="32" t="s">
         <v>132</v>
       </c>
-      <c r="D46" s="36" t="s">
+      <c r="D46" s="32" t="s">
         <v>133</v>
       </c>
-      <c r="E46" s="36" t="s">
+      <c r="E46" s="32" t="s">
         <v>134</v>
       </c>
-      <c r="F46" s="36" t="s">
+      <c r="F46" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="G46" s="36" t="s">
+      <c r="G46" s="32" t="s">
         <v>136</v>
       </c>
-      <c r="H46" s="36" t="s">
+      <c r="H46" s="32" t="s">
         <v>137</v>
       </c>
-      <c r="I46" s="36" t="s">
+      <c r="I46" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="J46" s="36" t="s">
+      <c r="J46" s="32" t="s">
         <v>158</v>
       </c>
-      <c r="K46" s="36" t="s">
+      <c r="K46" s="32" t="s">
         <v>145</v>
       </c>
-      <c r="L46" s="36" t="s">
+      <c r="L46" s="32" t="s">
         <v>159</v>
       </c>
-      <c r="M46" s="36" t="s">
+      <c r="M46" s="32" t="s">
         <v>146</v>
       </c>
-      <c r="N46" s="36" t="s">
+      <c r="N46" s="32" t="s">
         <v>140</v>
       </c>
-      <c r="O46" s="36" t="s">
+      <c r="O46" s="32" t="s">
         <v>160</v>
       </c>
-      <c r="P46" s="21"/>
+      <c r="P46" s="17"/>
     </row>
     <row r="47" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B47" s="22">
+      <c r="B47" s="18">
         <v>1990</v>
       </c>
-      <c r="C47" s="23">
+      <c r="C47" s="19">
         <v>51.9</v>
       </c>
-      <c r="D47" s="23">
+      <c r="D47" s="19">
         <v>28.9</v>
       </c>
-      <c r="E47" s="23">
+      <c r="E47" s="19">
         <v>30.3</v>
       </c>
-      <c r="F47" s="23">
+      <c r="F47" s="19">
         <v>35.5</v>
       </c>
-      <c r="G47" s="23">
+      <c r="G47" s="19">
         <v>36.4</v>
       </c>
-      <c r="H47" s="23">
+      <c r="H47" s="19">
         <v>54</v>
       </c>
-      <c r="I47" s="23">
+      <c r="I47" s="19">
         <v>45</v>
       </c>
-      <c r="J47" s="23">
+      <c r="J47" s="19">
         <v>50</v>
       </c>
-      <c r="K47" s="23">
-        <v>0</v>
-      </c>
-      <c r="L47" s="37">
+      <c r="K47" s="19">
+        <v>0</v>
+      </c>
+      <c r="L47" s="33">
         <v>100</v>
       </c>
-      <c r="M47" s="23">
+      <c r="M47" s="19">
         <v>33</v>
       </c>
-      <c r="N47" s="23">
+      <c r="N47" s="19">
         <v>55</v>
       </c>
-      <c r="O47" s="23">
-        <v>0</v>
-      </c>
-      <c r="P47" s="24"/>
+      <c r="O47" s="19">
+        <v>0</v>
+      </c>
+      <c r="P47" s="20"/>
     </row>
     <row r="48" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B48" s="22">
+      <c r="B48" s="18">
         <v>1995</v>
       </c>
-      <c r="C48" s="23">
+      <c r="C48" s="19">
         <v>43.8</v>
       </c>
-      <c r="D48" s="23">
+      <c r="D48" s="19">
         <v>23.4</v>
       </c>
-      <c r="E48" s="23">
+      <c r="E48" s="19">
         <v>24.5</v>
       </c>
-      <c r="F48" s="23">
+      <c r="F48" s="19">
         <v>28.7</v>
       </c>
-      <c r="G48" s="23">
+      <c r="G48" s="19">
         <v>29.4</v>
       </c>
-      <c r="H48" s="23">
+      <c r="H48" s="19">
         <v>35</v>
       </c>
-      <c r="I48" s="23">
+      <c r="I48" s="19">
         <v>26</v>
       </c>
-      <c r="J48" s="23">
+      <c r="J48" s="19">
         <v>50</v>
       </c>
-      <c r="K48" s="23">
-        <v>0</v>
-      </c>
-      <c r="L48" s="37">
+      <c r="K48" s="19">
+        <v>0</v>
+      </c>
+      <c r="L48" s="33">
         <v>100</v>
       </c>
-      <c r="M48" s="23">
+      <c r="M48" s="19">
         <v>33</v>
       </c>
-      <c r="N48" s="23">
+      <c r="N48" s="19">
         <v>55</v>
       </c>
-      <c r="O48" s="23">
-        <v>0</v>
-      </c>
-      <c r="P48" s="24"/>
+      <c r="O48" s="19">
+        <v>0</v>
+      </c>
+      <c r="P48" s="20"/>
     </row>
     <row r="49" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B49" s="22">
+      <c r="B49" s="18">
         <v>2000</v>
       </c>
-      <c r="C49" s="23">
+      <c r="C49" s="19">
         <v>35.299999999999997</v>
       </c>
-      <c r="D49" s="23">
+      <c r="D49" s="19">
         <v>28</v>
       </c>
-      <c r="E49" s="23">
+      <c r="E49" s="19">
         <v>29.5</v>
       </c>
-      <c r="F49" s="23">
+      <c r="F49" s="19">
         <v>36.700000000000003</v>
       </c>
-      <c r="G49" s="23">
+      <c r="G49" s="19">
         <v>36.700000000000003</v>
       </c>
-      <c r="H49" s="23">
+      <c r="H49" s="19">
         <v>18</v>
       </c>
-      <c r="I49" s="23">
+      <c r="I49" s="19">
         <v>67</v>
       </c>
-      <c r="J49" s="23">
+      <c r="J49" s="19">
         <v>50</v>
       </c>
-      <c r="K49" s="23">
-        <v>0</v>
-      </c>
-      <c r="L49" s="37">
+      <c r="K49" s="19">
+        <v>0</v>
+      </c>
+      <c r="L49" s="33">
         <v>100</v>
       </c>
-      <c r="M49" s="23">
+      <c r="M49" s="19">
         <v>33</v>
       </c>
-      <c r="N49" s="23">
+      <c r="N49" s="19">
         <v>55</v>
       </c>
-      <c r="O49" s="23">
-        <v>0</v>
-      </c>
-      <c r="P49" s="24"/>
+      <c r="O49" s="19">
+        <v>0</v>
+      </c>
+      <c r="P49" s="20"/>
     </row>
     <row r="50" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B50" s="22">
+      <c r="B50" s="18">
         <v>2005</v>
       </c>
-      <c r="C50" s="23">
+      <c r="C50" s="19">
         <v>22.4</v>
       </c>
-      <c r="D50" s="23">
+      <c r="D50" s="19">
         <v>19</v>
       </c>
-      <c r="E50" s="23">
+      <c r="E50" s="19">
         <v>16.7</v>
       </c>
-      <c r="F50" s="23">
+      <c r="F50" s="19">
         <v>27.2</v>
       </c>
-      <c r="G50" s="23">
+      <c r="G50" s="19">
         <v>22.8</v>
       </c>
-      <c r="H50" s="23">
+      <c r="H50" s="19">
         <v>6.2</v>
       </c>
-      <c r="I50" s="23">
+      <c r="I50" s="19">
         <v>45.6</v>
       </c>
-      <c r="J50" s="23">
+      <c r="J50" s="19">
         <v>50</v>
       </c>
-      <c r="K50" s="23">
-        <v>0</v>
-      </c>
-      <c r="L50" s="37">
+      <c r="K50" s="19">
+        <v>0</v>
+      </c>
+      <c r="L50" s="33">
         <v>100</v>
       </c>
-      <c r="M50" s="23">
+      <c r="M50" s="19">
         <v>33</v>
       </c>
-      <c r="N50" s="23">
+      <c r="N50" s="19">
         <v>72.599999999999994</v>
       </c>
-      <c r="O50" s="23">
-        <v>0</v>
-      </c>
-      <c r="P50" s="24"/>
+      <c r="O50" s="19">
+        <v>0</v>
+      </c>
+      <c r="P50" s="20"/>
     </row>
     <row r="51" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B51" s="22">
+      <c r="B51" s="18">
         <v>2010</v>
       </c>
-      <c r="C51" s="23">
+      <c r="C51" s="19">
         <v>16.399999999999999</v>
       </c>
-      <c r="D51" s="23">
+      <c r="D51" s="19">
         <v>20.100000000000001</v>
       </c>
-      <c r="E51" s="23">
+      <c r="E51" s="19">
         <v>15.2</v>
       </c>
-      <c r="F51" s="23">
+      <c r="F51" s="19">
         <v>25.8</v>
       </c>
-      <c r="G51" s="23">
+      <c r="G51" s="19">
         <v>22</v>
       </c>
-      <c r="H51" s="23">
+      <c r="H51" s="19">
         <v>5.2</v>
       </c>
-      <c r="I51" s="23">
+      <c r="I51" s="19">
         <v>30.4</v>
       </c>
-      <c r="J51" s="23">
+      <c r="J51" s="19">
         <v>50</v>
       </c>
-      <c r="K51" s="23">
-        <v>0</v>
-      </c>
-      <c r="L51" s="37">
+      <c r="K51" s="19">
+        <v>0</v>
+      </c>
+      <c r="L51" s="33">
         <v>100</v>
       </c>
-      <c r="M51" s="23">
+      <c r="M51" s="19">
         <v>33</v>
       </c>
-      <c r="N51" s="23">
+      <c r="N51" s="19">
         <v>88</v>
       </c>
-      <c r="O51" s="23">
-        <v>0</v>
-      </c>
-      <c r="P51" s="24"/>
+      <c r="O51" s="19">
+        <v>0</v>
+      </c>
+      <c r="P51" s="20"/>
     </row>
     <row r="52" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B52" s="22">
+      <c r="B52" s="18">
         <v>2015</v>
       </c>
-      <c r="C52" s="23">
+      <c r="C52" s="19">
         <v>10.8</v>
       </c>
-      <c r="D52" s="23">
+      <c r="D52" s="19">
         <v>19.899999999999999</v>
       </c>
-      <c r="E52" s="23">
+      <c r="E52" s="19">
         <v>11.9</v>
       </c>
-      <c r="F52" s="23">
+      <c r="F52" s="19">
         <v>25.3</v>
       </c>
-      <c r="G52" s="23">
+      <c r="G52" s="19">
         <v>16.100000000000001</v>
       </c>
-      <c r="H52" s="23">
+      <c r="H52" s="19">
         <v>3.4</v>
       </c>
-      <c r="I52" s="23">
+      <c r="I52" s="19">
         <v>36</v>
       </c>
-      <c r="J52" s="23">
+      <c r="J52" s="19">
         <v>50</v>
       </c>
-      <c r="K52" s="23">
-        <v>0</v>
-      </c>
-      <c r="L52" s="37">
+      <c r="K52" s="19">
+        <v>0</v>
+      </c>
+      <c r="L52" s="33">
         <v>100</v>
       </c>
-      <c r="M52" s="23">
+      <c r="M52" s="19">
         <v>33</v>
       </c>
-      <c r="N52" s="23">
+      <c r="N52" s="19">
         <v>78.099999999999994</v>
       </c>
-      <c r="O52" s="23">
-        <v>0</v>
-      </c>
-      <c r="P52" s="24"/>
+      <c r="O52" s="19">
+        <v>0</v>
+      </c>
+      <c r="P52" s="20"/>
     </row>
     <row r="53" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B53" s="22">
+      <c r="B53" s="18">
         <v>2019</v>
       </c>
-      <c r="C53" s="23">
+      <c r="C53" s="19">
         <v>5.0999999999999996</v>
       </c>
-      <c r="D53" s="23">
+      <c r="D53" s="19">
         <v>10.3</v>
       </c>
-      <c r="E53" s="23">
+      <c r="E53" s="19">
         <v>7.9</v>
       </c>
-      <c r="F53" s="23">
+      <c r="F53" s="19">
         <v>10.6</v>
       </c>
-      <c r="G53" s="23">
+      <c r="G53" s="19">
         <v>12</v>
       </c>
-      <c r="H53" s="23">
+      <c r="H53" s="19">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I53" s="23">
+      <c r="I53" s="19">
         <v>23.8</v>
       </c>
-      <c r="J53" s="23">
+      <c r="J53" s="19">
         <v>50</v>
       </c>
-      <c r="K53" s="23">
-        <v>0</v>
-      </c>
-      <c r="L53" s="37">
+      <c r="K53" s="19">
+        <v>0</v>
+      </c>
+      <c r="L53" s="33">
         <v>100</v>
       </c>
-      <c r="M53" s="23">
+      <c r="M53" s="19">
         <v>33</v>
       </c>
-      <c r="N53" s="23">
+      <c r="N53" s="19">
         <v>89.9</v>
       </c>
-      <c r="O53" s="23">
-        <v>0</v>
-      </c>
-      <c r="P53" s="24"/>
+      <c r="O53" s="19">
+        <v>0</v>
+      </c>
+      <c r="P53" s="20"/>
     </row>
     <row r="54" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B54" s="22">
+      <c r="B54" s="18">
         <v>2020</v>
       </c>
-      <c r="C54" s="23">
+      <c r="C54" s="19">
         <v>5.0999999999999996</v>
       </c>
-      <c r="D54" s="23">
+      <c r="D54" s="19">
         <v>10.3</v>
       </c>
-      <c r="E54" s="23">
+      <c r="E54" s="19">
         <v>7.9</v>
       </c>
-      <c r="F54" s="23">
+      <c r="F54" s="19">
         <v>10.6</v>
       </c>
-      <c r="G54" s="23">
+      <c r="G54" s="19">
         <v>11.9</v>
       </c>
-      <c r="H54" s="23">
+      <c r="H54" s="19">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I54" s="23">
+      <c r="I54" s="19">
         <v>23.8</v>
       </c>
-      <c r="J54" s="23">
+      <c r="J54" s="19">
         <v>50</v>
       </c>
-      <c r="K54" s="23">
-        <v>0</v>
-      </c>
-      <c r="L54" s="37">
+      <c r="K54" s="19">
+        <v>0</v>
+      </c>
+      <c r="L54" s="33">
         <v>100</v>
       </c>
-      <c r="M54" s="23">
+      <c r="M54" s="19">
         <v>33</v>
       </c>
-      <c r="N54" s="23">
+      <c r="N54" s="19">
         <v>89.9</v>
       </c>
-      <c r="O54" s="23">
-        <v>0</v>
-      </c>
-      <c r="P54" s="24"/>
+      <c r="O54" s="19">
+        <v>0</v>
+      </c>
+      <c r="P54" s="20"/>
     </row>
     <row r="55" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B55" s="22">
+      <c r="B55" s="18">
         <v>2021</v>
       </c>
-      <c r="C55" s="23">
+      <c r="C55" s="19">
         <v>5.0999999999999996</v>
       </c>
-      <c r="D55" s="23">
+      <c r="D55" s="19">
         <v>10.3</v>
       </c>
-      <c r="E55" s="23">
+      <c r="E55" s="19">
         <v>7.9</v>
       </c>
-      <c r="F55" s="23">
+      <c r="F55" s="19">
         <v>10.6</v>
       </c>
-      <c r="G55" s="23">
+      <c r="G55" s="19">
         <v>11.9</v>
       </c>
-      <c r="H55" s="23">
+      <c r="H55" s="19">
         <v>2.2999999999999998</v>
       </c>
-      <c r="I55" s="23">
+      <c r="I55" s="19">
         <v>23.8</v>
       </c>
-      <c r="J55" s="23">
+      <c r="J55" s="19">
         <v>50</v>
       </c>
-      <c r="K55" s="23">
-        <v>0</v>
-      </c>
-      <c r="L55" s="37">
+      <c r="K55" s="19">
+        <v>0</v>
+      </c>
+      <c r="L55" s="33">
         <v>100</v>
       </c>
-      <c r="M55" s="23">
+      <c r="M55" s="19">
         <v>33</v>
       </c>
-      <c r="N55" s="23">
+      <c r="N55" s="19">
         <v>89.9</v>
       </c>
-      <c r="O55" s="23">
-        <v>0</v>
-      </c>
-      <c r="P55" s="24"/>
+      <c r="O55" s="19">
+        <v>0</v>
+      </c>
+      <c r="P55" s="20"/>
     </row>
     <row r="56" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B56" s="39" t="s">
+      <c r="B56" s="35" t="s">
         <v>163</v>
       </c>
-      <c r="C56" s="40">
+      <c r="C56" s="36">
         <f>AVERAGE(C52:C54)</f>
         <v>7</v>
       </c>
-      <c r="D56" s="40">
+      <c r="D56" s="36">
         <f t="shared" ref="D56:O56" si="17">AVERAGE(D52:D54)</f>
         <v>13.5</v>
       </c>
-      <c r="E56" s="40">
+      <c r="E56" s="36">
         <f t="shared" si="17"/>
         <v>9.2333333333333343</v>
       </c>
-      <c r="F56" s="40">
+      <c r="F56" s="36">
         <f t="shared" si="17"/>
         <v>15.5</v>
       </c>
-      <c r="G56" s="40">
+      <c r="G56" s="36">
         <f t="shared" si="17"/>
         <v>13.333333333333334</v>
       </c>
-      <c r="H56" s="40">
+      <c r="H56" s="36">
         <f t="shared" si="17"/>
         <v>2.6666666666666665</v>
       </c>
-      <c r="I56" s="40">
+      <c r="I56" s="36">
         <f t="shared" si="17"/>
         <v>27.866666666666664</v>
       </c>
-      <c r="J56" s="40">
+      <c r="J56" s="36">
         <f t="shared" si="17"/>
         <v>50</v>
       </c>
-      <c r="K56" s="40">
+      <c r="K56" s="36">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="L56" s="40">
+      <c r="L56" s="36">
         <f t="shared" si="17"/>
         <v>100</v>
       </c>
-      <c r="M56" s="40">
+      <c r="M56" s="36">
         <f t="shared" si="17"/>
         <v>33</v>
       </c>
-      <c r="N56" s="40">
+      <c r="N56" s="36">
         <f t="shared" si="17"/>
         <v>85.966666666666654</v>
       </c>
-      <c r="O56" s="40">
+      <c r="O56" s="36">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="P56" s="24"/>
+      <c r="P56" s="20"/>
     </row>
     <row r="58" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B58" s="61" t="s">
+      <c r="B58" s="53" t="s">
         <v>161</v>
       </c>
-      <c r="C58" s="61"/>
-      <c r="D58" s="61"/>
-      <c r="E58" s="61"/>
-      <c r="F58" s="61"/>
-      <c r="G58" s="61"/>
-      <c r="H58" s="61"/>
-      <c r="I58" s="61"/>
-      <c r="J58" s="61"/>
-      <c r="K58" s="61"/>
-      <c r="L58" s="61"/>
-      <c r="M58" s="61"/>
-      <c r="N58" s="61"/>
+      <c r="C58" s="53"/>
+      <c r="D58" s="53"/>
+      <c r="E58" s="53"/>
+      <c r="F58" s="53"/>
+      <c r="G58" s="53"/>
+      <c r="H58" s="53"/>
+      <c r="I58" s="53"/>
+      <c r="J58" s="53"/>
+      <c r="K58" s="53"/>
+      <c r="L58" s="53"/>
+      <c r="M58" s="53"/>
+      <c r="N58" s="53"/>
     </row>
     <row r="59" spans="2:16" ht="65.25" x14ac:dyDescent="0.25">
-      <c r="B59" s="38" t="s">
+      <c r="B59" s="34" t="s">
         <v>131</v>
       </c>
-      <c r="C59" s="36" t="s">
+      <c r="C59" s="32" t="s">
         <v>132</v>
       </c>
-      <c r="D59" s="36" t="s">
+      <c r="D59" s="32" t="s">
         <v>133</v>
       </c>
-      <c r="E59" s="36" t="s">
+      <c r="E59" s="32" t="s">
         <v>134</v>
       </c>
-      <c r="F59" s="36" t="s">
+      <c r="F59" s="32" t="s">
         <v>135</v>
       </c>
-      <c r="G59" s="36" t="s">
+      <c r="G59" s="32" t="s">
         <v>136</v>
       </c>
-      <c r="H59" s="36" t="s">
+      <c r="H59" s="32" t="s">
         <v>137</v>
       </c>
-      <c r="I59" s="36" t="s">
+      <c r="I59" s="32" t="s">
         <v>138</v>
       </c>
-      <c r="J59" s="36" t="s">
+      <c r="J59" s="32" t="s">
         <v>162</v>
       </c>
-      <c r="K59" s="36" t="s">
+      <c r="K59" s="32" t="s">
         <v>146</v>
       </c>
-      <c r="L59" s="36" t="s">
+      <c r="L59" s="32" t="s">
         <v>140</v>
       </c>
-      <c r="M59" s="36" t="s">
+      <c r="M59" s="32" t="s">
         <v>160</v>
       </c>
-      <c r="N59" s="21"/>
+      <c r="N59" s="17"/>
     </row>
     <row r="60" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B60" s="27">
+      <c r="B60" s="23">
         <v>1990</v>
       </c>
-      <c r="C60" s="23">
+      <c r="C60" s="19">
         <v>0.8</v>
       </c>
-      <c r="D60" s="23">
+      <c r="D60" s="19">
         <v>7.2</v>
       </c>
-      <c r="E60" s="23">
+      <c r="E60" s="19">
         <v>7.6</v>
       </c>
-      <c r="F60" s="23">
+      <c r="F60" s="19">
         <v>8.9</v>
       </c>
-      <c r="G60" s="23">
+      <c r="G60" s="19">
         <v>9.1</v>
       </c>
-      <c r="H60" s="23">
+      <c r="H60" s="19">
         <v>2</v>
       </c>
-      <c r="I60" s="23">
+      <c r="I60" s="19">
         <v>11</v>
       </c>
-      <c r="J60" s="23">
-        <v>0</v>
-      </c>
-      <c r="K60" s="23">
+      <c r="J60" s="19">
+        <v>0</v>
+      </c>
+      <c r="K60" s="19">
         <v>2</v>
       </c>
-      <c r="L60" s="23">
+      <c r="L60" s="19">
         <v>20</v>
       </c>
-      <c r="M60" s="29">
+      <c r="M60" s="25">
         <v>100</v>
       </c>
-      <c r="N60" s="24"/>
+      <c r="N60" s="20"/>
     </row>
     <row r="61" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B61" s="27">
+      <c r="B61" s="23">
         <v>1995</v>
       </c>
-      <c r="C61" s="23">
+      <c r="C61" s="19">
         <v>0.8</v>
       </c>
-      <c r="D61" s="23">
+      <c r="D61" s="19">
         <v>7.2</v>
       </c>
-      <c r="E61" s="23">
+      <c r="E61" s="19">
         <v>7.6</v>
       </c>
-      <c r="F61" s="23">
+      <c r="F61" s="19">
         <v>8.9</v>
       </c>
-      <c r="G61" s="23">
+      <c r="G61" s="19">
         <v>9.1</v>
       </c>
-      <c r="H61" s="23">
+      <c r="H61" s="19">
         <v>2</v>
       </c>
-      <c r="I61" s="23">
+      <c r="I61" s="19">
         <v>11</v>
       </c>
-      <c r="J61" s="23">
-        <v>0</v>
-      </c>
-      <c r="K61" s="23">
+      <c r="J61" s="19">
+        <v>0</v>
+      </c>
+      <c r="K61" s="19">
         <v>2</v>
       </c>
-      <c r="L61" s="23">
+      <c r="L61" s="19">
         <v>20</v>
       </c>
-      <c r="M61" s="29">
+      <c r="M61" s="25">
         <v>100</v>
       </c>
-      <c r="N61" s="24"/>
+      <c r="N61" s="20"/>
     </row>
     <row r="62" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B62" s="27">
+      <c r="B62" s="23">
         <v>2000</v>
       </c>
-      <c r="C62" s="23">
+      <c r="C62" s="19">
         <v>0.8</v>
       </c>
-      <c r="D62" s="23">
+      <c r="D62" s="19">
         <v>7.7</v>
       </c>
-      <c r="E62" s="23">
+      <c r="E62" s="19">
         <v>8.1</v>
       </c>
-      <c r="F62" s="23">
+      <c r="F62" s="19">
         <v>10.1</v>
       </c>
-      <c r="G62" s="23">
+      <c r="G62" s="19">
         <v>10.1</v>
       </c>
-      <c r="H62" s="23">
+      <c r="H62" s="19">
         <v>1</v>
       </c>
-      <c r="I62" s="23">
+      <c r="I62" s="19">
         <v>7</v>
       </c>
-      <c r="J62" s="23">
-        <v>0</v>
-      </c>
-      <c r="K62" s="23">
+      <c r="J62" s="19">
+        <v>0</v>
+      </c>
+      <c r="K62" s="19">
         <v>2</v>
       </c>
-      <c r="L62" s="23">
+      <c r="L62" s="19">
         <v>20</v>
       </c>
-      <c r="M62" s="29">
+      <c r="M62" s="25">
         <v>100</v>
       </c>
-      <c r="N62" s="24"/>
+      <c r="N62" s="20"/>
     </row>
     <row r="63" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B63" s="27">
+      <c r="B63" s="23">
         <v>2005</v>
       </c>
-      <c r="C63" s="23">
+      <c r="C63" s="19">
         <v>0.4</v>
       </c>
-      <c r="D63" s="23">
+      <c r="D63" s="19">
         <v>16</v>
       </c>
-      <c r="E63" s="23">
+      <c r="E63" s="19">
         <v>9.8000000000000007</v>
       </c>
-      <c r="F63" s="23">
+      <c r="F63" s="19">
         <v>19.899999999999999</v>
       </c>
-      <c r="G63" s="23">
+      <c r="G63" s="19">
         <v>21.6</v>
       </c>
-      <c r="H63" s="23">
+      <c r="H63" s="19">
         <v>1.3</v>
       </c>
-      <c r="I63" s="23">
+      <c r="I63" s="19">
         <v>22.1</v>
       </c>
-      <c r="J63" s="23">
-        <v>0</v>
-      </c>
-      <c r="K63" s="23">
+      <c r="J63" s="19">
+        <v>0</v>
+      </c>
+      <c r="K63" s="19">
         <v>2</v>
       </c>
-      <c r="L63" s="23">
+      <c r="L63" s="19">
         <v>6.6</v>
       </c>
-      <c r="M63" s="29">
+      <c r="M63" s="25">
         <v>100</v>
       </c>
-      <c r="N63" s="24"/>
+      <c r="N63" s="20"/>
     </row>
     <row r="64" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B64" s="27">
+      <c r="B64" s="23">
         <v>2010</v>
       </c>
-      <c r="C64" s="23">
+      <c r="C64" s="19">
         <v>0.8</v>
       </c>
-      <c r="D64" s="23">
+      <c r="D64" s="19">
         <v>14.5</v>
       </c>
-      <c r="E64" s="23">
+      <c r="E64" s="19">
         <v>10.5</v>
       </c>
-      <c r="F64" s="23">
+      <c r="F64" s="19">
         <v>18.8</v>
       </c>
-      <c r="G64" s="23">
+      <c r="G64" s="19">
         <v>29.5</v>
       </c>
-      <c r="H64" s="23">
+      <c r="H64" s="19">
         <v>0.9</v>
       </c>
-      <c r="I64" s="23">
+      <c r="I64" s="19">
         <v>7.4</v>
       </c>
-      <c r="J64" s="23">
-        <v>0</v>
-      </c>
-      <c r="K64" s="23">
+      <c r="J64" s="19">
+        <v>0</v>
+      </c>
+      <c r="K64" s="19">
         <v>2</v>
       </c>
-      <c r="L64" s="23">
-        <v>0</v>
-      </c>
-      <c r="M64" s="29">
+      <c r="L64" s="19">
+        <v>0</v>
+      </c>
+      <c r="M64" s="25">
         <v>100</v>
       </c>
-      <c r="N64" s="24"/>
+      <c r="N64" s="20"/>
     </row>
     <row r="65" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B65" s="27">
+      <c r="B65" s="23">
         <v>2015</v>
       </c>
-      <c r="C65" s="23">
+      <c r="C65" s="19">
         <v>0.9</v>
       </c>
-      <c r="D65" s="23">
+      <c r="D65" s="19">
         <v>17.100000000000001</v>
       </c>
-      <c r="E65" s="23">
+      <c r="E65" s="19">
         <v>11.9</v>
       </c>
-      <c r="F65" s="23">
+      <c r="F65" s="19">
         <v>22.4</v>
       </c>
-      <c r="G65" s="23">
+      <c r="G65" s="19">
         <v>34.5</v>
       </c>
-      <c r="H65" s="23">
+      <c r="H65" s="19">
         <v>1.5</v>
       </c>
-      <c r="I65" s="23">
+      <c r="I65" s="19">
         <v>6</v>
       </c>
-      <c r="J65" s="23">
-        <v>0</v>
-      </c>
-      <c r="K65" s="23">
+      <c r="J65" s="19">
+        <v>0</v>
+      </c>
+      <c r="K65" s="19">
         <v>2</v>
       </c>
-      <c r="L65" s="23">
+      <c r="L65" s="19">
         <v>12.6</v>
       </c>
-      <c r="M65" s="29">
+      <c r="M65" s="25">
         <v>100</v>
       </c>
-      <c r="N65" s="24"/>
+      <c r="N65" s="20"/>
     </row>
     <row r="66" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B66" s="27">
+      <c r="B66" s="23">
         <v>2019</v>
       </c>
-      <c r="C66" s="23">
+      <c r="C66" s="19">
         <v>1</v>
       </c>
-      <c r="D66" s="23">
+      <c r="D66" s="19">
         <v>21.3</v>
       </c>
-      <c r="E66" s="23">
+      <c r="E66" s="19">
         <v>13.3</v>
       </c>
-      <c r="F66" s="23">
+      <c r="F66" s="19">
         <v>25.6</v>
       </c>
-      <c r="G66" s="23">
+      <c r="G66" s="19">
         <v>33.5</v>
       </c>
-      <c r="H66" s="23">
+      <c r="H66" s="19">
         <v>1</v>
       </c>
-      <c r="I66" s="23">
+      <c r="I66" s="19">
         <v>19.8</v>
       </c>
-      <c r="J66" s="23">
-        <v>0</v>
-      </c>
-      <c r="K66" s="23">
+      <c r="J66" s="19">
+        <v>0</v>
+      </c>
+      <c r="K66" s="19">
         <v>2</v>
       </c>
-      <c r="L66" s="23">
+      <c r="L66" s="19">
         <v>3.2</v>
       </c>
-      <c r="M66" s="29">
+      <c r="M66" s="25">
         <v>100</v>
       </c>
-      <c r="N66" s="24"/>
+      <c r="N66" s="20"/>
     </row>
     <row r="67" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B67" s="27">
+      <c r="B67" s="23">
         <v>2020</v>
       </c>
-      <c r="C67" s="23">
+      <c r="C67" s="19">
         <v>1</v>
       </c>
-      <c r="D67" s="23">
+      <c r="D67" s="19">
         <v>21.3</v>
       </c>
-      <c r="E67" s="23">
+      <c r="E67" s="19">
         <v>13.3</v>
       </c>
-      <c r="F67" s="23">
+      <c r="F67" s="19">
         <v>25.6</v>
       </c>
-      <c r="G67" s="23">
+      <c r="G67" s="19">
         <v>33.5</v>
       </c>
-      <c r="H67" s="23">
+      <c r="H67" s="19">
         <v>1</v>
       </c>
-      <c r="I67" s="23">
+      <c r="I67" s="19">
         <v>19.8</v>
       </c>
-      <c r="J67" s="23">
-        <v>0</v>
-      </c>
-      <c r="K67" s="23">
+      <c r="J67" s="19">
+        <v>0</v>
+      </c>
+      <c r="K67" s="19">
         <v>2</v>
       </c>
-      <c r="L67" s="23">
+      <c r="L67" s="19">
         <v>3.2</v>
       </c>
-      <c r="M67" s="29">
+      <c r="M67" s="25">
         <v>100</v>
       </c>
-      <c r="N67" s="24"/>
+      <c r="N67" s="20"/>
     </row>
     <row r="68" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B68" s="27">
+      <c r="B68" s="23">
         <v>2021</v>
       </c>
-      <c r="C68" s="23">
+      <c r="C68" s="19">
         <v>1</v>
       </c>
-      <c r="D68" s="23">
+      <c r="D68" s="19">
         <v>21.2</v>
       </c>
-      <c r="E68" s="23">
+      <c r="E68" s="19">
         <v>13.3</v>
       </c>
-      <c r="F68" s="23">
+      <c r="F68" s="19">
         <v>25.6</v>
       </c>
-      <c r="G68" s="23">
+      <c r="G68" s="19">
         <v>33.5</v>
       </c>
-      <c r="H68" s="23">
+      <c r="H68" s="19">
         <v>1</v>
       </c>
-      <c r="I68" s="23">
+      <c r="I68" s="19">
         <v>19.8</v>
       </c>
-      <c r="J68" s="23">
-        <v>0</v>
-      </c>
-      <c r="K68" s="23">
+      <c r="J68" s="19">
+        <v>0</v>
+      </c>
+      <c r="K68" s="19">
         <v>2</v>
       </c>
-      <c r="L68" s="23">
+      <c r="L68" s="19">
         <v>3.2</v>
       </c>
-      <c r="M68" s="29">
+      <c r="M68" s="25">
         <v>100</v>
       </c>
-      <c r="N68" s="24"/>
+      <c r="N68" s="20"/>
     </row>
     <row r="69" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B69" s="39" t="s">
+      <c r="B69" s="35" t="s">
         <v>163</v>
       </c>
-      <c r="C69" s="40">
+      <c r="C69" s="36">
         <f>AVERAGE(C65:C67)</f>
         <v>0.96666666666666667</v>
       </c>
-      <c r="D69" s="40">
+      <c r="D69" s="36">
         <f t="shared" ref="D69:M69" si="18">AVERAGE(D65:D67)</f>
         <v>19.900000000000002</v>
       </c>
-      <c r="E69" s="40">
+      <c r="E69" s="36">
         <f t="shared" si="18"/>
         <v>12.833333333333334</v>
       </c>
-      <c r="F69" s="40">
+      <c r="F69" s="36">
         <f t="shared" si="18"/>
         <v>24.533333333333331</v>
       </c>
-      <c r="G69" s="40">
+      <c r="G69" s="36">
         <f t="shared" si="18"/>
         <v>33.833333333333336</v>
       </c>
-      <c r="H69" s="40">
+      <c r="H69" s="36">
         <f t="shared" si="18"/>
         <v>1.1666666666666667</v>
       </c>
-      <c r="I69" s="40">
+      <c r="I69" s="36">
         <f t="shared" si="18"/>
         <v>15.200000000000001</v>
       </c>
-      <c r="J69" s="40">
+      <c r="J69" s="36">
         <f t="shared" si="18"/>
         <v>0</v>
       </c>
-      <c r="K69" s="40">
+      <c r="K69" s="36">
         <f t="shared" si="18"/>
         <v>2</v>
       </c>
-      <c r="L69" s="40">
+      <c r="L69" s="36">
         <f t="shared" si="18"/>
         <v>6.333333333333333</v>
       </c>
-      <c r="M69" s="40">
+      <c r="M69" s="36">
         <f t="shared" si="18"/>
         <v>100</v>
       </c>
-      <c r="N69" s="24"/>
+      <c r="N69" s="20"/>
     </row>
     <row r="71" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="55" t="s">
+      <c r="B71" s="52" t="s">
         <v>150</v>
       </c>
-      <c r="C71" s="55"/>
-      <c r="D71" s="55"/>
-      <c r="E71" s="55"/>
-      <c r="F71" s="55"/>
-      <c r="G71" s="55"/>
-      <c r="H71" s="55"/>
-      <c r="I71" s="55"/>
-      <c r="J71" s="55"/>
-      <c r="K71" s="55"/>
-      <c r="L71" s="55"/>
-      <c r="M71" s="55"/>
+      <c r="C71" s="52"/>
+      <c r="D71" s="52"/>
+      <c r="E71" s="52"/>
+      <c r="F71" s="52"/>
+      <c r="G71" s="52"/>
+      <c r="H71" s="52"/>
+      <c r="I71" s="52"/>
+      <c r="J71" s="52"/>
+      <c r="K71" s="52"/>
+      <c r="L71" s="52"/>
+      <c r="M71" s="52"/>
     </row>
     <row r="72" spans="2:14" ht="24" x14ac:dyDescent="0.25">
-      <c r="B72" s="56" t="s">
+      <c r="B72" s="54" t="s">
         <v>131</v>
       </c>
-      <c r="C72" s="58" t="s">
+      <c r="C72" s="56" t="s">
         <v>151</v>
       </c>
-      <c r="D72" s="59"/>
-      <c r="E72" s="59"/>
-      <c r="F72" s="59"/>
-      <c r="G72" s="59"/>
-      <c r="H72" s="59"/>
-      <c r="I72" s="59"/>
-      <c r="J72" s="59"/>
-      <c r="K72" s="60"/>
-      <c r="L72" s="30" t="s">
+      <c r="D72" s="57"/>
+      <c r="E72" s="57"/>
+      <c r="F72" s="57"/>
+      <c r="G72" s="57"/>
+      <c r="H72" s="57"/>
+      <c r="I72" s="57"/>
+      <c r="J72" s="57"/>
+      <c r="K72" s="58"/>
+      <c r="L72" s="26" t="s">
         <v>152</v>
       </c>
-      <c r="M72" s="31"/>
+      <c r="M72" s="27"/>
     </row>
     <row r="73" spans="2:14" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="B73" s="57"/>
-      <c r="C73" s="20" t="s">
+      <c r="B73" s="55"/>
+      <c r="C73" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="D73" s="32" t="s">
+      <c r="D73" s="28" t="s">
         <v>133</v>
       </c>
-      <c r="E73" s="32" t="s">
+      <c r="E73" s="28" t="s">
         <v>134</v>
       </c>
-      <c r="F73" s="32" t="s">
+      <c r="F73" s="28" t="s">
         <v>135</v>
       </c>
-      <c r="G73" s="32" t="s">
+      <c r="G73" s="28" t="s">
         <v>136</v>
       </c>
-      <c r="H73" s="20" t="s">
+      <c r="H73" s="16" t="s">
         <v>153</v>
       </c>
-      <c r="I73" s="32" t="s">
+      <c r="I73" s="28" t="s">
         <v>137</v>
       </c>
-      <c r="J73" s="32" t="s">
+      <c r="J73" s="28" t="s">
         <v>138</v>
       </c>
-      <c r="K73" s="20" t="s">
+      <c r="K73" s="16" t="s">
         <v>143</v>
       </c>
-      <c r="L73" s="20" t="s">
+      <c r="L73" s="16" t="s">
         <v>146</v>
       </c>
-      <c r="M73" s="21"/>
+      <c r="M73" s="17"/>
     </row>
     <row r="74" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B74" s="27">
+      <c r="B74" s="23">
         <v>1990</v>
       </c>
-      <c r="C74" s="23">
-        <v>0</v>
-      </c>
-      <c r="D74" s="23">
-        <v>0</v>
-      </c>
-      <c r="E74" s="23">
-        <v>0</v>
-      </c>
-      <c r="F74" s="23">
-        <v>0</v>
-      </c>
-      <c r="G74" s="23">
-        <v>0</v>
-      </c>
-      <c r="H74" s="23">
-        <v>0</v>
-      </c>
-      <c r="I74" s="23">
-        <v>0</v>
-      </c>
-      <c r="J74" s="23">
-        <v>0</v>
-      </c>
-      <c r="K74" s="23">
-        <v>0</v>
-      </c>
-      <c r="L74" s="23">
+      <c r="C74" s="19">
+        <v>0</v>
+      </c>
+      <c r="D74" s="19">
+        <v>0</v>
+      </c>
+      <c r="E74" s="19">
+        <v>0</v>
+      </c>
+      <c r="F74" s="19">
+        <v>0</v>
+      </c>
+      <c r="G74" s="19">
+        <v>0</v>
+      </c>
+      <c r="H74" s="19">
+        <v>0</v>
+      </c>
+      <c r="I74" s="19">
+        <v>0</v>
+      </c>
+      <c r="J74" s="19">
+        <v>0</v>
+      </c>
+      <c r="K74" s="19">
+        <v>0</v>
+      </c>
+      <c r="L74" s="19">
         <v>15</v>
       </c>
-      <c r="M74" s="24"/>
+      <c r="M74" s="20"/>
     </row>
     <row r="75" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B75" s="27">
+      <c r="B75" s="23">
         <v>1995</v>
       </c>
-      <c r="C75" s="23">
-        <v>0</v>
-      </c>
-      <c r="D75" s="23">
-        <v>0</v>
-      </c>
-      <c r="E75" s="23">
-        <v>0</v>
-      </c>
-      <c r="F75" s="23">
-        <v>0</v>
-      </c>
-      <c r="G75" s="23">
-        <v>0</v>
-      </c>
-      <c r="H75" s="23">
-        <v>0</v>
-      </c>
-      <c r="I75" s="23">
-        <v>0</v>
-      </c>
-      <c r="J75" s="23">
-        <v>0</v>
-      </c>
-      <c r="K75" s="23">
-        <v>0</v>
-      </c>
-      <c r="L75" s="23">
+      <c r="C75" s="19">
+        <v>0</v>
+      </c>
+      <c r="D75" s="19">
+        <v>0</v>
+      </c>
+      <c r="E75" s="19">
+        <v>0</v>
+      </c>
+      <c r="F75" s="19">
+        <v>0</v>
+      </c>
+      <c r="G75" s="19">
+        <v>0</v>
+      </c>
+      <c r="H75" s="19">
+        <v>0</v>
+      </c>
+      <c r="I75" s="19">
+        <v>0</v>
+      </c>
+      <c r="J75" s="19">
+        <v>0</v>
+      </c>
+      <c r="K75" s="19">
+        <v>0</v>
+      </c>
+      <c r="L75" s="19">
         <v>15</v>
       </c>
-      <c r="M75" s="24"/>
+      <c r="M75" s="20"/>
     </row>
     <row r="76" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B76" s="27">
+      <c r="B76" s="23">
         <v>2000</v>
       </c>
-      <c r="C76" s="23">
-        <v>0</v>
-      </c>
-      <c r="D76" s="23">
-        <v>0</v>
-      </c>
-      <c r="E76" s="23">
-        <v>0</v>
-      </c>
-      <c r="F76" s="23">
-        <v>0</v>
-      </c>
-      <c r="G76" s="23">
-        <v>0</v>
-      </c>
-      <c r="H76" s="23">
-        <v>0</v>
-      </c>
-      <c r="I76" s="23">
+      <c r="C76" s="19">
+        <v>0</v>
+      </c>
+      <c r="D76" s="19">
+        <v>0</v>
+      </c>
+      <c r="E76" s="19">
+        <v>0</v>
+      </c>
+      <c r="F76" s="19">
+        <v>0</v>
+      </c>
+      <c r="G76" s="19">
+        <v>0</v>
+      </c>
+      <c r="H76" s="19">
+        <v>0</v>
+      </c>
+      <c r="I76" s="19">
         <v>0.2</v>
       </c>
-      <c r="J76" s="23">
+      <c r="J76" s="19">
         <v>0.1</v>
       </c>
-      <c r="K76" s="23">
+      <c r="K76" s="19">
         <v>0.1</v>
       </c>
-      <c r="L76" s="23">
+      <c r="L76" s="19">
         <v>15</v>
       </c>
-      <c r="M76" s="24"/>
+      <c r="M76" s="20"/>
     </row>
     <row r="77" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B77" s="27">
+      <c r="B77" s="23">
         <v>2005</v>
       </c>
-      <c r="C77" s="23">
+      <c r="C77" s="19">
         <v>0.1</v>
       </c>
-      <c r="D77" s="23">
-        <v>0</v>
-      </c>
-      <c r="E77" s="23">
-        <v>0</v>
-      </c>
-      <c r="F77" s="23">
+      <c r="D77" s="19">
+        <v>0</v>
+      </c>
+      <c r="E77" s="19">
+        <v>0</v>
+      </c>
+      <c r="F77" s="19">
         <v>0.1</v>
       </c>
-      <c r="G77" s="23">
+      <c r="G77" s="19">
         <v>0.1</v>
       </c>
-      <c r="H77" s="23">
-        <v>0</v>
-      </c>
-      <c r="I77" s="23">
+      <c r="H77" s="19">
+        <v>0</v>
+      </c>
+      <c r="I77" s="19">
         <v>0.4</v>
       </c>
-      <c r="J77" s="23">
+      <c r="J77" s="19">
         <v>0.1</v>
       </c>
-      <c r="K77" s="23">
+      <c r="K77" s="19">
         <v>0.3</v>
       </c>
-      <c r="L77" s="23">
+      <c r="L77" s="19">
         <v>15</v>
       </c>
-      <c r="M77" s="24"/>
+      <c r="M77" s="20"/>
     </row>
     <row r="78" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B78" s="27">
+      <c r="B78" s="23">
         <v>2010</v>
       </c>
-      <c r="C78" s="23">
+      <c r="C78" s="19">
         <v>0.2</v>
       </c>
-      <c r="D78" s="23">
+      <c r="D78" s="19">
         <v>0.1</v>
       </c>
-      <c r="E78" s="23">
+      <c r="E78" s="19">
         <v>0.1</v>
       </c>
-      <c r="F78" s="23">
+      <c r="F78" s="19">
         <v>0.1</v>
       </c>
-      <c r="G78" s="23">
+      <c r="G78" s="19">
         <v>0.1</v>
       </c>
-      <c r="H78" s="23">
+      <c r="H78" s="19">
         <v>0.1</v>
       </c>
-      <c r="I78" s="23">
+      <c r="I78" s="19">
         <v>0.8</v>
       </c>
-      <c r="J78" s="23">
+      <c r="J78" s="19">
         <v>0.6</v>
       </c>
-      <c r="K78" s="23">
+      <c r="K78" s="19">
         <v>0.8</v>
       </c>
-      <c r="L78" s="23">
+      <c r="L78" s="19">
         <v>15</v>
       </c>
-      <c r="M78" s="24"/>
+      <c r="M78" s="20"/>
     </row>
     <row r="79" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B79" s="27">
+      <c r="B79" s="23">
         <v>2015</v>
       </c>
-      <c r="C79" s="23">
+      <c r="C79" s="19">
         <v>1.2</v>
       </c>
-      <c r="D79" s="23">
+      <c r="D79" s="19">
         <v>0.3</v>
       </c>
-      <c r="E79" s="23">
+      <c r="E79" s="19">
         <v>0.6</v>
       </c>
-      <c r="F79" s="23">
+      <c r="F79" s="19">
         <v>0.8</v>
       </c>
-      <c r="G79" s="23">
+      <c r="G79" s="19">
         <v>0.5</v>
       </c>
-      <c r="H79" s="23">
+      <c r="H79" s="19">
         <v>0.5</v>
       </c>
-      <c r="I79" s="23">
+      <c r="I79" s="19">
         <v>4.7</v>
       </c>
-      <c r="J79" s="23">
+      <c r="J79" s="19">
         <v>2.9</v>
       </c>
-      <c r="K79" s="23">
+      <c r="K79" s="19">
         <v>4.2</v>
       </c>
-      <c r="L79" s="23">
+      <c r="L79" s="19">
         <v>15</v>
       </c>
-      <c r="M79" s="24"/>
+      <c r="M79" s="20"/>
     </row>
     <row r="80" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B80" s="27">
+      <c r="B80" s="23">
         <v>2019</v>
       </c>
-      <c r="C80" s="23">
+      <c r="C80" s="19">
         <v>1.4</v>
       </c>
-      <c r="D80" s="23">
+      <c r="D80" s="19">
         <v>0.4</v>
       </c>
-      <c r="E80" s="23">
+      <c r="E80" s="19">
         <v>0.6</v>
       </c>
-      <c r="F80" s="23">
+      <c r="F80" s="19">
         <v>1</v>
       </c>
-      <c r="G80" s="23">
+      <c r="G80" s="19">
         <v>0.6</v>
       </c>
-      <c r="H80" s="23">
+      <c r="H80" s="19">
         <v>0.6</v>
       </c>
-      <c r="I80" s="23">
+      <c r="I80" s="19">
         <v>5.7</v>
       </c>
-      <c r="J80" s="23">
+      <c r="J80" s="19">
         <v>3.3</v>
       </c>
-      <c r="K80" s="23">
+      <c r="K80" s="19">
         <v>5.0999999999999996</v>
       </c>
-      <c r="L80" s="23">
+      <c r="L80" s="19">
         <v>15</v>
       </c>
-      <c r="M80" s="24"/>
+      <c r="M80" s="20"/>
     </row>
     <row r="81" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B81" s="27">
+      <c r="B81" s="23">
         <v>2020</v>
       </c>
-      <c r="C81" s="23">
+      <c r="C81" s="19">
         <v>1.7</v>
       </c>
-      <c r="D81" s="23">
+      <c r="D81" s="19">
         <v>0.5</v>
       </c>
-      <c r="E81" s="23">
+      <c r="E81" s="19">
         <v>0.8</v>
       </c>
-      <c r="F81" s="23">
+      <c r="F81" s="19">
         <v>1.2</v>
       </c>
-      <c r="G81" s="23">
+      <c r="G81" s="19">
         <v>0.7</v>
       </c>
-      <c r="H81" s="23">
+      <c r="H81" s="19">
         <v>0.7</v>
       </c>
-      <c r="I81" s="23">
+      <c r="I81" s="19">
         <v>6.6</v>
       </c>
-      <c r="J81" s="23">
+      <c r="J81" s="19">
         <v>3.8</v>
       </c>
-      <c r="K81" s="23">
+      <c r="K81" s="19">
         <v>5.9</v>
       </c>
-      <c r="L81" s="23">
+      <c r="L81" s="19">
         <v>15</v>
       </c>
-      <c r="M81" s="24"/>
+      <c r="M81" s="20"/>
     </row>
     <row r="82" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B82" s="27">
+      <c r="B82" s="23">
         <v>2021</v>
       </c>
-      <c r="C82" s="23">
+      <c r="C82" s="19">
         <v>2</v>
       </c>
-      <c r="D82" s="23">
+      <c r="D82" s="19">
         <v>0.5</v>
       </c>
-      <c r="E82" s="23">
+      <c r="E82" s="19">
         <v>0.9</v>
       </c>
-      <c r="F82" s="23">
+      <c r="F82" s="19">
         <v>1.4</v>
       </c>
-      <c r="G82" s="23">
+      <c r="G82" s="19">
         <v>0.9</v>
       </c>
-      <c r="H82" s="23">
+      <c r="H82" s="19">
         <v>0.9</v>
       </c>
-      <c r="I82" s="23">
+      <c r="I82" s="19">
         <v>7.6</v>
       </c>
-      <c r="J82" s="23">
+      <c r="J82" s="19">
         <v>4.5</v>
       </c>
-      <c r="K82" s="23">
+      <c r="K82" s="19">
         <v>6.8</v>
       </c>
-      <c r="L82" s="23">
+      <c r="L82" s="19">
         <v>15</v>
       </c>
-      <c r="M82" s="24"/>
+      <c r="M82" s="20"/>
     </row>
     <row r="83" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B83" s="39" t="s">
+      <c r="B83" s="35" t="s">
         <v>163</v>
       </c>
-      <c r="C83" s="40">
+      <c r="C83" s="36">
         <f>AVERAGE(C79:C81)</f>
         <v>1.4333333333333333</v>
       </c>
-      <c r="D83" s="40">
+      <c r="D83" s="36">
         <f t="shared" ref="D83:L83" si="19">AVERAGE(D79:D81)</f>
         <v>0.39999999999999997</v>
       </c>
-      <c r="E83" s="40">
+      <c r="E83" s="36">
         <f t="shared" si="19"/>
         <v>0.66666666666666663</v>
       </c>
-      <c r="F83" s="40">
+      <c r="F83" s="36">
         <f t="shared" si="19"/>
         <v>1</v>
       </c>
-      <c r="G83" s="40">
+      <c r="G83" s="36">
         <f t="shared" si="19"/>
         <v>0.6</v>
       </c>
-      <c r="H83" s="40">
+      <c r="H83" s="36">
         <f t="shared" si="19"/>
         <v>0.6</v>
       </c>
-      <c r="I83" s="40">
+      <c r="I83" s="36">
         <f t="shared" si="19"/>
         <v>5.666666666666667</v>
       </c>
-      <c r="J83" s="40">
+      <c r="J83" s="36">
         <f t="shared" si="19"/>
         <v>3.3333333333333335</v>
       </c>
-      <c r="K83" s="40">
+      <c r="K83" s="36">
         <f t="shared" si="19"/>
         <v>5.0666666666666673</v>
       </c>
-      <c r="L83" s="40">
+      <c r="L83" s="36">
         <f t="shared" si="19"/>
         <v>15</v>
       </c>
-      <c r="M83" s="24"/>
+      <c r="M83" s="20"/>
     </row>
     <row r="85" spans="2:13" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B85" s="61" t="s">
+      <c r="B85" s="53" t="s">
         <v>154</v>
       </c>
-      <c r="C85" s="61"/>
-      <c r="D85" s="61"/>
-      <c r="E85" s="61"/>
-      <c r="F85" s="61"/>
-      <c r="G85" s="61"/>
-      <c r="H85" s="61"/>
-      <c r="I85" s="61"/>
-      <c r="J85" s="61"/>
-      <c r="K85" s="61"/>
-      <c r="L85" s="61"/>
+      <c r="C85" s="53"/>
+      <c r="D85" s="53"/>
+      <c r="E85" s="53"/>
+      <c r="F85" s="53"/>
+      <c r="G85" s="53"/>
+      <c r="H85" s="53"/>
+      <c r="I85" s="53"/>
+      <c r="J85" s="53"/>
+      <c r="K85" s="53"/>
+      <c r="L85" s="53"/>
     </row>
     <row r="86" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B86" s="62"/>
-      <c r="C86" s="64" t="s">
+      <c r="B86" s="47"/>
+      <c r="C86" s="49" t="s">
         <v>155</v>
       </c>
-      <c r="D86" s="65"/>
-      <c r="E86" s="65"/>
-      <c r="F86" s="65"/>
-      <c r="G86" s="65"/>
-      <c r="H86" s="65"/>
-      <c r="I86" s="65"/>
-      <c r="J86" s="65"/>
-      <c r="K86" s="66"/>
-      <c r="L86" s="24"/>
+      <c r="D86" s="50"/>
+      <c r="E86" s="50"/>
+      <c r="F86" s="50"/>
+      <c r="G86" s="50"/>
+      <c r="H86" s="50"/>
+      <c r="I86" s="50"/>
+      <c r="J86" s="50"/>
+      <c r="K86" s="51"/>
+      <c r="L86" s="20"/>
     </row>
     <row r="87" spans="2:13" ht="42" x14ac:dyDescent="0.25">
-      <c r="B87" s="63"/>
-      <c r="C87" s="33" t="s">
+      <c r="B87" s="48"/>
+      <c r="C87" s="29" t="s">
         <v>132</v>
       </c>
-      <c r="D87" s="34" t="s">
+      <c r="D87" s="30" t="s">
         <v>133</v>
       </c>
-      <c r="E87" s="34" t="s">
+      <c r="E87" s="30" t="s">
         <v>134</v>
       </c>
-      <c r="F87" s="34" t="s">
+      <c r="F87" s="30" t="s">
         <v>135</v>
       </c>
-      <c r="G87" s="34" t="s">
+      <c r="G87" s="30" t="s">
         <v>136</v>
       </c>
-      <c r="H87" s="33" t="s">
+      <c r="H87" s="29" t="s">
         <v>153</v>
       </c>
-      <c r="I87" s="34" t="s">
+      <c r="I87" s="30" t="s">
         <v>156</v>
       </c>
-      <c r="J87" s="34" t="s">
+      <c r="J87" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="K87" s="33" t="s">
+      <c r="K87" s="29" t="s">
         <v>143</v>
       </c>
-      <c r="L87" s="21"/>
+      <c r="L87" s="17"/>
     </row>
     <row r="88" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B88" s="27">
+      <c r="B88" s="23">
         <v>1990</v>
       </c>
-      <c r="C88" s="23">
-        <v>0</v>
-      </c>
-      <c r="D88" s="23">
-        <v>0</v>
-      </c>
-      <c r="E88" s="23">
-        <v>0</v>
-      </c>
-      <c r="F88" s="23">
-        <v>0</v>
-      </c>
-      <c r="G88" s="23">
-        <v>0</v>
-      </c>
-      <c r="H88" s="23">
-        <v>0</v>
-      </c>
-      <c r="I88" s="23">
-        <v>0</v>
-      </c>
-      <c r="J88" s="23">
-        <v>0</v>
-      </c>
-      <c r="K88" s="23">
-        <v>0</v>
-      </c>
-      <c r="L88" s="31"/>
+      <c r="C88" s="19">
+        <v>0</v>
+      </c>
+      <c r="D88" s="19">
+        <v>0</v>
+      </c>
+      <c r="E88" s="19">
+        <v>0</v>
+      </c>
+      <c r="F88" s="19">
+        <v>0</v>
+      </c>
+      <c r="G88" s="19">
+        <v>0</v>
+      </c>
+      <c r="H88" s="19">
+        <v>0</v>
+      </c>
+      <c r="I88" s="19">
+        <v>0</v>
+      </c>
+      <c r="J88" s="19">
+        <v>0</v>
+      </c>
+      <c r="K88" s="19">
+        <v>0</v>
+      </c>
+      <c r="L88" s="27"/>
     </row>
     <row r="89" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B89" s="27">
+      <c r="B89" s="23">
         <v>1995</v>
       </c>
-      <c r="C89" s="23">
-        <v>0</v>
-      </c>
-      <c r="D89" s="23">
-        <v>0</v>
-      </c>
-      <c r="E89" s="23">
-        <v>0</v>
-      </c>
-      <c r="F89" s="23">
-        <v>0</v>
-      </c>
-      <c r="G89" s="23">
-        <v>0</v>
-      </c>
-      <c r="H89" s="23">
-        <v>0</v>
-      </c>
-      <c r="I89" s="23">
-        <v>0</v>
-      </c>
-      <c r="J89" s="23">
-        <v>0</v>
-      </c>
-      <c r="K89" s="23">
-        <v>0</v>
-      </c>
-      <c r="L89" s="24"/>
+      <c r="C89" s="19">
+        <v>0</v>
+      </c>
+      <c r="D89" s="19">
+        <v>0</v>
+      </c>
+      <c r="E89" s="19">
+        <v>0</v>
+      </c>
+      <c r="F89" s="19">
+        <v>0</v>
+      </c>
+      <c r="G89" s="19">
+        <v>0</v>
+      </c>
+      <c r="H89" s="19">
+        <v>0</v>
+      </c>
+      <c r="I89" s="19">
+        <v>0</v>
+      </c>
+      <c r="J89" s="19">
+        <v>0</v>
+      </c>
+      <c r="K89" s="19">
+        <v>0</v>
+      </c>
+      <c r="L89" s="20"/>
     </row>
     <row r="90" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B90" s="27">
+      <c r="B90" s="23">
         <v>2000</v>
       </c>
-      <c r="C90" s="23">
+      <c r="C90" s="19">
         <v>0.1</v>
       </c>
-      <c r="D90" s="23">
-        <v>0</v>
-      </c>
-      <c r="E90" s="23">
-        <v>0</v>
-      </c>
-      <c r="F90" s="23">
+      <c r="D90" s="19">
+        <v>0</v>
+      </c>
+      <c r="E90" s="19">
+        <v>0</v>
+      </c>
+      <c r="F90" s="19">
         <v>0.1</v>
       </c>
-      <c r="G90" s="23">
+      <c r="G90" s="19">
         <v>0.1</v>
       </c>
-      <c r="H90" s="23">
-        <v>0</v>
-      </c>
-      <c r="I90" s="23">
+      <c r="H90" s="19">
+        <v>0</v>
+      </c>
+      <c r="I90" s="19">
         <v>0.4</v>
       </c>
-      <c r="J90" s="23">
+      <c r="J90" s="19">
         <v>0.1</v>
       </c>
-      <c r="K90" s="23">
+      <c r="K90" s="19">
         <v>0.3</v>
       </c>
-      <c r="L90" s="31"/>
+      <c r="L90" s="27"/>
     </row>
     <row r="91" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B91" s="27">
+      <c r="B91" s="23">
         <v>2005</v>
       </c>
-      <c r="C91" s="23">
+      <c r="C91" s="19">
         <v>0.2</v>
       </c>
-      <c r="D91" s="23">
+      <c r="D91" s="19">
         <v>0.1</v>
       </c>
-      <c r="E91" s="23">
+      <c r="E91" s="19">
         <v>0.1</v>
       </c>
-      <c r="F91" s="23">
+      <c r="F91" s="19">
         <v>0.1</v>
       </c>
-      <c r="G91" s="23">
+      <c r="G91" s="19">
         <v>0.1</v>
       </c>
-      <c r="H91" s="23">
+      <c r="H91" s="19">
         <v>0.1</v>
       </c>
-      <c r="I91" s="23">
+      <c r="I91" s="19">
         <v>0.9</v>
       </c>
-      <c r="J91" s="23">
+      <c r="J91" s="19">
         <v>0.3</v>
       </c>
-      <c r="K91" s="23">
+      <c r="K91" s="19">
         <v>0.7</v>
       </c>
-      <c r="L91" s="24"/>
+      <c r="L91" s="20"/>
     </row>
     <row r="92" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B92" s="27">
+      <c r="B92" s="23">
         <v>2010</v>
       </c>
-      <c r="C92" s="23">
+      <c r="C92" s="19">
         <v>0.5</v>
       </c>
-      <c r="D92" s="23">
+      <c r="D92" s="19">
         <v>0.1</v>
       </c>
-      <c r="E92" s="23">
+      <c r="E92" s="19">
         <v>0.2</v>
       </c>
-      <c r="F92" s="23">
+      <c r="F92" s="19">
         <v>0.3</v>
       </c>
-      <c r="G92" s="23">
+      <c r="G92" s="19">
         <v>0.2</v>
       </c>
-      <c r="H92" s="23">
+      <c r="H92" s="19">
         <v>0.2</v>
       </c>
-      <c r="I92" s="23">
+      <c r="I92" s="19">
         <v>1.8</v>
       </c>
-      <c r="J92" s="23">
+      <c r="J92" s="19">
         <v>1.2</v>
       </c>
-      <c r="K92" s="23">
+      <c r="K92" s="19">
         <v>1.6</v>
       </c>
-      <c r="L92" s="31"/>
+      <c r="L92" s="27"/>
     </row>
     <row r="93" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B93" s="27">
+      <c r="B93" s="23">
         <v>2015</v>
       </c>
-      <c r="C93" s="23">
+      <c r="C93" s="19">
         <v>2.2000000000000002</v>
       </c>
-      <c r="D93" s="23">
+      <c r="D93" s="19">
         <v>0.6</v>
       </c>
-      <c r="E93" s="23">
+      <c r="E93" s="19">
         <v>1.1000000000000001</v>
       </c>
-      <c r="F93" s="23">
+      <c r="F93" s="19">
         <v>1.5</v>
       </c>
-      <c r="G93" s="23">
+      <c r="G93" s="19">
         <v>1</v>
       </c>
-      <c r="H93" s="23">
+      <c r="H93" s="19">
         <v>1</v>
       </c>
-      <c r="I93" s="23">
+      <c r="I93" s="19">
         <v>8.9</v>
       </c>
-      <c r="J93" s="23">
+      <c r="J93" s="19">
         <v>5.5</v>
       </c>
-      <c r="K93" s="23">
+      <c r="K93" s="19">
         <v>8</v>
       </c>
-      <c r="L93" s="31"/>
+      <c r="L93" s="27"/>
     </row>
     <row r="94" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B94" s="27">
+      <c r="B94" s="23">
         <v>2019</v>
       </c>
-      <c r="C94" s="23">
+      <c r="C94" s="19">
         <v>3</v>
       </c>
-      <c r="D94" s="23">
+      <c r="D94" s="19">
         <v>0.8</v>
       </c>
-      <c r="E94" s="23">
+      <c r="E94" s="19">
         <v>1.3</v>
       </c>
-      <c r="F94" s="23">
+      <c r="F94" s="19">
         <v>2.1</v>
       </c>
-      <c r="G94" s="23">
+      <c r="G94" s="19">
         <v>1.3</v>
       </c>
-      <c r="H94" s="23">
+      <c r="H94" s="19">
         <v>1.3</v>
       </c>
-      <c r="I94" s="23">
+      <c r="I94" s="19">
         <v>12.1</v>
       </c>
-      <c r="J94" s="23">
+      <c r="J94" s="19">
         <v>7</v>
       </c>
-      <c r="K94" s="23">
+      <c r="K94" s="19">
         <v>10.8</v>
       </c>
-      <c r="L94" s="24"/>
+      <c r="L94" s="20"/>
     </row>
     <row r="95" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B95" s="27">
+      <c r="B95" s="23">
         <v>2020</v>
       </c>
-      <c r="C95" s="23">
+      <c r="C95" s="19">
         <v>3</v>
       </c>
-      <c r="D95" s="23">
+      <c r="D95" s="19">
         <v>0.8</v>
       </c>
-      <c r="E95" s="23">
+      <c r="E95" s="19">
         <v>1.4</v>
       </c>
-      <c r="F95" s="23">
+      <c r="F95" s="19">
         <v>2.1</v>
       </c>
-      <c r="G95" s="23">
+      <c r="G95" s="19">
         <v>1.3</v>
       </c>
-      <c r="H95" s="23">
+      <c r="H95" s="19">
         <v>1.3</v>
       </c>
-      <c r="I95" s="23">
+      <c r="I95" s="19">
         <v>11.9</v>
       </c>
-      <c r="J95" s="23">
+      <c r="J95" s="19">
         <v>6.9</v>
       </c>
-      <c r="K95" s="23">
+      <c r="K95" s="19">
         <v>10.6</v>
       </c>
-      <c r="L95" s="31"/>
+      <c r="L95" s="27"/>
     </row>
     <row r="96" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B96" s="27">
+      <c r="B96" s="23">
         <v>2021</v>
       </c>
-      <c r="C96" s="23">
+      <c r="C96" s="19">
         <v>2.9</v>
       </c>
-      <c r="D96" s="23">
+      <c r="D96" s="19">
         <v>0.8</v>
       </c>
-      <c r="E96" s="23">
+      <c r="E96" s="19">
         <v>1.3</v>
       </c>
-      <c r="F96" s="23">
+      <c r="F96" s="19">
         <v>2</v>
       </c>
-      <c r="G96" s="23">
+      <c r="G96" s="19">
         <v>1.3</v>
       </c>
-      <c r="H96" s="23">
+      <c r="H96" s="19">
         <v>1.3</v>
       </c>
-      <c r="I96" s="23">
+      <c r="I96" s="19">
         <v>11.3</v>
       </c>
-      <c r="J96" s="23">
+      <c r="J96" s="19">
         <v>6.6</v>
       </c>
-      <c r="K96" s="23">
+      <c r="K96" s="19">
         <v>10.1</v>
       </c>
-      <c r="L96" s="24"/>
+      <c r="L96" s="20"/>
     </row>
     <row r="97" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B97" s="39" t="s">
+      <c r="B97" s="35" t="s">
         <v>163</v>
       </c>
-      <c r="C97" s="40">
+      <c r="C97" s="36">
         <f>AVERAGE(C93:C95)</f>
         <v>2.7333333333333329</v>
       </c>
-      <c r="D97" s="40">
+      <c r="D97" s="36">
         <f t="shared" ref="D97:K97" si="20">AVERAGE(D93:D95)</f>
         <v>0.73333333333333339</v>
       </c>
-      <c r="E97" s="40">
+      <c r="E97" s="36">
         <f t="shared" si="20"/>
         <v>1.2666666666666668</v>
       </c>
-      <c r="F97" s="40">
+      <c r="F97" s="36">
         <f t="shared" si="20"/>
         <v>1.9000000000000001</v>
       </c>
-      <c r="G97" s="40">
+      <c r="G97" s="36">
         <f t="shared" si="20"/>
         <v>1.2</v>
       </c>
-      <c r="H97" s="40">
+      <c r="H97" s="36">
         <f t="shared" si="20"/>
         <v>1.2</v>
       </c>
-      <c r="I97" s="40">
+      <c r="I97" s="36">
         <f t="shared" si="20"/>
         <v>10.966666666666667</v>
       </c>
-      <c r="J97" s="40">
+      <c r="J97" s="36">
         <f t="shared" si="20"/>
         <v>6.4666666666666659</v>
       </c>
-      <c r="K97" s="40">
+      <c r="K97" s="36">
         <f t="shared" si="20"/>
         <v>9.7999999999999989</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B19:M19"/>
+    <mergeCell ref="B71:M71"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:K72"/>
+    <mergeCell ref="B85:L85"/>
     <mergeCell ref="B86:B87"/>
     <mergeCell ref="C86:K86"/>
     <mergeCell ref="B45:P45"/>
     <mergeCell ref="B58:N58"/>
     <mergeCell ref="B32:M32"/>
-    <mergeCell ref="B19:M19"/>
-    <mergeCell ref="B71:M71"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:K72"/>
-    <mergeCell ref="B85:L85"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data/default/ManureMgmt.xlsx
+++ b/data/default/ManureMgmt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jnka0003\Git repos\CIBUSmod\data\default\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E10BFD5-DF70-4A22-BAE4-C5B0B3E77FC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CCE5617-CD6F-4CE5-9E2A-5E848FF4E913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="references" sheetId="2" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1671" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1717" uniqueCount="216">
   <si>
     <t>value</t>
   </si>
@@ -550,9 +550,6 @@
     <t>Swedish IIR 2023 Table 5-8</t>
   </si>
   <si>
-    <t>Swedish IIR 2023 Table 5-11</t>
-  </si>
-  <si>
     <t>Swedish IIR 2023 Table 5-12</t>
   </si>
   <si>
@@ -671,6 +668,21 @@
   </si>
   <si>
     <t>OBS. Fel i källtabell (står 0,25% där)</t>
+  </si>
+  <si>
+    <t>"loose housing"</t>
+  </si>
+  <si>
+    <t>Swedish IIR 2025 Table 5-11</t>
+  </si>
+  <si>
+    <t>typo in source table</t>
+  </si>
+  <si>
+    <t>typo in source table "same as liquid"</t>
+  </si>
+  <si>
+    <t>"floor system"</t>
   </si>
 </sst>
 </file>
@@ -1432,26 +1444,8 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="10"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="10"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="10"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1467,6 +1461,24 @@
     </xf>
     <xf numFmtId="0" fontId="25" fillId="35" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="9"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="10"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="10"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="10"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1815,7 +1827,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O322"/>
+  <dimension ref="A1:O327"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
@@ -1844,7 +1856,7 @@
         <v>28</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>110</v>
@@ -1988,7 +2000,7 @@
         <v>3</v>
       </c>
       <c r="G6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K6" t="s">
         <v>14</v>
@@ -2123,7 +2135,7 @@
         <v>3</v>
       </c>
       <c r="G11" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K11" t="s">
         <v>14</v>
@@ -2246,7 +2258,7 @@
         <v>9</v>
       </c>
       <c r="G16" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K16" t="s">
         <v>14</v>
@@ -2366,7 +2378,7 @@
         <v>8</v>
       </c>
       <c r="G21" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K21" t="s">
         <v>14</v>
@@ -2411,7 +2423,7 @@
         <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G23" t="s">
         <v>16</v>
@@ -2435,7 +2447,7 @@
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G24" t="s">
         <v>17</v>
@@ -2459,7 +2471,7 @@
         <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G25" t="s">
         <v>18</v>
@@ -2483,10 +2495,10 @@
         <v>1</v>
       </c>
       <c r="E26" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G26" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K26" t="s">
         <v>14</v>
@@ -2507,7 +2519,7 @@
         <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G27" t="s">
         <v>166</v>
@@ -2594,7 +2606,7 @@
         <v>48</v>
       </c>
       <c r="G31" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K31" t="s">
         <v>14</v>
@@ -2699,7 +2711,7 @@
         <v>54</v>
       </c>
       <c r="G36" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K36" t="s">
         <v>14</v>
@@ -2804,7 +2816,7 @@
         <v>35</v>
       </c>
       <c r="G41" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K41" t="s">
         <v>14</v>
@@ -2846,7 +2858,7 @@
         <v>35</v>
       </c>
       <c r="E43" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G43" t="s">
         <v>16</v>
@@ -2870,7 +2882,7 @@
         <v>35</v>
       </c>
       <c r="E44" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G44" t="s">
         <v>17</v>
@@ -2894,7 +2906,7 @@
         <v>35</v>
       </c>
       <c r="E45" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G45" t="s">
         <v>18</v>
@@ -2918,10 +2930,10 @@
         <v>35</v>
       </c>
       <c r="E46" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G46" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K46" t="s">
         <v>14</v>
@@ -2942,7 +2954,7 @@
         <v>35</v>
       </c>
       <c r="E47" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G47" t="s">
         <v>166</v>
@@ -3029,7 +3041,7 @@
         <v>45</v>
       </c>
       <c r="G51" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K51" t="s">
         <v>14</v>
@@ -3146,7 +3158,7 @@
         <v>47</v>
       </c>
       <c r="G56" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K56" t="s">
         <v>14</v>
@@ -3188,17 +3200,17 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="44" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="44" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="K61" s="6" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L61" s="6">
         <v>0</v>
@@ -3221,10 +3233,10 @@
         <v>3</v>
       </c>
       <c r="G62" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K62" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L62" s="37">
         <f>INDEX(MMS!$P$16:$Z$16,MATCH(A62&amp;C62&amp;E62,MMS!$P$8:$Z$8,0))</f>
@@ -3234,7 +3246,7 @@
         <v>15</v>
       </c>
       <c r="N62" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="O62" t="s">
         <v>169</v>
@@ -3251,10 +3263,10 @@
         <v>3</v>
       </c>
       <c r="G63" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K63" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L63" s="37">
         <f>INDEX(MMS!$P$16:$Z$16,MATCH(A63&amp;C63&amp;E63,MMS!$P$8:$Z$8,0))</f>
@@ -3272,10 +3284,10 @@
         <v>9</v>
       </c>
       <c r="G64" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K64" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L64" s="37">
         <f>INDEX(MMS!$P$16:$Z$16,MATCH(A64&amp;C64&amp;E64,MMS!$P$8:$Z$8,0))</f>
@@ -3293,10 +3305,10 @@
         <v>8</v>
       </c>
       <c r="G65" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K65" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L65" s="37">
         <f>INDEX(MMS!$P$16:$Z$16,MATCH(A65&amp;C65&amp;E65,MMS!$P$8:$Z$8,0))</f>
@@ -3311,13 +3323,13 @@
         <v>1</v>
       </c>
       <c r="E66" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G66" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K66" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L66" s="37">
         <f>INDEX(MMS!$P$16:$Z$16,MATCH(A66&amp;C66&amp;E66,MMS!$P$8:$Z$8,0))</f>
@@ -3332,10 +3344,10 @@
         <v>48</v>
       </c>
       <c r="G67" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K67" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L67" s="37">
         <f>INDEX(MMS!$P$16:$Z$16,MATCH(A67&amp;C67&amp;E67,MMS!$P$8:$Z$8,0))</f>
@@ -3350,10 +3362,10 @@
         <v>54</v>
       </c>
       <c r="G68" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K68" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L68" s="37">
         <f>INDEX(MMS!$P$16:$Z$16,MATCH(A68&amp;C68&amp;E68,MMS!$P$8:$Z$8,0))</f>
@@ -3368,10 +3380,10 @@
         <v>35</v>
       </c>
       <c r="G69" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K69" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L69" s="37">
         <f>INDEX(MMS!$P$16:$Z$16,MATCH(A69&amp;C69&amp;E69,MMS!$P$8:$Z$8,0))</f>
@@ -3386,13 +3398,13 @@
         <v>35</v>
       </c>
       <c r="E70" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G70" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K70" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L70" s="37">
         <f>INDEX(MMS!$P$16:$Z$16,MATCH(A70&amp;C70&amp;E70,MMS!$P$8:$Z$8,0))</f>
@@ -3407,10 +3419,10 @@
         <v>45</v>
       </c>
       <c r="G71" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K71" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L71" s="37">
         <f>INDEX(MMS!$P$16:$Z$16,MATCH(A71&amp;C71&amp;E71,MMS!$P$8:$Z$8,0))</f>
@@ -3428,10 +3440,10 @@
         <v>47</v>
       </c>
       <c r="G72" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K72" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L72" s="37">
         <f>INDEX(MMS!$P$16:$Z$16,MATCH(A72&amp;C72&amp;E72,MMS!$P$8:$Z$8,0))</f>
@@ -3589,7 +3601,7 @@
         <v>1</v>
       </c>
       <c r="E84" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="J84" t="s">
         <v>121</v>
@@ -4133,7 +4145,7 @@
     </row>
     <row r="120" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G120" s="5" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K120" t="s">
         <v>56</v>
@@ -4165,7 +4177,7 @@
         <v>57</v>
       </c>
       <c r="N121" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="O121" t="s">
         <v>66</v>
@@ -4188,7 +4200,7 @@
         <v>57</v>
       </c>
       <c r="N122" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O122" t="s">
         <v>66</v>
@@ -4211,7 +4223,7 @@
         <v>57</v>
       </c>
       <c r="N123" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="O123" t="s">
         <v>66</v>
@@ -4271,7 +4283,7 @@
     </row>
     <row r="129" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
@@ -4398,7 +4410,7 @@
         <v>100</v>
       </c>
       <c r="O135" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="136" spans="1:15" x14ac:dyDescent="0.25">
@@ -4416,7 +4428,7 @@
         <v>101</v>
       </c>
       <c r="O136" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="137" spans="1:15" x14ac:dyDescent="0.25">
@@ -4436,7 +4448,7 @@
         <v>5</v>
       </c>
       <c r="N137" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="O137" t="s">
         <v>7</v>
@@ -4481,7 +4493,7 @@
         <v>45</v>
       </c>
       <c r="E140" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K140" t="s">
         <v>4</v>
@@ -4501,7 +4513,7 @@
         <v>45</v>
       </c>
       <c r="E141" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K141" t="s">
         <v>97</v>
@@ -4525,7 +4537,7 @@
         <v>45</v>
       </c>
       <c r="E142" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="K142" t="s">
         <v>98</v>
@@ -4617,7 +4629,7 @@
         <v>45</v>
       </c>
       <c r="E146" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K146" t="s">
         <v>4</v>
@@ -4637,7 +4649,7 @@
         <v>45</v>
       </c>
       <c r="E147" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K147" t="s">
         <v>97</v>
@@ -4653,7 +4665,7 @@
         <v>102</v>
       </c>
       <c r="O147" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="148" spans="1:15" x14ac:dyDescent="0.25">
@@ -4661,7 +4673,7 @@
         <v>45</v>
       </c>
       <c r="E148" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="K148" t="s">
         <v>98</v>
@@ -4677,7 +4689,7 @@
         <v>103</v>
       </c>
       <c r="O148" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="149" spans="1:15" x14ac:dyDescent="0.25">
@@ -4793,7 +4805,7 @@
         <v>1</v>
       </c>
       <c r="D156" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G156" s="5"/>
       <c r="K156" t="s">
@@ -4817,7 +4829,7 @@
         <v>1</v>
       </c>
       <c r="D157" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G157" s="5"/>
       <c r="K157" t="s">
@@ -4838,7 +4850,7 @@
         <v>1</v>
       </c>
       <c r="D158" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="G158" s="5"/>
       <c r="K158" t="s">
@@ -4859,7 +4871,7 @@
         <v>1</v>
       </c>
       <c r="D159" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G159" s="5"/>
       <c r="K159" s="45" t="s">
@@ -4878,7 +4890,7 @@
         <v>1</v>
       </c>
       <c r="D160" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G160" s="5"/>
       <c r="K160" s="45" t="s">
@@ -4897,7 +4909,7 @@
         <v>1</v>
       </c>
       <c r="D161" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="G161" s="5"/>
       <c r="K161" s="45" t="s">
@@ -4916,7 +4928,7 @@
         <v>1</v>
       </c>
       <c r="D162" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G162" s="5"/>
       <c r="K162" s="45" t="s">
@@ -4935,7 +4947,7 @@
         <v>1</v>
       </c>
       <c r="D163" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G163" s="5"/>
       <c r="K163" s="45" t="s">
@@ -4954,7 +4966,7 @@
         <v>1</v>
       </c>
       <c r="D164" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G164" s="5"/>
       <c r="K164" s="45" t="s">
@@ -4973,7 +4985,7 @@
         <v>1</v>
       </c>
       <c r="D165" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G165" s="5"/>
       <c r="K165" s="45" t="s">
@@ -4992,7 +5004,7 @@
         <v>1</v>
       </c>
       <c r="D166" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G166" s="5"/>
       <c r="K166" s="45" t="s">
@@ -5011,7 +5023,7 @@
         <v>1</v>
       </c>
       <c r="D167" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="G167" s="5"/>
       <c r="K167" s="45" t="s">
@@ -5030,7 +5042,7 @@
         <v>1</v>
       </c>
       <c r="D168" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G168" s="5"/>
       <c r="K168" s="45" t="s">
@@ -5049,7 +5061,7 @@
         <v>1</v>
       </c>
       <c r="D169" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G169" s="5"/>
       <c r="K169" s="45" t="s">
@@ -5068,7 +5080,7 @@
         <v>1</v>
       </c>
       <c r="D170" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="G170" s="5"/>
       <c r="K170" s="45" t="s">
@@ -5559,7 +5571,7 @@
         <v>87</v>
       </c>
       <c r="O195" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="196" spans="1:15" x14ac:dyDescent="0.25">
@@ -5580,7 +5592,7 @@
         <v>79</v>
       </c>
       <c r="O196" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="197" spans="1:15" x14ac:dyDescent="0.25">
@@ -5601,7 +5613,7 @@
         <v>80</v>
       </c>
       <c r="O197" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="198" spans="1:15" x14ac:dyDescent="0.25">
@@ -5624,7 +5636,7 @@
         <v>88</v>
       </c>
       <c r="O198" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="199" spans="1:15" x14ac:dyDescent="0.25">
@@ -5644,7 +5656,7 @@
         <v>79</v>
       </c>
       <c r="O199" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="200" spans="1:15" x14ac:dyDescent="0.25">
@@ -5664,7 +5676,7 @@
         <v>80</v>
       </c>
       <c r="O200" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="201" spans="1:15" x14ac:dyDescent="0.25">
@@ -5687,7 +5699,7 @@
         <v>89</v>
       </c>
       <c r="O201" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="202" spans="1:15" x14ac:dyDescent="0.25">
@@ -5707,7 +5719,7 @@
         <v>79</v>
       </c>
       <c r="O202" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="203" spans="1:15" x14ac:dyDescent="0.25">
@@ -5727,7 +5739,7 @@
         <v>80</v>
       </c>
       <c r="O203" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="204" spans="1:15" x14ac:dyDescent="0.25">
@@ -5751,7 +5763,7 @@
         <v>90</v>
       </c>
       <c r="O204" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="205" spans="1:15" x14ac:dyDescent="0.25">
@@ -5772,7 +5784,7 @@
         <v>79</v>
       </c>
       <c r="O205" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="206" spans="1:15" x14ac:dyDescent="0.25">
@@ -5793,7 +5805,7 @@
         <v>80</v>
       </c>
       <c r="O206" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="207" spans="1:15" x14ac:dyDescent="0.25">
@@ -5814,10 +5826,10 @@
         <v>78</v>
       </c>
       <c r="N207" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="O207" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="208" spans="1:15" x14ac:dyDescent="0.25">
@@ -5838,7 +5850,7 @@
         <v>79</v>
       </c>
       <c r="O208" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="209" spans="1:15" x14ac:dyDescent="0.25">
@@ -5859,7 +5871,7 @@
         <v>80</v>
       </c>
       <c r="O209" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="210" spans="1:15" x14ac:dyDescent="0.25">
@@ -5883,7 +5895,7 @@
         <v>91</v>
       </c>
       <c r="O210" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="211" spans="1:15" x14ac:dyDescent="0.25">
@@ -5904,7 +5916,7 @@
         <v>79</v>
       </c>
       <c r="O211" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="212" spans="1:15" x14ac:dyDescent="0.25">
@@ -5925,7 +5937,7 @@
         <v>80</v>
       </c>
       <c r="O212" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="213" spans="1:15" x14ac:dyDescent="0.25">
@@ -6034,7 +6046,7 @@
     </row>
     <row r="221" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A221" s="7" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="B221" s="8"/>
       <c r="C221" s="8"/>
@@ -6056,7 +6068,7 @@
     </row>
     <row r="223" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="G223" s="5"/>
     </row>
@@ -6090,7 +6102,7 @@
         <v>49</v>
       </c>
       <c r="O225" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="226" spans="1:15" x14ac:dyDescent="0.25">
@@ -6116,7 +6128,7 @@
         <v>49</v>
       </c>
       <c r="O226" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="227" spans="1:15" x14ac:dyDescent="0.25">
@@ -6142,7 +6154,7 @@
         <v>49</v>
       </c>
       <c r="O227" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="228" spans="1:15" x14ac:dyDescent="0.25">
@@ -6165,7 +6177,7 @@
         <v>49</v>
       </c>
       <c r="O228" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="229" spans="1:15" x14ac:dyDescent="0.25">
@@ -6188,7 +6200,7 @@
         <v>49</v>
       </c>
       <c r="O229" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="230" spans="1:15" x14ac:dyDescent="0.25">
@@ -6196,7 +6208,7 @@
         <v>1</v>
       </c>
       <c r="E230" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G230" t="s">
         <v>17</v>
@@ -6211,7 +6223,7 @@
         <v>49</v>
       </c>
       <c r="O230" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="231" spans="1:15" x14ac:dyDescent="0.25">
@@ -6231,7 +6243,7 @@
         <v>49</v>
       </c>
       <c r="O231" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="232" spans="1:15" x14ac:dyDescent="0.25">
@@ -6239,7 +6251,7 @@
         <v>1</v>
       </c>
       <c r="G232" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K232" t="s">
         <v>25</v>
@@ -6251,7 +6263,7 @@
         <v>49</v>
       </c>
       <c r="O232" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="233" spans="1:15" x14ac:dyDescent="0.25">
@@ -6275,7 +6287,7 @@
       </c>
       <c r="N233" s="1"/>
       <c r="O233" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="234" spans="1:15" x14ac:dyDescent="0.25">
@@ -6304,7 +6316,7 @@
       </c>
       <c r="N234" s="1"/>
       <c r="O234" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="235" spans="1:15" x14ac:dyDescent="0.25">
@@ -6333,7 +6345,7 @@
       </c>
       <c r="N235" s="1"/>
       <c r="O235" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="236" spans="1:15" x14ac:dyDescent="0.25">
@@ -6362,7 +6374,7 @@
       </c>
       <c r="N236" s="1"/>
       <c r="O236" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="237" spans="1:15" x14ac:dyDescent="0.25">
@@ -6391,7 +6403,7 @@
       </c>
       <c r="N237" s="1"/>
       <c r="O237" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="238" spans="1:15" x14ac:dyDescent="0.25">
@@ -6420,7 +6432,7 @@
       </c>
       <c r="N238" s="1"/>
       <c r="O238" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="239" spans="1:15" x14ac:dyDescent="0.25">
@@ -6449,7 +6461,7 @@
       </c>
       <c r="N239" s="1"/>
       <c r="O239" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="240" spans="1:15" x14ac:dyDescent="0.25">
@@ -6478,7 +6490,7 @@
       </c>
       <c r="N240" s="1"/>
       <c r="O240" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="241" spans="1:15" x14ac:dyDescent="0.25">
@@ -6507,7 +6519,7 @@
       </c>
       <c r="N241" s="1"/>
       <c r="O241" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
     </row>
     <row r="242" spans="1:15" x14ac:dyDescent="0.25">
@@ -6527,7 +6539,7 @@
         <v>49</v>
       </c>
       <c r="O242" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="243" spans="1:15" x14ac:dyDescent="0.25">
@@ -6547,7 +6559,7 @@
         <v>49</v>
       </c>
       <c r="O243" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="244" spans="1:15" x14ac:dyDescent="0.25">
@@ -6567,7 +6579,7 @@
         <v>49</v>
       </c>
       <c r="O244" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="245" spans="1:15" x14ac:dyDescent="0.25">
@@ -6575,7 +6587,7 @@
         <v>35</v>
       </c>
       <c r="G245" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="K245" t="s">
         <v>25</v>
@@ -6587,7 +6599,7 @@
         <v>49</v>
       </c>
       <c r="O245" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="246" spans="1:15" x14ac:dyDescent="0.25">
@@ -6616,7 +6628,7 @@
       </c>
       <c r="N246" s="1"/>
       <c r="O246" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="247" spans="1:15" x14ac:dyDescent="0.25">
@@ -6645,7 +6657,7 @@
       </c>
       <c r="N247" s="1"/>
       <c r="O247" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="248" spans="1:15" x14ac:dyDescent="0.25">
@@ -6674,7 +6686,7 @@
       </c>
       <c r="N248" s="1"/>
       <c r="O248" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="249" spans="1:15" x14ac:dyDescent="0.25">
@@ -6697,7 +6709,7 @@
         <v>49</v>
       </c>
       <c r="O249" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="250" spans="1:15" x14ac:dyDescent="0.25">
@@ -6720,7 +6732,7 @@
         <v>49</v>
       </c>
       <c r="O250" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="251" spans="1:15" x14ac:dyDescent="0.25">
@@ -6743,7 +6755,7 @@
         <v>49</v>
       </c>
       <c r="O251" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="252" spans="1:15" x14ac:dyDescent="0.25">
@@ -6773,7 +6785,7 @@
     </row>
     <row r="255" spans="1:15" x14ac:dyDescent="0.25">
       <c r="H255" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I255" s="6"/>
       <c r="J255" s="6"/>
@@ -6788,7 +6800,7 @@
     </row>
     <row r="256" spans="1:15" x14ac:dyDescent="0.25">
       <c r="H256" s="6" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I256" s="6"/>
       <c r="J256" s="6"/>
@@ -6807,7 +6819,7 @@
       <c r="I257" s="6"/>
       <c r="J257" s="6"/>
       <c r="K257" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L257" s="6">
         <v>0</v>
@@ -6829,7 +6841,7 @@
         <v>16</v>
       </c>
       <c r="H259" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I259" t="s">
         <v>19</v>
@@ -6838,13 +6850,16 @@
         <v>20</v>
       </c>
       <c r="L259">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M259" t="s">
         <v>49</v>
       </c>
+      <c r="N259" t="s">
+        <v>211</v>
+      </c>
       <c r="O259" t="s">
-        <v>171</v>
+        <v>212</v>
       </c>
     </row>
     <row r="260" spans="1:15" x14ac:dyDescent="0.25">
@@ -6855,7 +6870,7 @@
         <v>17</v>
       </c>
       <c r="H260" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I260" t="s">
         <v>19</v>
@@ -6870,7 +6885,7 @@
         <v>49</v>
       </c>
       <c r="O260" t="s">
-        <v>171</v>
+        <v>212</v>
       </c>
     </row>
     <row r="261" spans="1:15" x14ac:dyDescent="0.25">
@@ -6881,7 +6896,7 @@
         <v>18</v>
       </c>
       <c r="H261" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I261" t="s">
         <v>19</v>
@@ -6890,13 +6905,13 @@
         <v>20</v>
       </c>
       <c r="L261">
-        <v>20</v>
+        <v>7</v>
       </c>
       <c r="M261" t="s">
         <v>49</v>
       </c>
       <c r="O261" t="s">
-        <v>171</v>
+        <v>212</v>
       </c>
     </row>
     <row r="262" spans="1:15" x14ac:dyDescent="0.25">
@@ -6904,10 +6919,10 @@
         <v>1</v>
       </c>
       <c r="G262" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H262" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I262" t="s">
         <v>19</v>
@@ -6916,13 +6931,16 @@
         <v>20</v>
       </c>
       <c r="L262">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="M262" t="s">
         <v>49</v>
       </c>
+      <c r="N262" t="s">
+        <v>214</v>
+      </c>
       <c r="O262" t="s">
-        <v>171</v>
+        <v>212</v>
       </c>
     </row>
     <row r="263" spans="1:15" x14ac:dyDescent="0.25">
@@ -6933,7 +6951,7 @@
         <v>17</v>
       </c>
       <c r="H263" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I263" t="s">
         <v>19</v>
@@ -6949,7 +6967,7 @@
       </c>
       <c r="N263" s="1"/>
       <c r="O263" t="s">
-        <v>171</v>
+        <v>212</v>
       </c>
     </row>
     <row r="264" spans="1:15" x14ac:dyDescent="0.25">
@@ -6960,7 +6978,7 @@
         <v>18</v>
       </c>
       <c r="H264" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I264" t="s">
         <v>19</v>
@@ -6976,7 +6994,7 @@
       </c>
       <c r="N264" s="1"/>
       <c r="O264" t="s">
-        <v>171</v>
+        <v>212</v>
       </c>
     </row>
     <row r="265" spans="1:15" x14ac:dyDescent="0.25">
@@ -6987,7 +7005,7 @@
         <v>166</v>
       </c>
       <c r="H265" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I265" t="s">
         <v>19</v>
@@ -7003,7 +7021,7 @@
       </c>
       <c r="N265" s="1"/>
       <c r="O265" t="s">
-        <v>171</v>
+        <v>212</v>
       </c>
     </row>
     <row r="266" spans="1:15" x14ac:dyDescent="0.25">
@@ -7014,7 +7032,7 @@
         <v>17</v>
       </c>
       <c r="H266" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I266" t="s">
         <v>19</v>
@@ -7023,14 +7041,14 @@
         <v>20</v>
       </c>
       <c r="L266">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="M266" t="s">
         <v>49</v>
       </c>
       <c r="N266" s="1"/>
       <c r="O266" t="s">
-        <v>171</v>
+        <v>212</v>
       </c>
     </row>
     <row r="267" spans="1:15" x14ac:dyDescent="0.25">
@@ -7041,7 +7059,7 @@
         <v>18</v>
       </c>
       <c r="H267" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I267" t="s">
         <v>19</v>
@@ -7050,14 +7068,14 @@
         <v>20</v>
       </c>
       <c r="L267">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="M267" t="s">
         <v>49</v>
       </c>
       <c r="N267" s="1"/>
       <c r="O267" t="s">
-        <v>171</v>
+        <v>212</v>
       </c>
     </row>
     <row r="268" spans="1:15" x14ac:dyDescent="0.25">
@@ -7068,7 +7086,7 @@
         <v>16</v>
       </c>
       <c r="H268" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I268" t="s">
         <v>19</v>
@@ -7077,13 +7095,13 @@
         <v>20</v>
       </c>
       <c r="L268">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M268" t="s">
         <v>49</v>
       </c>
       <c r="O268" t="s">
-        <v>171</v>
+        <v>212</v>
       </c>
     </row>
     <row r="269" spans="1:15" x14ac:dyDescent="0.25">
@@ -7094,7 +7112,7 @@
         <v>17</v>
       </c>
       <c r="H269" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I269" t="s">
         <v>19</v>
@@ -7103,13 +7121,13 @@
         <v>20</v>
       </c>
       <c r="L269">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="M269" t="s">
         <v>49</v>
       </c>
       <c r="O269" t="s">
-        <v>171</v>
+        <v>212</v>
       </c>
     </row>
     <row r="270" spans="1:15" x14ac:dyDescent="0.25">
@@ -7120,7 +7138,7 @@
         <v>18</v>
       </c>
       <c r="H270" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I270" t="s">
         <v>19</v>
@@ -7129,13 +7147,16 @@
         <v>20</v>
       </c>
       <c r="L270">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="M270" t="s">
         <v>49</v>
       </c>
+      <c r="N270" t="s">
+        <v>213</v>
+      </c>
       <c r="O270" t="s">
-        <v>171</v>
+        <v>212</v>
       </c>
     </row>
     <row r="271" spans="1:15" x14ac:dyDescent="0.25">
@@ -7143,10 +7164,10 @@
         <v>35</v>
       </c>
       <c r="G271" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H271" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I271" t="s">
         <v>19</v>
@@ -7155,24 +7176,30 @@
         <v>20</v>
       </c>
       <c r="L271">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M271" t="s">
         <v>49</v>
       </c>
+      <c r="N271" t="s">
+        <v>214</v>
+      </c>
       <c r="O271" t="s">
-        <v>171</v>
+        <v>212</v>
       </c>
     </row>
     <row r="272" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
-        <v>45</v>
+        <v>35</v>
+      </c>
+      <c r="E272" t="s">
+        <v>41</v>
       </c>
       <c r="G272" t="s">
         <v>16</v>
       </c>
       <c r="H272" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I272" t="s">
         <v>19</v>
@@ -7181,24 +7208,27 @@
         <v>20</v>
       </c>
       <c r="L272">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M272" t="s">
         <v>49</v>
       </c>
       <c r="O272" t="s">
-        <v>171</v>
+        <v>212</v>
       </c>
     </row>
     <row r="273" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
-        <v>45</v>
+        <v>35</v>
+      </c>
+      <c r="E273" t="s">
+        <v>41</v>
       </c>
       <c r="G273" t="s">
         <v>17</v>
       </c>
       <c r="H273" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I273" t="s">
         <v>19</v>
@@ -7207,24 +7237,27 @@
         <v>20</v>
       </c>
       <c r="L273">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="M273" t="s">
         <v>49</v>
       </c>
       <c r="O273" t="s">
-        <v>171</v>
+        <v>212</v>
       </c>
     </row>
     <row r="274" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
-        <v>45</v>
+        <v>35</v>
+      </c>
+      <c r="E274" t="s">
+        <v>41</v>
       </c>
       <c r="G274" t="s">
         <v>18</v>
       </c>
       <c r="H274" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I274" t="s">
         <v>19</v>
@@ -7233,27 +7266,27 @@
         <v>20</v>
       </c>
       <c r="L274">
-        <v>35</v>
+        <v>6</v>
       </c>
       <c r="M274" t="s">
         <v>49</v>
       </c>
       <c r="O274" t="s">
-        <v>171</v>
+        <v>212</v>
       </c>
     </row>
     <row r="275" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="E275" t="s">
-        <v>205</v>
+        <v>41</v>
       </c>
       <c r="G275" t="s">
-        <v>18</v>
+        <v>173</v>
       </c>
       <c r="H275" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I275" t="s">
         <v>19</v>
@@ -7262,27 +7295,24 @@
         <v>20</v>
       </c>
       <c r="L275">
-        <v>20</v>
+        <v>6</v>
       </c>
       <c r="M275" t="s">
         <v>49</v>
       </c>
       <c r="O275" t="s">
-        <v>171</v>
+        <v>212</v>
       </c>
     </row>
     <row r="276" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>45</v>
       </c>
-      <c r="E276" t="s">
-        <v>47</v>
-      </c>
       <c r="G276" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="H276" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I276" t="s">
         <v>19</v>
@@ -7296,186 +7326,180 @@
       <c r="M276" t="s">
         <v>49</v>
       </c>
+      <c r="N276" t="s">
+        <v>215</v>
+      </c>
       <c r="O276" t="s">
-        <v>171</v>
+        <v>212</v>
       </c>
     </row>
     <row r="277" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A277" s="1"/>
-      <c r="B277" s="1"/>
-      <c r="C277" s="1"/>
-      <c r="D277" s="1"/>
-      <c r="E277" s="1"/>
-      <c r="F277" s="1"/>
-      <c r="G277" s="1"/>
-      <c r="H277" s="1"/>
-      <c r="I277" s="1"/>
-      <c r="J277" s="1"/>
-      <c r="K277" s="1"/>
-      <c r="L277" s="1"/>
-      <c r="M277" s="1"/>
-      <c r="N277" s="1"/>
+      <c r="A277" t="s">
+        <v>45</v>
+      </c>
+      <c r="G277" t="s">
+        <v>17</v>
+      </c>
+      <c r="H277" t="s">
+        <v>183</v>
+      </c>
+      <c r="I277" t="s">
+        <v>19</v>
+      </c>
+      <c r="K277" t="s">
+        <v>20</v>
+      </c>
+      <c r="L277">
+        <v>10</v>
+      </c>
+      <c r="M277" t="s">
+        <v>49</v>
+      </c>
+      <c r="N277" t="s">
+        <v>215</v>
+      </c>
+      <c r="O277" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="278" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="G278" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H278" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I278" t="s">
         <v>19</v>
       </c>
       <c r="K278" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L278">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="M278" t="s">
         <v>49</v>
       </c>
       <c r="O278" t="s">
-        <v>172</v>
+        <v>212</v>
       </c>
     </row>
     <row r="279" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
-        <v>1</v>
-      </c>
-      <c r="C279" t="s">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="E279" t="s">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="G279" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H279" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I279" t="s">
         <v>19</v>
       </c>
       <c r="K279" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L279">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="M279" t="s">
         <v>49</v>
       </c>
       <c r="O279" t="s">
-        <v>172</v>
+        <v>212</v>
       </c>
     </row>
     <row r="280" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
-        <v>1</v>
-      </c>
-      <c r="C280" t="s">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="E280" t="s">
-        <v>3</v>
+        <v>47</v>
       </c>
       <c r="G280" t="s">
         <v>17</v>
       </c>
       <c r="H280" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I280" t="s">
         <v>19</v>
       </c>
       <c r="K280" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L280">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="M280" t="s">
         <v>49</v>
       </c>
       <c r="O280" t="s">
-        <v>172</v>
+        <v>212</v>
       </c>
     </row>
     <row r="281" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A281" t="s">
-        <v>1</v>
+        <v>45</v>
       </c>
       <c r="E281" t="s">
-        <v>9</v>
+        <v>47</v>
       </c>
       <c r="G281" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H281" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I281" t="s">
         <v>19</v>
       </c>
       <c r="K281" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="L281">
-        <v>18</v>
+        <v>6</v>
       </c>
       <c r="M281" t="s">
         <v>49</v>
       </c>
       <c r="O281" t="s">
-        <v>172</v>
+        <v>212</v>
       </c>
     </row>
     <row r="282" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A282" t="s">
-        <v>1</v>
-      </c>
-      <c r="E282" t="s">
-        <v>8</v>
-      </c>
-      <c r="G282" t="s">
-        <v>17</v>
-      </c>
-      <c r="H282" t="s">
-        <v>184</v>
-      </c>
-      <c r="I282" t="s">
-        <v>19</v>
-      </c>
-      <c r="K282" t="s">
-        <v>21</v>
-      </c>
-      <c r="L282">
-        <v>18</v>
-      </c>
-      <c r="M282" t="s">
-        <v>49</v>
-      </c>
-      <c r="O282" t="s">
-        <v>172</v>
-      </c>
+      <c r="A282" s="1"/>
+      <c r="B282" s="1"/>
+      <c r="C282" s="1"/>
+      <c r="D282" s="1"/>
+      <c r="E282" s="1"/>
+      <c r="F282" s="1"/>
+      <c r="G282" s="1"/>
+      <c r="H282" s="1"/>
+      <c r="I282" s="1"/>
+      <c r="J282" s="1"/>
+      <c r="K282" s="1"/>
+      <c r="L282" s="1"/>
+      <c r="M282" s="1"/>
+      <c r="N282" s="1"/>
     </row>
     <row r="283" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>1</v>
       </c>
-      <c r="E283" t="s">
-        <v>196</v>
-      </c>
       <c r="G283" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H283" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I283" t="s">
         <v>19</v>
@@ -7484,24 +7508,30 @@
         <v>21</v>
       </c>
       <c r="L283">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="M283" t="s">
         <v>49</v>
       </c>
       <c r="O283" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="284" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>1</v>
       </c>
+      <c r="C284" t="s">
+        <v>2</v>
+      </c>
+      <c r="E284" t="s">
+        <v>3</v>
+      </c>
       <c r="G284" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H284" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I284" t="s">
         <v>19</v>
@@ -7510,24 +7540,30 @@
         <v>21</v>
       </c>
       <c r="L284">
-        <v>30</v>
+        <v>18</v>
       </c>
       <c r="M284" t="s">
         <v>49</v>
       </c>
       <c r="O284" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="285" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>1</v>
       </c>
+      <c r="C285" t="s">
+        <v>6</v>
+      </c>
+      <c r="E285" t="s">
+        <v>3</v>
+      </c>
       <c r="G285" t="s">
-        <v>174</v>
+        <v>17</v>
       </c>
       <c r="H285" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I285" t="s">
         <v>19</v>
@@ -7536,24 +7572,27 @@
         <v>21</v>
       </c>
       <c r="L285">
-        <v>2.75</v>
+        <v>17</v>
       </c>
       <c r="M285" t="s">
         <v>49</v>
       </c>
       <c r="O285" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="286" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
-        <v>54</v>
+        <v>1</v>
+      </c>
+      <c r="E286" t="s">
+        <v>9</v>
       </c>
       <c r="G286" t="s">
         <v>17</v>
       </c>
       <c r="H286" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I286" t="s">
         <v>19</v>
@@ -7562,25 +7601,27 @@
         <v>21</v>
       </c>
       <c r="L286">
-        <v>25</v>
+        <v>18</v>
       </c>
       <c r="M286" t="s">
         <v>49</v>
       </c>
-      <c r="N286" s="1"/>
       <c r="O286" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="287" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A287" t="s">
-        <v>54</v>
+        <v>1</v>
+      </c>
+      <c r="E287" t="s">
+        <v>8</v>
       </c>
       <c r="G287" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H287" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I287" t="s">
         <v>19</v>
@@ -7589,25 +7630,27 @@
         <v>21</v>
       </c>
       <c r="L287">
-        <v>33</v>
+        <v>18</v>
       </c>
       <c r="M287" t="s">
         <v>49</v>
       </c>
-      <c r="N287" s="1"/>
       <c r="O287" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="288" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
-        <v>54</v>
+        <v>1</v>
+      </c>
+      <c r="E288" t="s">
+        <v>195</v>
       </c>
       <c r="G288" t="s">
-        <v>166</v>
+        <v>17</v>
       </c>
       <c r="H288" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I288" t="s">
         <v>19</v>
@@ -7615,28 +7658,25 @@
       <c r="K288" t="s">
         <v>21</v>
       </c>
-      <c r="L288" s="5">
-        <v>25</v>
+      <c r="L288">
+        <v>17</v>
       </c>
       <c r="M288" t="s">
         <v>49</v>
       </c>
-      <c r="N288" s="5" t="s">
-        <v>211</v>
-      </c>
       <c r="O288" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="289" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="G289" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H289" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I289" t="s">
         <v>19</v>
@@ -7645,25 +7685,24 @@
         <v>21</v>
       </c>
       <c r="L289">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="M289" t="s">
         <v>49</v>
       </c>
-      <c r="N289" s="1"/>
       <c r="O289" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="290" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="G290" t="s">
-        <v>18</v>
+        <v>173</v>
       </c>
       <c r="H290" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I290" t="s">
         <v>19</v>
@@ -7672,25 +7711,24 @@
         <v>21</v>
       </c>
       <c r="L290">
-        <v>33</v>
+        <v>2.75</v>
       </c>
       <c r="M290" t="s">
         <v>49</v>
       </c>
-      <c r="N290" s="1"/>
       <c r="O290" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="291" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="G291" t="s">
-        <v>166</v>
+        <v>17</v>
       </c>
       <c r="H291" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I291" t="s">
         <v>19</v>
@@ -7698,28 +7736,26 @@
       <c r="K291" t="s">
         <v>21</v>
       </c>
-      <c r="L291" s="5">
+      <c r="L291">
         <v>25</v>
       </c>
       <c r="M291" t="s">
         <v>49</v>
       </c>
-      <c r="N291" s="5" t="s">
-        <v>211</v>
-      </c>
+      <c r="N291" s="1"/>
       <c r="O291" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="292" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="G292" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="H292" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I292" t="s">
         <v>19</v>
@@ -7728,24 +7764,25 @@
         <v>21</v>
       </c>
       <c r="L292">
-        <v>4</v>
+        <v>33</v>
       </c>
       <c r="M292" t="s">
         <v>49</v>
       </c>
+      <c r="N292" s="1"/>
       <c r="O292" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="293" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A293" t="s">
-        <v>35</v>
+        <v>54</v>
       </c>
       <c r="G293" t="s">
-        <v>17</v>
+        <v>166</v>
       </c>
       <c r="H293" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I293" t="s">
         <v>19</v>
@@ -7753,25 +7790,28 @@
       <c r="K293" t="s">
         <v>21</v>
       </c>
-      <c r="L293">
-        <v>18</v>
+      <c r="L293" s="5">
+        <v>25</v>
       </c>
       <c r="M293" t="s">
         <v>49</v>
       </c>
+      <c r="N293" s="5" t="s">
+        <v>210</v>
+      </c>
       <c r="O293" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="294" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="G294" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H294" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I294" t="s">
         <v>19</v>
@@ -7780,24 +7820,25 @@
         <v>21</v>
       </c>
       <c r="L294">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="M294" t="s">
         <v>49</v>
       </c>
+      <c r="N294" s="1"/>
       <c r="O294" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="295" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
-        <v>35</v>
+        <v>48</v>
       </c>
       <c r="G295" t="s">
-        <v>174</v>
+        <v>18</v>
       </c>
       <c r="H295" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I295" t="s">
         <v>19</v>
@@ -7806,24 +7847,25 @@
         <v>21</v>
       </c>
       <c r="L295">
-        <v>2.75</v>
+        <v>33</v>
       </c>
       <c r="M295" t="s">
         <v>49</v>
       </c>
+      <c r="N295" s="1"/>
       <c r="O295" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="296" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="G296" t="s">
-        <v>16</v>
+        <v>166</v>
       </c>
       <c r="H296" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I296" t="s">
         <v>19</v>
@@ -7831,25 +7873,28 @@
       <c r="K296" t="s">
         <v>21</v>
       </c>
-      <c r="L296">
-        <v>4</v>
+      <c r="L296" s="5">
+        <v>25</v>
       </c>
       <c r="M296" t="s">
         <v>49</v>
       </c>
+      <c r="N296" s="5" t="s">
+        <v>210</v>
+      </c>
       <c r="O296" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="297" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A297" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="G297" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H297" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I297" t="s">
         <v>19</v>
@@ -7858,24 +7903,24 @@
         <v>21</v>
       </c>
       <c r="L297">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="M297" t="s">
         <v>49</v>
       </c>
       <c r="O297" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="298" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="G298" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H298" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I298" t="s">
         <v>19</v>
@@ -7884,27 +7929,24 @@
         <v>21</v>
       </c>
       <c r="L298">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="M298" t="s">
         <v>49</v>
       </c>
       <c r="O298" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="299" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A299" t="s">
-        <v>45</v>
-      </c>
-      <c r="E299" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G299" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H299" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I299" t="s">
         <v>19</v>
@@ -7913,27 +7955,24 @@
         <v>21</v>
       </c>
       <c r="L299">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="M299" t="s">
         <v>49</v>
       </c>
       <c r="O299" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="300" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
-        <v>45</v>
-      </c>
-      <c r="E300" t="s">
-        <v>47</v>
+        <v>35</v>
       </c>
       <c r="G300" t="s">
-        <v>18</v>
+        <v>173</v>
       </c>
       <c r="H300" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I300" t="s">
         <v>19</v>
@@ -7942,105 +7981,149 @@
         <v>21</v>
       </c>
       <c r="L300">
-        <v>5</v>
+        <v>2.75</v>
       </c>
       <c r="M300" t="s">
         <v>49</v>
       </c>
       <c r="O300" t="s">
-        <v>172</v>
+        <v>171</v>
+      </c>
+    </row>
+    <row r="301" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A301" t="s">
+        <v>45</v>
+      </c>
+      <c r="G301" t="s">
+        <v>16</v>
+      </c>
+      <c r="H301" t="s">
+        <v>183</v>
+      </c>
+      <c r="I301" t="s">
+        <v>19</v>
+      </c>
+      <c r="K301" t="s">
+        <v>21</v>
+      </c>
+      <c r="L301">
+        <v>4</v>
+      </c>
+      <c r="M301" t="s">
+        <v>49</v>
+      </c>
+      <c r="O301" t="s">
+        <v>171</v>
       </c>
     </row>
     <row r="302" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A302" t="s">
+        <v>45</v>
+      </c>
       <c r="G302" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H302" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I302" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K302" t="s">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="L302">
-        <v>0.01</v>
+        <v>12</v>
       </c>
       <c r="M302" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O302" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="303" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A303" t="s">
+        <v>45</v>
+      </c>
       <c r="G303" t="s">
+        <v>18</v>
+      </c>
+      <c r="H303" t="s">
+        <v>183</v>
+      </c>
+      <c r="I303" t="s">
+        <v>19</v>
+      </c>
+      <c r="K303" t="s">
+        <v>21</v>
+      </c>
+      <c r="L303">
+        <v>20</v>
+      </c>
+      <c r="M303" t="s">
+        <v>49</v>
+      </c>
+      <c r="O303" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="304" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A304" t="s">
+        <v>45</v>
+      </c>
+      <c r="E304" t="s">
+        <v>47</v>
+      </c>
+      <c r="G304" t="s">
         <v>17</v>
       </c>
-      <c r="H303" t="s">
-        <v>184</v>
-      </c>
-      <c r="I303" t="s">
-        <v>22</v>
-      </c>
-      <c r="K303" t="s">
-        <v>192</v>
-      </c>
-      <c r="L303">
-        <v>1</v>
-      </c>
-      <c r="M303" t="s">
-        <v>50</v>
-      </c>
-      <c r="O303" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="304" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="G304" t="s">
+      <c r="H304" t="s">
+        <v>183</v>
+      </c>
+      <c r="I304" t="s">
+        <v>19</v>
+      </c>
+      <c r="K304" t="s">
+        <v>21</v>
+      </c>
+      <c r="L304">
+        <v>5</v>
+      </c>
+      <c r="M304" t="s">
+        <v>49</v>
+      </c>
+      <c r="O304" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="305" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A305" t="s">
+        <v>45</v>
+      </c>
+      <c r="E305" t="s">
+        <v>47</v>
+      </c>
+      <c r="G305" t="s">
         <v>18</v>
       </c>
-      <c r="H304" t="s">
-        <v>184</v>
-      </c>
-      <c r="I304" t="s">
-        <v>22</v>
-      </c>
-      <c r="K304" t="s">
-        <v>192</v>
-      </c>
-      <c r="L304">
-        <v>1</v>
-      </c>
-      <c r="M304" t="s">
-        <v>50</v>
-      </c>
-      <c r="O304" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="305" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="G305" t="s">
-        <v>166</v>
-      </c>
       <c r="H305" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I305" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="K305" t="s">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="L305">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M305" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="O305" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
     </row>
     <row r="307" spans="1:15" x14ac:dyDescent="0.25">
@@ -8048,19 +8131,19 @@
         <v>16</v>
       </c>
       <c r="H307" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I307" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K307" t="s">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="L307">
-        <v>0.5</v>
+        <v>0.01</v>
       </c>
       <c r="M307" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O307" t="s">
         <v>178</v>
@@ -8071,19 +8154,19 @@
         <v>17</v>
       </c>
       <c r="H308" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I308" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K308" t="s">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="L308">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="M308" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O308" t="s">
         <v>178</v>
@@ -8094,19 +8177,19 @@
         <v>18</v>
       </c>
       <c r="H309" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I309" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K309" t="s">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="L309">
         <v>1</v>
       </c>
       <c r="M309" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O309" t="s">
         <v>178</v>
@@ -8114,126 +8197,117 @@
     </row>
     <row r="310" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G310" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="H310" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I310" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="K310" t="s">
-        <v>21</v>
+        <v>191</v>
       </c>
       <c r="L310">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M310" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="O310" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="311" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="G311" t="s">
-        <v>166</v>
-      </c>
-      <c r="H311" t="s">
-        <v>184</v>
-      </c>
-      <c r="I311" t="s">
+    <row r="312" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G312" t="s">
+        <v>16</v>
+      </c>
+      <c r="H312" t="s">
+        <v>183</v>
+      </c>
+      <c r="I312" t="s">
         <v>23</v>
       </c>
-      <c r="K311" t="s">
+      <c r="K312" t="s">
         <v>21</v>
       </c>
-      <c r="L311">
-        <v>1</v>
-      </c>
-      <c r="M311" t="s">
+      <c r="L312">
+        <v>0.5</v>
+      </c>
+      <c r="M312" t="s">
         <v>49</v>
       </c>
-      <c r="O311" t="s">
-        <v>178</v>
+      <c r="O312" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="313" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G313" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H313" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I313" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K313" t="s">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="L313">
-        <v>0.31</v>
+        <v>0.5</v>
       </c>
       <c r="M313" t="s">
-        <v>50</v>
-      </c>
-      <c r="N313" t="s">
+        <v>49</v>
+      </c>
+      <c r="O313" t="s">
         <v>177</v>
-      </c>
-      <c r="O313" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="314" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G314" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H314" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I314" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K314" t="s">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="L314">
-        <v>31</v>
+        <v>1</v>
       </c>
       <c r="M314" t="s">
-        <v>50</v>
-      </c>
-      <c r="N314" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="O314" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="315" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G315" t="s">
-        <v>18</v>
+        <v>173</v>
       </c>
       <c r="H315" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="I315" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="K315" t="s">
-        <v>192</v>
+        <v>21</v>
       </c>
       <c r="L315">
-        <v>31</v>
+        <v>0</v>
       </c>
       <c r="M315" t="s">
-        <v>50</v>
-      </c>
-      <c r="N315" t="s">
-        <v>17</v>
+        <v>49</v>
       </c>
       <c r="O315" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
     </row>
     <row r="316" spans="1:15" x14ac:dyDescent="0.25">
@@ -8241,85 +8315,186 @@
         <v>166</v>
       </c>
       <c r="H316" t="s">
+        <v>183</v>
+      </c>
+      <c r="I316" t="s">
+        <v>23</v>
+      </c>
+      <c r="K316" t="s">
+        <v>21</v>
+      </c>
+      <c r="L316">
+        <v>1</v>
+      </c>
+      <c r="M316" t="s">
+        <v>49</v>
+      </c>
+      <c r="O316" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="318" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G318" t="s">
+        <v>16</v>
+      </c>
+      <c r="H318" t="s">
+        <v>183</v>
+      </c>
+      <c r="I318" t="s">
+        <v>24</v>
+      </c>
+      <c r="K318" t="s">
+        <v>191</v>
+      </c>
+      <c r="L318">
+        <v>0.31</v>
+      </c>
+      <c r="M318" t="s">
+        <v>50</v>
+      </c>
+      <c r="N318" t="s">
+        <v>176</v>
+      </c>
+      <c r="O318" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="319" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G319" t="s">
+        <v>17</v>
+      </c>
+      <c r="H319" t="s">
+        <v>183</v>
+      </c>
+      <c r="I319" t="s">
+        <v>24</v>
+      </c>
+      <c r="K319" t="s">
+        <v>191</v>
+      </c>
+      <c r="L319">
+        <v>31</v>
+      </c>
+      <c r="M319" t="s">
+        <v>50</v>
+      </c>
+      <c r="N319" t="s">
+        <v>17</v>
+      </c>
+      <c r="O319" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="320" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G320" t="s">
+        <v>18</v>
+      </c>
+      <c r="H320" t="s">
+        <v>183</v>
+      </c>
+      <c r="I320" t="s">
+        <v>24</v>
+      </c>
+      <c r="K320" t="s">
+        <v>191</v>
+      </c>
+      <c r="L320">
+        <v>31</v>
+      </c>
+      <c r="M320" t="s">
+        <v>50</v>
+      </c>
+      <c r="N320" t="s">
+        <v>17</v>
+      </c>
+      <c r="O320" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="321" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G321" t="s">
+        <v>166</v>
+      </c>
+      <c r="H321" t="s">
+        <v>183</v>
+      </c>
+      <c r="I321" t="s">
+        <v>24</v>
+      </c>
+      <c r="K321" t="s">
+        <v>191</v>
+      </c>
+      <c r="L321">
+        <v>31</v>
+      </c>
+      <c r="M321" t="s">
+        <v>50</v>
+      </c>
+      <c r="N321" t="s">
+        <v>17</v>
+      </c>
+      <c r="O321" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="323" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A323" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="324" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="H324" t="s">
         <v>184</v>
       </c>
-      <c r="I316" t="s">
-        <v>24</v>
-      </c>
-      <c r="K316" t="s">
-        <v>192</v>
-      </c>
-      <c r="L316">
-        <v>31</v>
-      </c>
-      <c r="M316" t="s">
-        <v>50</v>
-      </c>
-      <c r="N316" t="s">
-        <v>17</v>
-      </c>
-      <c r="O316" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="318" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A318" s="1" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="319" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="H319" t="s">
+      <c r="I324" t="s">
+        <v>184</v>
+      </c>
+      <c r="K324" t="s">
+        <v>20</v>
+      </c>
+      <c r="L324">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="325" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="H325" t="s">
+        <v>184</v>
+      </c>
+      <c r="I325" t="s">
+        <v>184</v>
+      </c>
+      <c r="K325" t="s">
+        <v>21</v>
+      </c>
+      <c r="L325">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="326" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="H326" t="s">
         <v>185</v>
       </c>
-      <c r="I319" t="s">
+      <c r="I326" t="s">
         <v>185</v>
       </c>
-      <c r="K319" t="s">
+      <c r="K326" t="s">
         <v>20</v>
       </c>
-      <c r="L319">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="320" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="H320" t="s">
+      <c r="L326" s="37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="327" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="H327" t="s">
         <v>185</v>
       </c>
-      <c r="I320" t="s">
+      <c r="I327" t="s">
         <v>185</v>
       </c>
-      <c r="K320" t="s">
+      <c r="K327" t="s">
         <v>21</v>
       </c>
-      <c r="L320">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="321" spans="8:12" x14ac:dyDescent="0.25">
-      <c r="H321" t="s">
-        <v>186</v>
-      </c>
-      <c r="I321" t="s">
-        <v>186</v>
-      </c>
-      <c r="K321" t="s">
-        <v>20</v>
-      </c>
-      <c r="L321" s="37">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="322" spans="8:12" x14ac:dyDescent="0.25">
-      <c r="H322" t="s">
-        <v>186</v>
-      </c>
-      <c r="I322" t="s">
-        <v>186</v>
-      </c>
-      <c r="K322" t="s">
-        <v>21</v>
-      </c>
-      <c r="L322">
+      <c r="L327">
         <v>0</v>
       </c>
     </row>
@@ -8471,7 +8646,7 @@
     </row>
     <row r="7" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B7" s="38" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C7" s="39" t="s">
         <v>3</v>
@@ -8483,7 +8658,7 @@
         <v>8</v>
       </c>
       <c r="F7" s="39" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="G7" s="39" t="s">
         <v>9</v>
@@ -8492,14 +8667,14 @@
       <c r="I7" s="39"/>
       <c r="J7" s="39"/>
       <c r="K7" s="39" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="L7" s="39"/>
       <c r="M7" s="39" t="s">
         <v>47</v>
       </c>
       <c r="O7" s="38" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="P7" s="39" t="str">
         <f>C7</f>
@@ -8579,7 +8754,7 @@
         <v>0</v>
       </c>
       <c r="O8" s="38" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="P8" s="41" t="str">
         <f>P5&amp;P6&amp;P7</f>
@@ -8916,7 +9091,7 @@
     </row>
     <row r="12" spans="2:26" x14ac:dyDescent="0.25">
       <c r="B12" s="39" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C12" s="37">
         <f>C83+C97</f>
@@ -8959,7 +9134,7 @@
         <v>0</v>
       </c>
       <c r="O12" s="39" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="P12" s="37">
         <f t="shared" si="3"/>
@@ -9311,20 +9486,20 @@
       </c>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B19" s="52" t="s">
+      <c r="B19" s="47" t="s">
         <v>142</v>
       </c>
-      <c r="C19" s="52"/>
-      <c r="D19" s="52"/>
-      <c r="E19" s="52"/>
-      <c r="F19" s="52"/>
-      <c r="G19" s="52"/>
-      <c r="H19" s="52"/>
-      <c r="I19" s="52"/>
-      <c r="J19" s="52"/>
-      <c r="K19" s="52"/>
-      <c r="L19" s="52"/>
-      <c r="M19" s="52"/>
+      <c r="C19" s="47"/>
+      <c r="D19" s="47"/>
+      <c r="E19" s="47"/>
+      <c r="F19" s="47"/>
+      <c r="G19" s="47"/>
+      <c r="H19" s="47"/>
+      <c r="I19" s="47"/>
+      <c r="J19" s="47"/>
+      <c r="K19" s="47"/>
+      <c r="L19" s="47"/>
+      <c r="M19" s="47"/>
     </row>
     <row r="20" spans="2:13" ht="33" x14ac:dyDescent="0.25">
       <c r="B20" s="21" t="s">
@@ -10149,23 +10324,23 @@
       <c r="M43" s="20"/>
     </row>
     <row r="45" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B45" s="52" t="s">
+      <c r="B45" s="47" t="s">
         <v>157</v>
       </c>
-      <c r="C45" s="52"/>
-      <c r="D45" s="52"/>
-      <c r="E45" s="52"/>
-      <c r="F45" s="52"/>
-      <c r="G45" s="52"/>
-      <c r="H45" s="52"/>
-      <c r="I45" s="52"/>
-      <c r="J45" s="52"/>
-      <c r="K45" s="52"/>
-      <c r="L45" s="52"/>
-      <c r="M45" s="52"/>
-      <c r="N45" s="52"/>
-      <c r="O45" s="52"/>
-      <c r="P45" s="52"/>
+      <c r="C45" s="47"/>
+      <c r="D45" s="47"/>
+      <c r="E45" s="47"/>
+      <c r="F45" s="47"/>
+      <c r="G45" s="47"/>
+      <c r="H45" s="47"/>
+      <c r="I45" s="47"/>
+      <c r="J45" s="47"/>
+      <c r="K45" s="47"/>
+      <c r="L45" s="47"/>
+      <c r="M45" s="47"/>
+      <c r="N45" s="47"/>
+      <c r="O45" s="47"/>
+      <c r="P45" s="47"/>
     </row>
     <row r="46" spans="2:16" ht="44.25" x14ac:dyDescent="0.25">
       <c r="B46" s="31" t="s">
@@ -11133,43 +11308,43 @@
       <c r="N69" s="20"/>
     </row>
     <row r="71" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="52" t="s">
+      <c r="B71" s="47" t="s">
         <v>150</v>
       </c>
-      <c r="C71" s="52"/>
-      <c r="D71" s="52"/>
-      <c r="E71" s="52"/>
-      <c r="F71" s="52"/>
-      <c r="G71" s="52"/>
-      <c r="H71" s="52"/>
-      <c r="I71" s="52"/>
-      <c r="J71" s="52"/>
-      <c r="K71" s="52"/>
-      <c r="L71" s="52"/>
-      <c r="M71" s="52"/>
+      <c r="C71" s="47"/>
+      <c r="D71" s="47"/>
+      <c r="E71" s="47"/>
+      <c r="F71" s="47"/>
+      <c r="G71" s="47"/>
+      <c r="H71" s="47"/>
+      <c r="I71" s="47"/>
+      <c r="J71" s="47"/>
+      <c r="K71" s="47"/>
+      <c r="L71" s="47"/>
+      <c r="M71" s="47"/>
     </row>
     <row r="72" spans="2:14" ht="24" x14ac:dyDescent="0.25">
-      <c r="B72" s="54" t="s">
+      <c r="B72" s="48" t="s">
         <v>131</v>
       </c>
-      <c r="C72" s="56" t="s">
+      <c r="C72" s="50" t="s">
         <v>151</v>
       </c>
-      <c r="D72" s="57"/>
-      <c r="E72" s="57"/>
-      <c r="F72" s="57"/>
-      <c r="G72" s="57"/>
-      <c r="H72" s="57"/>
-      <c r="I72" s="57"/>
-      <c r="J72" s="57"/>
-      <c r="K72" s="58"/>
+      <c r="D72" s="51"/>
+      <c r="E72" s="51"/>
+      <c r="F72" s="51"/>
+      <c r="G72" s="51"/>
+      <c r="H72" s="51"/>
+      <c r="I72" s="51"/>
+      <c r="J72" s="51"/>
+      <c r="K72" s="52"/>
       <c r="L72" s="26" t="s">
         <v>152</v>
       </c>
       <c r="M72" s="27"/>
     </row>
     <row r="73" spans="2:14" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="B73" s="55"/>
+      <c r="B73" s="49"/>
       <c r="C73" s="16" t="s">
         <v>132</v>
       </c>
@@ -11588,22 +11763,22 @@
       <c r="L85" s="53"/>
     </row>
     <row r="86" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B86" s="47"/>
-      <c r="C86" s="49" t="s">
+      <c r="B86" s="54"/>
+      <c r="C86" s="56" t="s">
         <v>155</v>
       </c>
-      <c r="D86" s="50"/>
-      <c r="E86" s="50"/>
-      <c r="F86" s="50"/>
-      <c r="G86" s="50"/>
-      <c r="H86" s="50"/>
-      <c r="I86" s="50"/>
-      <c r="J86" s="50"/>
-      <c r="K86" s="51"/>
+      <c r="D86" s="57"/>
+      <c r="E86" s="57"/>
+      <c r="F86" s="57"/>
+      <c r="G86" s="57"/>
+      <c r="H86" s="57"/>
+      <c r="I86" s="57"/>
+      <c r="J86" s="57"/>
+      <c r="K86" s="58"/>
       <c r="L86" s="20"/>
     </row>
     <row r="87" spans="2:13" ht="42" x14ac:dyDescent="0.25">
-      <c r="B87" s="48"/>
+      <c r="B87" s="55"/>
       <c r="C87" s="29" t="s">
         <v>132</v>
       </c>
@@ -11973,16 +12148,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B86:B87"/>
+    <mergeCell ref="C86:K86"/>
+    <mergeCell ref="B45:P45"/>
+    <mergeCell ref="B58:N58"/>
+    <mergeCell ref="B32:M32"/>
     <mergeCell ref="B19:M19"/>
     <mergeCell ref="B71:M71"/>
     <mergeCell ref="B72:B73"/>
     <mergeCell ref="C72:K72"/>
     <mergeCell ref="B85:L85"/>
-    <mergeCell ref="B86:B87"/>
-    <mergeCell ref="C86:K86"/>
-    <mergeCell ref="B45:P45"/>
-    <mergeCell ref="B58:N58"/>
-    <mergeCell ref="B32:M32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/data/default/ManureMgmt.xlsx
+++ b/data/default/ManureMgmt.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jnka0003\Git repos\CIBUSmod\data\default\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CCE5617-CD6F-4CE5-9E2A-5E848FF4E913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC0BD568-61C6-40F1-9963-75B76F55BF7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1717" uniqueCount="216">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1730" uniqueCount="216">
   <si>
     <t>value</t>
   </si>
@@ -1444,8 +1444,26 @@
     <xf numFmtId="0" fontId="28" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="10"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="10"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="35" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="10"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -1461,24 +1479,6 @@
     </xf>
     <xf numFmtId="0" fontId="25" fillId="35" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="9"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="10"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="10"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="35" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="10"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1827,7 +1827,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:O327"/>
+  <dimension ref="A1:O329"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="14.28515625" bestFit="1" customWidth="1"/>
@@ -8197,7 +8197,7 @@
     </row>
     <row r="310" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G310" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="H310" t="s">
         <v>183</v>
@@ -8209,7 +8209,7 @@
         <v>191</v>
       </c>
       <c r="L310">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="M310" t="s">
         <v>50</v>
@@ -8218,32 +8218,32 @@
         <v>178</v>
       </c>
     </row>
-    <row r="312" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="G312" t="s">
-        <v>16</v>
-      </c>
-      <c r="H312" t="s">
+    <row r="311" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G311" t="s">
+        <v>166</v>
+      </c>
+      <c r="H311" t="s">
         <v>183</v>
       </c>
-      <c r="I312" t="s">
-        <v>23</v>
-      </c>
-      <c r="K312" t="s">
-        <v>21</v>
-      </c>
-      <c r="L312">
-        <v>0.5</v>
-      </c>
-      <c r="M312" t="s">
-        <v>49</v>
-      </c>
-      <c r="O312" t="s">
-        <v>177</v>
+      <c r="I311" t="s">
+        <v>22</v>
+      </c>
+      <c r="K311" t="s">
+        <v>191</v>
+      </c>
+      <c r="L311">
+        <v>1</v>
+      </c>
+      <c r="M311" t="s">
+        <v>50</v>
+      </c>
+      <c r="O311" t="s">
+        <v>178</v>
       </c>
     </row>
     <row r="313" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G313" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H313" t="s">
         <v>183</v>
@@ -8266,7 +8266,7 @@
     </row>
     <row r="314" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G314" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H314" t="s">
         <v>183</v>
@@ -8278,7 +8278,7 @@
         <v>21</v>
       </c>
       <c r="L314">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="M314" t="s">
         <v>49</v>
@@ -8289,7 +8289,7 @@
     </row>
     <row r="315" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G315" t="s">
-        <v>173</v>
+        <v>18</v>
       </c>
       <c r="H315" t="s">
         <v>183</v>
@@ -8301,7 +8301,7 @@
         <v>21</v>
       </c>
       <c r="L315">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M315" t="s">
         <v>49</v>
@@ -8312,7 +8312,7 @@
     </row>
     <row r="316" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G316" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="H316" t="s">
         <v>183</v>
@@ -8324,7 +8324,7 @@
         <v>21</v>
       </c>
       <c r="L316">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M316" t="s">
         <v>49</v>
@@ -8333,35 +8333,32 @@
         <v>177</v>
       </c>
     </row>
-    <row r="318" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="G318" t="s">
-        <v>16</v>
-      </c>
-      <c r="H318" t="s">
+    <row r="317" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G317" t="s">
+        <v>166</v>
+      </c>
+      <c r="H317" t="s">
         <v>183</v>
       </c>
-      <c r="I318" t="s">
-        <v>24</v>
-      </c>
-      <c r="K318" t="s">
-        <v>191</v>
-      </c>
-      <c r="L318">
-        <v>0.31</v>
-      </c>
-      <c r="M318" t="s">
-        <v>50</v>
-      </c>
-      <c r="N318" t="s">
-        <v>176</v>
-      </c>
-      <c r="O318" t="s">
-        <v>175</v>
+      <c r="I317" t="s">
+        <v>23</v>
+      </c>
+      <c r="K317" t="s">
+        <v>21</v>
+      </c>
+      <c r="L317">
+        <v>1</v>
+      </c>
+      <c r="M317" t="s">
+        <v>49</v>
+      </c>
+      <c r="O317" t="s">
+        <v>177</v>
       </c>
     </row>
     <row r="319" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G319" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H319" t="s">
         <v>183</v>
@@ -8373,13 +8370,13 @@
         <v>191</v>
       </c>
       <c r="L319">
-        <v>31</v>
+        <v>0.3</v>
       </c>
       <c r="M319" t="s">
         <v>50</v>
       </c>
       <c r="N319" t="s">
-        <v>17</v>
+        <v>176</v>
       </c>
       <c r="O319" t="s">
         <v>175</v>
@@ -8387,7 +8384,7 @@
     </row>
     <row r="320" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G320" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H320" t="s">
         <v>183</v>
@@ -8399,7 +8396,7 @@
         <v>191</v>
       </c>
       <c r="L320">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M320" t="s">
         <v>50</v>
@@ -8413,7 +8410,7 @@
     </row>
     <row r="321" spans="1:15" x14ac:dyDescent="0.25">
       <c r="G321" t="s">
-        <v>166</v>
+        <v>18</v>
       </c>
       <c r="H321" t="s">
         <v>183</v>
@@ -8425,7 +8422,7 @@
         <v>191</v>
       </c>
       <c r="L321">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="M321" t="s">
         <v>50</v>
@@ -8437,64 +8434,116 @@
         <v>175</v>
       </c>
     </row>
+    <row r="322" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="G322" t="s">
+        <v>173</v>
+      </c>
+      <c r="H322" t="s">
+        <v>183</v>
+      </c>
+      <c r="I322" t="s">
+        <v>24</v>
+      </c>
+      <c r="K322" t="s">
+        <v>191</v>
+      </c>
+      <c r="L322">
+        <v>0.3</v>
+      </c>
+      <c r="M322" t="s">
+        <v>50</v>
+      </c>
+      <c r="N322" t="s">
+        <v>176</v>
+      </c>
+      <c r="O322" t="s">
+        <v>175</v>
+      </c>
+    </row>
     <row r="323" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A323" s="1" t="s">
+      <c r="G323" t="s">
+        <v>166</v>
+      </c>
+      <c r="H323" t="s">
+        <v>183</v>
+      </c>
+      <c r="I323" t="s">
+        <v>24</v>
+      </c>
+      <c r="K323" t="s">
+        <v>191</v>
+      </c>
+      <c r="L323">
+        <v>30</v>
+      </c>
+      <c r="M323" t="s">
+        <v>50</v>
+      </c>
+      <c r="N323" t="s">
+        <v>17</v>
+      </c>
+      <c r="O323" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="325" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A325" s="1" t="s">
         <v>186</v>
-      </c>
-    </row>
-    <row r="324" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="H324" t="s">
-        <v>184</v>
-      </c>
-      <c r="I324" t="s">
-        <v>184</v>
-      </c>
-      <c r="K324" t="s">
-        <v>20</v>
-      </c>
-      <c r="L324">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="325" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="H325" t="s">
-        <v>184</v>
-      </c>
-      <c r="I325" t="s">
-        <v>184</v>
-      </c>
-      <c r="K325" t="s">
-        <v>21</v>
-      </c>
-      <c r="L325">
-        <v>0</v>
       </c>
     </row>
     <row r="326" spans="1:15" x14ac:dyDescent="0.25">
       <c r="H326" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I326" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K326" t="s">
         <v>20</v>
       </c>
-      <c r="L326" s="37">
+      <c r="L326">
         <v>0</v>
       </c>
     </row>
     <row r="327" spans="1:15" x14ac:dyDescent="0.25">
       <c r="H327" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I327" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="K327" t="s">
         <v>21</v>
       </c>
       <c r="L327">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="328" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="H328" t="s">
+        <v>185</v>
+      </c>
+      <c r="I328" t="s">
+        <v>185</v>
+      </c>
+      <c r="K328" t="s">
+        <v>20</v>
+      </c>
+      <c r="L328" s="37">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="329" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="H329" t="s">
+        <v>185</v>
+      </c>
+      <c r="I329" t="s">
+        <v>185</v>
+      </c>
+      <c r="K329" t="s">
+        <v>21</v>
+      </c>
+      <c r="L329">
         <v>0</v>
       </c>
     </row>
@@ -9486,20 +9535,20 @@
       </c>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B19" s="47" t="s">
+      <c r="B19" s="52" t="s">
         <v>142</v>
       </c>
-      <c r="C19" s="47"/>
-      <c r="D19" s="47"/>
-      <c r="E19" s="47"/>
-      <c r="F19" s="47"/>
-      <c r="G19" s="47"/>
-      <c r="H19" s="47"/>
-      <c r="I19" s="47"/>
-      <c r="J19" s="47"/>
-      <c r="K19" s="47"/>
-      <c r="L19" s="47"/>
-      <c r="M19" s="47"/>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="52"/>
+      <c r="G19" s="52"/>
+      <c r="H19" s="52"/>
+      <c r="I19" s="52"/>
+      <c r="J19" s="52"/>
+      <c r="K19" s="52"/>
+      <c r="L19" s="52"/>
+      <c r="M19" s="52"/>
     </row>
     <row r="20" spans="2:13" ht="33" x14ac:dyDescent="0.25">
       <c r="B20" s="21" t="s">
@@ -10324,23 +10373,23 @@
       <c r="M43" s="20"/>
     </row>
     <row r="45" spans="2:16" x14ac:dyDescent="0.25">
-      <c r="B45" s="47" t="s">
+      <c r="B45" s="52" t="s">
         <v>157</v>
       </c>
-      <c r="C45" s="47"/>
-      <c r="D45" s="47"/>
-      <c r="E45" s="47"/>
-      <c r="F45" s="47"/>
-      <c r="G45" s="47"/>
-      <c r="H45" s="47"/>
-      <c r="I45" s="47"/>
-      <c r="J45" s="47"/>
-      <c r="K45" s="47"/>
-      <c r="L45" s="47"/>
-      <c r="M45" s="47"/>
-      <c r="N45" s="47"/>
-      <c r="O45" s="47"/>
-      <c r="P45" s="47"/>
+      <c r="C45" s="52"/>
+      <c r="D45" s="52"/>
+      <c r="E45" s="52"/>
+      <c r="F45" s="52"/>
+      <c r="G45" s="52"/>
+      <c r="H45" s="52"/>
+      <c r="I45" s="52"/>
+      <c r="J45" s="52"/>
+      <c r="K45" s="52"/>
+      <c r="L45" s="52"/>
+      <c r="M45" s="52"/>
+      <c r="N45" s="52"/>
+      <c r="O45" s="52"/>
+      <c r="P45" s="52"/>
     </row>
     <row r="46" spans="2:16" ht="44.25" x14ac:dyDescent="0.25">
       <c r="B46" s="31" t="s">
@@ -11308,43 +11357,43 @@
       <c r="N69" s="20"/>
     </row>
     <row r="71" spans="2:14" ht="22.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="47" t="s">
+      <c r="B71" s="52" t="s">
         <v>150</v>
       </c>
-      <c r="C71" s="47"/>
-      <c r="D71" s="47"/>
-      <c r="E71" s="47"/>
-      <c r="F71" s="47"/>
-      <c r="G71" s="47"/>
-      <c r="H71" s="47"/>
-      <c r="I71" s="47"/>
-      <c r="J71" s="47"/>
-      <c r="K71" s="47"/>
-      <c r="L71" s="47"/>
-      <c r="M71" s="47"/>
+      <c r="C71" s="52"/>
+      <c r="D71" s="52"/>
+      <c r="E71" s="52"/>
+      <c r="F71" s="52"/>
+      <c r="G71" s="52"/>
+      <c r="H71" s="52"/>
+      <c r="I71" s="52"/>
+      <c r="J71" s="52"/>
+      <c r="K71" s="52"/>
+      <c r="L71" s="52"/>
+      <c r="M71" s="52"/>
     </row>
     <row r="72" spans="2:14" ht="24" x14ac:dyDescent="0.25">
-      <c r="B72" s="48" t="s">
+      <c r="B72" s="54" t="s">
         <v>131</v>
       </c>
-      <c r="C72" s="50" t="s">
+      <c r="C72" s="56" t="s">
         <v>151</v>
       </c>
-      <c r="D72" s="51"/>
-      <c r="E72" s="51"/>
-      <c r="F72" s="51"/>
-      <c r="G72" s="51"/>
-      <c r="H72" s="51"/>
-      <c r="I72" s="51"/>
-      <c r="J72" s="51"/>
-      <c r="K72" s="52"/>
+      <c r="D72" s="57"/>
+      <c r="E72" s="57"/>
+      <c r="F72" s="57"/>
+      <c r="G72" s="57"/>
+      <c r="H72" s="57"/>
+      <c r="I72" s="57"/>
+      <c r="J72" s="57"/>
+      <c r="K72" s="58"/>
       <c r="L72" s="26" t="s">
         <v>152</v>
       </c>
       <c r="M72" s="27"/>
     </row>
     <row r="73" spans="2:14" ht="49.5" x14ac:dyDescent="0.25">
-      <c r="B73" s="49"/>
+      <c r="B73" s="55"/>
       <c r="C73" s="16" t="s">
         <v>132</v>
       </c>
@@ -11763,22 +11812,22 @@
       <c r="L85" s="53"/>
     </row>
     <row r="86" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B86" s="54"/>
-      <c r="C86" s="56" t="s">
+      <c r="B86" s="47"/>
+      <c r="C86" s="49" t="s">
         <v>155</v>
       </c>
-      <c r="D86" s="57"/>
-      <c r="E86" s="57"/>
-      <c r="F86" s="57"/>
-      <c r="G86" s="57"/>
-      <c r="H86" s="57"/>
-      <c r="I86" s="57"/>
-      <c r="J86" s="57"/>
-      <c r="K86" s="58"/>
+      <c r="D86" s="50"/>
+      <c r="E86" s="50"/>
+      <c r="F86" s="50"/>
+      <c r="G86" s="50"/>
+      <c r="H86" s="50"/>
+      <c r="I86" s="50"/>
+      <c r="J86" s="50"/>
+      <c r="K86" s="51"/>
       <c r="L86" s="20"/>
     </row>
     <row r="87" spans="2:13" ht="42" x14ac:dyDescent="0.25">
-      <c r="B87" s="55"/>
+      <c r="B87" s="48"/>
       <c r="C87" s="29" t="s">
         <v>132</v>
       </c>
@@ -12148,16 +12197,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B19:M19"/>
+    <mergeCell ref="B71:M71"/>
+    <mergeCell ref="B72:B73"/>
+    <mergeCell ref="C72:K72"/>
+    <mergeCell ref="B85:L85"/>
     <mergeCell ref="B86:B87"/>
     <mergeCell ref="C86:K86"/>
     <mergeCell ref="B45:P45"/>
     <mergeCell ref="B58:N58"/>
     <mergeCell ref="B32:M32"/>
-    <mergeCell ref="B19:M19"/>
-    <mergeCell ref="B71:M71"/>
-    <mergeCell ref="B72:B73"/>
-    <mergeCell ref="C72:K72"/>
-    <mergeCell ref="B85:L85"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
